--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="203">
   <si>
     <t>f_crop</t>
   </si>
@@ -620,6 +620,39 @@
   </si>
   <si>
     <t>f_po8:region</t>
+  </si>
+  <si>
+    <t>2015/16</t>
+  </si>
+  <si>
+    <t>Leaching</t>
+  </si>
+  <si>
+    <t>N_leaching_frac</t>
+  </si>
+  <si>
+    <t>IPCC Guidelines 2019</t>
+  </si>
+  <si>
+    <t>kg N leached/kg N added</t>
+  </si>
+  <si>
+    <t>NO3-N</t>
+  </si>
+  <si>
+    <t>f_land_use</t>
+  </si>
+  <si>
+    <t>cropland</t>
+  </si>
+  <si>
+    <t>semi-natural grasslands</t>
+  </si>
+  <si>
+    <t>greenhouse</t>
+  </si>
+  <si>
+    <t>No leaching from greenhouses?</t>
   </si>
 </sst>
 </file>
@@ -1019,71 +1052,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R294"/>
+  <dimension ref="A1:S300"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="11.140625" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.42578125" customWidth="1"/>
-    <col min="15" max="15" width="27.42578125" customWidth="1"/>
+    <col min="1" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="11.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.42578125" customWidth="1"/>
+    <col min="16" max="16" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>123</v>
       </c>
@@ -1101,45 +1137,46 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
         <v>113</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>120</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>91</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>112</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>121</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K5" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L5" t="s">
         <v>115</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>22</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>114</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>119</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>164</v>
       </c>
@@ -1157,88 +1194,89 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
         <v>113</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>160</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>127</v>
       </c>
-      <c r="N8" s="5" t="s">
+      <c r="O8" s="5" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
         <v>163</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>125</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>160</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>59</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>127</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="O9" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
         <v>163</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>126</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>160</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>7</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>127</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
         <v>163</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>124</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>160</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>34</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>127</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>117</v>
       </c>
@@ -1254,1389 +1292,1390 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
-      <c r="N13" s="3"/>
+      <c r="N13" s="2"/>
       <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K14" s="6" t="s">
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="6">
+      <c r="M14" s="6">
         <v>0</v>
       </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="6"/>
+      <c r="O14" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K15" s="6" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="L15" s="6">
+      <c r="M15" s="6">
         <v>0</v>
       </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6" t="s">
+      <c r="N15" s="6"/>
+      <c r="O15" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K16" s="6" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L16" s="6">
+      <c r="M16" s="6">
         <v>0</v>
       </c>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6" t="s">
+      <c r="N16" s="6"/>
+      <c r="O16" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>10</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>-0.80359999999999998</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>11</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>24.088999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>12</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>50.213999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>9</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>12</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>55.213999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>96</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>10</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>-0.71430000000000005</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>7</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>96</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>11</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>23.143000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>96</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>12</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>42.570999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>7</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>96</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>9</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>12</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>47.570999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>7</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>95</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="9">
-        <f>L21</f>
+      <c r="M25" s="9">
+        <f>M21</f>
         <v>-0.71430000000000005</v>
       </c>
-      <c r="N25" s="9" t="str">
-        <f>N21</f>
+      <c r="O25" s="9" t="str">
+        <f>O21</f>
         <v>Höstvete foder/bröd, södra götaland</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>95</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>11</v>
       </c>
-      <c r="L26" s="9">
-        <f t="shared" ref="L26:L28" si="0">L22</f>
+      <c r="M26" s="9">
+        <f t="shared" ref="M26:M28" si="0">M22</f>
         <v>23.143000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>95</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>12</v>
       </c>
-      <c r="L27" s="9">
+      <c r="M27" s="9">
         <f t="shared" si="0"/>
         <v>42.570999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>7</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>95</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>9</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>12</v>
       </c>
-      <c r="L28" s="9">
+      <c r="M28" s="9">
         <f t="shared" si="0"/>
         <v>47.570999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>16</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>11</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>16</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>12</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" t="s">
         <v>10</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>-1.7857000000000001</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>11</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>30.786000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>27</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" t="s">
         <v>12</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>27</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>96</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
         <v>10</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>-1.25</v>
       </c>
-      <c r="N34" t="s">
+      <c r="O34" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>96</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>11</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>27.75</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>27</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>96</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36" t="s">
         <v>12</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>18.25</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>95</v>
       </c>
-      <c r="K37" t="s">
+      <c r="L37" t="s">
         <v>10</v>
       </c>
-      <c r="L37" s="9">
-        <f>L34</f>
+      <c r="M37" s="9">
+        <f>M34</f>
         <v>-1.25</v>
       </c>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9" t="str">
-        <f>N34</f>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9" t="str">
+        <f>O34</f>
         <v>Råg, södra götaland</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>95</v>
       </c>
-      <c r="K38" t="s">
+      <c r="L38" t="s">
         <v>11</v>
       </c>
-      <c r="L38" s="9">
-        <f>L35</f>
+      <c r="M38" s="9">
+        <f>M35</f>
         <v>27.75</v>
       </c>
-      <c r="M38" s="9"/>
       <c r="N38" s="9"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O38" s="9"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>95</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="9">
-        <f>L36</f>
+      <c r="M39" s="9">
+        <f>M36</f>
         <v>18.25</v>
       </c>
-      <c r="M39" s="9"/>
       <c r="N39" s="9"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O39" s="9"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>23</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>11</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>16.856999999999999</v>
       </c>
-      <c r="N40" t="s">
+      <c r="O40" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>23</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
         <v>12</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>59.143000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>23</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>96</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L42" t="s">
         <v>10</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>-0.71430000000000005</v>
       </c>
-      <c r="N42" t="s">
+      <c r="O42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>23</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>96</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L43" t="s">
         <v>11</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>23.143000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>23</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>96</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" t="s">
         <v>12</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>37.570999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>23</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>95</v>
       </c>
-      <c r="K45" t="s">
+      <c r="L45" t="s">
         <v>10</v>
       </c>
-      <c r="L45" s="9">
-        <f>L42</f>
+      <c r="M45" s="9">
+        <f>M42</f>
         <v>-0.71430000000000005</v>
       </c>
-      <c r="N45" s="9" t="str">
-        <f>N42</f>
+      <c r="O45" s="9" t="str">
+        <f>O42</f>
         <v>Rågvete/höstkorn, södra götaland</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>23</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>95</v>
       </c>
-      <c r="K46" t="s">
+      <c r="L46" t="s">
         <v>11</v>
       </c>
-      <c r="L46" s="9">
-        <f>L43</f>
+      <c r="M46" s="9">
+        <f>M43</f>
         <v>23.143000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>23</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>95</v>
       </c>
-      <c r="K47" t="s">
+      <c r="L47" t="s">
         <v>12</v>
       </c>
-      <c r="L47" s="9">
-        <f>L44</f>
+      <c r="M47" s="9">
+        <f>M44</f>
         <v>37.570999999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" t="s">
         <v>10</v>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>-1.0713999999999999</v>
       </c>
-      <c r="N48" t="s">
+      <c r="O48" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>17</v>
       </c>
-      <c r="K49" t="s">
+      <c r="L49" t="s">
         <v>11</v>
       </c>
-      <c r="L49">
+      <c r="M49">
         <v>23.928999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>17</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L50" t="s">
         <v>12</v>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>17</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>9</v>
       </c>
-      <c r="K51" t="s">
+      <c r="L51" t="s">
         <v>10</v>
       </c>
-      <c r="L51" s="8">
+      <c r="M51" s="8">
         <v>1E-13</v>
       </c>
-      <c r="N51" t="s">
+      <c r="O51" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>17</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>9</v>
       </c>
-      <c r="K52" t="s">
+      <c r="L52" t="s">
         <v>11</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>17</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>9</v>
       </c>
-      <c r="K53" t="s">
+      <c r="L53" t="s">
         <v>12</v>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>45</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>96</v>
       </c>
-      <c r="K54" t="s">
+      <c r="L54" t="s">
         <v>10</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>-1.25</v>
       </c>
-      <c r="N54" t="s">
+      <c r="O54" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>17</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>96</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" t="s">
         <v>11</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>25.25</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>17</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>96</v>
       </c>
-      <c r="K56" t="s">
+      <c r="L56" t="s">
         <v>12</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>19.75</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>96</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>9</v>
       </c>
-      <c r="K57" t="s">
+      <c r="L57" t="s">
         <v>10</v>
       </c>
-      <c r="L57" s="8">
+      <c r="M57" s="8">
         <v>-2E-12</v>
       </c>
-      <c r="N57" t="s">
+      <c r="O57" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>17</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>96</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>9</v>
       </c>
-      <c r="K58" t="s">
+      <c r="L58" t="s">
         <v>11</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>96</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>9</v>
       </c>
-      <c r="K59" t="s">
+      <c r="L59" t="s">
         <v>12</v>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>17</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>95</v>
       </c>
-      <c r="K60" t="s">
+      <c r="L60" t="s">
         <v>10</v>
       </c>
-      <c r="L60" s="9">
-        <f t="shared" ref="L60:L65" si="1">L54</f>
+      <c r="M60" s="9">
+        <f t="shared" ref="M60:M65" si="1">M54</f>
         <v>-1.25</v>
       </c>
-      <c r="N60" s="9" t="str">
-        <f>N54</f>
+      <c r="O60" s="9" t="str">
+        <f>O54</f>
         <v>Korn foder, södra götaland</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>17</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>95</v>
       </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>11</v>
       </c>
-      <c r="L61" s="9">
+      <c r="M61" s="9">
         <f t="shared" si="1"/>
         <v>25.25</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>17</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>95</v>
       </c>
-      <c r="K62" t="s">
+      <c r="L62" t="s">
         <v>12</v>
       </c>
-      <c r="L62" s="9">
+      <c r="M62" s="9">
         <f t="shared" si="1"/>
         <v>19.75</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>17</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>95</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>9</v>
       </c>
-      <c r="K63" t="s">
+      <c r="L63" t="s">
         <v>10</v>
       </c>
-      <c r="L63" s="9">
+      <c r="M63" s="9">
         <f t="shared" si="1"/>
         <v>-2E-12</v>
       </c>
-      <c r="N63" s="9" t="str">
-        <f>N57</f>
+      <c r="O63" s="9" t="str">
+        <f>O57</f>
         <v>Korn, malt södra götaland</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>17</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>95</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>9</v>
       </c>
-      <c r="K64" t="s">
+      <c r="L64" t="s">
         <v>11</v>
       </c>
-      <c r="L64" s="9">
+      <c r="M64" s="9">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>17</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>95</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>9</v>
       </c>
-      <c r="K65" t="s">
+      <c r="L65" t="s">
         <v>12</v>
       </c>
-      <c r="L65" s="9">
+      <c r="M65" s="9">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>17</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>97</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" t="s">
         <v>10</v>
       </c>
-      <c r="L66" s="5">
+      <c r="M66" s="5">
         <v>0</v>
       </c>
-      <c r="N66" t="s">
+      <c r="O66" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>17</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>97</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>11</v>
       </c>
-      <c r="L67" s="5">
+      <c r="M67" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>17</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>97</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
         <v>12</v>
       </c>
-      <c r="L68" s="5">
+      <c r="M68" s="5">
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>17</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>97</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>9</v>
       </c>
-      <c r="K69" t="s">
+      <c r="L69" t="s">
         <v>10</v>
       </c>
-      <c r="L69" s="9">
-        <f t="shared" ref="L69:L77" si="2">L66</f>
+      <c r="M69" s="9">
+        <f t="shared" ref="M69:M77" si="2">M66</f>
         <v>0</v>
       </c>
-      <c r="N69" s="9" t="str">
-        <f>N66</f>
+      <c r="O69" s="9" t="str">
+        <f>O66</f>
         <v>Korn, norrland</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>17</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>97</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>9</v>
       </c>
-      <c r="K70" t="s">
+      <c r="L70" t="s">
         <v>11</v>
       </c>
-      <c r="L70" s="9">
+      <c r="M70" s="9">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>17</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>97</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>9</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>12</v>
       </c>
-      <c r="L71" s="9">
+      <c r="M71" s="9">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>17</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>98</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
         <v>10</v>
       </c>
-      <c r="L72" s="9">
+      <c r="M72" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N72" s="9" t="str">
-        <f>N69</f>
+      <c r="O72" s="9" t="str">
+        <f>O69</f>
         <v>Korn, norrland</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>17</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>98</v>
       </c>
-      <c r="K73" t="s">
+      <c r="L73" t="s">
         <v>11</v>
       </c>
-      <c r="L73" s="9">
+      <c r="M73" s="9">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>17</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>98</v>
       </c>
-      <c r="K74" t="s">
+      <c r="L74" t="s">
         <v>12</v>
       </c>
-      <c r="L74" s="9">
+      <c r="M74" s="9">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>17</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>98</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>9</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>10</v>
       </c>
-      <c r="L75" s="9">
+      <c r="M75" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N75" s="9" t="str">
-        <f>N72</f>
+      <c r="O75" s="9" t="str">
+        <f>O72</f>
         <v>Korn, norrland</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>17</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>98</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>9</v>
       </c>
-      <c r="K76" t="s">
+      <c r="L76" t="s">
         <v>11</v>
       </c>
-      <c r="L76" s="9">
+      <c r="M76" s="9">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>17</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>98</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>9</v>
       </c>
-      <c r="K77" t="s">
+      <c r="L77" t="s">
         <v>12</v>
       </c>
-      <c r="L77" s="9">
+      <c r="M77" s="9">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>21</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" t="s">
         <v>10</v>
       </c>
-      <c r="L78">
+      <c r="M78">
         <v>-1.0713999999999999</v>
       </c>
-      <c r="N78" t="s">
+      <c r="O78" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>21</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" t="s">
         <v>11</v>
       </c>
-      <c r="L79">
+      <c r="M79">
         <v>23.928999999999998</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>21</v>
       </c>
-      <c r="K80" t="s">
+      <c r="L80" t="s">
         <v>12</v>
       </c>
-      <c r="L80">
+      <c r="M80">
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>21</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>96</v>
       </c>
-      <c r="K81" t="s">
+      <c r="L81" t="s">
         <v>10</v>
       </c>
-      <c r="L81">
+      <c r="M81">
         <v>-1.25</v>
       </c>
-      <c r="N81" t="s">
+      <c r="O81" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>21</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>96</v>
       </c>
-      <c r="K82" t="s">
+      <c r="L82" t="s">
         <v>11</v>
       </c>
-      <c r="L82">
+      <c r="M82">
         <v>25.25</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>21</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>96</v>
       </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
         <v>12</v>
       </c>
-      <c r="L83">
+      <c r="M83">
         <v>9.75</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>21</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>95</v>
       </c>
-      <c r="K84" t="s">
+      <c r="L84" t="s">
         <v>10</v>
       </c>
-      <c r="L84" s="9">
-        <f>L81</f>
+      <c r="M84" s="9">
+        <f>M81</f>
         <v>-1.25</v>
       </c>
-      <c r="N84" s="9" t="str">
-        <f>N81</f>
+      <c r="O84" s="9" t="str">
+        <f>O81</f>
         <v>Havre södra götaland</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>21</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>95</v>
       </c>
-      <c r="K85" t="s">
+      <c r="L85" t="s">
         <v>11</v>
       </c>
-      <c r="L85" s="9">
-        <f>L82</f>
+      <c r="M85" s="9">
+        <f>M82</f>
         <v>25.25</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>21</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>95</v>
       </c>
-      <c r="K86" t="s">
+      <c r="L86" t="s">
         <v>12</v>
       </c>
-      <c r="L86" s="9">
-        <f>L83</f>
+      <c r="M86" s="9">
+        <f>M83</f>
         <v>9.75</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>25</v>
       </c>
-      <c r="K87" t="s">
+      <c r="L87" t="s">
         <v>11</v>
       </c>
-      <c r="L87" s="9">
-        <f>L40</f>
+      <c r="M87" s="9">
+        <f>M40</f>
         <v>16.856999999999999</v>
       </c>
-      <c r="N87" s="9" t="str">
-        <f>N40</f>
+      <c r="O87" s="9" t="str">
+        <f>O40</f>
         <v>Rågvete/höstkorn, norra  götaland och svealand</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>25</v>
       </c>
-      <c r="K88" t="s">
+      <c r="L88" t="s">
         <v>12</v>
       </c>
-      <c r="L88" s="9">
-        <f>L41</f>
+      <c r="M88" s="9">
+        <f>M41</f>
         <v>59.143000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>25</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>96</v>
       </c>
-      <c r="K89" t="s">
+      <c r="L89" t="s">
         <v>10</v>
       </c>
-      <c r="L89" s="9">
-        <f>L45</f>
+      <c r="M89" s="9">
+        <f>M45</f>
         <v>-0.71430000000000005</v>
       </c>
-      <c r="N89" s="9" t="str">
-        <f>N45</f>
+      <c r="O89" s="9" t="str">
+        <f>O45</f>
         <v>Rågvete/höstkorn, södra götaland</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>25</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>96</v>
       </c>
-      <c r="K90" t="s">
+      <c r="L90" t="s">
         <v>11</v>
       </c>
-      <c r="L90" s="9">
-        <f>L46</f>
+      <c r="M90" s="9">
+        <f>M46</f>
         <v>23.143000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>25</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>96</v>
       </c>
-      <c r="K91" t="s">
+      <c r="L91" t="s">
         <v>12</v>
       </c>
-      <c r="L91" s="9">
-        <f>L47</f>
+      <c r="M91" s="9">
+        <f>M47</f>
         <v>37.570999999999998</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>25</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>95</v>
       </c>
-      <c r="K92" t="s">
+      <c r="L92" t="s">
         <v>10</v>
       </c>
-      <c r="L92" s="9">
-        <f>L45</f>
+      <c r="M92" s="9">
+        <f>M45</f>
         <v>-0.71430000000000005</v>
       </c>
-      <c r="N92" s="9" t="str">
-        <f>N45</f>
+      <c r="O92" s="9" t="str">
+        <f>O45</f>
         <v>Rågvete/höstkorn, södra götaland</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>25</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>95</v>
       </c>
-      <c r="K93" t="s">
+      <c r="L93" t="s">
         <v>11</v>
       </c>
-      <c r="L93" s="9">
-        <f>L46</f>
+      <c r="M93" s="9">
+        <f>M46</f>
         <v>23.143000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>25</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>95</v>
       </c>
-      <c r="K94" t="s">
+      <c r="L94" t="s">
         <v>12</v>
       </c>
-      <c r="L94" s="9">
-        <f>L47</f>
+      <c r="M94" s="9">
+        <f>M47</f>
         <v>37.570999999999998</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>24</v>
       </c>
-      <c r="K95" t="s">
+      <c r="L95" t="s">
         <v>11</v>
       </c>
-      <c r="L95" s="9">
-        <f>L40</f>
+      <c r="M95" s="9">
+        <f>M40</f>
         <v>16.856999999999999</v>
       </c>
-      <c r="N95" s="9" t="str">
-        <f>N40</f>
+      <c r="O95" s="9" t="str">
+        <f>O40</f>
         <v>Rågvete/höstkorn, norra  götaland och svealand</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>24</v>
       </c>
-      <c r="K96" t="s">
+      <c r="L96" t="s">
         <v>12</v>
       </c>
-      <c r="L96" s="9">
-        <f>L41</f>
+      <c r="M96" s="9">
+        <f>M41</f>
         <v>59.143000000000001</v>
       </c>
-      <c r="N96" s="9"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O96" s="9"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>24</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>96</v>
       </c>
-      <c r="K97" t="s">
+      <c r="L97" t="s">
         <v>10</v>
       </c>
-      <c r="L97" s="9">
-        <f>L45</f>
+      <c r="M97" s="9">
+        <f>M45</f>
         <v>-0.71430000000000005</v>
       </c>
-      <c r="N97" s="9" t="str">
-        <f>N45</f>
+      <c r="O97" s="9" t="str">
+        <f>O45</f>
         <v>Rågvete/höstkorn, södra götaland</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>24</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>96</v>
       </c>
-      <c r="K98" t="s">
+      <c r="L98" t="s">
         <v>11</v>
       </c>
-      <c r="L98" s="9">
-        <f>L46</f>
+      <c r="M98" s="9">
+        <f>M46</f>
         <v>23.143000000000001</v>
       </c>
-      <c r="N98" s="9"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O98" s="9"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>24</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>96</v>
       </c>
-      <c r="K99" t="s">
+      <c r="L99" t="s">
         <v>12</v>
       </c>
-      <c r="L99" s="9">
-        <f>L47</f>
+      <c r="M99" s="9">
+        <f>M47</f>
         <v>37.570999999999998</v>
       </c>
-      <c r="N99" s="9"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O99" s="9"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>24</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>95</v>
       </c>
-      <c r="K100" t="s">
+      <c r="L100" t="s">
         <v>10</v>
       </c>
-      <c r="L100" s="9">
-        <f>L45</f>
+      <c r="M100" s="9">
+        <f>M45</f>
         <v>-0.71430000000000005</v>
       </c>
-      <c r="N100" s="9" t="str">
-        <f>N45</f>
+      <c r="O100" s="9" t="str">
+        <f>O45</f>
         <v>Rågvete/höstkorn, södra götaland</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>24</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>95</v>
       </c>
-      <c r="K101" t="s">
+      <c r="L101" t="s">
         <v>11</v>
       </c>
-      <c r="L101" s="9">
-        <f>L46</f>
+      <c r="M101" s="9">
+        <f>M46</f>
         <v>23.143000000000001</v>
       </c>
-      <c r="N101" s="9"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O101" s="9"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>24</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>95</v>
       </c>
-      <c r="K102" t="s">
+      <c r="L102" t="s">
         <v>12</v>
       </c>
-      <c r="L102" s="9">
-        <f>L47</f>
+      <c r="M102" s="9">
+        <f>M47</f>
         <v>37.570999999999998</v>
       </c>
-      <c r="N102" s="9"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O102" s="9"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E103" s="7"/>
+      <c r="B103" s="7"/>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
@@ -2644,309 +2683,325 @@
       <c r="J103" s="7"/>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
-      <c r="N103" s="7"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M103" s="7"/>
+      <c r="O103" s="7"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>28</v>
       </c>
-      <c r="K104" t="s">
+      <c r="L104" t="s">
         <v>12</v>
       </c>
-      <c r="L104">
+      <c r="M104">
         <v>50</v>
       </c>
-      <c r="N104" t="s">
+      <c r="O104" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>30</v>
       </c>
-      <c r="K105" t="s">
+      <c r="L105" t="s">
         <v>12</v>
       </c>
-      <c r="L105">
+      <c r="M105">
         <v>0</v>
       </c>
-      <c r="N105" t="s">
+      <c r="O105" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>31</v>
       </c>
-      <c r="K106" t="s">
+      <c r="L106" t="s">
         <v>12</v>
       </c>
-      <c r="L106">
+      <c r="M106">
         <v>0</v>
       </c>
-      <c r="N106" t="s">
+      <c r="O106" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>32</v>
       </c>
-      <c r="K107" t="s">
+      <c r="L107" t="s">
         <v>12</v>
       </c>
-      <c r="L107">
+      <c r="M107">
         <v>0</v>
       </c>
-      <c r="N107" t="s">
+      <c r="O107" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>33</v>
       </c>
-      <c r="K108" t="s">
+      <c r="L108" t="s">
         <v>12</v>
       </c>
-      <c r="L108">
+      <c r="M108">
         <v>30</v>
       </c>
-      <c r="N108" t="s">
+      <c r="O108" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>34</v>
       </c>
-      <c r="K109" t="s">
+      <c r="L109" t="s">
         <v>11</v>
       </c>
-      <c r="L109">
+      <c r="M109">
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>34</v>
       </c>
-      <c r="K110" t="s">
+      <c r="L110" t="s">
         <v>12</v>
       </c>
-      <c r="L110">
+      <c r="M110">
         <v>65</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>35</v>
       </c>
-      <c r="K111" t="s">
+      <c r="L111" t="s">
         <v>11</v>
       </c>
-      <c r="L111">
+      <c r="M111">
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>35</v>
       </c>
-      <c r="K112" t="s">
+      <c r="L112" t="s">
         <v>12</v>
       </c>
-      <c r="L112">
+      <c r="M112">
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>36</v>
       </c>
-      <c r="K113" t="s">
+      <c r="L113" t="s">
         <v>10</v>
       </c>
-      <c r="L113">
+      <c r="M113">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="N113" t="s">
+      <c r="O113" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>36</v>
       </c>
-      <c r="K114" t="s">
+      <c r="L114" t="s">
         <v>11</v>
       </c>
-      <c r="L114">
+      <c r="M114">
         <v>4.95</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>36</v>
       </c>
-      <c r="K115" t="s">
+      <c r="L115" t="s">
         <v>12</v>
       </c>
-      <c r="L115">
+      <c r="M115">
         <v>-31.5</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>37</v>
       </c>
-      <c r="K116" t="s">
+      <c r="L116" t="s">
         <v>10</v>
       </c>
-      <c r="L116" s="9">
-        <f>L113</f>
+      <c r="M116" s="9">
+        <f>M113</f>
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="N116" s="9" t="str">
-        <f>N113</f>
+      <c r="O116" s="9" t="str">
+        <f>O113</f>
         <v>Potatis</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>37</v>
       </c>
-      <c r="K117" t="s">
+      <c r="L117" t="s">
         <v>11</v>
       </c>
-      <c r="L117" s="9">
-        <f t="shared" ref="L117:L118" si="3">L114</f>
+      <c r="M117" s="9">
+        <f t="shared" ref="M117:M118" si="3">M114</f>
         <v>4.95</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>37</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L118" t="s">
         <v>12</v>
       </c>
-      <c r="L118" s="9">
+      <c r="M118" s="9">
         <f t="shared" si="3"/>
         <v>-31.5</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>38</v>
       </c>
-      <c r="K119" t="s">
+      <c r="L119" t="s">
         <v>12</v>
       </c>
-      <c r="L119">
+      <c r="M119">
         <v>110</v>
       </c>
-      <c r="N119" t="s">
+      <c r="O119" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E120" s="7"/>
+      <c r="B120" s="7"/>
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
       <c r="I120" s="7"/>
       <c r="J120" s="7"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K120" s="7"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E121" s="10"/>
+      <c r="B121" s="10"/>
       <c r="F121" s="10"/>
       <c r="G121" s="10"/>
       <c r="H121" s="10"/>
       <c r="I121" s="10"/>
       <c r="J121" s="10"/>
-      <c r="K121" t="s">
+      <c r="K121" s="10"/>
+      <c r="L121" t="s">
         <v>10</v>
       </c>
-      <c r="L121">
+      <c r="M121">
         <v>-1.4286000000000001</v>
       </c>
-      <c r="N121" t="s">
+      <c r="O121" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E122" s="10"/>
+      <c r="B122" s="10"/>
       <c r="F122" s="10"/>
       <c r="G122" s="10"/>
       <c r="H122" s="10"/>
       <c r="I122" s="10"/>
       <c r="J122" s="10"/>
-      <c r="K122" t="s">
+      <c r="K122" s="10"/>
+      <c r="L122" t="s">
         <v>11</v>
       </c>
-      <c r="L122">
+      <c r="M122">
         <v>40.713999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E123" s="10"/>
+      <c r="B123" s="10"/>
       <c r="F123" s="10"/>
       <c r="G123" s="10"/>
       <c r="H123" s="10"/>
       <c r="I123" s="10"/>
       <c r="J123" s="10"/>
-      <c r="K123" t="s">
+      <c r="K123" s="10"/>
+      <c r="L123" t="s">
         <v>12</v>
       </c>
-      <c r="L123">
+      <c r="M123">
         <v>-74.856999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E124" s="11"/>
+      <c r="B124" s="11"/>
       <c r="F124" s="11"/>
       <c r="G124" s="11"/>
       <c r="H124" s="11"/>
       <c r="I124" s="11"/>
       <c r="J124" s="11"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K124" s="11"/>
+      <c r="L124" t="s">
+        <v>12</v>
+      </c>
+      <c r="M124">
+        <v>11</v>
+      </c>
+      <c r="O124" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E125" s="5"/>
+      <c r="B125" s="5"/>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
-      <c r="K125" t="s">
+      <c r="K125" s="5"/>
+      <c r="L125" t="s">
         <v>12</v>
       </c>
-      <c r="L125">
+      <c r="M125">
         <v>0</v>
       </c>
-      <c r="N125" t="s">
+      <c r="O125" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>42</v>
       </c>
@@ -2959,15 +3014,16 @@
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
-      <c r="K126" s="5" t="s">
+      <c r="K126" s="5"/>
+      <c r="L126" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L126" s="5">
+      <c r="M126" s="5">
         <v>-1.7857000000000001</v>
       </c>
-      <c r="N126" s="7"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O126" s="7"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>42</v>
       </c>
@@ -2980,15 +3036,16 @@
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
-      <c r="K127" s="5" t="s">
+      <c r="K127" s="5"/>
+      <c r="L127" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L127" s="5">
+      <c r="M127" s="5">
         <v>43.570999999999998</v>
       </c>
-      <c r="N127" s="7"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O127" s="7"/>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>42</v>
       </c>
@@ -3001,675 +3058,712 @@
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
-      <c r="K128" s="5" t="s">
+      <c r="K128" s="5"/>
+      <c r="L128" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L128" s="5">
+      <c r="M128" s="5">
         <v>-112.5</v>
       </c>
-      <c r="N128" s="7"/>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O128" s="7"/>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E129" s="11"/>
+      <c r="B129" s="11"/>
       <c r="F129" s="11"/>
       <c r="G129" s="11"/>
       <c r="H129" s="11"/>
       <c r="I129" s="11"/>
       <c r="J129" s="11"/>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K129" s="11"/>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="11"/>
+      <c r="B130" s="11"/>
       <c r="F130" s="11"/>
       <c r="G130" s="11"/>
       <c r="H130" s="11"/>
       <c r="I130" s="11"/>
       <c r="J130" s="11"/>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K130" s="11"/>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E131" s="10"/>
+      <c r="B131" s="10"/>
       <c r="F131" s="10"/>
       <c r="G131" s="10"/>
       <c r="H131" s="10"/>
       <c r="I131" s="10"/>
       <c r="J131" s="10"/>
-      <c r="K131" t="s">
+      <c r="K131" s="10"/>
+      <c r="L131" t="s">
         <v>12</v>
       </c>
-      <c r="L131">
+      <c r="M131">
         <v>0</v>
       </c>
-      <c r="N131" t="s">
+      <c r="O131" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E132" s="10"/>
+      <c r="B132" s="10"/>
       <c r="F132" s="10"/>
       <c r="G132" s="10"/>
       <c r="H132" s="10"/>
       <c r="I132" s="10"/>
       <c r="J132" s="10"/>
-      <c r="K132" t="s">
+      <c r="K132" s="10"/>
+      <c r="L132" t="s">
         <v>12</v>
       </c>
-      <c r="L132">
+      <c r="M132">
         <v>0</v>
       </c>
-      <c r="N132" t="s">
+      <c r="O132" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>47</v>
       </c>
-      <c r="K133" t="s">
+      <c r="L133" t="s">
         <v>11</v>
       </c>
-      <c r="L133">
+      <c r="M133">
         <v>2.5</v>
       </c>
-      <c r="N133" t="s">
+      <c r="O133" t="s">
         <v>85</v>
       </c>
-      <c r="O133" t="s">
+      <c r="P133" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>47</v>
       </c>
-      <c r="K134" t="s">
+      <c r="L134" t="s">
         <v>12</v>
       </c>
-      <c r="L134">
+      <c r="M134">
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>48</v>
       </c>
-      <c r="K135" t="s">
+      <c r="L135" t="s">
         <v>11</v>
       </c>
-      <c r="L135">
+      <c r="M135">
         <v>1.3846000000000001</v>
       </c>
-      <c r="N135" t="s">
+      <c r="O135" t="s">
         <v>85</v>
       </c>
-      <c r="O135" t="s">
+      <c r="P135" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>48</v>
       </c>
-      <c r="K136" t="s">
+      <c r="L136" t="s">
         <v>12</v>
       </c>
-      <c r="L136">
+      <c r="M136">
         <v>11.538</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E137" s="5"/>
+      <c r="B137" s="5"/>
       <c r="F137" s="5"/>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
-      <c r="K137" t="s">
+      <c r="K137" s="5"/>
+      <c r="L137" t="s">
         <v>11</v>
       </c>
-      <c r="L137" s="9">
-        <f>L135</f>
+      <c r="M137" s="9">
+        <f>M135</f>
         <v>1.3846000000000001</v>
       </c>
-      <c r="N137" s="7" t="s">
+      <c r="O137" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E138" s="5"/>
+      <c r="B138" s="5"/>
       <c r="F138" s="5"/>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
-      <c r="K138" t="s">
+      <c r="K138" s="5"/>
+      <c r="L138" t="s">
         <v>12</v>
       </c>
-      <c r="L138" s="9">
-        <f>L136</f>
+      <c r="M138" s="9">
+        <f>M136</f>
         <v>11.538</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E139" s="5"/>
+      <c r="B139" s="5"/>
       <c r="F139" s="5"/>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
-      <c r="K139" t="s">
+      <c r="K139" s="5"/>
+      <c r="L139" t="s">
         <v>11</v>
       </c>
-      <c r="L139">
+      <c r="M139">
         <v>3.3332999999999999</v>
       </c>
-      <c r="N139" t="s">
+      <c r="O139" t="s">
         <v>87</v>
       </c>
-      <c r="O139" t="s">
+      <c r="P139" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E140" s="5"/>
+      <c r="B140" s="5"/>
       <c r="F140" s="5"/>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
-      <c r="K140" t="s">
+      <c r="K140" s="5"/>
+      <c r="L140" t="s">
         <v>12</v>
       </c>
-      <c r="L140">
+      <c r="M140">
         <v>33.332999999999998</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E141" s="5"/>
+      <c r="B141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
-      <c r="K141" t="s">
+      <c r="K141" s="5"/>
+      <c r="L141" t="s">
         <v>11</v>
       </c>
-      <c r="L141">
+      <c r="M141">
         <v>3</v>
       </c>
-      <c r="N141" t="s">
+      <c r="O141" t="s">
         <v>88</v>
       </c>
-      <c r="O141" t="s">
+      <c r="P141" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E142" s="5"/>
+      <c r="B142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
-      <c r="K142" t="s">
+      <c r="K142" s="5"/>
+      <c r="L142" t="s">
         <v>12</v>
       </c>
-      <c r="L142">
+      <c r="M142">
         <v>90</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E143" s="5"/>
+      <c r="B143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
-      <c r="K143" s="5" t="s">
+      <c r="K143" s="5"/>
+      <c r="L143" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L143">
+      <c r="M143">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="N143" t="s">
+      <c r="O143" t="s">
         <v>89</v>
       </c>
-      <c r="O143" t="s">
+      <c r="P143" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E144" s="5"/>
+      <c r="B144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
-      <c r="K144" t="s">
+      <c r="K144" s="5"/>
+      <c r="L144" t="s">
         <v>11</v>
       </c>
-      <c r="L144">
+      <c r="M144">
         <v>1.2583</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E145" s="5"/>
+      <c r="B145" s="5"/>
       <c r="F145" s="5"/>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
-      <c r="K145" t="s">
+      <c r="K145" s="5"/>
+      <c r="L145" t="s">
         <v>12</v>
       </c>
-      <c r="L145">
+      <c r="M145">
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E146" s="5"/>
+      <c r="B146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
-      <c r="K146" s="5" t="s">
+      <c r="K146" s="5"/>
+      <c r="L146" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L146" s="9">
-        <f>L143</f>
+      <c r="M146" s="9">
+        <f>M143</f>
         <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="N146" s="9" t="str">
-        <f>N143</f>
-        <v xml:space="preserve">yield in fresh weight 5% DM </v>
       </c>
       <c r="O146" s="9" t="str">
         <f>O143</f>
+        <v xml:space="preserve">yield in fresh weight 5% DM </v>
+      </c>
+      <c r="P146" s="9" t="str">
+        <f>P143</f>
         <v>Yara (2018)</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E147" s="5"/>
+      <c r="B147" s="5"/>
       <c r="F147" s="5"/>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
-      <c r="K147" t="s">
+      <c r="K147" s="5"/>
+      <c r="L147" t="s">
         <v>11</v>
       </c>
-      <c r="L147" s="9">
-        <f>L144</f>
+      <c r="M147" s="9">
+        <f>M144</f>
         <v>1.2583</v>
       </c>
-      <c r="M147" s="9"/>
       <c r="N147" s="9"/>
       <c r="O147" s="9"/>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P147" s="9"/>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E148" s="5"/>
+      <c r="B148" s="5"/>
       <c r="F148" s="5"/>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
-      <c r="K148" t="s">
+      <c r="K148" s="5"/>
+      <c r="L148" t="s">
         <v>12</v>
       </c>
-      <c r="L148" s="9">
-        <f>L145</f>
+      <c r="M148" s="9">
+        <f>M145</f>
         <v>0</v>
       </c>
-      <c r="M148" s="9"/>
       <c r="N148" s="9"/>
       <c r="O148" s="9"/>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P148" s="9"/>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E149" s="5"/>
+      <c r="B149" s="5"/>
       <c r="F149" s="5"/>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
-      <c r="K149" t="s">
+      <c r="K149" s="5"/>
+      <c r="L149" t="s">
         <v>11</v>
       </c>
-      <c r="L149" s="9">
-        <f>L139</f>
+      <c r="M149" s="9">
+        <f>M139</f>
         <v>3.3332999999999999</v>
       </c>
-      <c r="N149" s="7" t="s">
+      <c r="O149" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E150" s="5"/>
+      <c r="B150" s="5"/>
       <c r="F150" s="5"/>
       <c r="G150" s="5"/>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
-      <c r="K150" t="s">
+      <c r="K150" s="5"/>
+      <c r="L150" t="s">
         <v>12</v>
       </c>
-      <c r="L150" s="9">
-        <f>L140</f>
+      <c r="M150" s="9">
+        <f>M140</f>
         <v>33.332999999999998</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E151" s="7"/>
+      <c r="B151" s="7"/>
       <c r="F151" s="7"/>
       <c r="G151" s="7"/>
       <c r="H151" s="7"/>
       <c r="I151" s="7"/>
       <c r="J151" s="7"/>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K151" s="7"/>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E152" s="5"/>
+      <c r="B152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
-      <c r="K152" t="s">
+      <c r="K152" s="5"/>
+      <c r="L152" t="s">
         <v>12</v>
       </c>
-      <c r="L152">
+      <c r="M152">
         <v>65</v>
       </c>
-      <c r="N152" t="s">
+      <c r="O152" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E153" s="7"/>
+      <c r="B153" s="7"/>
       <c r="F153" s="7"/>
       <c r="G153" s="7"/>
       <c r="H153" s="7"/>
       <c r="I153" s="7"/>
       <c r="J153" s="7"/>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K153" s="7"/>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E154" s="5"/>
+      <c r="B154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
-      <c r="K154" t="s">
+      <c r="K154" s="5"/>
+      <c r="L154" t="s">
         <v>12</v>
       </c>
-      <c r="L154">
+      <c r="M154">
         <v>65</v>
       </c>
-      <c r="N154" t="s">
+      <c r="O154" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E155" s="5"/>
+      <c r="B155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
-      <c r="K155" t="s">
+      <c r="K155" s="5"/>
+      <c r="L155" t="s">
         <v>12</v>
       </c>
-      <c r="L155">
+      <c r="M155">
         <v>100</v>
       </c>
-      <c r="N155" t="s">
+      <c r="O155" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E156" s="5"/>
+      <c r="B156" s="5"/>
       <c r="F156" s="5"/>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
       <c r="I156" s="5"/>
       <c r="J156" s="5"/>
-      <c r="K156" t="s">
+      <c r="K156" s="5"/>
+      <c r="L156" t="s">
         <v>12</v>
       </c>
-      <c r="L156">
+      <c r="M156">
         <v>110</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E157" s="5"/>
+      <c r="B157" s="5"/>
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
-      <c r="K157" t="s">
+      <c r="K157" s="5"/>
+      <c r="L157" t="s">
         <v>12</v>
       </c>
-      <c r="L157" s="9">
-        <f>L155</f>
+      <c r="M157" s="9">
+        <f>M155</f>
         <v>100</v>
       </c>
-      <c r="N157" s="7" t="s">
+      <c r="O157" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E158" s="7"/>
+      <c r="B158" s="7"/>
       <c r="F158" s="7"/>
       <c r="G158" s="7"/>
       <c r="H158" s="7"/>
       <c r="I158" s="7"/>
       <c r="J158" s="7"/>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K158" s="7"/>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E159" s="7"/>
+      <c r="B159" s="7"/>
       <c r="F159" s="7"/>
       <c r="G159" s="7"/>
       <c r="H159" s="7"/>
       <c r="I159" s="7"/>
       <c r="J159" s="7"/>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K159" s="7"/>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E160" s="7"/>
+      <c r="B160" s="7"/>
       <c r="F160" s="7"/>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
       <c r="I160" s="7"/>
       <c r="J160" s="7"/>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K160" s="7"/>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E161" s="7"/>
+      <c r="B161" s="7"/>
       <c r="F161" s="7"/>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
       <c r="I161" s="7"/>
       <c r="J161" s="7"/>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K161" s="7"/>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E162" s="7"/>
+      <c r="B162" s="7"/>
       <c r="F162" s="7"/>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
       <c r="I162" s="7"/>
       <c r="J162" s="7"/>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K162" s="7"/>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E163" s="7"/>
+      <c r="B163" s="7"/>
       <c r="F163" s="7"/>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
       <c r="I163" s="7"/>
       <c r="J163" s="7"/>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K163" s="7"/>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E164" s="7"/>
+      <c r="B164" s="7"/>
       <c r="F164" s="7"/>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
       <c r="I164" s="7"/>
       <c r="J164" s="7"/>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K164" s="7"/>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E165" s="5"/>
+      <c r="B165" s="5"/>
       <c r="F165" s="5"/>
       <c r="G165" s="5"/>
       <c r="H165" s="5"/>
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
-      <c r="K165" t="s">
+      <c r="K165" s="5"/>
+      <c r="L165" t="s">
         <v>12</v>
       </c>
-      <c r="L165">
+      <c r="M165">
         <v>0</v>
       </c>
-      <c r="N165" t="s">
+      <c r="O165" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E166" s="7"/>
+      <c r="B166" s="7"/>
       <c r="F166" s="7"/>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
       <c r="I166" s="7"/>
       <c r="J166" s="7"/>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K166" s="7"/>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E167" s="7"/>
+      <c r="B167" s="7"/>
       <c r="F167" s="7"/>
       <c r="G167" s="7"/>
       <c r="H167" s="7"/>
       <c r="I167" s="7"/>
       <c r="J167" s="7"/>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K167" s="7"/>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E168" s="5"/>
+      <c r="B168" s="5"/>
       <c r="F168" s="5"/>
       <c r="G168" s="5"/>
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
-      <c r="K168" t="s">
+      <c r="K168" s="5"/>
+      <c r="L168" t="s">
         <v>12</v>
       </c>
-      <c r="L168">
+      <c r="M168">
         <v>0</v>
       </c>
-      <c r="N168" t="s">
+      <c r="O168" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>118</v>
       </c>
@@ -3685,1063 +3779,1110 @@
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
-      <c r="N170" s="3"/>
+      <c r="N170" s="2"/>
       <c r="O170" s="3"/>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K171" s="6" t="s">
+      <c r="P170" s="3"/>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L171" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L171" s="6">
+      <c r="M171" s="6">
         <v>0</v>
       </c>
-      <c r="M171" s="6"/>
-      <c r="N171" s="6" t="s">
+      <c r="N171" s="6"/>
+      <c r="O171" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K172" s="6" t="s">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L172" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L172" s="6">
+      <c r="M172" s="6">
         <v>1</v>
       </c>
-      <c r="M172" s="6"/>
-      <c r="N172" s="6" t="s">
+      <c r="N172" s="6"/>
+      <c r="O172" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>7</v>
       </c>
-      <c r="K173" t="s">
+      <c r="L173" t="s">
         <v>13</v>
       </c>
-      <c r="L173">
+      <c r="M173">
         <v>-0.32340000000000002</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>7</v>
       </c>
-      <c r="K174" t="s">
+      <c r="L174" t="s">
         <v>14</v>
       </c>
-      <c r="L174">
+      <c r="M174">
         <v>0.97240000000000004</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>16</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" t="s">
         <v>13</v>
       </c>
-      <c r="L175">
+      <c r="M175">
         <v>-0.32500000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>16</v>
       </c>
-      <c r="K176" t="s">
+      <c r="L176" t="s">
         <v>14</v>
       </c>
-      <c r="L176">
+      <c r="M176">
         <v>0.81369999999999998</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>27</v>
       </c>
-      <c r="K177" t="s">
+      <c r="L177" t="s">
         <v>13</v>
       </c>
-      <c r="L177">
+      <c r="M177">
         <v>-0.58699999999999997</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>27</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" t="s">
         <v>14</v>
       </c>
-      <c r="L178">
+      <c r="M178">
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>23</v>
       </c>
-      <c r="K179" t="s">
+      <c r="L179" t="s">
         <v>13</v>
       </c>
-      <c r="L179">
+      <c r="M179">
         <v>-0.35070000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>23</v>
       </c>
-      <c r="K180" t="s">
+      <c r="L180" t="s">
         <v>14</v>
       </c>
-      <c r="L180">
+      <c r="M180">
         <v>0.9234</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>17</v>
       </c>
-      <c r="K181" t="s">
+      <c r="L181" t="s">
         <v>13</v>
       </c>
-      <c r="L181">
+      <c r="M181">
         <v>-0.41710000000000003</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>17</v>
       </c>
-      <c r="K182" t="s">
+      <c r="L182" t="s">
         <v>14</v>
       </c>
-      <c r="L182">
+      <c r="M182">
         <v>0.91610000000000003</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>21</v>
       </c>
-      <c r="K183" t="s">
+      <c r="L183" t="s">
         <v>13</v>
       </c>
-      <c r="L183">
+      <c r="M183">
         <v>-0.74150000000000005</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>21</v>
       </c>
-      <c r="K184" t="s">
+      <c r="L184" t="s">
         <v>14</v>
       </c>
-      <c r="L184">
+      <c r="M184">
         <v>0.96550000000000002</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>25</v>
       </c>
-      <c r="K185" t="s">
+      <c r="L185" t="s">
         <v>13</v>
       </c>
-      <c r="L185" s="9">
-        <f>L187</f>
+      <c r="M185" s="9">
+        <f>M187</f>
         <v>-0.58699999999999997</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>25</v>
       </c>
-      <c r="K186" t="s">
+      <c r="L186" t="s">
         <v>14</v>
       </c>
-      <c r="L186" s="9">
-        <f>L188</f>
+      <c r="M186" s="9">
+        <f>M188</f>
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>24</v>
       </c>
-      <c r="K187" t="s">
+      <c r="L187" t="s">
         <v>13</v>
       </c>
-      <c r="L187">
+      <c r="M187">
         <v>-0.58699999999999997</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>24</v>
       </c>
-      <c r="K188" t="s">
+      <c r="L188" t="s">
         <v>14</v>
       </c>
-      <c r="L188">
+      <c r="M188">
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E189" s="7"/>
+      <c r="B189" s="7"/>
       <c r="F189" s="7"/>
       <c r="G189" s="7"/>
       <c r="H189" s="7"/>
       <c r="I189" s="7"/>
       <c r="J189" s="7"/>
-      <c r="L189" s="9"/>
-      <c r="N189" s="7"/>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K189" s="7"/>
+      <c r="M189" s="9"/>
+      <c r="O189" s="7"/>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E190" s="5"/>
+      <c r="B190" s="5"/>
       <c r="F190" s="5"/>
       <c r="G190" s="5"/>
       <c r="H190" s="5"/>
       <c r="I190" s="5"/>
       <c r="J190" s="5"/>
-      <c r="K190" t="s">
+      <c r="K190" s="5"/>
+      <c r="L190" t="s">
         <v>14</v>
       </c>
-      <c r="L190" s="5">
+      <c r="M190" s="5">
         <v>1</v>
       </c>
-      <c r="M190" s="5"/>
-      <c r="N190" s="5" t="s">
+      <c r="N190" s="5"/>
+      <c r="O190" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>30</v>
       </c>
-      <c r="K191" t="s">
+      <c r="L191" t="s">
         <v>14</v>
       </c>
-      <c r="L191">
+      <c r="M191">
         <v>1</v>
       </c>
-      <c r="N191" s="5" t="s">
+      <c r="O191" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>31</v>
       </c>
-      <c r="K192" t="s">
+      <c r="L192" t="s">
         <v>14</v>
       </c>
-      <c r="L192">
+      <c r="M192">
         <v>1</v>
       </c>
-      <c r="N192" s="5" t="s">
+      <c r="O192" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>32</v>
       </c>
-      <c r="K193" t="s">
+      <c r="L193" t="s">
         <v>14</v>
       </c>
-      <c r="L193">
+      <c r="M193">
         <v>1</v>
       </c>
-      <c r="N193" s="5" t="s">
+      <c r="O193" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>33</v>
       </c>
-      <c r="K194" t="s">
+      <c r="L194" t="s">
         <v>14</v>
       </c>
-      <c r="L194">
+      <c r="M194">
         <v>1</v>
       </c>
-      <c r="N194" s="5" t="s">
+      <c r="O194" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>34</v>
       </c>
-      <c r="K195" t="s">
+      <c r="L195" t="s">
         <v>13</v>
       </c>
-      <c r="L195">
+      <c r="M195">
         <v>-9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>34</v>
       </c>
-      <c r="K196" t="s">
+      <c r="L196" t="s">
         <v>14</v>
       </c>
-      <c r="L196">
+      <c r="M196">
         <v>1.2939000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>35</v>
       </c>
-      <c r="K197" t="s">
+      <c r="L197" t="s">
         <v>14</v>
       </c>
-      <c r="L197">
+      <c r="M197">
         <v>0.94</v>
       </c>
-      <c r="N197" s="5" t="s">
+      <c r="O197" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>36</v>
       </c>
-      <c r="K198" t="s">
+      <c r="L198" t="s">
         <v>14</v>
       </c>
-      <c r="L198">
+      <c r="M198">
         <v>1</v>
       </c>
-      <c r="N198" s="5" t="s">
+      <c r="O198" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>37</v>
       </c>
-      <c r="K199" t="s">
+      <c r="L199" t="s">
         <v>14</v>
       </c>
-      <c r="L199">
+      <c r="M199">
         <v>1</v>
       </c>
-      <c r="N199" s="5" t="s">
+      <c r="O199" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>38</v>
       </c>
-      <c r="K200" t="s">
+      <c r="L200" t="s">
         <v>14</v>
       </c>
-      <c r="L200">
+      <c r="M200">
         <v>1</v>
       </c>
-      <c r="N200" s="5" t="s">
+      <c r="O200" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E201" s="7"/>
+      <c r="B201" s="7"/>
       <c r="F201" s="7"/>
       <c r="G201" s="7"/>
       <c r="H201" s="7"/>
       <c r="I201" s="7"/>
       <c r="J201" s="7"/>
-      <c r="R201" s="4"/>
-    </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K201" s="7"/>
+      <c r="S201" s="4"/>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E202" s="10"/>
+      <c r="B202" s="10"/>
       <c r="F202" s="10"/>
       <c r="G202" s="10"/>
       <c r="H202" s="10"/>
       <c r="I202" s="10"/>
       <c r="J202" s="10"/>
-      <c r="K202" t="s">
+      <c r="K202" s="10"/>
+      <c r="L202" t="s">
         <v>13</v>
       </c>
-      <c r="L202">
+      <c r="M202">
         <v>-8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E203" s="10"/>
+      <c r="B203" s="10"/>
       <c r="F203" s="10"/>
       <c r="G203" s="10"/>
       <c r="H203" s="10"/>
       <c r="I203" s="10"/>
       <c r="J203" s="10"/>
-      <c r="K203" t="s">
+      <c r="K203" s="10"/>
+      <c r="L203" t="s">
         <v>14</v>
       </c>
-      <c r="L203">
+      <c r="M203">
         <v>0.72799999999999998</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E204" s="11"/>
+      <c r="B204" s="11"/>
       <c r="F204" s="11"/>
       <c r="G204" s="11"/>
       <c r="H204" s="11"/>
       <c r="I204" s="11"/>
       <c r="J204" s="11"/>
-    </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K204" s="11"/>
+      <c r="L204" t="s">
+        <v>14</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="O204" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E205" s="5"/>
+      <c r="B205" s="5"/>
       <c r="F205" s="5"/>
       <c r="G205" s="5"/>
       <c r="H205" s="5"/>
       <c r="I205" s="5"/>
       <c r="J205" s="5"/>
-      <c r="K205" t="s">
+      <c r="K205" s="5"/>
+      <c r="L205" t="s">
         <v>14</v>
       </c>
-      <c r="L205">
+      <c r="M205">
         <v>1</v>
       </c>
-      <c r="N205" s="5" t="s">
+      <c r="O205" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E206" s="10"/>
+      <c r="B206" s="10"/>
       <c r="F206" s="10"/>
       <c r="G206" s="10"/>
       <c r="H206" s="10"/>
       <c r="I206" s="10"/>
       <c r="J206" s="10"/>
-      <c r="K206" t="s">
+      <c r="K206" s="10"/>
+      <c r="L206" t="s">
         <v>13</v>
       </c>
-      <c r="L206">
+      <c r="M206">
         <v>-3.2399999999999998E-2</v>
       </c>
-      <c r="N206" s="7"/>
-    </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O206" s="7"/>
+    </row>
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E207" s="10"/>
+      <c r="B207" s="10"/>
       <c r="F207" s="10"/>
       <c r="G207" s="10"/>
       <c r="H207" s="10"/>
       <c r="I207" s="10"/>
       <c r="J207" s="10"/>
-      <c r="K207" t="s">
+      <c r="K207" s="10"/>
+      <c r="L207" t="s">
         <v>14</v>
       </c>
-      <c r="L207">
+      <c r="M207">
         <v>0.82120000000000004</v>
       </c>
-      <c r="N207" s="7"/>
-    </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O207" s="7"/>
+    </row>
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E208" s="11"/>
+      <c r="B208" s="11"/>
       <c r="F208" s="11"/>
       <c r="G208" s="11"/>
       <c r="H208" s="11"/>
       <c r="I208" s="11"/>
       <c r="J208" s="11"/>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K208" s="11"/>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E209" s="11"/>
+      <c r="B209" s="11"/>
       <c r="F209" s="11"/>
       <c r="G209" s="11"/>
       <c r="H209" s="11"/>
       <c r="I209" s="11"/>
       <c r="J209" s="11"/>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K209" s="11"/>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E210" s="10"/>
+      <c r="B210" s="10"/>
       <c r="F210" s="10"/>
       <c r="G210" s="10"/>
       <c r="H210" s="10"/>
       <c r="I210" s="10"/>
       <c r="J210" s="10"/>
-      <c r="K210" t="s">
+      <c r="K210" s="10"/>
+      <c r="L210" t="s">
         <v>14</v>
       </c>
-      <c r="L210">
+      <c r="M210">
         <v>1</v>
       </c>
-      <c r="N210" s="5" t="s">
+      <c r="O210" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E211" s="10"/>
+      <c r="B211" s="10"/>
       <c r="F211" s="10"/>
       <c r="G211" s="10"/>
       <c r="H211" s="10"/>
       <c r="I211" s="10"/>
       <c r="J211" s="10"/>
-      <c r="K211" t="s">
+      <c r="K211" s="10"/>
+      <c r="L211" t="s">
         <v>14</v>
       </c>
-      <c r="L211">
+      <c r="M211">
         <v>1</v>
       </c>
-      <c r="N211" s="5" t="s">
+      <c r="O211" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>47</v>
       </c>
-      <c r="K212" t="s">
+      <c r="L212" t="s">
         <v>14</v>
       </c>
-      <c r="L212">
+      <c r="M212">
         <v>1</v>
       </c>
-      <c r="N212" s="5" t="s">
+      <c r="O212" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>48</v>
       </c>
-      <c r="K213" t="s">
+      <c r="L213" t="s">
         <v>14</v>
       </c>
-      <c r="L213">
+      <c r="M213">
         <v>1</v>
       </c>
-      <c r="N213" s="5" t="s">
+      <c r="O213" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E214" s="5"/>
+      <c r="B214" s="5"/>
       <c r="F214" s="5"/>
       <c r="G214" s="5"/>
       <c r="H214" s="5"/>
       <c r="I214" s="5"/>
       <c r="J214" s="5"/>
-      <c r="K214" t="s">
+      <c r="K214" s="5"/>
+      <c r="L214" t="s">
         <v>14</v>
       </c>
-      <c r="L214">
+      <c r="M214">
         <v>1</v>
       </c>
-      <c r="N214" s="5" t="s">
+      <c r="O214" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E215" s="5"/>
+      <c r="B215" s="5"/>
       <c r="F215" s="5"/>
       <c r="G215" s="5"/>
       <c r="H215" s="5"/>
       <c r="I215" s="5"/>
       <c r="J215" s="5"/>
-      <c r="K215" t="s">
+      <c r="K215" s="5"/>
+      <c r="L215" t="s">
         <v>14</v>
       </c>
-      <c r="L215">
+      <c r="M215">
         <v>1</v>
       </c>
-      <c r="N215" s="5" t="s">
+      <c r="O215" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E216" s="5"/>
+      <c r="B216" s="5"/>
       <c r="F216" s="5"/>
       <c r="G216" s="5"/>
       <c r="H216" s="5"/>
       <c r="I216" s="5"/>
       <c r="J216" s="5"/>
-      <c r="K216" t="s">
+      <c r="K216" s="5"/>
+      <c r="L216" t="s">
         <v>14</v>
       </c>
-      <c r="L216">
+      <c r="M216">
         <v>1</v>
       </c>
-      <c r="N216" s="5" t="s">
+      <c r="O216" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E217" s="5"/>
+      <c r="B217" s="5"/>
       <c r="F217" s="5"/>
       <c r="G217" s="5"/>
       <c r="H217" s="5"/>
       <c r="I217" s="5"/>
       <c r="J217" s="5"/>
-      <c r="K217" t="s">
+      <c r="K217" s="5"/>
+      <c r="L217" t="s">
         <v>14</v>
       </c>
-      <c r="L217">
+      <c r="M217">
         <v>1</v>
       </c>
-      <c r="N217" s="5" t="s">
+      <c r="O217" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E218" s="5"/>
+      <c r="B218" s="5"/>
       <c r="F218" s="5"/>
       <c r="G218" s="5"/>
       <c r="H218" s="5"/>
       <c r="I218" s="5"/>
       <c r="J218" s="5"/>
-      <c r="K218" t="s">
+      <c r="K218" s="5"/>
+      <c r="L218" t="s">
         <v>14</v>
       </c>
-      <c r="L218">
+      <c r="M218">
         <v>1</v>
       </c>
-      <c r="N218" s="5" t="s">
+      <c r="O218" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E219" s="5"/>
+      <c r="B219" s="5"/>
       <c r="F219" s="5"/>
       <c r="G219" s="5"/>
       <c r="H219" s="5"/>
       <c r="I219" s="5"/>
       <c r="J219" s="5"/>
-      <c r="K219" t="s">
+      <c r="K219" s="5"/>
+      <c r="L219" t="s">
         <v>14</v>
       </c>
-      <c r="L219">
+      <c r="M219">
         <v>1</v>
       </c>
-      <c r="N219" s="5" t="s">
+      <c r="O219" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E220" s="5"/>
+      <c r="B220" s="5"/>
       <c r="F220" s="5"/>
       <c r="G220" s="5"/>
       <c r="H220" s="5"/>
       <c r="I220" s="5"/>
       <c r="J220" s="5"/>
-      <c r="K220" t="s">
+      <c r="K220" s="5"/>
+      <c r="L220" t="s">
         <v>14</v>
       </c>
-      <c r="L220">
+      <c r="M220">
         <v>1</v>
       </c>
-      <c r="N220" s="5" t="s">
+      <c r="O220" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E221" s="5"/>
+      <c r="B221" s="5"/>
       <c r="F221" s="5"/>
       <c r="G221" s="5"/>
       <c r="H221" s="5"/>
       <c r="I221" s="5"/>
       <c r="J221" s="5"/>
-      <c r="K221" t="s">
+      <c r="K221" s="5"/>
+      <c r="L221" t="s">
         <v>14</v>
       </c>
-      <c r="L221">
+      <c r="M221">
         <v>1</v>
       </c>
-      <c r="N221" s="5" t="s">
+      <c r="O221" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E222" s="5"/>
+      <c r="B222" s="5"/>
       <c r="F222" s="5"/>
       <c r="G222" s="5"/>
       <c r="H222" s="5"/>
       <c r="I222" s="5"/>
       <c r="J222" s="5"/>
-      <c r="K222" t="s">
+      <c r="K222" s="5"/>
+      <c r="L222" t="s">
         <v>14</v>
       </c>
-      <c r="L222">
+      <c r="M222">
         <v>1</v>
       </c>
-      <c r="N222" s="5" t="s">
+      <c r="O222" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E223" s="5"/>
+      <c r="B223" s="5"/>
       <c r="F223" s="5"/>
       <c r="G223" s="5"/>
       <c r="H223" s="5"/>
       <c r="I223" s="5"/>
       <c r="J223" s="5"/>
-      <c r="K223" t="s">
+      <c r="K223" s="5"/>
+      <c r="L223" t="s">
         <v>14</v>
       </c>
-      <c r="L223">
+      <c r="M223">
         <v>1</v>
       </c>
-      <c r="N223" s="5" t="s">
+      <c r="O223" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E224" s="5"/>
+      <c r="B224" s="5"/>
       <c r="F224" s="5"/>
       <c r="G224" s="5"/>
       <c r="H224" s="5"/>
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
-      <c r="K224" t="s">
+      <c r="K224" s="5"/>
+      <c r="L224" t="s">
         <v>14</v>
       </c>
-      <c r="L224">
+      <c r="M224">
         <v>1</v>
       </c>
-      <c r="N224" s="5" t="s">
+      <c r="O224" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E225" s="5"/>
+      <c r="B225" s="5"/>
       <c r="F225" s="5"/>
       <c r="G225" s="5"/>
       <c r="H225" s="5"/>
       <c r="I225" s="5"/>
       <c r="J225" s="5"/>
-      <c r="K225" t="s">
+      <c r="K225" s="5"/>
+      <c r="L225" t="s">
         <v>14</v>
       </c>
-      <c r="L225">
+      <c r="M225">
         <v>1</v>
       </c>
-      <c r="N225" s="5" t="s">
+      <c r="O225" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E226" s="5"/>
+      <c r="B226" s="5"/>
       <c r="F226" s="5"/>
       <c r="G226" s="5"/>
       <c r="H226" s="5"/>
       <c r="I226" s="5"/>
       <c r="J226" s="5"/>
-      <c r="K226" t="s">
+      <c r="K226" s="5"/>
+      <c r="L226" t="s">
         <v>14</v>
       </c>
-      <c r="L226">
+      <c r="M226">
         <v>1</v>
       </c>
-      <c r="N226" s="5" t="s">
+      <c r="O226" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E227" s="5"/>
+      <c r="B227" s="5"/>
       <c r="F227" s="5"/>
       <c r="G227" s="5"/>
       <c r="H227" s="5"/>
       <c r="I227" s="5"/>
       <c r="J227" s="5"/>
-      <c r="K227" t="s">
+      <c r="K227" s="5"/>
+      <c r="L227" t="s">
         <v>14</v>
       </c>
-      <c r="L227">
+      <c r="M227">
         <v>1</v>
       </c>
-      <c r="N227" s="5" t="s">
+      <c r="O227" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E228" s="5"/>
+      <c r="B228" s="5"/>
       <c r="F228" s="5"/>
       <c r="G228" s="5"/>
       <c r="H228" s="5"/>
       <c r="I228" s="5"/>
       <c r="J228" s="5"/>
-      <c r="K228" t="s">
+      <c r="K228" s="5"/>
+      <c r="L228" t="s">
         <v>14</v>
       </c>
-      <c r="L228">
+      <c r="M228">
         <v>1</v>
       </c>
-      <c r="N228" s="5" t="s">
+      <c r="O228" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E229" s="5"/>
+      <c r="B229" s="5"/>
       <c r="F229" s="5"/>
       <c r="G229" s="5"/>
       <c r="H229" s="5"/>
       <c r="I229" s="5"/>
       <c r="J229" s="5"/>
-      <c r="K229" t="s">
+      <c r="K229" s="5"/>
+      <c r="L229" t="s">
         <v>14</v>
       </c>
-      <c r="L229">
+      <c r="M229">
         <v>1</v>
       </c>
-      <c r="N229" s="5" t="s">
+      <c r="O229" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E230" s="5"/>
+      <c r="B230" s="5"/>
       <c r="F230" s="5"/>
       <c r="G230" s="5"/>
       <c r="H230" s="5"/>
       <c r="I230" s="5"/>
       <c r="J230" s="5"/>
-      <c r="K230" t="s">
+      <c r="K230" s="5"/>
+      <c r="L230" t="s">
         <v>14</v>
       </c>
-      <c r="L230">
+      <c r="M230">
         <v>1</v>
       </c>
-      <c r="N230" s="5" t="s">
+      <c r="O230" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E231" s="5"/>
+      <c r="B231" s="5"/>
       <c r="F231" s="5"/>
       <c r="G231" s="5"/>
       <c r="H231" s="5"/>
       <c r="I231" s="5"/>
       <c r="J231" s="5"/>
-      <c r="K231" t="s">
+      <c r="K231" s="5"/>
+      <c r="L231" t="s">
         <v>14</v>
       </c>
-      <c r="L231">
+      <c r="M231">
         <v>1</v>
       </c>
-      <c r="N231" s="5" t="s">
+      <c r="O231" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E232" s="5"/>
+      <c r="B232" s="5"/>
       <c r="F232" s="5"/>
       <c r="G232" s="5"/>
       <c r="H232" s="5"/>
       <c r="I232" s="5"/>
       <c r="J232" s="5"/>
-      <c r="K232" t="s">
+      <c r="K232" s="5"/>
+      <c r="L232" t="s">
         <v>14</v>
       </c>
-      <c r="L232">
+      <c r="M232">
         <v>1</v>
       </c>
-      <c r="N232" s="5" t="s">
+      <c r="O232" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E233" s="5"/>
+      <c r="B233" s="5"/>
       <c r="F233" s="5"/>
       <c r="G233" s="5"/>
       <c r="H233" s="5"/>
       <c r="I233" s="5"/>
       <c r="J233" s="5"/>
-      <c r="K233" t="s">
+      <c r="K233" s="5"/>
+      <c r="L233" t="s">
         <v>14</v>
       </c>
-      <c r="L233">
+      <c r="M233">
         <v>1</v>
       </c>
-      <c r="N233" s="5" t="s">
+      <c r="O233" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E234" s="5"/>
+      <c r="B234" s="5"/>
       <c r="F234" s="5"/>
       <c r="G234" s="5"/>
       <c r="H234" s="5"/>
       <c r="I234" s="5"/>
       <c r="J234" s="5"/>
-      <c r="K234" t="s">
+      <c r="K234" s="5"/>
+      <c r="L234" t="s">
         <v>14</v>
       </c>
-      <c r="L234">
+      <c r="M234">
         <v>1</v>
       </c>
-      <c r="N234" s="5" t="s">
+      <c r="O234" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E235" s="5"/>
+      <c r="B235" s="5"/>
       <c r="F235" s="5"/>
       <c r="G235" s="5"/>
       <c r="H235" s="5"/>
       <c r="I235" s="5"/>
       <c r="J235" s="5"/>
-      <c r="K235" t="s">
+      <c r="K235" s="5"/>
+      <c r="L235" t="s">
         <v>14</v>
       </c>
-      <c r="L235">
+      <c r="M235">
         <v>1</v>
       </c>
-      <c r="N235" s="5" t="s">
+      <c r="O235" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E236" s="5"/>
+      <c r="B236" s="5"/>
       <c r="F236" s="5"/>
       <c r="G236" s="5"/>
       <c r="H236" s="5"/>
       <c r="I236" s="5"/>
       <c r="J236" s="5"/>
-      <c r="K236" t="s">
+      <c r="K236" s="5"/>
+      <c r="L236" t="s">
         <v>14</v>
       </c>
-      <c r="L236">
+      <c r="M236">
         <v>1</v>
       </c>
-      <c r="N236" s="5" t="s">
+      <c r="O236" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E237" s="5"/>
+      <c r="B237" s="5"/>
       <c r="F237" s="5"/>
       <c r="G237" s="5"/>
       <c r="H237" s="5"/>
       <c r="I237" s="5"/>
       <c r="J237" s="5"/>
-      <c r="K237" t="s">
+      <c r="K237" s="5"/>
+      <c r="L237" t="s">
         <v>14</v>
       </c>
-      <c r="L237">
+      <c r="M237">
         <v>1</v>
       </c>
-      <c r="N237" s="5" t="s">
+      <c r="O237" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>180</v>
       </c>
@@ -4759,1068 +4900,1072 @@
       <c r="M239" s="2"/>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
-    </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J240" s="6" t="s">
+      <c r="P239" s="2"/>
+    </row>
+    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K240" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="K240" s="6" t="s">
+      <c r="L240" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L240" s="14">
+      <c r="M240" s="14">
         <v>0</v>
       </c>
-      <c r="M240" s="6" t="s">
+      <c r="N240" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="N240" s="6" t="s">
+      <c r="O240" s="6" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J241" s="6"/>
+      <c r="B241" s="1"/>
       <c r="K241" s="6"/>
-      <c r="L241" s="14"/>
-      <c r="M241" s="6"/>
+      <c r="L241" s="6"/>
+      <c r="M241" s="14"/>
       <c r="N241" s="6"/>
-    </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E242" t="s">
+      <c r="O241" s="6"/>
+    </row>
+    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F242" t="s">
         <v>125</v>
       </c>
-      <c r="J242" t="s">
+      <c r="K242" t="s">
         <v>131</v>
       </c>
-      <c r="K242" t="s">
+      <c r="L242" t="s">
         <v>162</v>
       </c>
-      <c r="L242" s="12">
+      <c r="M242" s="12">
         <f>8/1000*(14/(1*14+3*2))*100</f>
         <v>0.55999999999999994</v>
       </c>
-      <c r="M242" t="s">
+      <c r="N242" t="s">
         <v>132</v>
       </c>
-      <c r="N242" s="5" t="s">
+      <c r="O242" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="O242" t="s">
+      <c r="P242" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E243" t="s">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F243" t="s">
         <v>126</v>
       </c>
-      <c r="J243" t="s">
+      <c r="K243" t="s">
         <v>131</v>
       </c>
-      <c r="K243" t="s">
+      <c r="L243" t="s">
         <v>162</v>
       </c>
-      <c r="L243" s="12">
+      <c r="M243" s="12">
         <f>15/1000*(14/(1*14+3*2))*100</f>
         <v>1.0499999999999998</v>
       </c>
-      <c r="M243" t="s">
+      <c r="N243" t="s">
         <v>132</v>
       </c>
-      <c r="O243" t="s">
+      <c r="P243" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E244" t="s">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F244" t="s">
         <v>124</v>
       </c>
-      <c r="J244" t="s">
+      <c r="K244" t="s">
         <v>131</v>
       </c>
-      <c r="K244" t="s">
+      <c r="L244" t="s">
         <v>162</v>
       </c>
-      <c r="L244" s="12">
+      <c r="M244" s="12">
         <f>50/1000*(14/(1*14+3*2))*100</f>
         <v>3.4999999999999996</v>
       </c>
-      <c r="M244" t="s">
+      <c r="N244" t="s">
         <v>132</v>
       </c>
-      <c r="O244" t="s">
+      <c r="P244" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B245" s="7" t="s">
+      <c r="B245" s="1"/>
+      <c r="C245" s="7" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F246" t="s">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G246" t="s">
         <v>140</v>
       </c>
-      <c r="G246" t="s">
+      <c r="H246" t="s">
         <v>141</v>
       </c>
-      <c r="H246" t="s">
+      <c r="I246" t="s">
         <v>142</v>
       </c>
-      <c r="I246" t="s">
+      <c r="J246" t="s">
         <v>153</v>
       </c>
-      <c r="J246" t="s">
+      <c r="K246" t="s">
         <v>131</v>
       </c>
-      <c r="K246" t="s">
+      <c r="L246" t="s">
         <v>162</v>
       </c>
-      <c r="L246">
+      <c r="M246">
         <v>33</v>
       </c>
-      <c r="M246" t="s">
+      <c r="N246" t="s">
         <v>132</v>
       </c>
-      <c r="O246" t="s">
+      <c r="P246" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F247" t="s">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G247" t="s">
         <v>140</v>
       </c>
-      <c r="G247" t="s">
+      <c r="H247" t="s">
         <v>141</v>
       </c>
-      <c r="H247" t="s">
+      <c r="I247" t="s">
         <v>142</v>
       </c>
-      <c r="I247" t="s">
+      <c r="J247" t="s">
         <v>154</v>
       </c>
-      <c r="J247" t="s">
+      <c r="K247" t="s">
         <v>131</v>
       </c>
-      <c r="K247" t="s">
+      <c r="L247" t="s">
         <v>162</v>
       </c>
-      <c r="L247">
+      <c r="M247">
         <v>38</v>
       </c>
-      <c r="M247" t="s">
+      <c r="N247" t="s">
         <v>132</v>
       </c>
-      <c r="O247" t="s">
+      <c r="P247" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F248" t="s">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G248" t="s">
         <v>140</v>
       </c>
-      <c r="G248" t="s">
+      <c r="H248" t="s">
         <v>141</v>
       </c>
-      <c r="H248" t="s">
+      <c r="I248" t="s">
         <v>142</v>
       </c>
-      <c r="I248" t="s">
+      <c r="J248" t="s">
         <v>155</v>
       </c>
-      <c r="J248" t="s">
+      <c r="K248" t="s">
         <v>131</v>
       </c>
-      <c r="K248" t="s">
+      <c r="L248" t="s">
         <v>162</v>
       </c>
-      <c r="L248">
+      <c r="M248">
         <v>41</v>
       </c>
-      <c r="M248" t="s">
+      <c r="N248" t="s">
         <v>132</v>
       </c>
-      <c r="O248" t="s">
+      <c r="P248" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F249" t="s">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G249" t="s">
         <v>140</v>
       </c>
-      <c r="G249" t="s">
+      <c r="H249" t="s">
         <v>143</v>
       </c>
-      <c r="H249" t="s">
+      <c r="I249" t="s">
         <v>142</v>
       </c>
-      <c r="I249" t="s">
+      <c r="J249" t="s">
         <v>153</v>
       </c>
-      <c r="J249" t="s">
+      <c r="K249" t="s">
         <v>131</v>
       </c>
-      <c r="K249" t="s">
+      <c r="L249" t="s">
         <v>162</v>
       </c>
-      <c r="L249">
+      <c r="M249">
         <v>32</v>
       </c>
-      <c r="M249" t="s">
+      <c r="N249" t="s">
         <v>132</v>
       </c>
-      <c r="O249" t="s">
+      <c r="P249" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F250" t="s">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G250" t="s">
         <v>140</v>
       </c>
-      <c r="G250" t="s">
+      <c r="H250" t="s">
         <v>143</v>
       </c>
-      <c r="H250" t="s">
+      <c r="I250" t="s">
         <v>142</v>
       </c>
-      <c r="I250" t="s">
+      <c r="J250" t="s">
         <v>154</v>
       </c>
-      <c r="J250" t="s">
+      <c r="K250" t="s">
         <v>131</v>
       </c>
-      <c r="K250" t="s">
+      <c r="L250" t="s">
         <v>162</v>
       </c>
-      <c r="L250">
+      <c r="M250">
         <v>39</v>
       </c>
-      <c r="M250" t="s">
+      <c r="N250" t="s">
         <v>132</v>
       </c>
-      <c r="O250" t="s">
+      <c r="P250" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F251" t="s">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G251" t="s">
         <v>140</v>
       </c>
-      <c r="G251" t="s">
+      <c r="H251" t="s">
         <v>143</v>
       </c>
-      <c r="H251" t="s">
+      <c r="I251" t="s">
         <v>142</v>
       </c>
-      <c r="I251" t="s">
+      <c r="J251" t="s">
         <v>155</v>
       </c>
-      <c r="J251" t="s">
+      <c r="K251" t="s">
         <v>131</v>
       </c>
-      <c r="K251" t="s">
+      <c r="L251" t="s">
         <v>162</v>
       </c>
-      <c r="L251">
+      <c r="M251">
         <v>46</v>
       </c>
-      <c r="M251" t="s">
+      <c r="N251" t="s">
         <v>132</v>
       </c>
-      <c r="O251" t="s">
+      <c r="P251" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F252" t="s">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G252" t="s">
         <v>140</v>
       </c>
-      <c r="H252" t="s">
+      <c r="I252" t="s">
         <v>144</v>
       </c>
-      <c r="I252" t="s">
+      <c r="J252" t="s">
         <v>153</v>
       </c>
-      <c r="J252" t="s">
+      <c r="K252" t="s">
         <v>131</v>
       </c>
-      <c r="K252" t="s">
+      <c r="L252" t="s">
         <v>162</v>
       </c>
-      <c r="L252">
+      <c r="M252">
         <v>32</v>
       </c>
-      <c r="M252" t="s">
+      <c r="N252" t="s">
         <v>132</v>
       </c>
-      <c r="O252" t="s">
+      <c r="P252" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F253" t="s">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G253" t="s">
         <v>140</v>
       </c>
-      <c r="H253" t="s">
+      <c r="I253" t="s">
         <v>144</v>
       </c>
-      <c r="I253" t="s">
+      <c r="J253" t="s">
         <v>154</v>
       </c>
-      <c r="J253" t="s">
+      <c r="K253" t="s">
         <v>131</v>
       </c>
-      <c r="K253" t="s">
+      <c r="L253" t="s">
         <v>162</v>
       </c>
-      <c r="L253">
+      <c r="M253">
         <v>38</v>
       </c>
-      <c r="M253" t="s">
+      <c r="N253" t="s">
         <v>132</v>
       </c>
-      <c r="O253" t="s">
+      <c r="P253" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F254" t="s">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G254" t="s">
         <v>140</v>
       </c>
-      <c r="H254" t="s">
+      <c r="I254" t="s">
         <v>144</v>
       </c>
-      <c r="I254" t="s">
+      <c r="J254" t="s">
         <v>155</v>
       </c>
-      <c r="J254" t="s">
+      <c r="K254" t="s">
         <v>131</v>
       </c>
-      <c r="K254" t="s">
+      <c r="L254" t="s">
         <v>162</v>
       </c>
-      <c r="L254">
+      <c r="M254">
         <v>47</v>
       </c>
-      <c r="M254" t="s">
+      <c r="N254" t="s">
         <v>132</v>
       </c>
-      <c r="O254" t="s">
+      <c r="P254" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F255" t="s">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G255" t="s">
         <v>140</v>
       </c>
-      <c r="H255" t="s">
+      <c r="I255" t="s">
         <v>145</v>
       </c>
-      <c r="I255" t="s">
+      <c r="J255" t="s">
         <v>153</v>
       </c>
-      <c r="J255" t="s">
+      <c r="K255" t="s">
         <v>131</v>
       </c>
-      <c r="K255" t="s">
+      <c r="L255" t="s">
         <v>162</v>
       </c>
-      <c r="L255">
+      <c r="M255">
         <v>33</v>
       </c>
-      <c r="M255" t="s">
+      <c r="N255" t="s">
         <v>132</v>
       </c>
-      <c r="O255" t="s">
+      <c r="P255" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F256" t="s">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G256" t="s">
         <v>140</v>
       </c>
-      <c r="H256" t="s">
+      <c r="I256" t="s">
         <v>145</v>
       </c>
-      <c r="I256" t="s">
+      <c r="J256" t="s">
         <v>154</v>
       </c>
-      <c r="J256" t="s">
+      <c r="K256" t="s">
         <v>131</v>
       </c>
-      <c r="K256" t="s">
+      <c r="L256" t="s">
         <v>162</v>
       </c>
-      <c r="L256">
+      <c r="M256">
         <v>39</v>
       </c>
-      <c r="M256" t="s">
+      <c r="N256" t="s">
         <v>132</v>
       </c>
-      <c r="O256" t="s">
+      <c r="P256" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="257" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F257" t="s">
+    <row r="257" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G257" t="s">
         <v>140</v>
       </c>
-      <c r="H257" t="s">
+      <c r="I257" t="s">
         <v>145</v>
       </c>
-      <c r="I257" t="s">
+      <c r="J257" t="s">
         <v>155</v>
       </c>
-      <c r="J257" t="s">
+      <c r="K257" t="s">
         <v>131</v>
       </c>
-      <c r="K257" t="s">
+      <c r="L257" t="s">
         <v>162</v>
       </c>
-      <c r="L257">
+      <c r="M257">
         <v>47</v>
       </c>
-      <c r="M257" t="s">
+      <c r="N257" t="s">
         <v>132</v>
       </c>
-      <c r="O257" t="s">
+      <c r="P257" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="258" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F258" t="s">
+    <row r="258" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G258" t="s">
         <v>140</v>
       </c>
-      <c r="I258" t="s">
+      <c r="J258" t="s">
         <v>153</v>
       </c>
-      <c r="J258" t="s">
+      <c r="K258" t="s">
         <v>131</v>
       </c>
-      <c r="K258" t="s">
+      <c r="L258" t="s">
         <v>162</v>
       </c>
-      <c r="L258">
+      <c r="M258">
         <v>32</v>
       </c>
-      <c r="M258" t="s">
+      <c r="N258" t="s">
         <v>132</v>
       </c>
-      <c r="N258" t="s">
+      <c r="O258" t="s">
         <v>156</v>
       </c>
-      <c r="O258" t="s">
+      <c r="P258" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="259" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F259" t="s">
+    <row r="259" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G259" t="s">
         <v>140</v>
       </c>
-      <c r="I259" t="s">
+      <c r="J259" t="s">
         <v>154</v>
       </c>
-      <c r="J259" t="s">
+      <c r="K259" t="s">
         <v>131</v>
       </c>
-      <c r="K259" t="s">
+      <c r="L259" t="s">
         <v>162</v>
       </c>
-      <c r="L259">
+      <c r="M259">
         <v>39</v>
       </c>
-      <c r="M259" t="s">
+      <c r="N259" t="s">
         <v>132</v>
       </c>
-      <c r="N259" t="s">
+      <c r="O259" t="s">
         <v>156</v>
       </c>
-      <c r="O259" t="s">
+      <c r="P259" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="260" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F260" t="s">
+    <row r="260" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G260" t="s">
         <v>140</v>
       </c>
-      <c r="I260" t="s">
+      <c r="J260" t="s">
         <v>155</v>
       </c>
-      <c r="J260" t="s">
+      <c r="K260" t="s">
         <v>131</v>
       </c>
-      <c r="K260" t="s">
+      <c r="L260" t="s">
         <v>162</v>
       </c>
-      <c r="L260">
+      <c r="M260">
         <v>46</v>
       </c>
-      <c r="M260" t="s">
+      <c r="N260" t="s">
         <v>132</v>
       </c>
-      <c r="N260" t="s">
+      <c r="O260" t="s">
         <v>156</v>
       </c>
-      <c r="O260" t="s">
+      <c r="P260" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="261" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F261" t="s">
+    <row r="261" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G261" t="s">
         <v>140</v>
       </c>
-      <c r="I261" t="s">
+      <c r="J261" t="s">
         <v>171</v>
       </c>
-      <c r="J261" t="s">
+      <c r="K261" t="s">
         <v>131</v>
       </c>
-      <c r="K261" t="s">
+      <c r="L261" t="s">
         <v>162</v>
       </c>
-      <c r="L261">
+      <c r="M261">
         <v>14</v>
       </c>
-      <c r="M261" t="s">
+      <c r="N261" t="s">
         <v>132</v>
       </c>
-      <c r="O261" t="s">
+      <c r="P261" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="262" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F262" t="s">
+    <row r="262" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G262" t="s">
         <v>159</v>
       </c>
-      <c r="I262" t="s">
+      <c r="J262" t="s">
         <v>154</v>
       </c>
-      <c r="J262" t="s">
+      <c r="K262" t="s">
         <v>131</v>
       </c>
-      <c r="K262" t="s">
+      <c r="L262" t="s">
         <v>162</v>
       </c>
-      <c r="L262">
+      <c r="M262">
         <v>43</v>
       </c>
-      <c r="M262" t="s">
+      <c r="N262" t="s">
         <v>132</v>
       </c>
-      <c r="O262" t="s">
+      <c r="P262" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="263" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F263" t="s">
+    <row r="263" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G263" t="s">
         <v>159</v>
       </c>
-      <c r="I263" t="s">
+      <c r="J263" t="s">
         <v>155</v>
       </c>
-      <c r="J263" t="s">
+      <c r="K263" t="s">
         <v>131</v>
       </c>
-      <c r="K263" t="s">
+      <c r="L263" t="s">
         <v>162</v>
       </c>
-      <c r="L263">
+      <c r="M263">
         <v>47</v>
       </c>
-      <c r="M263" t="s">
+      <c r="N263" t="s">
         <v>132</v>
       </c>
-      <c r="O263" t="s">
+      <c r="P263" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="264" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F264" t="s">
+    <row r="264" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G264" t="s">
         <v>159</v>
       </c>
-      <c r="I264" t="s">
+      <c r="J264" t="s">
         <v>171</v>
       </c>
-      <c r="J264" t="s">
+      <c r="K264" t="s">
         <v>131</v>
       </c>
-      <c r="K264" t="s">
+      <c r="L264" t="s">
         <v>162</v>
       </c>
-      <c r="L264">
+      <c r="M264">
         <v>35</v>
       </c>
-      <c r="M264" t="s">
+      <c r="N264" t="s">
         <v>132</v>
       </c>
-      <c r="O264" t="s">
+      <c r="P264" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="265" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F265" t="s">
+    <row r="265" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G265" t="s">
         <v>146</v>
       </c>
-      <c r="H265" t="s">
+      <c r="I265" t="s">
         <v>147</v>
       </c>
-      <c r="I265" t="s">
+      <c r="J265" t="s">
         <v>153</v>
       </c>
-      <c r="J265" t="s">
+      <c r="K265" t="s">
         <v>131</v>
       </c>
-      <c r="K265" t="s">
+      <c r="L265" t="s">
         <v>162</v>
       </c>
-      <c r="L265">
+      <c r="M265">
         <v>30</v>
       </c>
-      <c r="M265" t="s">
+      <c r="N265" t="s">
         <v>132</v>
       </c>
-      <c r="O265" t="s">
+      <c r="P265" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="266" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F266" t="s">
+    <row r="266" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G266" t="s">
         <v>146</v>
       </c>
-      <c r="H266" t="s">
+      <c r="I266" t="s">
         <v>147</v>
       </c>
-      <c r="I266" t="s">
+      <c r="J266" t="s">
         <v>154</v>
       </c>
-      <c r="J266" t="s">
+      <c r="K266" t="s">
         <v>131</v>
       </c>
-      <c r="K266" t="s">
+      <c r="L266" t="s">
         <v>162</v>
       </c>
-      <c r="L266">
+      <c r="M266">
         <v>35</v>
       </c>
-      <c r="M266" t="s">
+      <c r="N266" t="s">
         <v>132</v>
       </c>
-      <c r="O266" t="s">
+      <c r="P266" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="267" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F267" t="s">
+    <row r="267" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G267" t="s">
         <v>146</v>
       </c>
-      <c r="H267" t="s">
+      <c r="I267" t="s">
         <v>147</v>
       </c>
-      <c r="I267" t="s">
+      <c r="J267" t="s">
         <v>155</v>
       </c>
-      <c r="J267" t="s">
+      <c r="K267" t="s">
         <v>131</v>
       </c>
-      <c r="K267" t="s">
+      <c r="L267" t="s">
         <v>162</v>
       </c>
-      <c r="L267">
+      <c r="M267">
         <v>48</v>
       </c>
-      <c r="M267" t="s">
+      <c r="N267" t="s">
         <v>132</v>
       </c>
-      <c r="O267" t="s">
+      <c r="P267" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="268" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F268" t="s">
+    <row r="268" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G268" t="s">
         <v>146</v>
       </c>
-      <c r="H268" t="s">
+      <c r="I268" t="s">
         <v>148</v>
       </c>
-      <c r="I268" t="s">
+      <c r="J268" t="s">
         <v>153</v>
       </c>
-      <c r="J268" t="s">
+      <c r="K268" t="s">
         <v>131</v>
       </c>
-      <c r="K268" t="s">
+      <c r="L268" t="s">
         <v>162</v>
       </c>
-      <c r="L268">
+      <c r="M268">
         <v>29</v>
       </c>
-      <c r="M268" t="s">
+      <c r="N268" t="s">
         <v>132</v>
       </c>
-      <c r="O268" t="s">
+      <c r="P268" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="269" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F269" t="s">
+    <row r="269" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G269" t="s">
         <v>146</v>
       </c>
-      <c r="H269" t="s">
+      <c r="I269" t="s">
         <v>148</v>
       </c>
-      <c r="I269" t="s">
+      <c r="J269" t="s">
         <v>154</v>
       </c>
-      <c r="J269" t="s">
+      <c r="K269" t="s">
         <v>131</v>
       </c>
-      <c r="K269" t="s">
+      <c r="L269" t="s">
         <v>162</v>
       </c>
-      <c r="L269">
+      <c r="M269">
         <v>34</v>
       </c>
-      <c r="M269" t="s">
+      <c r="N269" t="s">
         <v>132</v>
       </c>
-      <c r="O269" t="s">
+      <c r="P269" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="270" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F270" t="s">
+    <row r="270" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G270" t="s">
         <v>146</v>
       </c>
-      <c r="H270" t="s">
+      <c r="I270" t="s">
         <v>148</v>
       </c>
-      <c r="I270" t="s">
+      <c r="J270" t="s">
         <v>155</v>
       </c>
-      <c r="J270" t="s">
+      <c r="K270" t="s">
         <v>131</v>
       </c>
-      <c r="K270" t="s">
+      <c r="L270" t="s">
         <v>162</v>
       </c>
-      <c r="L270">
+      <c r="M270">
         <v>46</v>
       </c>
-      <c r="M270" t="s">
+      <c r="N270" t="s">
         <v>132</v>
       </c>
-      <c r="O270" t="s">
+      <c r="P270" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="271" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F271" t="s">
+    <row r="271" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G271" t="s">
         <v>146</v>
       </c>
-      <c r="H271" t="s">
+      <c r="I271" t="s">
         <v>149</v>
       </c>
-      <c r="I271" t="s">
+      <c r="J271" t="s">
         <v>153</v>
       </c>
-      <c r="J271" t="s">
+      <c r="K271" t="s">
         <v>131</v>
       </c>
-      <c r="K271" t="s">
+      <c r="L271" t="s">
         <v>162</v>
       </c>
-      <c r="L271">
+      <c r="M271">
         <v>29</v>
       </c>
-      <c r="M271" t="s">
+      <c r="N271" t="s">
         <v>132</v>
       </c>
-      <c r="O271" t="s">
+      <c r="P271" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="272" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F272" t="s">
+    <row r="272" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G272" t="s">
         <v>146</v>
       </c>
-      <c r="H272" t="s">
+      <c r="I272" t="s">
         <v>149</v>
       </c>
-      <c r="I272" t="s">
+      <c r="J272" t="s">
         <v>154</v>
       </c>
-      <c r="J272" t="s">
+      <c r="K272" t="s">
         <v>131</v>
       </c>
-      <c r="K272" t="s">
+      <c r="L272" t="s">
         <v>162</v>
       </c>
-      <c r="L272">
+      <c r="M272">
         <v>35</v>
       </c>
-      <c r="M272" t="s">
+      <c r="N272" t="s">
         <v>132</v>
       </c>
-      <c r="O272" t="s">
+      <c r="P272" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F273" t="s">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G273" t="s">
         <v>146</v>
       </c>
-      <c r="H273" t="s">
+      <c r="I273" t="s">
         <v>149</v>
       </c>
-      <c r="I273" t="s">
+      <c r="J273" t="s">
         <v>155</v>
       </c>
-      <c r="J273" t="s">
+      <c r="K273" t="s">
         <v>131</v>
       </c>
-      <c r="K273" t="s">
+      <c r="L273" t="s">
         <v>162</v>
       </c>
-      <c r="L273">
+      <c r="M273">
         <v>48</v>
       </c>
-      <c r="M273" t="s">
+      <c r="N273" t="s">
         <v>132</v>
       </c>
-      <c r="O273" t="s">
+      <c r="P273" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F274" t="s">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G274" t="s">
         <v>146</v>
       </c>
-      <c r="H274" t="s">
+      <c r="I274" t="s">
         <v>150</v>
       </c>
-      <c r="I274" t="s">
+      <c r="J274" t="s">
         <v>153</v>
       </c>
-      <c r="J274" t="s">
+      <c r="K274" t="s">
         <v>131</v>
       </c>
-      <c r="K274" t="s">
+      <c r="L274" t="s">
         <v>162</v>
       </c>
-      <c r="L274" s="13">
-        <f>L265</f>
+      <c r="M274" s="13">
+        <f>M265</f>
         <v>30</v>
       </c>
-      <c r="M274" t="s">
+      <c r="N274" t="s">
         <v>132</v>
       </c>
-      <c r="N274" t="s">
+      <c r="O274" t="s">
         <v>158</v>
       </c>
-      <c r="O274" t="s">
+      <c r="P274" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F275" t="s">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G275" t="s">
         <v>146</v>
       </c>
-      <c r="H275" t="s">
+      <c r="I275" t="s">
         <v>150</v>
       </c>
-      <c r="I275" t="s">
+      <c r="J275" t="s">
         <v>154</v>
       </c>
-      <c r="J275" t="s">
+      <c r="K275" t="s">
         <v>131</v>
       </c>
-      <c r="K275" t="s">
+      <c r="L275" t="s">
         <v>162</v>
       </c>
-      <c r="L275" s="13">
-        <f t="shared" ref="L275:L276" si="4">L266</f>
+      <c r="M275" s="13">
+        <f t="shared" ref="M275:M276" si="4">M266</f>
         <v>35</v>
       </c>
-      <c r="M275" t="s">
+      <c r="N275" t="s">
         <v>132</v>
       </c>
-      <c r="N275" t="s">
+      <c r="O275" t="s">
         <v>158</v>
       </c>
-      <c r="O275" t="s">
+      <c r="P275" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F276" t="s">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G276" t="s">
         <v>146</v>
       </c>
-      <c r="H276" t="s">
+      <c r="I276" t="s">
         <v>150</v>
       </c>
-      <c r="I276" t="s">
+      <c r="J276" t="s">
         <v>155</v>
       </c>
-      <c r="J276" t="s">
+      <c r="K276" t="s">
         <v>131</v>
       </c>
-      <c r="K276" t="s">
+      <c r="L276" t="s">
         <v>162</v>
       </c>
-      <c r="L276" s="13">
+      <c r="M276" s="13">
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="M276" t="s">
+      <c r="N276" t="s">
         <v>132</v>
       </c>
-      <c r="N276" t="s">
+      <c r="O276" t="s">
         <v>158</v>
       </c>
-      <c r="O276" t="s">
+      <c r="P276" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F277" t="s">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G277" t="s">
         <v>146</v>
       </c>
-      <c r="I277" t="s">
+      <c r="J277" t="s">
         <v>153</v>
       </c>
-      <c r="J277" t="s">
+      <c r="K277" t="s">
         <v>131</v>
       </c>
-      <c r="K277" t="s">
+      <c r="L277" t="s">
         <v>162</v>
       </c>
-      <c r="L277">
+      <c r="M277">
         <v>29</v>
       </c>
-      <c r="M277" t="s">
+      <c r="N277" t="s">
         <v>132</v>
       </c>
-      <c r="N277" t="s">
+      <c r="O277" t="s">
         <v>157</v>
       </c>
-      <c r="O277" t="s">
+      <c r="P277" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F278" t="s">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G278" t="s">
         <v>146</v>
       </c>
-      <c r="I278" t="s">
+      <c r="J278" t="s">
         <v>154</v>
       </c>
-      <c r="J278" t="s">
+      <c r="K278" t="s">
         <v>131</v>
       </c>
-      <c r="K278" t="s">
+      <c r="L278" t="s">
         <v>162</v>
       </c>
-      <c r="L278">
+      <c r="M278">
         <v>35</v>
       </c>
-      <c r="M278" t="s">
+      <c r="N278" t="s">
         <v>132</v>
       </c>
-      <c r="N278" t="s">
+      <c r="O278" t="s">
         <v>157</v>
       </c>
-      <c r="O278" t="s">
+      <c r="P278" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F279" t="s">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G279" t="s">
         <v>146</v>
       </c>
-      <c r="I279" t="s">
+      <c r="J279" t="s">
         <v>155</v>
       </c>
-      <c r="J279" t="s">
+      <c r="K279" t="s">
         <v>131</v>
       </c>
-      <c r="K279" t="s">
+      <c r="L279" t="s">
         <v>162</v>
       </c>
-      <c r="L279">
+      <c r="M279">
         <v>44</v>
       </c>
-      <c r="M279" t="s">
+      <c r="N279" t="s">
         <v>132</v>
       </c>
-      <c r="N279" t="s">
+      <c r="O279" t="s">
         <v>157</v>
       </c>
-      <c r="O279" t="s">
+      <c r="P279" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F280" t="s">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G280" t="s">
         <v>151</v>
       </c>
-      <c r="G280" t="s">
+      <c r="H280" t="s">
         <v>152</v>
       </c>
-      <c r="I280" t="s">
+      <c r="J280" t="s">
         <v>154</v>
       </c>
-      <c r="J280" t="s">
+      <c r="K280" t="s">
         <v>131</v>
       </c>
-      <c r="K280" t="s">
+      <c r="L280" t="s">
         <v>162</v>
       </c>
-      <c r="L280">
+      <c r="M280">
         <v>41</v>
       </c>
-      <c r="M280" t="s">
+      <c r="N280" t="s">
         <v>132</v>
       </c>
-      <c r="O280" t="s">
+      <c r="P280" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F281" t="s">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G281" t="s">
         <v>151</v>
       </c>
-      <c r="G281" t="s">
+      <c r="H281" t="s">
         <v>152</v>
       </c>
-      <c r="I281" t="s">
+      <c r="J281" t="s">
         <v>155</v>
       </c>
-      <c r="J281" t="s">
+      <c r="K281" t="s">
         <v>131</v>
       </c>
-      <c r="K281" t="s">
+      <c r="L281" t="s">
         <v>162</v>
       </c>
-      <c r="L281">
+      <c r="M281">
         <v>41</v>
       </c>
-      <c r="M281" t="s">
+      <c r="N281" t="s">
         <v>132</v>
       </c>
-      <c r="O281" t="s">
+      <c r="P281" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B283" s="7"/>
+    </row>
+    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>181</v>
       </c>
@@ -5838,148 +5983,229 @@
       <c r="M285" s="2"/>
       <c r="N285" s="2"/>
       <c r="O285" s="2"/>
-    </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J287" t="s">
+      <c r="P285" s="2"/>
+    </row>
+    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K287" t="s">
         <v>170</v>
       </c>
-      <c r="K287" t="s">
+      <c r="L287" t="s">
         <v>182</v>
       </c>
-      <c r="L287">
+      <c r="M287">
         <v>1</v>
       </c>
-      <c r="M287" t="s">
+      <c r="N287" t="s">
         <v>127</v>
       </c>
-      <c r="N287" t="s">
+      <c r="O287" t="s">
         <v>177</v>
       </c>
-      <c r="O287" t="s">
+      <c r="P287" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J288" t="s">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K288" t="s">
         <v>170</v>
       </c>
-      <c r="K288" t="s">
+      <c r="L288" t="s">
         <v>184</v>
       </c>
-      <c r="L288">
+      <c r="M288">
         <v>1</v>
       </c>
-      <c r="M288" t="s">
+      <c r="N288" t="s">
         <v>127</v>
       </c>
-      <c r="N288" t="s">
+      <c r="O288" t="s">
         <v>179</v>
       </c>
-      <c r="O288" t="s">
+      <c r="P288" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="289" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F289" t="s">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G289" t="s">
         <v>140</v>
       </c>
-      <c r="I289" t="s">
+      <c r="J289" t="s">
         <v>171</v>
       </c>
-      <c r="J289" t="s">
+      <c r="K289" t="s">
         <v>170</v>
       </c>
-      <c r="K289" t="s">
+      <c r="L289" t="s">
         <v>184</v>
       </c>
-      <c r="L289">
+      <c r="M289">
         <v>2</v>
       </c>
-      <c r="M289" t="s">
+      <c r="N289" t="s">
         <v>127</v>
       </c>
-      <c r="N289" t="s">
+      <c r="O289" t="s">
         <v>174</v>
       </c>
-      <c r="O289" t="s">
+      <c r="P289" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="290" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="I290" t="s">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J290" t="s">
         <v>171</v>
       </c>
-      <c r="J290" t="s">
+      <c r="K290" t="s">
         <v>170</v>
       </c>
-      <c r="K290" t="s">
+      <c r="L290" t="s">
         <v>184</v>
       </c>
-      <c r="L290">
+      <c r="M290">
         <v>1</v>
       </c>
-      <c r="M290" t="s">
+      <c r="N290" t="s">
         <v>127</v>
       </c>
-      <c r="N290" t="s">
+      <c r="O290" t="s">
         <v>175</v>
       </c>
-      <c r="O290" t="s">
+      <c r="P290" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="291" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="J291" t="s">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K291" t="s">
         <v>170</v>
       </c>
-      <c r="K291" t="s">
+      <c r="L291" t="s">
         <v>183</v>
       </c>
-      <c r="L291">
+      <c r="M291">
         <v>1</v>
       </c>
-      <c r="M291" t="s">
+      <c r="N291" t="s">
         <v>127</v>
       </c>
-      <c r="N291" t="s">
+      <c r="O291" t="s">
         <v>186</v>
       </c>
-      <c r="O291" t="s">
+      <c r="P291" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="292" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="J292" t="s">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K292" t="s">
         <v>170</v>
       </c>
-      <c r="K292" t="s">
+      <c r="L292" t="s">
         <v>185</v>
       </c>
-      <c r="L292">
+      <c r="M292">
         <v>1</v>
       </c>
-      <c r="M292" t="s">
+      <c r="N292" t="s">
         <v>127</v>
       </c>
-      <c r="N292" t="s">
+      <c r="O292" t="s">
         <v>176</v>
       </c>
-      <c r="O292" t="s">
+      <c r="P292" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="294" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="J294" t="s">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K294" t="s">
         <v>170</v>
       </c>
-      <c r="K294" t="s">
+      <c r="L294" t="s">
         <v>189</v>
       </c>
-      <c r="L294">
+      <c r="M294">
         <v>13</v>
       </c>
-      <c r="M294" t="s">
+      <c r="N294" t="s">
         <v>190</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B296" s="2"/>
+      <c r="C296" s="2"/>
+      <c r="D296" s="2"/>
+      <c r="E296" s="2"/>
+      <c r="F296" s="2"/>
+      <c r="G296" s="2"/>
+      <c r="H296" s="2"/>
+      <c r="I296" s="2"/>
+      <c r="J296" s="2"/>
+      <c r="K296" s="2"/>
+      <c r="L296" s="2"/>
+      <c r="M296" s="2"/>
+      <c r="N296" s="2"/>
+      <c r="O296" s="2"/>
+      <c r="P296" s="2"/>
+    </row>
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B298" t="s">
+        <v>199</v>
+      </c>
+      <c r="K298" t="s">
+        <v>197</v>
+      </c>
+      <c r="L298" t="s">
+        <v>194</v>
+      </c>
+      <c r="M298">
+        <v>0.24</v>
+      </c>
+      <c r="N298" t="s">
+        <v>196</v>
+      </c>
+      <c r="P298" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B299" t="s">
+        <v>200</v>
+      </c>
+      <c r="K299" t="s">
+        <v>197</v>
+      </c>
+      <c r="L299" t="s">
+        <v>194</v>
+      </c>
+      <c r="M299">
+        <v>0.24</v>
+      </c>
+      <c r="N299" t="s">
+        <v>196</v>
+      </c>
+      <c r="P299" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B300" t="s">
+        <v>201</v>
+      </c>
+      <c r="K300" t="s">
+        <v>197</v>
+      </c>
+      <c r="L300" t="s">
+        <v>194</v>
+      </c>
+      <c r="M300">
+        <v>0</v>
+      </c>
+      <c r="N300" t="s">
+        <v>196</v>
+      </c>
+      <c r="O300" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -622,9 +622,6 @@
     <t>f_po8:region</t>
   </si>
   <si>
-    <t>2015/16</t>
-  </si>
-  <si>
     <t>Leaching</t>
   </si>
   <si>
@@ -653,6 +650,9 @@
   </si>
   <si>
     <t>No leaching from greenhouses?</t>
+  </si>
+  <si>
+    <t>Avg. from statistics 2018/2019 &amp; 2021/2022</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>191</v>
@@ -2973,11 +2973,12 @@
       <c r="L124" t="s">
         <v>12</v>
       </c>
-      <c r="M124">
+      <c r="M124" s="7">
         <v>11</v>
       </c>
-      <c r="O124" t="s">
-        <v>192</v>
+      <c r="N124" s="7"/>
+      <c r="O124" s="7" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
@@ -6130,7 +6131,7 @@
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -6150,62 +6151,62 @@
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K298" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L298" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M298">
         <v>0.24</v>
       </c>
       <c r="N298" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P298" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K299" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L299" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M299">
         <v>0.24</v>
       </c>
       <c r="N299" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P299" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K300" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L300" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M300">
         <v>0</v>
       </c>
       <c r="N300" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O300" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="206">
   <si>
     <t>f_crop</t>
   </si>
@@ -502,9 +502,6 @@
     <t>poultry</t>
   </si>
   <si>
-    <t>broiler</t>
-  </si>
-  <si>
     <t>liquid</t>
   </si>
   <si>
@@ -580,9 +577,6 @@
     <t>mineral N fertiliser</t>
   </si>
   <si>
-    <t>NH3 from manure on pasture!!</t>
-  </si>
-  <si>
     <t>applied manure</t>
   </si>
   <si>
@@ -653,6 +647,21 @@
   </si>
   <si>
     <t>Avg. from statistics 2018/2019 &amp; 2021/2022</t>
+  </si>
+  <si>
+    <t>anaerobic digestion</t>
+  </si>
+  <si>
+    <t>composting</t>
+  </si>
+  <si>
+    <t>sheep</t>
+  </si>
+  <si>
+    <t>laying chicks</t>
+  </si>
+  <si>
+    <t>broilers</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S300"/>
+  <dimension ref="A1:S317"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="21" customWidth="1"/>
@@ -1074,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>90</v>
@@ -1086,7 +1095,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>136</v>
@@ -1178,7 +1187,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1201,7 +1210,7 @@
         <v>113</v>
       </c>
       <c r="L8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -1210,18 +1219,18 @@
         <v>127</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F9" t="s">
         <v>125</v>
       </c>
       <c r="L9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M9">
         <v>59</v>
@@ -1238,13 +1247,13 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F10" t="s">
         <v>126</v>
       </c>
       <c r="L10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -1258,13 +1267,13 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F11" t="s">
         <v>124</v>
       </c>
       <c r="L11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M11">
         <v>34</v>
@@ -2978,7 +2987,7 @@
       </c>
       <c r="N124" s="7"/>
       <c r="O124" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
@@ -4885,7 +4894,7 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -4908,7 +4917,7 @@
         <v>131</v>
       </c>
       <c r="L240" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M240" s="14">
         <v>0</v>
@@ -4917,12 +4926,12 @@
         <v>132</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B241" s="1"/>
       <c r="K241" s="6"/>
@@ -4939,7 +4948,7 @@
         <v>131</v>
       </c>
       <c r="L242" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M242" s="12">
         <f>8/1000*(14/(1*14+3*2))*100</f>
@@ -4963,7 +4972,7 @@
         <v>131</v>
       </c>
       <c r="L243" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M243" s="12">
         <f>15/1000*(14/(1*14+3*2))*100</f>
@@ -4984,7 +4993,7 @@
         <v>131</v>
       </c>
       <c r="L244" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M244" s="12">
         <f>50/1000*(14/(1*14+3*2))*100</f>
@@ -4999,11 +5008,11 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B245" s="1"/>
       <c r="C245" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.25">
@@ -5017,13 +5026,13 @@
         <v>142</v>
       </c>
       <c r="J246" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K246" t="s">
         <v>131</v>
       </c>
       <c r="L246" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M246">
         <v>33</v>
@@ -5032,7 +5041,7 @@
         <v>132</v>
       </c>
       <c r="P246" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.25">
@@ -5046,13 +5055,13 @@
         <v>142</v>
       </c>
       <c r="J247" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K247" t="s">
         <v>131</v>
       </c>
       <c r="L247" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M247">
         <v>38</v>
@@ -5061,7 +5070,7 @@
         <v>132</v>
       </c>
       <c r="P247" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.25">
@@ -5075,13 +5084,13 @@
         <v>142</v>
       </c>
       <c r="J248" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K248" t="s">
         <v>131</v>
       </c>
       <c r="L248" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M248">
         <v>41</v>
@@ -5090,7 +5099,7 @@
         <v>132</v>
       </c>
       <c r="P248" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
@@ -5098,28 +5107,28 @@
         <v>140</v>
       </c>
       <c r="H249" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I249" t="s">
         <v>142</v>
       </c>
       <c r="J249" t="s">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="K249" t="s">
         <v>131</v>
       </c>
       <c r="L249" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M249">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N249" t="s">
         <v>132</v>
       </c>
       <c r="P249" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.25">
@@ -5133,22 +5142,22 @@
         <v>142</v>
       </c>
       <c r="J250" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K250" t="s">
         <v>131</v>
       </c>
       <c r="L250" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M250">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="N250" t="s">
         <v>132</v>
       </c>
       <c r="P250" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.25">
@@ -5162,74 +5171,80 @@
         <v>142</v>
       </c>
       <c r="J251" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K251" t="s">
         <v>131</v>
       </c>
       <c r="L251" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M251">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N251" t="s">
         <v>132</v>
       </c>
       <c r="P251" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G252" t="s">
         <v>140</v>
       </c>
+      <c r="H252" t="s">
+        <v>143</v>
+      </c>
       <c r="I252" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J252" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K252" t="s">
         <v>131</v>
       </c>
       <c r="L252" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M252">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="N252" t="s">
         <v>132</v>
       </c>
       <c r="P252" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G253" t="s">
         <v>140</v>
       </c>
+      <c r="H253" t="s">
+        <v>143</v>
+      </c>
       <c r="I253" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J253" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="K253" t="s">
         <v>131</v>
       </c>
       <c r="L253" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M253">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N253" t="s">
         <v>132</v>
       </c>
       <c r="P253" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.25">
@@ -5240,22 +5255,22 @@
         <v>144</v>
       </c>
       <c r="J254" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K254" t="s">
         <v>131</v>
       </c>
       <c r="L254" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M254">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="N254" t="s">
         <v>132</v>
       </c>
       <c r="P254" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.25">
@@ -5263,7 +5278,7 @@
         <v>140</v>
       </c>
       <c r="I255" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J255" t="s">
         <v>153</v>
@@ -5272,16 +5287,16 @@
         <v>131</v>
       </c>
       <c r="L255" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M255">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N255" t="s">
         <v>132</v>
       </c>
       <c r="P255" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
@@ -5289,7 +5304,7 @@
         <v>140</v>
       </c>
       <c r="I256" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J256" t="s">
         <v>154</v>
@@ -5298,16 +5313,16 @@
         <v>131</v>
       </c>
       <c r="L256" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M256">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N256" t="s">
         <v>132</v>
       </c>
       <c r="P256" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="257" spans="7:16" x14ac:dyDescent="0.25">
@@ -5315,65 +5330,68 @@
         <v>140</v>
       </c>
       <c r="I257" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J257" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="K257" t="s">
         <v>131</v>
       </c>
       <c r="L257" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M257">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="N257" t="s">
         <v>132</v>
       </c>
       <c r="P257" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="258" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G258" t="s">
         <v>140</v>
       </c>
+      <c r="I258" t="s">
+        <v>145</v>
+      </c>
       <c r="J258" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K258" t="s">
         <v>131</v>
       </c>
       <c r="L258" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M258">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N258" t="s">
         <v>132</v>
       </c>
-      <c r="O258" t="s">
-        <v>156</v>
-      </c>
       <c r="P258" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="259" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G259" t="s">
         <v>140</v>
       </c>
+      <c r="I259" t="s">
+        <v>145</v>
+      </c>
       <c r="J259" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K259" t="s">
         <v>131</v>
       </c>
       <c r="L259" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M259">
         <v>39</v>
@@ -5381,293 +5399,284 @@
       <c r="N259" t="s">
         <v>132</v>
       </c>
-      <c r="O259" t="s">
-        <v>156</v>
-      </c>
       <c r="P259" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="260" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G260" t="s">
         <v>140</v>
       </c>
+      <c r="I260" t="s">
+        <v>145</v>
+      </c>
       <c r="J260" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K260" t="s">
         <v>131</v>
       </c>
       <c r="L260" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M260">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N260" t="s">
         <v>132</v>
       </c>
-      <c r="O260" t="s">
-        <v>156</v>
-      </c>
       <c r="P260" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="261" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G261" t="s">
         <v>140</v>
       </c>
+      <c r="I261" t="s">
+        <v>145</v>
+      </c>
       <c r="J261" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="K261" t="s">
         <v>131</v>
       </c>
       <c r="L261" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M261">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="N261" t="s">
         <v>132</v>
       </c>
       <c r="P261" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
     </row>
     <row r="262" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G262" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="J262" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K262" t="s">
         <v>131</v>
       </c>
       <c r="L262" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M262">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="N262" t="s">
         <v>132</v>
       </c>
+      <c r="O262" t="s">
+        <v>155</v>
+      </c>
       <c r="P262" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="263" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G263" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="J263" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K263" t="s">
         <v>131</v>
       </c>
       <c r="L263" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M263">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N263" t="s">
         <v>132</v>
       </c>
+      <c r="O263" t="s">
+        <v>155</v>
+      </c>
       <c r="P263" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="264" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G264" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="J264" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="K264" t="s">
         <v>131</v>
       </c>
       <c r="L264" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M264">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N264" t="s">
         <v>132</v>
       </c>
+      <c r="O264" t="s">
+        <v>155</v>
+      </c>
       <c r="P264" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
     </row>
     <row r="265" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G265" t="s">
-        <v>146</v>
-      </c>
-      <c r="I265" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="J265" t="s">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="K265" t="s">
         <v>131</v>
       </c>
       <c r="L265" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M265">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N265" t="s">
         <v>132</v>
       </c>
+      <c r="O265" t="s">
+        <v>155</v>
+      </c>
       <c r="P265" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="266" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G266" t="s">
-        <v>146</v>
-      </c>
-      <c r="I266" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="J266" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="K266" t="s">
         <v>131</v>
       </c>
       <c r="L266" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M266">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="N266" t="s">
         <v>132</v>
       </c>
       <c r="P266" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
     </row>
     <row r="267" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G267" t="s">
-        <v>146</v>
-      </c>
-      <c r="I267" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J267" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K267" t="s">
         <v>131</v>
       </c>
       <c r="L267" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M267">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N267" t="s">
         <v>132</v>
       </c>
       <c r="P267" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="268" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G268" t="s">
-        <v>146</v>
-      </c>
-      <c r="I268" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="J268" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K268" t="s">
         <v>131</v>
       </c>
       <c r="L268" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M268">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="N268" t="s">
         <v>132</v>
       </c>
       <c r="P268" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="269" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G269" t="s">
-        <v>146</v>
-      </c>
-      <c r="I269" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="J269" t="s">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="K269" t="s">
         <v>131</v>
       </c>
       <c r="L269" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M269">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="N269" t="s">
         <v>132</v>
       </c>
       <c r="P269" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="270" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G270" t="s">
-        <v>146</v>
-      </c>
-      <c r="I270" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="J270" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K270" t="s">
         <v>131</v>
       </c>
       <c r="L270" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M270">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="N270" t="s">
         <v>132</v>
       </c>
       <c r="P270" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
     </row>
     <row r="271" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G271" t="s">
-        <v>146</v>
-      </c>
-      <c r="I271" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="J271" t="s">
         <v>153</v>
@@ -5676,76 +5685,73 @@
         <v>131</v>
       </c>
       <c r="L271" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M271">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="N271" t="s">
         <v>132</v>
       </c>
       <c r="P271" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="272" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G272" t="s">
-        <v>146</v>
-      </c>
-      <c r="I272" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="J272" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="K272" t="s">
         <v>131</v>
       </c>
       <c r="L272" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M272">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="N272" t="s">
         <v>132</v>
       </c>
       <c r="P272" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="273" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G273" t="s">
         <v>146</v>
       </c>
       <c r="I273" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J273" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K273" t="s">
         <v>131</v>
       </c>
       <c r="L273" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M273">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="N273" t="s">
         <v>132</v>
       </c>
       <c r="P273" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="274" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G274" t="s">
         <v>146</v>
       </c>
       <c r="I274" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J274" t="s">
         <v>153</v>
@@ -5754,28 +5760,24 @@
         <v>131</v>
       </c>
       <c r="L274" t="s">
-        <v>162</v>
-      </c>
-      <c r="M274" s="13">
-        <f>M265</f>
-        <v>30</v>
+        <v>161</v>
+      </c>
+      <c r="M274">
+        <v>35</v>
       </c>
       <c r="N274" t="s">
         <v>132</v>
       </c>
-      <c r="O274" t="s">
-        <v>158</v>
-      </c>
       <c r="P274" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="275" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G275" t="s">
         <v>146</v>
       </c>
       <c r="I275" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J275" t="s">
         <v>154</v>
@@ -5784,67 +5786,63 @@
         <v>131</v>
       </c>
       <c r="L275" t="s">
-        <v>162</v>
-      </c>
-      <c r="M275" s="13">
-        <f t="shared" ref="M275:M276" si="4">M266</f>
-        <v>35</v>
+        <v>161</v>
+      </c>
+      <c r="M275">
+        <v>48</v>
       </c>
       <c r="N275" t="s">
         <v>132</v>
       </c>
-      <c r="O275" t="s">
-        <v>158</v>
-      </c>
       <c r="P275" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="276" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G276" t="s">
         <v>146</v>
       </c>
       <c r="I276" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J276" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="K276" t="s">
         <v>131</v>
       </c>
       <c r="L276" t="s">
-        <v>162</v>
-      </c>
-      <c r="M276" s="13">
-        <f t="shared" si="4"/>
-        <v>48</v>
+        <v>161</v>
+      </c>
+      <c r="M276">
+        <v>30</v>
       </c>
       <c r="N276" t="s">
         <v>132</v>
       </c>
-      <c r="O276" t="s">
-        <v>158</v>
-      </c>
       <c r="P276" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="277" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G277" t="s">
         <v>146</v>
       </c>
+      <c r="I277" t="s">
+        <v>150</v>
+      </c>
       <c r="J277" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K277" t="s">
         <v>131</v>
       </c>
       <c r="L277" t="s">
-        <v>162</v>
-      </c>
-      <c r="M277">
-        <v>29</v>
+        <v>161</v>
+      </c>
+      <c r="M277" s="13">
+        <f>M273</f>
+        <v>30</v>
       </c>
       <c r="N277" t="s">
         <v>132</v>
@@ -5852,24 +5850,25 @@
       <c r="O277" t="s">
         <v>157</v>
       </c>
-      <c r="P277" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G278" t="s">
         <v>146</v>
       </c>
+      <c r="I278" t="s">
+        <v>150</v>
+      </c>
       <c r="J278" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K278" t="s">
         <v>131</v>
       </c>
       <c r="L278" t="s">
-        <v>162</v>
-      </c>
-      <c r="M278">
+        <v>161</v>
+      </c>
+      <c r="M278" s="13">
+        <f>M274</f>
         <v>35</v>
       </c>
       <c r="N278" t="s">
@@ -5878,25 +5877,26 @@
       <c r="O278" t="s">
         <v>157</v>
       </c>
-      <c r="P278" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G279" t="s">
         <v>146</v>
       </c>
+      <c r="I279" t="s">
+        <v>150</v>
+      </c>
       <c r="J279" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K279" t="s">
         <v>131</v>
       </c>
       <c r="L279" t="s">
-        <v>162</v>
-      </c>
-      <c r="M279">
-        <v>44</v>
+        <v>161</v>
+      </c>
+      <c r="M279" s="13">
+        <f>M275</f>
+        <v>48</v>
       </c>
       <c r="N279" t="s">
         <v>132</v>
@@ -5904,309 +5904,786 @@
       <c r="O279" t="s">
         <v>157</v>
       </c>
-      <c r="P279" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G280" t="s">
-        <v>151</v>
-      </c>
-      <c r="H280" t="s">
-        <v>152</v>
+        <v>146</v>
+      </c>
+      <c r="I280" t="s">
+        <v>150</v>
       </c>
       <c r="J280" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="K280" t="s">
         <v>131</v>
       </c>
       <c r="L280" t="s">
-        <v>162</v>
-      </c>
-      <c r="M280">
-        <v>41</v>
+        <v>161</v>
+      </c>
+      <c r="M280" s="13">
+        <f>M276</f>
+        <v>30</v>
       </c>
       <c r="N280" t="s">
         <v>132</v>
       </c>
-      <c r="P280" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O280" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="281" spans="7:16" x14ac:dyDescent="0.25">
       <c r="G281" t="s">
-        <v>151</v>
-      </c>
-      <c r="H281" t="s">
+        <v>146</v>
+      </c>
+      <c r="I281" t="s">
+        <v>148</v>
+      </c>
+      <c r="J281" t="s">
         <v>152</v>
-      </c>
-      <c r="J281" t="s">
-        <v>155</v>
       </c>
       <c r="K281" t="s">
         <v>131</v>
       </c>
       <c r="L281" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M281">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="N281" t="s">
         <v>132</v>
       </c>
       <c r="P281" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A283" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B283" s="7"/>
-    </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A285" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B285" s="2"/>
-      <c r="C285" s="2"/>
-      <c r="D285" s="2"/>
-      <c r="E285" s="2"/>
-      <c r="F285" s="2"/>
-      <c r="G285" s="2"/>
-      <c r="H285" s="2"/>
-      <c r="I285" s="2"/>
-      <c r="J285" s="2"/>
-      <c r="K285" s="2"/>
-      <c r="L285" s="2"/>
-      <c r="M285" s="2"/>
-      <c r="N285" s="2"/>
-      <c r="O285" s="2"/>
-      <c r="P285" s="2"/>
-    </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="282" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G282" t="s">
+        <v>146</v>
+      </c>
+      <c r="I282" t="s">
+        <v>148</v>
+      </c>
+      <c r="J282" t="s">
+        <v>153</v>
+      </c>
+      <c r="K282" t="s">
+        <v>131</v>
+      </c>
+      <c r="L282" t="s">
+        <v>161</v>
+      </c>
+      <c r="M282">
+        <v>34</v>
+      </c>
+      <c r="N282" t="s">
+        <v>132</v>
+      </c>
+      <c r="P282" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="283" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G283" t="s">
+        <v>146</v>
+      </c>
+      <c r="I283" t="s">
+        <v>148</v>
+      </c>
+      <c r="J283" t="s">
+        <v>154</v>
+      </c>
+      <c r="K283" t="s">
+        <v>131</v>
+      </c>
+      <c r="L283" t="s">
+        <v>161</v>
+      </c>
+      <c r="M283">
+        <v>46</v>
+      </c>
+      <c r="N283" t="s">
+        <v>132</v>
+      </c>
+      <c r="P283" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="284" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G284" t="s">
+        <v>146</v>
+      </c>
+      <c r="I284" t="s">
+        <v>148</v>
+      </c>
+      <c r="J284" t="s">
+        <v>201</v>
+      </c>
+      <c r="K284" t="s">
+        <v>131</v>
+      </c>
+      <c r="L284" t="s">
+        <v>161</v>
+      </c>
+      <c r="M284">
+        <v>29</v>
+      </c>
+      <c r="N284" t="s">
+        <v>132</v>
+      </c>
+      <c r="P284" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="285" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G285" t="s">
+        <v>146</v>
+      </c>
+      <c r="I285" t="s">
+        <v>149</v>
+      </c>
+      <c r="J285" t="s">
+        <v>152</v>
+      </c>
+      <c r="K285" t="s">
+        <v>131</v>
+      </c>
+      <c r="L285" t="s">
+        <v>161</v>
+      </c>
+      <c r="M285">
+        <v>29</v>
+      </c>
+      <c r="N285" t="s">
+        <v>132</v>
+      </c>
+      <c r="P285" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="286" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G286" t="s">
+        <v>146</v>
+      </c>
+      <c r="I286" t="s">
+        <v>149</v>
+      </c>
+      <c r="J286" t="s">
+        <v>153</v>
+      </c>
+      <c r="K286" t="s">
+        <v>131</v>
+      </c>
+      <c r="L286" t="s">
+        <v>161</v>
+      </c>
+      <c r="M286">
+        <v>35</v>
+      </c>
+      <c r="N286" t="s">
+        <v>132</v>
+      </c>
+      <c r="P286" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="287" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G287" t="s">
+        <v>146</v>
+      </c>
+      <c r="I287" t="s">
+        <v>149</v>
+      </c>
+      <c r="J287" t="s">
+        <v>154</v>
+      </c>
       <c r="K287" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="L287" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="M287">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="N287" t="s">
-        <v>127</v>
-      </c>
-      <c r="O287" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="P287" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="288" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G288" t="s">
+        <v>146</v>
+      </c>
+      <c r="I288" t="s">
+        <v>149</v>
+      </c>
+      <c r="J288" t="s">
+        <v>201</v>
+      </c>
       <c r="K288" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="L288" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="M288">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="N288" t="s">
-        <v>127</v>
-      </c>
-      <c r="O288" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="P288" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G289" t="s">
+        <v>146</v>
+      </c>
+      <c r="J289" t="s">
+        <v>152</v>
+      </c>
+      <c r="K289" t="s">
+        <v>131</v>
+      </c>
+      <c r="L289" t="s">
+        <v>161</v>
+      </c>
+      <c r="M289">
+        <v>29</v>
+      </c>
+      <c r="N289" t="s">
+        <v>132</v>
+      </c>
+      <c r="O289" t="s">
+        <v>156</v>
+      </c>
+      <c r="P289" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G290" t="s">
+        <v>146</v>
+      </c>
+      <c r="J290" t="s">
+        <v>153</v>
+      </c>
+      <c r="K290" t="s">
+        <v>131</v>
+      </c>
+      <c r="L290" t="s">
+        <v>161</v>
+      </c>
+      <c r="M290">
+        <v>35</v>
+      </c>
+      <c r="N290" t="s">
+        <v>132</v>
+      </c>
+      <c r="O290" t="s">
+        <v>156</v>
+      </c>
+      <c r="P290" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G291" t="s">
+        <v>146</v>
+      </c>
+      <c r="J291" t="s">
+        <v>154</v>
+      </c>
+      <c r="K291" t="s">
+        <v>131</v>
+      </c>
+      <c r="L291" t="s">
+        <v>161</v>
+      </c>
+      <c r="M291">
+        <v>44</v>
+      </c>
+      <c r="N291" t="s">
+        <v>132</v>
+      </c>
+      <c r="O291" t="s">
+        <v>156</v>
+      </c>
+      <c r="P291" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G292" t="s">
+        <v>146</v>
+      </c>
+      <c r="J292" t="s">
+        <v>201</v>
+      </c>
+      <c r="K292" t="s">
+        <v>131</v>
+      </c>
+      <c r="L292" t="s">
+        <v>161</v>
+      </c>
+      <c r="M292">
+        <v>29</v>
+      </c>
+      <c r="N292" t="s">
+        <v>132</v>
+      </c>
+      <c r="O292" t="s">
+        <v>156</v>
+      </c>
+      <c r="P292" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G293" t="s">
+        <v>151</v>
+      </c>
+      <c r="J293" t="s">
+        <v>152</v>
+      </c>
+      <c r="K293" t="s">
+        <v>131</v>
+      </c>
+      <c r="L293" t="s">
+        <v>161</v>
+      </c>
+      <c r="M293">
+        <v>29</v>
+      </c>
+      <c r="N293" t="s">
+        <v>132</v>
+      </c>
+      <c r="P293" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G294" t="s">
+        <v>151</v>
+      </c>
+      <c r="J294" t="s">
+        <v>153</v>
+      </c>
+      <c r="K294" t="s">
+        <v>131</v>
+      </c>
+      <c r="L294" t="s">
+        <v>161</v>
+      </c>
+      <c r="M294">
+        <v>40</v>
+      </c>
+      <c r="N294" t="s">
+        <v>132</v>
+      </c>
+      <c r="P294" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G295" t="s">
+        <v>151</v>
+      </c>
+      <c r="J295" t="s">
+        <v>154</v>
+      </c>
+      <c r="K295" t="s">
+        <v>131</v>
+      </c>
+      <c r="L295" t="s">
+        <v>161</v>
+      </c>
+      <c r="M295">
+        <v>56</v>
+      </c>
+      <c r="N295" t="s">
+        <v>132</v>
+      </c>
+      <c r="P295" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G296" t="s">
+        <v>151</v>
+      </c>
+      <c r="I296" t="s">
+        <v>204</v>
+      </c>
+      <c r="J296" t="s">
+        <v>152</v>
+      </c>
+      <c r="K296" t="s">
+        <v>131</v>
+      </c>
+      <c r="L296" t="s">
+        <v>161</v>
+      </c>
+      <c r="M296">
+        <v>30</v>
+      </c>
+      <c r="N296" t="s">
+        <v>132</v>
+      </c>
+      <c r="P296" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G297" t="s">
+        <v>151</v>
+      </c>
+      <c r="I297" t="s">
+        <v>204</v>
+      </c>
+      <c r="J297" t="s">
+        <v>153</v>
+      </c>
+      <c r="K297" t="s">
+        <v>131</v>
+      </c>
+      <c r="L297" t="s">
+        <v>161</v>
+      </c>
+      <c r="M297">
+        <v>41</v>
+      </c>
+      <c r="N297" t="s">
+        <v>132</v>
+      </c>
+      <c r="P297" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G298" t="s">
+        <v>151</v>
+      </c>
+      <c r="I298" t="s">
+        <v>204</v>
+      </c>
+      <c r="J298" t="s">
+        <v>154</v>
+      </c>
+      <c r="K298" t="s">
+        <v>131</v>
+      </c>
+      <c r="L298" t="s">
+        <v>161</v>
+      </c>
+      <c r="M298">
+        <v>56</v>
+      </c>
+      <c r="N298" t="s">
+        <v>132</v>
+      </c>
+      <c r="P298" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G299" t="s">
+        <v>151</v>
+      </c>
+      <c r="I299" t="s">
+        <v>205</v>
+      </c>
+      <c r="J299" t="s">
+        <v>153</v>
+      </c>
+      <c r="K299" t="s">
+        <v>131</v>
+      </c>
+      <c r="L299" t="s">
+        <v>161</v>
+      </c>
+      <c r="M299">
+        <v>41</v>
+      </c>
+      <c r="N299" t="s">
+        <v>132</v>
+      </c>
+      <c r="P299" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G300" t="s">
+        <v>151</v>
+      </c>
+      <c r="I300" t="s">
+        <v>205</v>
+      </c>
+      <c r="J300" t="s">
+        <v>154</v>
+      </c>
+      <c r="K300" t="s">
+        <v>131</v>
+      </c>
+      <c r="L300" t="s">
+        <v>161</v>
+      </c>
+      <c r="M300">
+        <v>41</v>
+      </c>
+      <c r="N300" t="s">
+        <v>132</v>
+      </c>
+      <c r="P300" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A302" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B302" s="2"/>
+      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
+      <c r="E302" s="2"/>
+      <c r="F302" s="2"/>
+      <c r="G302" s="2"/>
+      <c r="H302" s="2"/>
+      <c r="I302" s="2"/>
+      <c r="J302" s="2"/>
+      <c r="K302" s="2"/>
+      <c r="L302" s="2"/>
+      <c r="M302" s="2"/>
+      <c r="N302" s="2"/>
+      <c r="O302" s="2"/>
+      <c r="P302" s="2"/>
+    </row>
+    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K304" t="s">
+        <v>169</v>
+      </c>
+      <c r="L304" t="s">
+        <v>180</v>
+      </c>
+      <c r="M304">
+        <v>1</v>
+      </c>
+      <c r="N304" t="s">
+        <v>127</v>
+      </c>
+      <c r="O304" t="s">
+        <v>176</v>
+      </c>
+      <c r="P304" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K305" t="s">
+        <v>169</v>
+      </c>
+      <c r="L305" t="s">
+        <v>182</v>
+      </c>
+      <c r="M305">
+        <v>1</v>
+      </c>
+      <c r="N305" t="s">
+        <v>127</v>
+      </c>
+      <c r="O305" t="s">
+        <v>177</v>
+      </c>
+      <c r="P305" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G306" t="s">
         <v>140</v>
       </c>
-      <c r="J289" t="s">
+      <c r="J306" t="s">
+        <v>170</v>
+      </c>
+      <c r="K306" t="s">
+        <v>169</v>
+      </c>
+      <c r="L306" t="s">
+        <v>182</v>
+      </c>
+      <c r="M306">
+        <v>2</v>
+      </c>
+      <c r="N306" t="s">
+        <v>127</v>
+      </c>
+      <c r="O306" t="s">
+        <v>173</v>
+      </c>
+      <c r="P306" t="s">
         <v>171</v>
       </c>
-      <c r="K289" t="s">
+    </row>
+    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J307" t="s">
         <v>170</v>
       </c>
-      <c r="L289" t="s">
+      <c r="K307" t="s">
+        <v>169</v>
+      </c>
+      <c r="L307" t="s">
+        <v>182</v>
+      </c>
+      <c r="M307">
+        <v>1</v>
+      </c>
+      <c r="N307" t="s">
+        <v>127</v>
+      </c>
+      <c r="O307" t="s">
+        <v>174</v>
+      </c>
+      <c r="P307" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K308" t="s">
+        <v>169</v>
+      </c>
+      <c r="L308" t="s">
+        <v>181</v>
+      </c>
+      <c r="M308">
+        <v>1</v>
+      </c>
+      <c r="N308" t="s">
+        <v>127</v>
+      </c>
+      <c r="O308" t="s">
         <v>184</v>
       </c>
-      <c r="M289">
-        <v>2</v>
-      </c>
-      <c r="N289" t="s">
+      <c r="P308" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K309" t="s">
+        <v>169</v>
+      </c>
+      <c r="L309" t="s">
+        <v>183</v>
+      </c>
+      <c r="M309">
+        <v>1</v>
+      </c>
+      <c r="N309" t="s">
         <v>127</v>
       </c>
-      <c r="O289" t="s">
-        <v>174</v>
-      </c>
-      <c r="P289" t="s">
+      <c r="O309" t="s">
+        <v>175</v>
+      </c>
+      <c r="P309" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J290" t="s">
-        <v>171</v>
-      </c>
-      <c r="K290" t="s">
-        <v>170</v>
-      </c>
-      <c r="L290" t="s">
-        <v>184</v>
-      </c>
-      <c r="M290">
-        <v>1</v>
-      </c>
-      <c r="N290" t="s">
-        <v>127</v>
-      </c>
-      <c r="O290" t="s">
-        <v>175</v>
-      </c>
-      <c r="P290" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K291" t="s">
-        <v>170</v>
-      </c>
-      <c r="L291" t="s">
-        <v>183</v>
-      </c>
-      <c r="M291">
-        <v>1</v>
-      </c>
-      <c r="N291" t="s">
-        <v>127</v>
-      </c>
-      <c r="O291" t="s">
-        <v>186</v>
-      </c>
-      <c r="P291" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K292" t="s">
-        <v>170</v>
-      </c>
-      <c r="L292" t="s">
-        <v>185</v>
-      </c>
-      <c r="M292">
-        <v>1</v>
-      </c>
-      <c r="N292" t="s">
-        <v>127</v>
-      </c>
-      <c r="O292" t="s">
-        <v>176</v>
-      </c>
-      <c r="P292" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K294" t="s">
-        <v>170</v>
-      </c>
-      <c r="L294" t="s">
-        <v>189</v>
-      </c>
-      <c r="M294">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K311" t="s">
+        <v>169</v>
+      </c>
+      <c r="L311" t="s">
+        <v>187</v>
+      </c>
+      <c r="M311">
         <v>13</v>
       </c>
-      <c r="N294" t="s">
+      <c r="N311" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A313" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A296" s="2" t="s">
+      <c r="B313" s="2"/>
+      <c r="C313" s="2"/>
+      <c r="D313" s="2"/>
+      <c r="E313" s="2"/>
+      <c r="F313" s="2"/>
+      <c r="G313" s="2"/>
+      <c r="H313" s="2"/>
+      <c r="I313" s="2"/>
+      <c r="J313" s="2"/>
+      <c r="K313" s="2"/>
+      <c r="L313" s="2"/>
+      <c r="M313" s="2"/>
+      <c r="N313" s="2"/>
+      <c r="O313" s="2"/>
+      <c r="P313" s="2"/>
+    </row>
+    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B315" t="s">
+        <v>196</v>
+      </c>
+      <c r="K315" t="s">
+        <v>194</v>
+      </c>
+      <c r="L315" t="s">
+        <v>191</v>
+      </c>
+      <c r="M315">
+        <v>0.24</v>
+      </c>
+      <c r="N315" t="s">
+        <v>193</v>
+      </c>
+      <c r="P315" t="s">
         <v>192</v>
       </c>
-      <c r="B296" s="2"/>
-      <c r="C296" s="2"/>
-      <c r="D296" s="2"/>
-      <c r="E296" s="2"/>
-      <c r="F296" s="2"/>
-      <c r="G296" s="2"/>
-      <c r="H296" s="2"/>
-      <c r="I296" s="2"/>
-      <c r="J296" s="2"/>
-      <c r="K296" s="2"/>
-      <c r="L296" s="2"/>
-      <c r="M296" s="2"/>
-      <c r="N296" s="2"/>
-      <c r="O296" s="2"/>
-      <c r="P296" s="2"/>
-    </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B298" t="s">
+    </row>
+    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B316" t="s">
+        <v>197</v>
+      </c>
+      <c r="K316" t="s">
+        <v>194</v>
+      </c>
+      <c r="L316" t="s">
+        <v>191</v>
+      </c>
+      <c r="M316">
+        <v>0.24</v>
+      </c>
+      <c r="N316" t="s">
+        <v>193</v>
+      </c>
+      <c r="P316" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B317" t="s">
         <v>198</v>
       </c>
-      <c r="K298" t="s">
-        <v>196</v>
-      </c>
-      <c r="L298" t="s">
+      <c r="K317" t="s">
+        <v>194</v>
+      </c>
+      <c r="L317" t="s">
+        <v>191</v>
+      </c>
+      <c r="M317">
+        <v>0</v>
+      </c>
+      <c r="N317" t="s">
         <v>193</v>
       </c>
-      <c r="M298">
-        <v>0.24</v>
-      </c>
-      <c r="N298" t="s">
-        <v>195</v>
-      </c>
-      <c r="P298" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B299" t="s">
+      <c r="O317" t="s">
         <v>199</v>
-      </c>
-      <c r="K299" t="s">
-        <v>196</v>
-      </c>
-      <c r="L299" t="s">
-        <v>193</v>
-      </c>
-      <c r="M299">
-        <v>0.24</v>
-      </c>
-      <c r="N299" t="s">
-        <v>195</v>
-      </c>
-      <c r="P299" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B300" t="s">
-        <v>200</v>
-      </c>
-      <c r="K300" t="s">
-        <v>196</v>
-      </c>
-      <c r="L300" t="s">
-        <v>193</v>
-      </c>
-      <c r="M300">
-        <v>0</v>
-      </c>
-      <c r="N300" t="s">
-        <v>195</v>
-      </c>
-      <c r="O300" t="s">
-        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="310">
   <si>
     <t>f_crop</t>
   </si>
@@ -13786,6 +13786,9 @@
       <c r="R783" t="s">
         <v>175</v>
       </c>
+      <c r="T783" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="785" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -934,9 +934,6 @@
     <t>grass clover ley (40% clover) and three harvest</t>
   </si>
   <si>
-    <t>grass clover ley (20% clover) and three harvest</t>
-  </si>
-  <si>
     <t>grass ley and three harvest</t>
   </si>
   <si>
@@ -962,6 +959,9 @@
   </si>
   <si>
     <t>Minimum share of total N from manure on area where manure is applied</t>
+  </si>
+  <si>
+    <t>grass clover ley (10% clover) and three harvest</t>
   </si>
 </sst>
 </file>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="P21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q21">
         <v>66</v>
@@ -1772,10 +1772,10 @@
         <v>103</v>
       </c>
       <c r="S21" t="s">
+        <v>309</v>
+      </c>
+      <c r="T21" t="s">
         <v>310</v>
-      </c>
-      <c r="T21" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3780,10 +3780,10 @@
         <v>11</v>
       </c>
       <c r="Q150">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="S150" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="151" spans="1:20" x14ac:dyDescent="0.25">
@@ -3808,7 +3808,7 @@
         <v>12</v>
       </c>
       <c r="Q151">
-        <v>20</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.25">
@@ -4817,7 +4817,7 @@
         <v>4.2</v>
       </c>
       <c r="T193" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="194" spans="1:20" x14ac:dyDescent="0.25">
@@ -4842,7 +4842,7 @@
         <v>3.3</v>
       </c>
       <c r="T194" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="195" spans="1:20" x14ac:dyDescent="0.25">
@@ -4868,7 +4868,7 @@
         <v>3.75</v>
       </c>
       <c r="S195" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="196" spans="1:20" x14ac:dyDescent="0.25">
@@ -5010,7 +5010,7 @@
         <v>20</v>
       </c>
       <c r="S201" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.25">
@@ -7098,7 +7098,7 @@
         <v>3</v>
       </c>
       <c r="S332" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="333" spans="1:19" x14ac:dyDescent="0.25">
@@ -7229,7 +7229,7 @@
         <v>3</v>
       </c>
       <c r="S340" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="341" spans="1:19" x14ac:dyDescent="0.25">
@@ -7677,7 +7677,7 @@
         <v>3</v>
       </c>
       <c r="S373" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="374" spans="1:19" x14ac:dyDescent="0.25">
@@ -8979,7 +8979,7 @@
         <v>0.6</v>
       </c>
       <c r="T477" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="478" spans="1:20" x14ac:dyDescent="0.25">
@@ -8994,7 +8994,7 @@
         <v>1.6</v>
       </c>
       <c r="T478" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="479" spans="1:20" x14ac:dyDescent="0.25">
@@ -9010,7 +9010,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="S479" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="480" spans="1:20" x14ac:dyDescent="0.25">
@@ -10314,7 +10314,7 @@
         <v>5</v>
       </c>
       <c r="S570" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="571" spans="1:19" x14ac:dyDescent="0.25">
@@ -10413,7 +10413,7 @@
         <v>5</v>
       </c>
       <c r="S576" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="577" spans="1:17" x14ac:dyDescent="0.25">
@@ -10830,7 +10830,7 @@
         <v>10</v>
       </c>
       <c r="S607" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="608" spans="1:19" x14ac:dyDescent="0.25">
@@ -11970,7 +11970,7 @@
         <v>5.6</v>
       </c>
       <c r="T700" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="701" spans="1:20" x14ac:dyDescent="0.25">
@@ -11985,7 +11985,7 @@
         <v>3</v>
       </c>
       <c r="T701" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="702" spans="1:20" x14ac:dyDescent="0.25">
@@ -12001,7 +12001,7 @@
         <v>4.3</v>
       </c>
       <c r="S702" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="703" spans="1:20" x14ac:dyDescent="0.25">

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="315">
   <si>
     <t>f_crop</t>
   </si>
@@ -962,6 +962,9 @@
   </si>
   <si>
     <t>grass clover ley (10% clover) and three harvest</t>
+  </si>
+  <si>
+    <t>Set to match K/ha in stat.</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T793"/>
+  <dimension ref="A1:T794"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="21" customWidth="1"/>
@@ -9140,7 +9143,7 @@
         <v>227</v>
       </c>
       <c r="Q490" s="22">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R490" s="4"/>
       <c r="S490" s="4" t="s">
@@ -9169,7 +9172,7 @@
         <v>227</v>
       </c>
       <c r="Q491" s="22">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R491" s="4"/>
       <c r="S491" s="4" t="s">
@@ -9197,8 +9200,8 @@
       <c r="P492" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="Q492" s="4">
-        <v>1.05</v>
+      <c r="Q492" s="22">
+        <v>1.2</v>
       </c>
       <c r="R492" s="4"/>
       <c r="S492" s="4" t="s">
@@ -9207,138 +9210,153 @@
       <c r="T492" s="4"/>
     </row>
     <row r="493" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A493" s="6"/>
-      <c r="B493" s="6"/>
-    </row>
-    <row r="494" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A494" s="15" t="s">
+      <c r="A493" t="s">
+        <v>38</v>
+      </c>
+      <c r="C493" s="4"/>
+      <c r="D493" s="4"/>
+      <c r="E493" s="4"/>
+      <c r="F493" s="4"/>
+      <c r="G493" s="4"/>
+      <c r="H493" s="4"/>
+      <c r="I493" s="4"/>
+      <c r="J493" s="4"/>
+      <c r="K493" s="4"/>
+      <c r="L493" s="4"/>
+      <c r="M493" s="4"/>
+      <c r="N493" s="4"/>
+      <c r="O493" s="4"/>
+      <c r="P493" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q493" s="22">
+        <v>1.25</v>
+      </c>
+      <c r="R493" s="4"/>
+      <c r="S493" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="T493" s="4"/>
+    </row>
+    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A494" s="6"/>
+      <c r="B494" s="6"/>
+    </row>
+    <row r="495" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A495" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="B494" s="15"/>
-      <c r="C494" s="14"/>
-      <c r="D494" s="14"/>
-      <c r="E494" s="14"/>
-      <c r="F494" s="14"/>
-      <c r="G494" s="14"/>
-      <c r="H494" s="14"/>
-      <c r="I494" s="14"/>
-      <c r="J494" s="14"/>
-      <c r="K494" s="14"/>
-      <c r="L494" s="14"/>
-      <c r="M494" s="14"/>
-      <c r="N494" s="14"/>
-      <c r="O494" s="14"/>
-      <c r="P494" s="14"/>
-      <c r="Q494" s="14"/>
-      <c r="R494" s="14"/>
-      <c r="S494" s="14"/>
-      <c r="T494" s="14"/>
-    </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A495" s="2" t="s">
+      <c r="B495" s="15"/>
+      <c r="C495" s="14"/>
+      <c r="D495" s="14"/>
+      <c r="E495" s="14"/>
+      <c r="F495" s="14"/>
+      <c r="G495" s="14"/>
+      <c r="H495" s="14"/>
+      <c r="I495" s="14"/>
+      <c r="J495" s="14"/>
+      <c r="K495" s="14"/>
+      <c r="L495" s="14"/>
+      <c r="M495" s="14"/>
+      <c r="N495" s="14"/>
+      <c r="O495" s="14"/>
+      <c r="P495" s="14"/>
+      <c r="Q495" s="14"/>
+      <c r="R495" s="14"/>
+      <c r="S495" s="14"/>
+      <c r="T495" s="14"/>
+    </row>
+    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A496" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B495" s="2"/>
-      <c r="C495" s="2"/>
-      <c r="D495" s="2"/>
-      <c r="E495" s="2"/>
-      <c r="F495" s="2"/>
-      <c r="G495" s="2"/>
-      <c r="H495" s="2"/>
-      <c r="I495" s="2"/>
-      <c r="J495" s="2"/>
-      <c r="K495" s="2"/>
-      <c r="L495" s="2"/>
-      <c r="M495" s="2"/>
-      <c r="N495" s="2"/>
-      <c r="O495" s="2"/>
-      <c r="P495" s="2"/>
-      <c r="Q495" s="2"/>
-      <c r="R495" s="2"/>
-      <c r="S495" s="3"/>
-      <c r="T495" s="3"/>
-    </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A496" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="B496" s="19"/>
+      <c r="B496" s="2"/>
+      <c r="C496" s="2"/>
+      <c r="D496" s="2"/>
+      <c r="E496" s="2"/>
+      <c r="F496" s="2"/>
+      <c r="G496" s="2"/>
+      <c r="H496" s="2"/>
+      <c r="I496" s="2"/>
+      <c r="J496" s="2"/>
+      <c r="K496" s="2"/>
+      <c r="L496" s="2"/>
+      <c r="M496" s="2"/>
+      <c r="N496" s="2"/>
+      <c r="O496" s="2"/>
+      <c r="P496" s="2"/>
+      <c r="Q496" s="2"/>
+      <c r="R496" s="2"/>
+      <c r="S496" s="3"/>
+      <c r="T496" s="3"/>
     </row>
     <row r="497" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A497" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B497" s="19"/>
+    </row>
+    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A498" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="B497" s="19"/>
-    </row>
-    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="P498" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q498" s="5">
-        <v>0</v>
-      </c>
-      <c r="R498" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="S498" s="5" t="s">
-        <v>152</v>
-      </c>
+      <c r="B498" s="19"/>
     </row>
     <row r="499" spans="1:19" x14ac:dyDescent="0.25">
       <c r="P499" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q499" s="5">
         <v>0</v>
       </c>
       <c r="R499" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S499" s="5" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="500" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="P500" s="5"/>
-      <c r="Q500" s="5"/>
-      <c r="R500" s="5"/>
-      <c r="S500" s="5"/>
+      <c r="P500" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q500" s="5">
+        <v>0</v>
+      </c>
+      <c r="R500" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="S500" s="5" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="501" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A501" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="B501" s="21"/>
       <c r="P501" s="5"/>
       <c r="Q501" s="5"/>
       <c r="R501" s="5"/>
       <c r="S501" s="5"/>
     </row>
     <row r="502" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
-        <v>7</v>
-      </c>
-      <c r="N502" t="s">
-        <v>198</v>
-      </c>
-      <c r="P502" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q502">
-        <v>5</v>
-      </c>
+      <c r="A502" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B502" s="21"/>
+      <c r="P502" s="5"/>
+      <c r="Q502" s="5"/>
+      <c r="R502" s="5"/>
+      <c r="S502" s="5"/>
     </row>
     <row r="503" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>7</v>
       </c>
       <c r="N503" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P503" t="s">
         <v>213</v>
       </c>
-      <c r="Q503" s="4">
+      <c r="Q503">
         <v>5</v>
       </c>
     </row>
@@ -9347,7 +9365,7 @@
         <v>7</v>
       </c>
       <c r="N504" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P504" t="s">
         <v>213</v>
@@ -9361,13 +9379,13 @@
         <v>7</v>
       </c>
       <c r="N505" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P505" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q505" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="506" spans="1:19" x14ac:dyDescent="0.25">
@@ -9375,13 +9393,13 @@
         <v>7</v>
       </c>
       <c r="N506" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P506" t="s">
         <v>214</v>
       </c>
       <c r="Q506" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="507" spans="1:19" x14ac:dyDescent="0.25">
@@ -9389,28 +9407,27 @@
         <v>7</v>
       </c>
       <c r="N507" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P507" t="s">
         <v>214</v>
       </c>
       <c r="Q507" s="4">
-        <v>-15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="508" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="N508" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P508" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q508" s="20">
-        <f t="shared" ref="Q508:Q513" si="19">Q502</f>
-        <v>5</v>
+        <v>214</v>
+      </c>
+      <c r="Q508" s="4">
+        <v>-15</v>
       </c>
     </row>
     <row r="509" spans="1:19" x14ac:dyDescent="0.25">
@@ -9418,13 +9435,13 @@
         <v>25</v>
       </c>
       <c r="N509" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P509" t="s">
         <v>213</v>
       </c>
       <c r="Q509" s="20">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="Q509:Q514" si="19">Q503</f>
         <v>5</v>
       </c>
     </row>
@@ -9433,7 +9450,7 @@
         <v>25</v>
       </c>
       <c r="N510" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P510" t="s">
         <v>213</v>
@@ -9448,14 +9465,14 @@
         <v>25</v>
       </c>
       <c r="N511" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P511" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q511" s="20">
         <f t="shared" si="19"/>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="512" spans="1:19" x14ac:dyDescent="0.25">
@@ -9463,14 +9480,14 @@
         <v>25</v>
       </c>
       <c r="N512" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P512" t="s">
         <v>214</v>
       </c>
       <c r="Q512" s="20">
         <f t="shared" si="19"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="513" spans="1:17" x14ac:dyDescent="0.25">
@@ -9478,29 +9495,29 @@
         <v>25</v>
       </c>
       <c r="N513" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P513" t="s">
         <v>214</v>
       </c>
       <c r="Q513" s="20">
         <f t="shared" si="19"/>
-        <v>-15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="514" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N514" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P514" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q514" s="20">
-        <f t="shared" ref="Q514:Q519" si="20">Q502</f>
-        <v>5</v>
+        <f t="shared" si="19"/>
+        <v>-15</v>
       </c>
     </row>
     <row r="515" spans="1:17" x14ac:dyDescent="0.25">
@@ -9508,13 +9525,13 @@
         <v>21</v>
       </c>
       <c r="N515" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P515" t="s">
         <v>213</v>
       </c>
       <c r="Q515" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="Q515:Q520" si="20">Q503</f>
         <v>5</v>
       </c>
     </row>
@@ -9523,7 +9540,7 @@
         <v>21</v>
       </c>
       <c r="N516" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P516" t="s">
         <v>213</v>
@@ -9538,14 +9555,14 @@
         <v>21</v>
       </c>
       <c r="N517" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P517" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q517" s="20">
         <f t="shared" si="20"/>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="518" spans="1:17" x14ac:dyDescent="0.25">
@@ -9553,14 +9570,14 @@
         <v>21</v>
       </c>
       <c r="N518" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P518" t="s">
         <v>214</v>
       </c>
       <c r="Q518" s="20">
         <f t="shared" si="20"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="519" spans="1:17" x14ac:dyDescent="0.25">
@@ -9568,29 +9585,29 @@
         <v>21</v>
       </c>
       <c r="N519" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P519" t="s">
         <v>214</v>
       </c>
       <c r="Q519" s="20">
         <f t="shared" si="20"/>
-        <v>-15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="520" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N520" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P520" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q520" s="20">
-        <f t="shared" ref="Q520:Q525" si="21">Q502</f>
-        <v>5</v>
+        <f t="shared" si="20"/>
+        <v>-15</v>
       </c>
     </row>
     <row r="521" spans="1:17" x14ac:dyDescent="0.25">
@@ -9598,13 +9615,13 @@
         <v>23</v>
       </c>
       <c r="N521" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P521" t="s">
         <v>213</v>
       </c>
       <c r="Q521" s="20">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="Q521:Q526" si="21">Q503</f>
         <v>5</v>
       </c>
     </row>
@@ -9613,7 +9630,7 @@
         <v>23</v>
       </c>
       <c r="N522" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P522" t="s">
         <v>213</v>
@@ -9628,14 +9645,14 @@
         <v>23</v>
       </c>
       <c r="N523" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P523" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q523" s="20">
         <f t="shared" si="21"/>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="524" spans="1:17" x14ac:dyDescent="0.25">
@@ -9643,14 +9660,14 @@
         <v>23</v>
       </c>
       <c r="N524" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P524" t="s">
         <v>214</v>
       </c>
       <c r="Q524" s="20">
         <f t="shared" si="21"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="525" spans="1:17" x14ac:dyDescent="0.25">
@@ -9658,42 +9675,43 @@
         <v>23</v>
       </c>
       <c r="N525" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P525" t="s">
         <v>214</v>
       </c>
       <c r="Q525" s="20">
         <f t="shared" si="21"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="526" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>23</v>
+      </c>
+      <c r="N526" t="s">
+        <v>200</v>
+      </c>
+      <c r="P526" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q526" s="20">
+        <f t="shared" si="21"/>
         <v>-15</v>
       </c>
     </row>
-    <row r="527" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A527" s="21" t="s">
+    <row r="528" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A528" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="B527" s="21"/>
-    </row>
-    <row r="528" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A528" t="s">
-        <v>14</v>
-      </c>
-      <c r="N528" t="s">
-        <v>198</v>
-      </c>
-      <c r="P528" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q528">
-        <v>5</v>
-      </c>
+      <c r="B528" s="21"/>
     </row>
     <row r="529" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>14</v>
       </c>
       <c r="N529" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P529" t="s">
         <v>213</v>
@@ -9707,7 +9725,7 @@
         <v>14</v>
       </c>
       <c r="N530" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P530" t="s">
         <v>213</v>
@@ -9721,13 +9739,13 @@
         <v>14</v>
       </c>
       <c r="N531" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P531" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q531">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="532" spans="1:17" x14ac:dyDescent="0.25">
@@ -9735,13 +9753,13 @@
         <v>14</v>
       </c>
       <c r="N532" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P532" t="s">
         <v>214</v>
       </c>
       <c r="Q532">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="533" spans="1:17" x14ac:dyDescent="0.25">
@@ -9749,28 +9767,27 @@
         <v>14</v>
       </c>
       <c r="N533" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P533" t="s">
         <v>214</v>
       </c>
       <c r="Q533">
-        <v>-15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="534" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N534" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P534" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q534" s="20">
-        <f t="shared" ref="Q534:Q539" si="22">Q528</f>
-        <v>5</v>
+        <v>214</v>
+      </c>
+      <c r="Q534">
+        <v>-15</v>
       </c>
     </row>
     <row r="535" spans="1:17" x14ac:dyDescent="0.25">
@@ -9778,13 +9795,13 @@
         <v>15</v>
       </c>
       <c r="N535" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P535" t="s">
         <v>213</v>
       </c>
       <c r="Q535" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="Q535:Q540" si="22">Q529</f>
         <v>5</v>
       </c>
     </row>
@@ -9793,7 +9810,7 @@
         <v>15</v>
       </c>
       <c r="N536" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P536" t="s">
         <v>213</v>
@@ -9808,14 +9825,14 @@
         <v>15</v>
       </c>
       <c r="N537" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P537" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q537" s="20">
         <f t="shared" si="22"/>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="538" spans="1:17" x14ac:dyDescent="0.25">
@@ -9823,14 +9840,14 @@
         <v>15</v>
       </c>
       <c r="N538" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P538" t="s">
         <v>214</v>
       </c>
       <c r="Q538" s="20">
         <f t="shared" si="22"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="539" spans="1:17" x14ac:dyDescent="0.25">
@@ -9838,29 +9855,29 @@
         <v>15</v>
       </c>
       <c r="N539" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P539" t="s">
         <v>214</v>
       </c>
       <c r="Q539" s="20">
         <f t="shared" si="22"/>
-        <v>-15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="540" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N540" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P540" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q540" s="20">
-        <f t="shared" ref="Q540:Q545" si="23">Q528</f>
-        <v>5</v>
+        <f t="shared" si="22"/>
+        <v>-15</v>
       </c>
     </row>
     <row r="541" spans="1:17" x14ac:dyDescent="0.25">
@@ -9868,13 +9885,13 @@
         <v>19</v>
       </c>
       <c r="N541" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P541" t="s">
         <v>213</v>
       </c>
       <c r="Q541" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="Q541:Q546" si="23">Q529</f>
         <v>5</v>
       </c>
     </row>
@@ -9883,7 +9900,7 @@
         <v>19</v>
       </c>
       <c r="N542" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P542" t="s">
         <v>213</v>
@@ -9898,14 +9915,14 @@
         <v>19</v>
       </c>
       <c r="N543" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P543" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q543" s="20">
         <f t="shared" si="23"/>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="544" spans="1:17" x14ac:dyDescent="0.25">
@@ -9913,14 +9930,14 @@
         <v>19</v>
       </c>
       <c r="N544" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P544" t="s">
         <v>214</v>
       </c>
       <c r="Q544" s="20">
         <f t="shared" si="23"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="545" spans="1:17" x14ac:dyDescent="0.25">
@@ -9928,29 +9945,29 @@
         <v>19</v>
       </c>
       <c r="N545" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P545" t="s">
         <v>214</v>
       </c>
       <c r="Q545" s="20">
         <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="546" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>19</v>
+      </c>
+      <c r="N546" t="s">
+        <v>200</v>
+      </c>
+      <c r="P546" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q546" s="20">
+        <f t="shared" si="23"/>
         <v>-15</v>
-      </c>
-    </row>
-    <row r="546" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A546" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="N546" t="s">
-        <v>198</v>
-      </c>
-      <c r="P546" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q546" s="20">
-        <f t="shared" ref="Q546:Q551" si="24">Q528</f>
-        <v>5</v>
       </c>
     </row>
     <row r="547" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9958,13 +9975,13 @@
         <v>267</v>
       </c>
       <c r="N547" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P547" s="4" t="s">
         <v>213</v>
       </c>
       <c r="Q547" s="20">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="Q547:Q552" si="24">Q529</f>
         <v>5</v>
       </c>
     </row>
@@ -9973,7 +9990,7 @@
         <v>267</v>
       </c>
       <c r="N548" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P548" s="4" t="s">
         <v>213</v>
@@ -9988,14 +10005,14 @@
         <v>267</v>
       </c>
       <c r="N549" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P549" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q549" s="20">
         <f t="shared" si="24"/>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="550" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10003,14 +10020,14 @@
         <v>267</v>
       </c>
       <c r="N550" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P550" s="4" t="s">
         <v>214</v>
       </c>
       <c r="Q550" s="20">
         <f t="shared" si="24"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="551" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10018,29 +10035,29 @@
         <v>267</v>
       </c>
       <c r="N551" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P551" s="4" t="s">
         <v>214</v>
       </c>
       <c r="Q551" s="20">
         <f t="shared" si="24"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="552" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A552" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="N552" t="s">
+        <v>200</v>
+      </c>
+      <c r="P552" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q552" s="20">
+        <f t="shared" si="24"/>
         <v>-15</v>
-      </c>
-    </row>
-    <row r="552" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A552" t="s">
-        <v>22</v>
-      </c>
-      <c r="N552" t="s">
-        <v>198</v>
-      </c>
-      <c r="P552" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q552" s="20">
-        <f t="shared" ref="Q552:Q557" si="25">Q528</f>
-        <v>5</v>
       </c>
     </row>
     <row r="553" spans="1:17" x14ac:dyDescent="0.25">
@@ -10048,13 +10065,13 @@
         <v>22</v>
       </c>
       <c r="N553" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P553" t="s">
         <v>213</v>
       </c>
       <c r="Q553" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="Q553:Q558" si="25">Q529</f>
         <v>5</v>
       </c>
     </row>
@@ -10063,7 +10080,7 @@
         <v>22</v>
       </c>
       <c r="N554" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P554" t="s">
         <v>213</v>
@@ -10078,14 +10095,14 @@
         <v>22</v>
       </c>
       <c r="N555" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P555" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q555" s="20">
         <f t="shared" si="25"/>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="556" spans="1:17" x14ac:dyDescent="0.25">
@@ -10093,14 +10110,14 @@
         <v>22</v>
       </c>
       <c r="N556" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P556" t="s">
         <v>214</v>
       </c>
       <c r="Q556" s="20">
         <f t="shared" si="25"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="557" spans="1:17" x14ac:dyDescent="0.25">
@@ -10108,29 +10125,29 @@
         <v>22</v>
       </c>
       <c r="N557" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P557" t="s">
         <v>214</v>
       </c>
       <c r="Q557" s="20">
         <f t="shared" si="25"/>
-        <v>-15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="558" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="N558" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P558" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q558" s="20">
-        <f t="shared" ref="Q558:Q563" si="26">Q528</f>
-        <v>5</v>
+        <f t="shared" si="25"/>
+        <v>-15</v>
       </c>
     </row>
     <row r="559" spans="1:17" x14ac:dyDescent="0.25">
@@ -10138,13 +10155,13 @@
         <v>27</v>
       </c>
       <c r="N559" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P559" t="s">
         <v>213</v>
       </c>
       <c r="Q559" s="20">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="Q559:Q564" si="26">Q529</f>
         <v>5</v>
       </c>
     </row>
@@ -10153,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="N560" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P560" t="s">
         <v>213</v>
@@ -10168,14 +10185,14 @@
         <v>27</v>
       </c>
       <c r="N561" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P561" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q561" s="20">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="562" spans="1:19" x14ac:dyDescent="0.25">
@@ -10183,14 +10200,14 @@
         <v>27</v>
       </c>
       <c r="N562" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P562" t="s">
         <v>214</v>
       </c>
       <c r="Q562" s="20">
         <f t="shared" si="26"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="563" spans="1:19" x14ac:dyDescent="0.25">
@@ -10198,29 +10215,29 @@
         <v>27</v>
       </c>
       <c r="N563" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P563" t="s">
         <v>214</v>
       </c>
       <c r="Q563" s="20">
         <f t="shared" si="26"/>
-        <v>-15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="564" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N564" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P564" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q564" s="20">
-        <f t="shared" ref="Q564:Q569" si="27">Q528</f>
-        <v>5</v>
+        <f t="shared" si="26"/>
+        <v>-15</v>
       </c>
     </row>
     <row r="565" spans="1:19" x14ac:dyDescent="0.25">
@@ -10228,13 +10245,13 @@
         <v>26</v>
       </c>
       <c r="N565" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P565" t="s">
         <v>213</v>
       </c>
       <c r="Q565" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="Q565:Q570" si="27">Q529</f>
         <v>5</v>
       </c>
     </row>
@@ -10243,7 +10260,7 @@
         <v>26</v>
       </c>
       <c r="N566" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P566" t="s">
         <v>213</v>
@@ -10258,14 +10275,14 @@
         <v>26</v>
       </c>
       <c r="N567" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P567" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q567" s="20">
         <f t="shared" si="27"/>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="568" spans="1:19" x14ac:dyDescent="0.25">
@@ -10273,14 +10290,14 @@
         <v>26</v>
       </c>
       <c r="N568" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P568" t="s">
         <v>214</v>
       </c>
       <c r="Q568" s="20">
         <f t="shared" si="27"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="569" spans="1:19" x14ac:dyDescent="0.25">
@@ -10288,33 +10305,29 @@
         <v>26</v>
       </c>
       <c r="N569" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P569" t="s">
         <v>214</v>
       </c>
       <c r="Q569" s="20">
         <f t="shared" si="27"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="570" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>26</v>
+      </c>
+      <c r="N570" t="s">
+        <v>200</v>
+      </c>
+      <c r="P570" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q570" s="20">
+        <f t="shared" si="27"/>
         <v>-15</v>
-      </c>
-    </row>
-    <row r="570" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A570" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B570" s="6"/>
-      <c r="N570" t="s">
-        <v>198</v>
-      </c>
-      <c r="P570" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q570" s="20">
-        <f t="shared" ref="Q570:Q575" si="28">Q528</f>
-        <v>5</v>
-      </c>
-      <c r="S570" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="571" spans="1:19" x14ac:dyDescent="0.25">
@@ -10323,14 +10336,17 @@
       </c>
       <c r="B571" s="6"/>
       <c r="N571" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P571" t="s">
         <v>213</v>
       </c>
       <c r="Q571" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="Q571:Q576" si="28">Q529</f>
         <v>5</v>
+      </c>
+      <c r="S571" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="572" spans="1:19" x14ac:dyDescent="0.25">
@@ -10339,7 +10355,7 @@
       </c>
       <c r="B572" s="6"/>
       <c r="N572" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P572" t="s">
         <v>213</v>
@@ -10355,14 +10371,14 @@
       </c>
       <c r="B573" s="6"/>
       <c r="N573" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P573" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q573" s="20">
         <f t="shared" si="28"/>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="574" spans="1:19" x14ac:dyDescent="0.25">
@@ -10371,14 +10387,14 @@
       </c>
       <c r="B574" s="6"/>
       <c r="N574" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P574" t="s">
         <v>214</v>
       </c>
       <c r="Q574" s="20">
         <f t="shared" si="28"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="575" spans="1:19" x14ac:dyDescent="0.25">
@@ -10387,58 +10403,58 @@
       </c>
       <c r="B575" s="6"/>
       <c r="N575" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P575" t="s">
         <v>214</v>
       </c>
       <c r="Q575" s="20">
         <f t="shared" si="28"/>
-        <v>-15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="576" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A576" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B576" s="6"/>
       <c r="N576" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P576" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q576" s="20">
-        <f t="shared" ref="Q576:Q581" si="29">Q528</f>
-        <v>5</v>
-      </c>
-      <c r="S576" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="577" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="28"/>
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="577" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A577" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B577" s="6"/>
       <c r="N577" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P577" t="s">
         <v>213</v>
       </c>
       <c r="Q577" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="Q577:Q582" si="29">Q529</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="578" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S577" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="578" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A578" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B578" s="6"/>
       <c r="N578" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P578" t="s">
         <v>213</v>
@@ -10448,79 +10464,81 @@
         <v>5</v>
       </c>
     </row>
-    <row r="579" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A579" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B579" s="6"/>
       <c r="N579" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P579" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q579" s="20">
         <f t="shared" si="29"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="580" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="580" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A580" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B580" s="6"/>
       <c r="N580" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P580" t="s">
         <v>214</v>
       </c>
       <c r="Q580" s="20">
         <f t="shared" si="29"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="581" spans="1:17" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="581" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A581" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="B581" s="6"/>
       <c r="N581" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P581" t="s">
         <v>214</v>
       </c>
       <c r="Q581" s="20">
         <f t="shared" si="29"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="582" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A582" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N582" t="s">
+        <v>200</v>
+      </c>
+      <c r="P582" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q582" s="20">
+        <f t="shared" si="29"/>
         <v>-15</v>
       </c>
     </row>
-    <row r="582" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A582" s="21" t="s">
+    <row r="583" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A583" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="B582" s="21"/>
-    </row>
-    <row r="583" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A583" t="s">
-        <v>32</v>
-      </c>
-      <c r="N583" t="s">
-        <v>198</v>
-      </c>
-      <c r="P583" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q583">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="584" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B583" s="21"/>
+    </row>
+    <row r="584" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>32</v>
       </c>
       <c r="N584" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P584" t="s">
         <v>213</v>
@@ -10529,12 +10547,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="585" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>32</v>
       </c>
       <c r="N585" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P585" t="s">
         <v>213</v>
@@ -10543,12 +10561,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="586" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>32</v>
       </c>
       <c r="N586" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P586" t="s">
         <v>213</v>
@@ -10557,82 +10575,82 @@
         <v>10</v>
       </c>
     </row>
-    <row r="587" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>32</v>
       </c>
       <c r="N587" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="P587" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q587">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="588" spans="1:17" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="588" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>32</v>
       </c>
       <c r="N588" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P588" t="s">
         <v>214</v>
       </c>
       <c r="Q588">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="589" spans="1:17" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="589" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>32</v>
       </c>
       <c r="N589" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P589" t="s">
         <v>214</v>
       </c>
       <c r="Q589">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="590" spans="1:17" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="590" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>32</v>
       </c>
       <c r="N590" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P590" t="s">
         <v>214</v>
       </c>
       <c r="Q590">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="591" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>32</v>
+      </c>
+      <c r="N591" t="s">
+        <v>201</v>
+      </c>
+      <c r="P591" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q591">
         <v>-25</v>
       </c>
     </row>
-    <row r="591" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A591" t="s">
-        <v>33</v>
-      </c>
-      <c r="N591" t="s">
-        <v>198</v>
-      </c>
-      <c r="P591" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q591">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="592" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>33</v>
       </c>
       <c r="N592" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P592" t="s">
         <v>213</v>
@@ -10646,7 +10664,7 @@
         <v>33</v>
       </c>
       <c r="N593" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P593" t="s">
         <v>213</v>
@@ -10660,13 +10678,13 @@
         <v>33</v>
       </c>
       <c r="N594" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P594" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q594">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="595" spans="1:19" x14ac:dyDescent="0.25">
@@ -10674,13 +10692,13 @@
         <v>33</v>
       </c>
       <c r="N595" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P595" t="s">
         <v>214</v>
       </c>
       <c r="Q595">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="596" spans="1:19" x14ac:dyDescent="0.25">
@@ -10688,41 +10706,41 @@
         <v>33</v>
       </c>
       <c r="N596" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P596" t="s">
         <v>214</v>
       </c>
       <c r="Q596">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="597" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>33</v>
+      </c>
+      <c r="N597" t="s">
+        <v>200</v>
+      </c>
+      <c r="P597" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q597">
         <v>-10</v>
       </c>
     </row>
-    <row r="598" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A598" s="21" t="s">
+    <row r="599" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A599" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B598" s="21"/>
-    </row>
-    <row r="599" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A599" t="s">
-        <v>38</v>
-      </c>
-      <c r="N599" t="s">
-        <v>198</v>
-      </c>
-      <c r="P599" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q599">
-        <v>10</v>
-      </c>
+      <c r="B599" s="21"/>
     </row>
     <row r="600" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>38</v>
       </c>
       <c r="N600" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P600" t="s">
         <v>213</v>
@@ -10736,7 +10754,7 @@
         <v>38</v>
       </c>
       <c r="N601" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P601" t="s">
         <v>213</v>
@@ -10750,7 +10768,7 @@
         <v>38</v>
       </c>
       <c r="N602" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P602" t="s">
         <v>213</v>
@@ -10764,13 +10782,13 @@
         <v>38</v>
       </c>
       <c r="N603" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P603" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q603">
-        <v>86.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="604" spans="1:19" x14ac:dyDescent="0.25">
@@ -10778,13 +10796,13 @@
         <v>38</v>
       </c>
       <c r="N604" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P604" t="s">
         <v>214</v>
       </c>
       <c r="Q604">
-        <v>46.7</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="605" spans="1:19" x14ac:dyDescent="0.25">
@@ -10792,13 +10810,13 @@
         <v>38</v>
       </c>
       <c r="N605" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P605" t="s">
         <v>214</v>
       </c>
       <c r="Q605">
-        <v>6.7</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="606" spans="1:19" x14ac:dyDescent="0.25">
@@ -10806,31 +10824,27 @@
         <v>38</v>
       </c>
       <c r="N606" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P606" t="s">
         <v>214</v>
       </c>
       <c r="Q606">
-        <v>-26.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="607" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="N607" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P607" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q607" s="24">
-        <f>Q599</f>
-        <v>10</v>
-      </c>
-      <c r="S607" t="s">
-        <v>305</v>
+        <v>214</v>
+      </c>
+      <c r="Q607">
+        <v>-26.7</v>
       </c>
     </row>
     <row r="608" spans="1:19" x14ac:dyDescent="0.25">
@@ -10838,14 +10852,17 @@
         <v>68</v>
       </c>
       <c r="N608" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P608" t="s">
         <v>213</v>
       </c>
       <c r="Q608" s="24">
-        <f t="shared" ref="Q608:Q614" si="30">Q600</f>
+        <f>Q600</f>
         <v>10</v>
+      </c>
+      <c r="S608" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="609" spans="1:17" x14ac:dyDescent="0.25">
@@ -10853,13 +10870,13 @@
         <v>68</v>
       </c>
       <c r="N609" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P609" t="s">
         <v>213</v>
       </c>
       <c r="Q609" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="Q609:Q615" si="30">Q601</f>
         <v>10</v>
       </c>
     </row>
@@ -10868,7 +10885,7 @@
         <v>68</v>
       </c>
       <c r="N610" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P610" t="s">
         <v>213</v>
@@ -10883,14 +10900,14 @@
         <v>68</v>
       </c>
       <c r="N611" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P611" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q611" s="24">
         <f t="shared" si="30"/>
-        <v>86.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="612" spans="1:17" x14ac:dyDescent="0.25">
@@ -10898,14 +10915,14 @@
         <v>68</v>
       </c>
       <c r="N612" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P612" t="s">
         <v>214</v>
       </c>
       <c r="Q612" s="24">
         <f t="shared" si="30"/>
-        <v>46.7</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="613" spans="1:17" x14ac:dyDescent="0.25">
@@ -10913,14 +10930,14 @@
         <v>68</v>
       </c>
       <c r="N613" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P613" t="s">
         <v>214</v>
       </c>
       <c r="Q613" s="24">
         <f t="shared" si="30"/>
-        <v>6.7</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="614" spans="1:17" x14ac:dyDescent="0.25">
@@ -10928,48 +10945,49 @@
         <v>68</v>
       </c>
       <c r="N614" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P614" t="s">
         <v>214</v>
       </c>
       <c r="Q614" s="24">
         <f t="shared" si="30"/>
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="615" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A615" t="s">
+        <v>68</v>
+      </c>
+      <c r="N615" t="s">
+        <v>283</v>
+      </c>
+      <c r="P615" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q615" s="24">
+        <f t="shared" si="30"/>
         <v>-26.7</v>
       </c>
     </row>
-    <row r="616" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A616" s="21" t="s">
+    <row r="617" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A617" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="B616" s="21"/>
-    </row>
-    <row r="617" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A617" t="s">
-        <v>40</v>
-      </c>
-      <c r="N617" t="s">
-        <v>198</v>
-      </c>
-      <c r="P617" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q617">
-        <v>6.9</v>
-      </c>
+      <c r="B617" s="21"/>
     </row>
     <row r="618" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>40</v>
       </c>
       <c r="N618" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P618" t="s">
         <v>213</v>
       </c>
       <c r="Q618">
-        <v>9.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="619" spans="1:17" x14ac:dyDescent="0.25">
@@ -10977,13 +10995,13 @@
         <v>40</v>
       </c>
       <c r="N619" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P619" t="s">
         <v>213</v>
       </c>
       <c r="Q619">
-        <v>10</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="620" spans="1:17" x14ac:dyDescent="0.25">
@@ -10991,7 +11009,7 @@
         <v>40</v>
       </c>
       <c r="N620" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P620" t="s">
         <v>213</v>
@@ -11005,13 +11023,13 @@
         <v>40</v>
       </c>
       <c r="N621" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P621" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q621">
-        <v>68.400000000000006</v>
+        <v>10</v>
       </c>
     </row>
     <row r="622" spans="1:17" x14ac:dyDescent="0.25">
@@ -11019,13 +11037,13 @@
         <v>40</v>
       </c>
       <c r="N622" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P622" t="s">
         <v>214</v>
       </c>
       <c r="Q622">
-        <v>22.4</v>
+        <v>68.400000000000006</v>
       </c>
     </row>
     <row r="623" spans="1:17" x14ac:dyDescent="0.25">
@@ -11033,13 +11051,13 @@
         <v>40</v>
       </c>
       <c r="N623" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P623" t="s">
         <v>214</v>
       </c>
       <c r="Q623">
-        <v>-20</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="624" spans="1:17" x14ac:dyDescent="0.25">
@@ -11047,41 +11065,41 @@
         <v>40</v>
       </c>
       <c r="N624" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P624" t="s">
         <v>214</v>
       </c>
       <c r="Q624">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="625" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A625" t="s">
+        <v>40</v>
+      </c>
+      <c r="N625" t="s">
+        <v>283</v>
+      </c>
+      <c r="P625" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q625">
         <v>-50</v>
       </c>
     </row>
-    <row r="626" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A626" s="21" t="s">
+    <row r="627" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A627" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="B626" s="21"/>
-    </row>
-    <row r="627" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A627" t="s">
-        <v>34</v>
-      </c>
-      <c r="N627" t="s">
-        <v>198</v>
-      </c>
-      <c r="P627" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q627">
-        <v>4</v>
-      </c>
+      <c r="B627" s="21"/>
     </row>
     <row r="628" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>34</v>
       </c>
       <c r="N628" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P628" t="s">
         <v>213</v>
@@ -11095,7 +11113,7 @@
         <v>34</v>
       </c>
       <c r="N629" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P629" t="s">
         <v>213</v>
@@ -11109,7 +11127,7 @@
         <v>34</v>
       </c>
       <c r="N630" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P630" t="s">
         <v>213</v>
@@ -11123,13 +11141,13 @@
         <v>34</v>
       </c>
       <c r="N631" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P631" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q631">
-        <v>140</v>
+        <v>4</v>
       </c>
     </row>
     <row r="632" spans="1:17" x14ac:dyDescent="0.25">
@@ -11137,13 +11155,13 @@
         <v>34</v>
       </c>
       <c r="N632" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P632" t="s">
         <v>214</v>
       </c>
       <c r="Q632">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="633" spans="1:17" x14ac:dyDescent="0.25">
@@ -11151,13 +11169,13 @@
         <v>34</v>
       </c>
       <c r="N633" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P633" t="s">
         <v>214</v>
       </c>
       <c r="Q633">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="634" spans="1:17" x14ac:dyDescent="0.25">
@@ -11165,28 +11183,27 @@
         <v>34</v>
       </c>
       <c r="N634" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P634" t="s">
         <v>214</v>
       </c>
       <c r="Q634">
-        <v>-10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="635" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N635" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P635" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q635" s="20">
-        <f t="shared" ref="Q635:Q642" si="31">Q627</f>
-        <v>4</v>
+        <v>214</v>
+      </c>
+      <c r="Q635">
+        <v>-10</v>
       </c>
     </row>
     <row r="636" spans="1:17" x14ac:dyDescent="0.25">
@@ -11194,13 +11211,13 @@
         <v>35</v>
       </c>
       <c r="N636" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P636" t="s">
         <v>213</v>
       </c>
       <c r="Q636" s="20">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="Q636:Q643" si="31">Q628</f>
         <v>4</v>
       </c>
     </row>
@@ -11209,7 +11226,7 @@
         <v>35</v>
       </c>
       <c r="N637" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P637" t="s">
         <v>213</v>
@@ -11224,7 +11241,7 @@
         <v>35</v>
       </c>
       <c r="N638" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P638" t="s">
         <v>213</v>
@@ -11239,14 +11256,14 @@
         <v>35</v>
       </c>
       <c r="N639" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P639" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q639" s="20">
         <f t="shared" si="31"/>
-        <v>140</v>
+        <v>4</v>
       </c>
     </row>
     <row r="640" spans="1:17" x14ac:dyDescent="0.25">
@@ -11254,14 +11271,14 @@
         <v>35</v>
       </c>
       <c r="N640" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P640" t="s">
         <v>214</v>
       </c>
       <c r="Q640" s="20">
         <f t="shared" si="31"/>
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="641" spans="1:19" x14ac:dyDescent="0.25">
@@ -11269,14 +11286,14 @@
         <v>35</v>
       </c>
       <c r="N641" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P641" t="s">
         <v>214</v>
       </c>
       <c r="Q641" s="20">
         <f t="shared" si="31"/>
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="642" spans="1:19" x14ac:dyDescent="0.25">
@@ -11284,48 +11301,49 @@
         <v>35</v>
       </c>
       <c r="N642" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P642" t="s">
         <v>214</v>
       </c>
       <c r="Q642" s="20">
         <f t="shared" si="31"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="643" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A643" t="s">
+        <v>35</v>
+      </c>
+      <c r="N643" t="s">
+        <v>283</v>
+      </c>
+      <c r="P643" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q643" s="20">
+        <f t="shared" si="31"/>
         <v>-10</v>
       </c>
     </row>
-    <row r="644" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A644" s="21" t="s">
+    <row r="645" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A645" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="B644" s="21"/>
-    </row>
-    <row r="645" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A645" t="s">
-        <v>28</v>
-      </c>
-      <c r="N645" t="s">
-        <v>198</v>
-      </c>
-      <c r="P645" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q645">
-        <v>50</v>
-      </c>
+      <c r="B645" s="21"/>
     </row>
     <row r="646" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>28</v>
       </c>
       <c r="N646" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P646" t="s">
         <v>214</v>
       </c>
       <c r="Q646">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="647" spans="1:19" x14ac:dyDescent="0.25">
@@ -11333,31 +11351,27 @@
         <v>28</v>
       </c>
       <c r="N647" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P647" t="s">
         <v>214</v>
       </c>
       <c r="Q647">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="648" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A648" t="s">
+        <v>28</v>
+      </c>
+      <c r="N648" t="s">
+        <v>200</v>
+      </c>
+      <c r="P648" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q648">
         <v>20</v>
-      </c>
-    </row>
-    <row r="648" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A648" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="N648" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="P648" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q648" s="20">
-        <f>Q645</f>
-        <v>50</v>
-      </c>
-      <c r="S648" s="4" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="649" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11365,14 +11379,17 @@
         <v>268</v>
       </c>
       <c r="N649" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P649" s="4" t="s">
         <v>214</v>
       </c>
       <c r="Q649" s="20">
-        <f t="shared" ref="Q649:Q650" si="32">Q646</f>
-        <v>40</v>
+        <f>Q646</f>
+        <v>50</v>
+      </c>
+      <c r="S649" s="4" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="650" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11380,29 +11397,29 @@
         <v>268</v>
       </c>
       <c r="N650" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P650" s="4" t="s">
         <v>214</v>
       </c>
       <c r="Q650" s="20">
+        <f t="shared" ref="Q650:Q651" si="32">Q647</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="651" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A651" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="N651" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="P651" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q651" s="20">
         <f t="shared" si="32"/>
         <v>20</v>
-      </c>
-    </row>
-    <row r="651" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A651" t="s">
-        <v>30</v>
-      </c>
-      <c r="N651" t="s">
-        <v>198</v>
-      </c>
-      <c r="P651" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q651" s="20">
-        <f>Q645</f>
-        <v>50</v>
       </c>
     </row>
     <row r="652" spans="1:19" x14ac:dyDescent="0.25">
@@ -11410,14 +11427,14 @@
         <v>30</v>
       </c>
       <c r="N652" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P652" t="s">
         <v>214</v>
       </c>
       <c r="Q652" s="20">
-        <f t="shared" ref="Q652:Q653" si="33">Q646</f>
-        <v>40</v>
+        <f>Q646</f>
+        <v>50</v>
       </c>
     </row>
     <row r="653" spans="1:19" x14ac:dyDescent="0.25">
@@ -11425,28 +11442,29 @@
         <v>30</v>
       </c>
       <c r="N653" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P653" t="s">
         <v>214</v>
       </c>
       <c r="Q653" s="20">
+        <f t="shared" ref="Q653:Q654" si="33">Q647</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="654" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A654" t="s">
+        <v>30</v>
+      </c>
+      <c r="N654" t="s">
+        <v>200</v>
+      </c>
+      <c r="P654" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q654" s="20">
         <f t="shared" si="33"/>
         <v>20</v>
-      </c>
-    </row>
-    <row r="654" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A654" t="s">
-        <v>36</v>
-      </c>
-      <c r="N654" t="s">
-        <v>198</v>
-      </c>
-      <c r="P654" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q654">
-        <v>120</v>
       </c>
     </row>
     <row r="655" spans="1:19" x14ac:dyDescent="0.25">
@@ -11454,13 +11472,13 @@
         <v>36</v>
       </c>
       <c r="N655" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P655" t="s">
         <v>214</v>
       </c>
       <c r="Q655">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="656" spans="1:19" x14ac:dyDescent="0.25">
@@ -11468,13 +11486,13 @@
         <v>36</v>
       </c>
       <c r="N656" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P656" t="s">
         <v>214</v>
       </c>
       <c r="Q656">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="657" spans="1:20" x14ac:dyDescent="0.25">
@@ -11482,27 +11500,27 @@
         <v>36</v>
       </c>
       <c r="N657" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="P657" t="s">
         <v>214</v>
       </c>
       <c r="Q657">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="658" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N658" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P658" t="s">
         <v>214</v>
       </c>
       <c r="Q658">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="659" spans="1:20" x14ac:dyDescent="0.25">
@@ -11510,34 +11528,27 @@
         <v>39</v>
       </c>
       <c r="N659" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P659" t="s">
         <v>214</v>
       </c>
       <c r="Q659">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="660" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A660" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B660" s="6"/>
+      <c r="A660" t="s">
+        <v>39</v>
+      </c>
       <c r="N660" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P660" t="s">
         <v>214</v>
       </c>
       <c r="Q660">
-        <v>155</v>
-      </c>
-      <c r="S660" t="s">
-        <v>289</v>
-      </c>
-      <c r="T660" t="s">
-        <v>288</v>
+        <v>20</v>
       </c>
     </row>
     <row r="661" spans="1:20" x14ac:dyDescent="0.25">
@@ -11546,13 +11557,19 @@
       </c>
       <c r="B661" s="6"/>
       <c r="N661" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P661" t="s">
         <v>214</v>
       </c>
       <c r="Q661">
         <v>155</v>
+      </c>
+      <c r="S661" t="s">
+        <v>289</v>
+      </c>
+      <c r="T661" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="662" spans="1:20" x14ac:dyDescent="0.25">
@@ -11561,7 +11578,7 @@
       </c>
       <c r="B662" s="6"/>
       <c r="N662" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P662" t="s">
         <v>214</v>
@@ -11570,48 +11587,47 @@
         <v>155</v>
       </c>
     </row>
-    <row r="664" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A664" s="21" t="s">
+    <row r="663" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A663" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B663" s="6"/>
+      <c r="N663" t="s">
+        <v>200</v>
+      </c>
+      <c r="P663" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q663">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="665" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A665" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="B664" s="21"/>
-    </row>
-    <row r="665" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A665" t="s">
-        <v>46</v>
-      </c>
-      <c r="P665" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q665">
-        <v>3.4</v>
-      </c>
+      <c r="B665" s="21"/>
     </row>
     <row r="666" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>46</v>
       </c>
       <c r="P666" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q666">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="667" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>46</v>
+      </c>
+      <c r="P667" t="s">
         <v>214</v>
       </c>
-      <c r="Q666">
+      <c r="Q667">
         <v>62</v>
-      </c>
-    </row>
-    <row r="667" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A667" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B667" s="6"/>
-      <c r="P667" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q667" s="20">
-        <f>Q665</f>
-        <v>3.4</v>
-      </c>
-      <c r="S667" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="668" spans="1:20" x14ac:dyDescent="0.25">
@@ -11620,22 +11636,27 @@
       </c>
       <c r="B668" s="6"/>
       <c r="P668" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q668" s="20">
         <f>Q666</f>
+        <v>3.4</v>
+      </c>
+      <c r="S668" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="669" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A669" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B669" s="6"/>
+      <c r="P669" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q669" s="20">
+        <f>Q667</f>
         <v>62</v>
-      </c>
-    </row>
-    <row r="669" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A669" t="s">
-        <v>45</v>
-      </c>
-      <c r="P669" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q669">
-        <v>0.31</v>
       </c>
     </row>
     <row r="670" spans="1:20" x14ac:dyDescent="0.25">
@@ -11643,24 +11664,21 @@
         <v>45</v>
       </c>
       <c r="P670" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q670">
-        <v>129</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="671" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P671" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q671">
-        <v>0.62</v>
-      </c>
-      <c r="S671" t="s">
-        <v>211</v>
+        <v>129</v>
       </c>
     </row>
     <row r="672" spans="1:20" x14ac:dyDescent="0.25">
@@ -11668,26 +11686,24 @@
         <v>48</v>
       </c>
       <c r="P672" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q672">
+        <v>0.62</v>
+      </c>
+      <c r="S672" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="673" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>48</v>
+      </c>
+      <c r="P673" t="s">
         <v>214</v>
       </c>
-      <c r="Q672">
+      <c r="Q673">
         <v>98</v>
-      </c>
-    </row>
-    <row r="673" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A673" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B673" s="6"/>
-      <c r="P673" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q673" s="20">
-        <f>Q671</f>
-        <v>0.62</v>
-      </c>
-      <c r="S673" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="674" spans="1:19" x14ac:dyDescent="0.25">
@@ -11696,26 +11712,27 @@
       </c>
       <c r="B674" s="6"/>
       <c r="P674" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q674" s="20">
         <f>Q672</f>
-        <v>98</v>
+        <v>0.62</v>
+      </c>
+      <c r="S674" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="675" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A675" s="4" t="s">
-        <v>53</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B675" s="6"/>
       <c r="P675" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q675" s="20">
         <f>Q673</f>
-        <v>0.62</v>
-      </c>
-      <c r="S675" t="s">
-        <v>241</v>
+        <v>98</v>
       </c>
     </row>
     <row r="676" spans="1:19" x14ac:dyDescent="0.25">
@@ -11723,22 +11740,26 @@
         <v>53</v>
       </c>
       <c r="P676" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q676" s="20">
         <f>Q674</f>
+        <v>0.62</v>
+      </c>
+      <c r="S676" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="677" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A677" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P677" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q677" s="20">
+        <f>Q675</f>
         <v>98</v>
-      </c>
-    </row>
-    <row r="677" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A677" t="s">
-        <v>49</v>
-      </c>
-      <c r="P677" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q677">
-        <v>2</v>
       </c>
     </row>
     <row r="678" spans="1:19" x14ac:dyDescent="0.25">
@@ -11746,18 +11767,21 @@
         <v>49</v>
       </c>
       <c r="P678" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q678">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="679" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>49</v>
+      </c>
+      <c r="P679" t="s">
         <v>214</v>
       </c>
-      <c r="Q678">
+      <c r="Q679">
         <v>120</v>
-      </c>
-    </row>
-    <row r="679" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A679" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="P679" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="680" spans="1:19" x14ac:dyDescent="0.25">
@@ -11765,19 +11789,15 @@
         <v>50</v>
       </c>
       <c r="P680" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="681" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A681" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="P681" t="s">
         <v>214</v>
-      </c>
-    </row>
-    <row r="681" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A681" t="s">
-        <v>51</v>
-      </c>
-      <c r="P681" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q681" s="20">
-        <f>Q679</f>
-        <v>0</v>
       </c>
     </row>
     <row r="682" spans="1:19" x14ac:dyDescent="0.25">
@@ -11785,30 +11805,28 @@
         <v>51</v>
       </c>
       <c r="P682" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q682" s="20">
         <f>Q680</f>
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A684" t="s">
-        <v>67</v>
-      </c>
-      <c r="P684" t="s">
+    <row r="683" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>51</v>
+      </c>
+      <c r="P683" t="s">
         <v>214</v>
       </c>
-      <c r="Q684">
+      <c r="Q683" s="20">
+        <f>Q681</f>
         <v>0</v>
-      </c>
-      <c r="S684" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="685" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P685" t="s">
         <v>214</v>
@@ -11816,10 +11834,13 @@
       <c r="Q685">
         <v>0</v>
       </c>
+      <c r="S685" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="686" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P686" t="s">
         <v>214</v>
@@ -11830,7 +11851,7 @@
     </row>
     <row r="687" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="P687" t="s">
         <v>214</v>
@@ -11841,7 +11862,7 @@
     </row>
     <row r="688" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P688" t="s">
         <v>214</v>
@@ -11850,104 +11871,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A690" s="6" t="s">
+    <row r="689" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>44</v>
+      </c>
+      <c r="P689" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q689">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A691" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B690" s="6"/>
-    </row>
-    <row r="691" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A691" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="B691" s="6"/>
-      <c r="P691" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q691">
-        <v>20</v>
-      </c>
-      <c r="T691" t="s">
-        <v>287</v>
-      </c>
     </row>
     <row r="692" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A692" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B692" s="6"/>
       <c r="P692" t="s">
         <v>214</v>
       </c>
       <c r="Q692">
+        <v>20</v>
+      </c>
+      <c r="T692" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="693" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A693" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B693" s="6"/>
+      <c r="P693" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q693">
         <v>22.5</v>
       </c>
-      <c r="S692" t="s">
+      <c r="S693" t="s">
         <v>256</v>
       </c>
-      <c r="T692" t="s">
+      <c r="T693" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="693" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A693" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B693" s="6"/>
     </row>
     <row r="694" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A694" s="6" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B694" s="6"/>
     </row>
     <row r="695" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A695" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B695" s="6"/>
+    </row>
+    <row r="696" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A696" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B695" s="6"/>
-    </row>
-    <row r="696" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A696" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="B696" s="6"/>
-      <c r="P696" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q696">
-        <v>105</v>
-      </c>
-      <c r="T696" s="25" t="s">
-        <v>286</v>
-      </c>
     </row>
     <row r="697" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A697" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B697" s="6"/>
       <c r="P697" t="s">
         <v>214</v>
       </c>
-      <c r="Q697" s="24">
-        <f>Q696</f>
+      <c r="Q697">
         <v>105</v>
       </c>
-      <c r="S697" t="s">
-        <v>285</v>
+      <c r="T697" s="25" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="698" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A698" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B698" s="6"/>
       <c r="P698" t="s">
         <v>214</v>
       </c>
       <c r="Q698" s="24">
-        <f>Q696</f>
+        <f>Q697</f>
         <v>105</v>
       </c>
       <c r="S698" t="s">
@@ -11955,34 +11971,35 @@
       </c>
     </row>
     <row r="699" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A699" s="6"/>
+      <c r="A699" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="B699" s="6"/>
+      <c r="P699" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q699" s="24">
+        <f>Q697</f>
+        <v>105</v>
+      </c>
+      <c r="S699" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="700" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A700" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="A700" s="6"/>
       <c r="B700" s="6"/>
-      <c r="P700" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q700">
-        <v>5.6</v>
-      </c>
-      <c r="T700" t="s">
-        <v>308</v>
-      </c>
     </row>
     <row r="701" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A701" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B701" s="6"/>
       <c r="P701" t="s">
         <v>213</v>
       </c>
-      <c r="Q701" s="26">
-        <v>3</v>
+      <c r="Q701">
+        <v>5.6</v>
       </c>
       <c r="T701" t="s">
         <v>308</v>
@@ -11990,268 +12007,254 @@
     </row>
     <row r="702" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A702" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B702" s="6"/>
       <c r="P702" t="s">
         <v>213</v>
       </c>
-      <c r="Q702" s="24">
-        <f>AVERAGE(Q700:Q701)</f>
-        <v>4.3</v>
-      </c>
-      <c r="S702" s="6" t="s">
-        <v>307</v>
+      <c r="Q702" s="26">
+        <v>3</v>
+      </c>
+      <c r="T702" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="703" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A703" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B703" s="6"/>
       <c r="P703" t="s">
         <v>213</v>
       </c>
       <c r="Q703" s="24">
-        <f>AVERAGE(Q700:Q701)</f>
+        <f>AVERAGE(Q701:Q702)</f>
         <v>4.3</v>
+      </c>
+      <c r="S703" s="6" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="704" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A704" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B704" s="6"/>
       <c r="P704" t="s">
         <v>213</v>
       </c>
       <c r="Q704" s="24">
-        <f>AVERAGE(Q700:Q701)</f>
+        <f>AVERAGE(Q701:Q702)</f>
         <v>4.3</v>
       </c>
     </row>
     <row r="705" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A705" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B705" s="6"/>
       <c r="P705" t="s">
         <v>213</v>
       </c>
       <c r="Q705" s="24">
-        <f>AVERAGE(Q700:Q701)</f>
+        <f>AVERAGE(Q701:Q702)</f>
         <v>4.3</v>
       </c>
     </row>
     <row r="706" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A706" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B706" s="6"/>
       <c r="P706" t="s">
         <v>213</v>
       </c>
       <c r="Q706" s="24">
-        <f>AVERAGE(Q700:Q701)</f>
+        <f>AVERAGE(Q701:Q702)</f>
         <v>4.3</v>
       </c>
     </row>
     <row r="707" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A707" s="6"/>
+      <c r="A707" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="B707" s="6"/>
+      <c r="P707" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q707" s="24">
+        <f>AVERAGE(Q701:Q702)</f>
+        <v>4.3</v>
+      </c>
     </row>
     <row r="708" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A708" s="2" t="s">
+      <c r="A708" s="6"/>
+      <c r="B708" s="6"/>
+    </row>
+    <row r="709" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A709" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B708" s="2"/>
-      <c r="C708" s="2"/>
-      <c r="D708" s="2"/>
-      <c r="E708" s="2"/>
-      <c r="F708" s="2"/>
-      <c r="G708" s="2"/>
-      <c r="H708" s="2"/>
-      <c r="I708" s="2"/>
-      <c r="J708" s="2"/>
-      <c r="K708" s="2"/>
-      <c r="L708" s="2"/>
-      <c r="M708" s="2"/>
-      <c r="N708" s="2"/>
-      <c r="O708" s="2"/>
-      <c r="P708" s="2"/>
-      <c r="Q708" s="2"/>
-      <c r="R708" s="2"/>
-      <c r="S708" s="3"/>
-      <c r="T708" s="3"/>
-    </row>
-    <row r="710" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="P710" s="5" t="s">
+      <c r="B709" s="2"/>
+      <c r="C709" s="2"/>
+      <c r="D709" s="2"/>
+      <c r="E709" s="2"/>
+      <c r="F709" s="2"/>
+      <c r="G709" s="2"/>
+      <c r="H709" s="2"/>
+      <c r="I709" s="2"/>
+      <c r="J709" s="2"/>
+      <c r="K709" s="2"/>
+      <c r="L709" s="2"/>
+      <c r="M709" s="2"/>
+      <c r="N709" s="2"/>
+      <c r="O709" s="2"/>
+      <c r="P709" s="2"/>
+      <c r="Q709" s="2"/>
+      <c r="R709" s="2"/>
+      <c r="S709" s="3"/>
+      <c r="T709" s="3"/>
+    </row>
+    <row r="711" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P711" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="Q710" s="23">
-        <v>1</v>
-      </c>
-      <c r="R710" s="5"/>
-      <c r="S710" s="5" t="s">
+      <c r="Q711" s="23">
+        <v>1.2</v>
+      </c>
+      <c r="R711" s="5"/>
+      <c r="S711" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="713" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A713" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B713" s="2"/>
+      <c r="C713" s="2"/>
+      <c r="D713" s="2"/>
+      <c r="E713" s="2"/>
+      <c r="F713" s="2"/>
+      <c r="G713" s="2"/>
+      <c r="H713" s="2"/>
+      <c r="I713" s="2"/>
+      <c r="J713" s="2"/>
+      <c r="K713" s="2"/>
+      <c r="L713" s="2"/>
+      <c r="M713" s="2"/>
+      <c r="N713" s="2"/>
+      <c r="O713" s="2"/>
+      <c r="P713" s="2"/>
+      <c r="Q713" s="2"/>
+      <c r="R713" s="2"/>
+      <c r="S713" s="2"/>
+      <c r="T713" s="2"/>
+    </row>
+    <row r="714" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O714" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="P714" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q714" s="13">
+        <v>0</v>
+      </c>
+      <c r="R714" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="S714" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="712" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A712" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B712" s="2"/>
-      <c r="C712" s="2"/>
-      <c r="D712" s="2"/>
-      <c r="E712" s="2"/>
-      <c r="F712" s="2"/>
-      <c r="G712" s="2"/>
-      <c r="H712" s="2"/>
-      <c r="I712" s="2"/>
-      <c r="J712" s="2"/>
-      <c r="K712" s="2"/>
-      <c r="L712" s="2"/>
-      <c r="M712" s="2"/>
-      <c r="N712" s="2"/>
-      <c r="O712" s="2"/>
-      <c r="P712" s="2"/>
-      <c r="Q712" s="2"/>
-      <c r="R712" s="2"/>
-      <c r="S712" s="2"/>
-      <c r="T712" s="2"/>
-    </row>
-    <row r="713" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="O713" s="5" t="s">
+    <row r="715" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A715" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B715" s="1"/>
+      <c r="C715" s="1"/>
+      <c r="O715" s="5"/>
+      <c r="P715" s="5"/>
+      <c r="Q715" s="13"/>
+      <c r="R715" s="5"/>
+      <c r="S715" s="5"/>
+    </row>
+    <row r="716" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="G716" t="s">
+        <v>114</v>
+      </c>
+      <c r="O716" t="s">
         <v>120</v>
       </c>
-      <c r="P713" s="5" t="s">
+      <c r="P716" t="s">
         <v>148</v>
       </c>
-      <c r="Q713" s="13">
-        <v>0</v>
-      </c>
-      <c r="R713" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="S713" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="714" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A714" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B714" s="1"/>
-      <c r="C714" s="1"/>
-      <c r="O714" s="5"/>
-      <c r="P714" s="5"/>
-      <c r="Q714" s="13"/>
-      <c r="R714" s="5"/>
-      <c r="S714" s="5"/>
-    </row>
-    <row r="715" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="G715" t="s">
-        <v>114</v>
-      </c>
-      <c r="O715" t="s">
-        <v>120</v>
-      </c>
-      <c r="P715" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q715" s="11">
+      <c r="Q716" s="11">
         <f>8/1000*(14/(1*14+3*2))*100</f>
         <v>0.55999999999999994</v>
       </c>
-      <c r="R715" t="s">
+      <c r="R716" t="s">
         <v>121</v>
       </c>
-      <c r="S715" s="4" t="s">
+      <c r="S716" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="T715" t="s">
+      <c r="T716" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="716" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="G716" t="s">
+    <row r="717" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="G717" t="s">
         <v>115</v>
       </c>
-      <c r="O716" t="s">
+      <c r="O717" t="s">
         <v>120</v>
       </c>
-      <c r="P716" t="s">
+      <c r="P717" t="s">
         <v>148</v>
       </c>
-      <c r="Q716" s="11">
+      <c r="Q717" s="11">
         <f>15/1000*(14/(1*14+3*2))*100</f>
         <v>1.0499999999999998</v>
       </c>
-      <c r="R716" t="s">
+      <c r="R717" t="s">
         <v>121</v>
       </c>
-      <c r="T716" t="s">
+      <c r="T717" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="717" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="G717" t="s">
+    <row r="718" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="G718" t="s">
         <v>113</v>
       </c>
-      <c r="O717" t="s">
+      <c r="O718" t="s">
         <v>120</v>
       </c>
-      <c r="P717" t="s">
+      <c r="P718" t="s">
         <v>148</v>
       </c>
-      <c r="Q717" s="11">
+      <c r="Q718" s="11">
         <f>50/1000*(14/(1*14+3*2))*100</f>
         <v>3.4999999999999996</v>
       </c>
-      <c r="R717" t="s">
+      <c r="R718" t="s">
         <v>121</v>
       </c>
-      <c r="T717" t="s">
+      <c r="T718" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="718" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A718" s="1" t="s">
+    <row r="719" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A719" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B718" s="1"/>
-      <c r="C718" s="1"/>
-      <c r="D718" s="6" t="s">
+      <c r="B719" s="1"/>
+      <c r="C719" s="1"/>
+      <c r="D719" s="6" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="719" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I719" t="s">
-        <v>127</v>
-      </c>
-      <c r="J719" t="s">
-        <v>128</v>
-      </c>
-      <c r="K719" t="s">
-        <v>129</v>
-      </c>
-      <c r="L719" t="s">
-        <v>139</v>
-      </c>
-      <c r="O719" t="s">
-        <v>120</v>
-      </c>
-      <c r="P719" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q719">
-        <v>33</v>
-      </c>
-      <c r="R719" t="s">
-        <v>121</v>
-      </c>
-      <c r="T719" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="720" spans="1:20" x14ac:dyDescent="0.25">
@@ -12265,7 +12268,7 @@
         <v>129</v>
       </c>
       <c r="L720" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O720" t="s">
         <v>120</v>
@@ -12274,7 +12277,7 @@
         <v>148</v>
       </c>
       <c r="Q720">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R720" t="s">
         <v>121</v>
@@ -12294,7 +12297,7 @@
         <v>129</v>
       </c>
       <c r="L721" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O721" t="s">
         <v>120</v>
@@ -12303,7 +12306,7 @@
         <v>148</v>
       </c>
       <c r="Q721">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R721" t="s">
         <v>121</v>
@@ -12323,7 +12326,7 @@
         <v>129</v>
       </c>
       <c r="L722" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="O722" t="s">
         <v>120</v>
@@ -12332,7 +12335,7 @@
         <v>148</v>
       </c>
       <c r="Q722">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="R722" t="s">
         <v>121</v>
@@ -12346,13 +12349,13 @@
         <v>127</v>
       </c>
       <c r="J723" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K723" t="s">
         <v>129</v>
       </c>
       <c r="L723" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="O723" t="s">
         <v>120</v>
@@ -12361,7 +12364,7 @@
         <v>148</v>
       </c>
       <c r="Q723">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R723" t="s">
         <v>121</v>
@@ -12381,7 +12384,7 @@
         <v>129</v>
       </c>
       <c r="L724" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O724" t="s">
         <v>120</v>
@@ -12390,7 +12393,7 @@
         <v>148</v>
       </c>
       <c r="Q724">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="R724" t="s">
         <v>121</v>
@@ -12410,7 +12413,7 @@
         <v>129</v>
       </c>
       <c r="L725" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O725" t="s">
         <v>120</v>
@@ -12419,7 +12422,7 @@
         <v>148</v>
       </c>
       <c r="Q725">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R725" t="s">
         <v>121</v>
@@ -12439,7 +12442,7 @@
         <v>129</v>
       </c>
       <c r="L726" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="O726" t="s">
         <v>120</v>
@@ -12448,7 +12451,7 @@
         <v>148</v>
       </c>
       <c r="Q726">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="R726" t="s">
         <v>121</v>
@@ -12461,11 +12464,14 @@
       <c r="I727" t="s">
         <v>127</v>
       </c>
+      <c r="J727" t="s">
+        <v>130</v>
+      </c>
       <c r="K727" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L727" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="O727" t="s">
         <v>120</v>
@@ -12491,7 +12497,7 @@
         <v>131</v>
       </c>
       <c r="L728" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O728" t="s">
         <v>120</v>
@@ -12500,7 +12506,7 @@
         <v>148</v>
       </c>
       <c r="Q728">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="R728" t="s">
         <v>121</v>
@@ -12517,7 +12523,7 @@
         <v>131</v>
       </c>
       <c r="L729" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O729" t="s">
         <v>120</v>
@@ -12526,7 +12532,7 @@
         <v>148</v>
       </c>
       <c r="Q729">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="R729" t="s">
         <v>121</v>
@@ -12543,7 +12549,7 @@
         <v>131</v>
       </c>
       <c r="L730" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="O730" t="s">
         <v>120</v>
@@ -12552,7 +12558,7 @@
         <v>148</v>
       </c>
       <c r="Q730">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="R730" t="s">
         <v>121</v>
@@ -12566,10 +12572,10 @@
         <v>127</v>
       </c>
       <c r="K731" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L731" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="O731" t="s">
         <v>120</v>
@@ -12578,7 +12584,7 @@
         <v>148</v>
       </c>
       <c r="Q731">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R731" t="s">
         <v>121</v>
@@ -12595,7 +12601,7 @@
         <v>132</v>
       </c>
       <c r="L732" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O732" t="s">
         <v>120</v>
@@ -12604,7 +12610,7 @@
         <v>148</v>
       </c>
       <c r="Q732">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R732" t="s">
         <v>121</v>
@@ -12621,7 +12627,7 @@
         <v>132</v>
       </c>
       <c r="L733" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O733" t="s">
         <v>120</v>
@@ -12630,7 +12636,7 @@
         <v>148</v>
       </c>
       <c r="Q733">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="R733" t="s">
         <v>121</v>
@@ -12647,7 +12653,7 @@
         <v>132</v>
       </c>
       <c r="L734" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="O734" t="s">
         <v>120</v>
@@ -12656,7 +12662,7 @@
         <v>148</v>
       </c>
       <c r="Q734">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="R734" t="s">
         <v>121</v>
@@ -12669,8 +12675,11 @@
       <c r="I735" t="s">
         <v>127</v>
       </c>
+      <c r="K735" t="s">
+        <v>132</v>
+      </c>
       <c r="L735" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="O735" t="s">
         <v>120</v>
@@ -12679,13 +12688,10 @@
         <v>148</v>
       </c>
       <c r="Q735">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R735" t="s">
         <v>121</v>
-      </c>
-      <c r="S735" t="s">
-        <v>142</v>
       </c>
       <c r="T735" t="s">
         <v>155</v>
@@ -12696,7 +12702,7 @@
         <v>127</v>
       </c>
       <c r="L736" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O736" t="s">
         <v>120</v>
@@ -12705,7 +12711,7 @@
         <v>148</v>
       </c>
       <c r="Q736">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="R736" t="s">
         <v>121</v>
@@ -12722,7 +12728,7 @@
         <v>127</v>
       </c>
       <c r="L737" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O737" t="s">
         <v>120</v>
@@ -12731,7 +12737,7 @@
         <v>148</v>
       </c>
       <c r="Q737">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R737" t="s">
         <v>121</v>
@@ -12748,7 +12754,7 @@
         <v>127</v>
       </c>
       <c r="L738" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="O738" t="s">
         <v>120</v>
@@ -12757,7 +12763,7 @@
         <v>148</v>
       </c>
       <c r="Q738">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="R738" t="s">
         <v>121</v>
@@ -12774,7 +12780,7 @@
         <v>127</v>
       </c>
       <c r="L739" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="O739" t="s">
         <v>120</v>
@@ -12783,21 +12789,24 @@
         <v>148</v>
       </c>
       <c r="Q739">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="R739" t="s">
         <v>121</v>
       </c>
+      <c r="S739" t="s">
+        <v>142</v>
+      </c>
       <c r="T739" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="740" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I740" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="L740" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="O740" t="s">
         <v>120</v>
@@ -12806,13 +12815,13 @@
         <v>148</v>
       </c>
       <c r="Q740">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="R740" t="s">
         <v>121</v>
       </c>
       <c r="T740" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
     </row>
     <row r="741" spans="9:20" x14ac:dyDescent="0.25">
@@ -12820,7 +12829,7 @@
         <v>145</v>
       </c>
       <c r="L741" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O741" t="s">
         <v>120</v>
@@ -12829,7 +12838,7 @@
         <v>148</v>
       </c>
       <c r="Q741">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="R741" t="s">
         <v>121</v>
@@ -12843,7 +12852,7 @@
         <v>145</v>
       </c>
       <c r="L742" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="O742" t="s">
         <v>120</v>
@@ -12852,7 +12861,7 @@
         <v>148</v>
       </c>
       <c r="Q742">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="R742" t="s">
         <v>121</v>
@@ -12866,7 +12875,7 @@
         <v>145</v>
       </c>
       <c r="L743" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="O743" t="s">
         <v>120</v>
@@ -12875,21 +12884,21 @@
         <v>148</v>
       </c>
       <c r="Q743">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R743" t="s">
         <v>121</v>
       </c>
       <c r="T743" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="744" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I744" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="L744" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="O744" t="s">
         <v>120</v>
@@ -12898,13 +12907,13 @@
         <v>148</v>
       </c>
       <c r="Q744">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="R744" t="s">
         <v>121</v>
       </c>
       <c r="T744" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
     </row>
     <row r="745" spans="9:20" x14ac:dyDescent="0.25">
@@ -12912,7 +12921,7 @@
         <v>190</v>
       </c>
       <c r="L745" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="O745" t="s">
         <v>120</v>
@@ -12921,24 +12930,21 @@
         <v>148</v>
       </c>
       <c r="Q745">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="R745" t="s">
         <v>121</v>
       </c>
       <c r="T745" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="746" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I746" t="s">
-        <v>133</v>
-      </c>
-      <c r="K746" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="L746" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="O746" t="s">
         <v>120</v>
@@ -12947,13 +12953,13 @@
         <v>148</v>
       </c>
       <c r="Q746">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="R746" t="s">
         <v>121</v>
       </c>
       <c r="T746" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
     </row>
     <row r="747" spans="9:20" x14ac:dyDescent="0.25">
@@ -12964,7 +12970,7 @@
         <v>134</v>
       </c>
       <c r="L747" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O747" t="s">
         <v>120</v>
@@ -12973,7 +12979,7 @@
         <v>148</v>
       </c>
       <c r="Q747">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R747" t="s">
         <v>121</v>
@@ -12990,7 +12996,7 @@
         <v>134</v>
       </c>
       <c r="L748" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O748" t="s">
         <v>120</v>
@@ -12999,7 +13005,7 @@
         <v>148</v>
       </c>
       <c r="Q748">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="R748" t="s">
         <v>121</v>
@@ -13016,7 +13022,7 @@
         <v>134</v>
       </c>
       <c r="L749" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="O749" t="s">
         <v>120</v>
@@ -13025,7 +13031,7 @@
         <v>148</v>
       </c>
       <c r="Q749">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="R749" t="s">
         <v>121</v>
@@ -13039,10 +13045,10 @@
         <v>133</v>
       </c>
       <c r="K750" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L750" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="O750" t="s">
         <v>120</v>
@@ -13050,15 +13056,14 @@
       <c r="P750" t="s">
         <v>148</v>
       </c>
-      <c r="Q750" s="12">
-        <f>Q746</f>
+      <c r="Q750">
         <v>30</v>
       </c>
       <c r="R750" t="s">
         <v>121</v>
       </c>
-      <c r="S750" t="s">
-        <v>144</v>
+      <c r="T750" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="751" spans="9:20" x14ac:dyDescent="0.25">
@@ -13069,7 +13074,7 @@
         <v>137</v>
       </c>
       <c r="L751" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O751" t="s">
         <v>120</v>
@@ -13079,7 +13084,7 @@
       </c>
       <c r="Q751" s="12">
         <f>Q747</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R751" t="s">
         <v>121</v>
@@ -13096,7 +13101,7 @@
         <v>137</v>
       </c>
       <c r="L752" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O752" t="s">
         <v>120</v>
@@ -13106,7 +13111,7 @@
       </c>
       <c r="Q752" s="12">
         <f>Q748</f>
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="R752" t="s">
         <v>121</v>
@@ -13123,7 +13128,7 @@
         <v>137</v>
       </c>
       <c r="L753" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="O753" t="s">
         <v>120</v>
@@ -13133,7 +13138,7 @@
       </c>
       <c r="Q753" s="12">
         <f>Q749</f>
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="R753" t="s">
         <v>121</v>
@@ -13147,10 +13152,10 @@
         <v>133</v>
       </c>
       <c r="K754" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L754" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="O754" t="s">
         <v>120</v>
@@ -13158,14 +13163,15 @@
       <c r="P754" t="s">
         <v>148</v>
       </c>
-      <c r="Q754">
-        <v>29</v>
+      <c r="Q754" s="12">
+        <f>Q750</f>
+        <v>30</v>
       </c>
       <c r="R754" t="s">
         <v>121</v>
       </c>
-      <c r="T754" t="s">
-        <v>155</v>
+      <c r="S754" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="755" spans="9:20" x14ac:dyDescent="0.25">
@@ -13176,7 +13182,7 @@
         <v>135</v>
       </c>
       <c r="L755" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O755" t="s">
         <v>120</v>
@@ -13185,7 +13191,7 @@
         <v>148</v>
       </c>
       <c r="Q755">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="R755" t="s">
         <v>121</v>
@@ -13202,7 +13208,7 @@
         <v>135</v>
       </c>
       <c r="L756" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O756" t="s">
         <v>120</v>
@@ -13211,7 +13217,7 @@
         <v>148</v>
       </c>
       <c r="Q756">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R756" t="s">
         <v>121</v>
@@ -13228,7 +13234,7 @@
         <v>135</v>
       </c>
       <c r="L757" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="O757" t="s">
         <v>120</v>
@@ -13237,7 +13243,7 @@
         <v>148</v>
       </c>
       <c r="Q757">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="R757" t="s">
         <v>121</v>
@@ -13251,10 +13257,10 @@
         <v>133</v>
       </c>
       <c r="K758" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L758" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="O758" t="s">
         <v>120</v>
@@ -13280,7 +13286,7 @@
         <v>136</v>
       </c>
       <c r="L759" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O759" t="s">
         <v>120</v>
@@ -13289,7 +13295,7 @@
         <v>148</v>
       </c>
       <c r="Q759">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R759" t="s">
         <v>121</v>
@@ -13306,7 +13312,7 @@
         <v>136</v>
       </c>
       <c r="L760" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O760" t="s">
         <v>120</v>
@@ -13315,7 +13321,7 @@
         <v>148</v>
       </c>
       <c r="Q760">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="R760" t="s">
         <v>121</v>
@@ -13332,7 +13338,7 @@
         <v>136</v>
       </c>
       <c r="L761" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="O761" t="s">
         <v>120</v>
@@ -13341,7 +13347,7 @@
         <v>148</v>
       </c>
       <c r="Q761">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="R761" t="s">
         <v>121</v>
@@ -13354,8 +13360,11 @@
       <c r="I762" t="s">
         <v>133</v>
       </c>
+      <c r="K762" t="s">
+        <v>136</v>
+      </c>
       <c r="L762" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="O762" t="s">
         <v>120</v>
@@ -13368,9 +13377,6 @@
       </c>
       <c r="R762" t="s">
         <v>121</v>
-      </c>
-      <c r="S762" t="s">
-        <v>143</v>
       </c>
       <c r="T762" t="s">
         <v>155</v>
@@ -13381,7 +13387,7 @@
         <v>133</v>
       </c>
       <c r="L763" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O763" t="s">
         <v>120</v>
@@ -13390,7 +13396,7 @@
         <v>148</v>
       </c>
       <c r="Q763">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R763" t="s">
         <v>121</v>
@@ -13407,7 +13413,7 @@
         <v>133</v>
       </c>
       <c r="L764" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O764" t="s">
         <v>120</v>
@@ -13416,7 +13422,7 @@
         <v>148</v>
       </c>
       <c r="Q764">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="R764" t="s">
         <v>121</v>
@@ -13433,7 +13439,7 @@
         <v>133</v>
       </c>
       <c r="L765" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="O765" t="s">
         <v>120</v>
@@ -13442,7 +13448,7 @@
         <v>148</v>
       </c>
       <c r="Q765">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="R765" t="s">
         <v>121</v>
@@ -13456,10 +13462,10 @@
     </row>
     <row r="766" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I766" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="L766" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="O766" t="s">
         <v>120</v>
@@ -13472,6 +13478,9 @@
       </c>
       <c r="R766" t="s">
         <v>121</v>
+      </c>
+      <c r="S766" t="s">
+        <v>143</v>
       </c>
       <c r="T766" t="s">
         <v>155</v>
@@ -13482,7 +13491,7 @@
         <v>138</v>
       </c>
       <c r="L767" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O767" t="s">
         <v>120</v>
@@ -13491,7 +13500,7 @@
         <v>148</v>
       </c>
       <c r="Q767">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="R767" t="s">
         <v>121</v>
@@ -13505,7 +13514,7 @@
         <v>138</v>
       </c>
       <c r="L768" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O768" t="s">
         <v>120</v>
@@ -13514,7 +13523,7 @@
         <v>148</v>
       </c>
       <c r="Q768">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="R768" t="s">
         <v>121</v>
@@ -13527,11 +13536,8 @@
       <c r="I769" t="s">
         <v>138</v>
       </c>
-      <c r="K769" t="s">
-        <v>191</v>
-      </c>
       <c r="L769" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O769" t="s">
         <v>120</v>
@@ -13540,7 +13546,7 @@
         <v>148</v>
       </c>
       <c r="Q769">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="R769" t="s">
         <v>121</v>
@@ -13557,7 +13563,7 @@
         <v>191</v>
       </c>
       <c r="L770" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O770" t="s">
         <v>120</v>
@@ -13566,7 +13572,7 @@
         <v>148</v>
       </c>
       <c r="Q770">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="R770" t="s">
         <v>121</v>
@@ -13583,7 +13589,7 @@
         <v>191</v>
       </c>
       <c r="L771" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O771" t="s">
         <v>120</v>
@@ -13592,7 +13598,7 @@
         <v>148</v>
       </c>
       <c r="Q771">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="R771" t="s">
         <v>121</v>
@@ -13606,10 +13612,10 @@
         <v>138</v>
       </c>
       <c r="K772" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L772" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O772" t="s">
         <v>120</v>
@@ -13618,7 +13624,7 @@
         <v>148</v>
       </c>
       <c r="Q772">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="R772" t="s">
         <v>121</v>
@@ -13635,7 +13641,7 @@
         <v>192</v>
       </c>
       <c r="L773" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O773" t="s">
         <v>120</v>
@@ -13653,81 +13659,87 @@
         <v>155</v>
       </c>
     </row>
-    <row r="775" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A775" s="1" t="s">
+    <row r="774" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="I774" t="s">
+        <v>138</v>
+      </c>
+      <c r="K774" t="s">
+        <v>192</v>
+      </c>
+      <c r="L774" t="s">
+        <v>141</v>
+      </c>
+      <c r="O774" t="s">
+        <v>120</v>
+      </c>
+      <c r="P774" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q774">
+        <v>41</v>
+      </c>
+      <c r="R774" t="s">
+        <v>121</v>
+      </c>
+      <c r="T774" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="776" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A776" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="776" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H776" t="s">
+    <row r="777" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="H777" t="s">
         <v>188</v>
       </c>
-      <c r="O776" t="s">
+      <c r="O777" t="s">
         <v>120</v>
       </c>
-      <c r="P776" t="s">
+      <c r="P777" t="s">
         <v>148</v>
       </c>
-      <c r="Q776" s="6">
+      <c r="Q777" s="6">
         <v>30</v>
       </c>
-      <c r="R776" t="s">
+      <c r="R777" t="s">
         <v>121</v>
       </c>
-      <c r="S776" s="6" t="s">
+      <c r="S777" s="6" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="778" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A778" s="2" t="s">
+    <row r="779" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A779" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B778" s="2"/>
-      <c r="C778" s="2"/>
-      <c r="D778" s="2"/>
-      <c r="E778" s="2"/>
-      <c r="F778" s="2"/>
-      <c r="G778" s="2"/>
-      <c r="H778" s="2"/>
-      <c r="I778" s="2"/>
-      <c r="J778" s="2"/>
-      <c r="K778" s="2"/>
-      <c r="L778" s="2"/>
-      <c r="M778" s="2"/>
-      <c r="N778" s="2"/>
-      <c r="O778" s="2"/>
-      <c r="P778" s="2"/>
-      <c r="Q778" s="2"/>
-      <c r="R778" s="2"/>
-      <c r="S778" s="2"/>
-      <c r="T778" s="2"/>
-    </row>
-    <row r="780" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="O780" t="s">
-        <v>156</v>
-      </c>
-      <c r="P780" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q780">
-        <v>1</v>
-      </c>
-      <c r="R780" t="s">
-        <v>116</v>
-      </c>
-      <c r="S780" t="s">
-        <v>163</v>
-      </c>
-      <c r="T780" t="s">
-        <v>159</v>
-      </c>
+      <c r="B779" s="2"/>
+      <c r="C779" s="2"/>
+      <c r="D779" s="2"/>
+      <c r="E779" s="2"/>
+      <c r="F779" s="2"/>
+      <c r="G779" s="2"/>
+      <c r="H779" s="2"/>
+      <c r="I779" s="2"/>
+      <c r="J779" s="2"/>
+      <c r="K779" s="2"/>
+      <c r="L779" s="2"/>
+      <c r="M779" s="2"/>
+      <c r="N779" s="2"/>
+      <c r="O779" s="2"/>
+      <c r="P779" s="2"/>
+      <c r="Q779" s="2"/>
+      <c r="R779" s="2"/>
+      <c r="S779" s="2"/>
+      <c r="T779" s="2"/>
     </row>
     <row r="781" spans="1:20" x14ac:dyDescent="0.25">
       <c r="O781" t="s">
         <v>156</v>
       </c>
       <c r="P781" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q781">
         <v>1</v>
@@ -13736,19 +13748,13 @@
         <v>116</v>
       </c>
       <c r="S781" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T781" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="782" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I782" t="s">
-        <v>127</v>
-      </c>
-      <c r="L782" t="s">
-        <v>157</v>
-      </c>
       <c r="O782" t="s">
         <v>156</v>
       </c>
@@ -13756,19 +13762,22 @@
         <v>169</v>
       </c>
       <c r="Q782">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R782" t="s">
         <v>116</v>
       </c>
       <c r="S782" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="T782" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="783" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="I783" t="s">
+        <v>127</v>
+      </c>
       <c r="L783" t="s">
         <v>157</v>
       </c>
@@ -13779,24 +13788,27 @@
         <v>169</v>
       </c>
       <c r="Q783">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R783" t="s">
         <v>116</v>
       </c>
       <c r="S783" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T783" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="784" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L784" t="s">
+        <v>157</v>
+      </c>
       <c r="O784" t="s">
         <v>156</v>
       </c>
       <c r="P784" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q784">
         <v>1</v>
@@ -13805,10 +13817,10 @@
         <v>116</v>
       </c>
       <c r="S784" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="T784" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="785" spans="1:20" x14ac:dyDescent="0.25">
@@ -13816,7 +13828,7 @@
         <v>156</v>
       </c>
       <c r="P785" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q785">
         <v>1</v>
@@ -13825,76 +13837,76 @@
         <v>116</v>
       </c>
       <c r="S785" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="T785" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="787" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="O787" t="s">
+    <row r="786" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O786" t="s">
         <v>156</v>
       </c>
-      <c r="P787" t="s">
+      <c r="P786" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q786">
+        <v>1</v>
+      </c>
+      <c r="R786" t="s">
+        <v>116</v>
+      </c>
+      <c r="S786" t="s">
+        <v>162</v>
+      </c>
+      <c r="T786" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="788" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O788" t="s">
+        <v>156</v>
+      </c>
+      <c r="P788" t="s">
         <v>174</v>
       </c>
-      <c r="Q787">
+      <c r="Q788">
         <v>13</v>
       </c>
-      <c r="R787" t="s">
+      <c r="R788" t="s">
         <v>175</v>
       </c>
-      <c r="T787" t="s">
+      <c r="T788" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="789" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A789" s="2" t="s">
+    <row r="790" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A790" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B789" s="2"/>
-      <c r="C789" s="2"/>
-      <c r="D789" s="2"/>
-      <c r="E789" s="2"/>
-      <c r="F789" s="2"/>
-      <c r="G789" s="2"/>
-      <c r="H789" s="2"/>
-      <c r="I789" s="2"/>
-      <c r="J789" s="2"/>
-      <c r="K789" s="2"/>
-      <c r="L789" s="2"/>
-      <c r="M789" s="2"/>
-      <c r="N789" s="2"/>
-      <c r="O789" s="2"/>
-      <c r="P789" s="2"/>
-      <c r="Q789" s="2"/>
-      <c r="R789" s="2"/>
-      <c r="S789" s="2"/>
-      <c r="T789" s="2"/>
-    </row>
-    <row r="791" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C791" t="s">
-        <v>183</v>
-      </c>
-      <c r="O791" t="s">
-        <v>181</v>
-      </c>
-      <c r="P791" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q791">
-        <v>0.24</v>
-      </c>
-      <c r="R791" t="s">
-        <v>180</v>
-      </c>
-      <c r="T791" t="s">
-        <v>179</v>
-      </c>
+      <c r="B790" s="2"/>
+      <c r="C790" s="2"/>
+      <c r="D790" s="2"/>
+      <c r="E790" s="2"/>
+      <c r="F790" s="2"/>
+      <c r="G790" s="2"/>
+      <c r="H790" s="2"/>
+      <c r="I790" s="2"/>
+      <c r="J790" s="2"/>
+      <c r="K790" s="2"/>
+      <c r="L790" s="2"/>
+      <c r="M790" s="2"/>
+      <c r="N790" s="2"/>
+      <c r="O790" s="2"/>
+      <c r="P790" s="2"/>
+      <c r="Q790" s="2"/>
+      <c r="R790" s="2"/>
+      <c r="S790" s="2"/>
+      <c r="T790" s="2"/>
     </row>
     <row r="792" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C792" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O792" t="s">
         <v>181</v>
@@ -13914,7 +13926,7 @@
     </row>
     <row r="793" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C793" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O793" t="s">
         <v>181</v>
@@ -13923,19 +13935,39 @@
         <v>178</v>
       </c>
       <c r="Q793">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="R793" t="s">
         <v>180</v>
       </c>
-      <c r="S793" t="s">
+      <c r="T793" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="794" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C794" t="s">
+        <v>185</v>
+      </c>
+      <c r="O794" t="s">
+        <v>181</v>
+      </c>
+      <c r="P794" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q794">
+        <v>0</v>
+      </c>
+      <c r="R794" t="s">
+        <v>180</v>
+      </c>
+      <c r="S794" t="s">
         <v>186</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="T473" r:id="rId1"/>
-    <hyperlink ref="T696" r:id="rId2"/>
+    <hyperlink ref="T697" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="316">
   <si>
     <t>f_crop</t>
   </si>
@@ -965,6 +965,9 @@
   </si>
   <si>
     <t>Set to match K/ha in stat.</t>
+  </si>
+  <si>
+    <t>zero for all non-cropland</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T794"/>
+  <dimension ref="A1:T795"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="21" customWidth="1"/>
@@ -13871,62 +13874,62 @@
         <v>174</v>
       </c>
       <c r="Q788">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R788" t="s">
         <v>175</v>
       </c>
-      <c r="T788" t="s">
+      <c r="S788" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="789" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C789" t="s">
+        <v>183</v>
+      </c>
+      <c r="O789" t="s">
+        <v>156</v>
+      </c>
+      <c r="P789" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q789">
+        <v>13</v>
+      </c>
+      <c r="R789" t="s">
+        <v>175</v>
+      </c>
+      <c r="T789" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="790" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A790" s="2" t="s">
+    <row r="791" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A791" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B790" s="2"/>
-      <c r="C790" s="2"/>
-      <c r="D790" s="2"/>
-      <c r="E790" s="2"/>
-      <c r="F790" s="2"/>
-      <c r="G790" s="2"/>
-      <c r="H790" s="2"/>
-      <c r="I790" s="2"/>
-      <c r="J790" s="2"/>
-      <c r="K790" s="2"/>
-      <c r="L790" s="2"/>
-      <c r="M790" s="2"/>
-      <c r="N790" s="2"/>
-      <c r="O790" s="2"/>
-      <c r="P790" s="2"/>
-      <c r="Q790" s="2"/>
-      <c r="R790" s="2"/>
-      <c r="S790" s="2"/>
-      <c r="T790" s="2"/>
-    </row>
-    <row r="792" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C792" t="s">
-        <v>183</v>
-      </c>
-      <c r="O792" t="s">
-        <v>181</v>
-      </c>
-      <c r="P792" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q792">
-        <v>0.24</v>
-      </c>
-      <c r="R792" t="s">
-        <v>180</v>
-      </c>
-      <c r="T792" t="s">
-        <v>179</v>
-      </c>
+      <c r="B791" s="2"/>
+      <c r="C791" s="2"/>
+      <c r="D791" s="2"/>
+      <c r="E791" s="2"/>
+      <c r="F791" s="2"/>
+      <c r="G791" s="2"/>
+      <c r="H791" s="2"/>
+      <c r="I791" s="2"/>
+      <c r="J791" s="2"/>
+      <c r="K791" s="2"/>
+      <c r="L791" s="2"/>
+      <c r="M791" s="2"/>
+      <c r="N791" s="2"/>
+      <c r="O791" s="2"/>
+      <c r="P791" s="2"/>
+      <c r="Q791" s="2"/>
+      <c r="R791" s="2"/>
+      <c r="S791" s="2"/>
+      <c r="T791" s="2"/>
     </row>
     <row r="793" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C793" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O793" t="s">
         <v>181</v>
@@ -13946,7 +13949,7 @@
     </row>
     <row r="794" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C794" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O794" t="s">
         <v>181</v>
@@ -13955,12 +13958,32 @@
         <v>178</v>
       </c>
       <c r="Q794">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="R794" t="s">
         <v>180</v>
       </c>
-      <c r="S794" t="s">
+      <c r="T794" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="795" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C795" t="s">
+        <v>185</v>
+      </c>
+      <c r="O795" t="s">
+        <v>181</v>
+      </c>
+      <c r="P795" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q795">
+        <v>0</v>
+      </c>
+      <c r="R795" t="s">
+        <v>180</v>
+      </c>
+      <c r="S795" t="s">
         <v>186</v>
       </c>
     </row>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="342">
   <si>
     <t>f_crop</t>
   </si>
@@ -478,9 +478,6 @@
     <t>fallback</t>
   </si>
   <si>
-    <t>Mineral fertilisers</t>
-  </si>
-  <si>
     <t>Manure</t>
   </si>
   <si>
@@ -1037,6 +1034,18 @@
   </si>
   <si>
     <t>REKOMMENDATIONER FÖR GÖDSLING OCH KALKNING 2024, s. 109</t>
+  </si>
+  <si>
+    <t>Mineral fertilisers and lime</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>kg CO2/kg applied liming agent</t>
+  </si>
+  <si>
+    <t>liming_emissions</t>
   </si>
 </sst>
 </file>
@@ -1511,7 +1520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U824"/>
+  <dimension ref="A1:U832"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="21" customWidth="1"/>
@@ -1536,16 +1545,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>84</v>
@@ -1557,7 +1566,7 @@
         <v>146</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>122</v>
@@ -1572,10 +1581,10 @@
         <v>125</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>118</v>
@@ -1748,7 +1757,7 @@
         <v>148</v>
       </c>
       <c r="H11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q11" t="s">
         <v>145</v>
@@ -1768,13 +1777,13 @@
         <v>104</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R13" s="6">
         <v>0</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -1782,19 +1791,19 @@
         <v>148</v>
       </c>
       <c r="H14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="U14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -1802,13 +1811,13 @@
         <v>104</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="R16" s="6">
         <v>0</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -1816,16 +1825,16 @@
         <v>148</v>
       </c>
       <c r="H17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="R17" s="6">
         <v>100</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -1835,7 +1844,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1860,7 +1869,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="Q21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="R21">
         <v>66</v>
@@ -1869,15 +1878,15 @@
         <v>103</v>
       </c>
       <c r="T21" t="s">
+        <v>307</v>
+      </c>
+      <c r="U21" t="s">
         <v>308</v>
-      </c>
-      <c r="U21" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -1902,7 +1911,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -1927,7 +1936,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -1952,7 +1961,7 @@
     </row>
     <row r="26" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -1977,7 +1986,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2002,7 +2011,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -2027,7 +2036,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -3170,7 +3179,7 @@
     </row>
     <row r="103" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q103" s="4" t="s">
         <v>10</v>
@@ -3184,7 +3193,7 @@
     </row>
     <row r="104" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q104" s="4" t="s">
         <v>11</v>
@@ -3195,7 +3204,7 @@
     </row>
     <row r="105" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q105" s="4" t="s">
         <v>12</v>
@@ -3206,7 +3215,7 @@
     </row>
     <row r="106" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>90</v>
@@ -3223,7 +3232,7 @@
     </row>
     <row r="107" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>90</v>
@@ -3237,7 +3246,7 @@
     </row>
     <row r="108" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>90</v>
@@ -3251,7 +3260,7 @@
     </row>
     <row r="109" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>89</v>
@@ -3270,7 +3279,7 @@
     </row>
     <row r="110" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>89</v>
@@ -3285,7 +3294,7 @@
     </row>
     <row r="111" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>89</v>
@@ -3619,7 +3628,7 @@
     </row>
     <row r="132" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q132" s="4" t="s">
         <v>12</v>
@@ -3628,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="T132" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
@@ -3661,7 +3670,7 @@
     </row>
     <row r="135" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q135" s="4" t="s">
         <v>12</v>
@@ -3670,12 +3679,12 @@
         <v>30</v>
       </c>
       <c r="T135" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="136" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q136" s="4" t="s">
         <v>12</v>
@@ -3684,12 +3693,12 @@
         <v>30</v>
       </c>
       <c r="T136" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="137" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q137" s="4" t="s">
         <v>12</v>
@@ -3698,7 +3707,7 @@
         <v>75</v>
       </c>
       <c r="U137" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -3858,10 +3867,10 @@
         <v>75</v>
       </c>
       <c r="T149" t="s">
+        <v>254</v>
+      </c>
+      <c r="U149" t="s">
         <v>255</v>
-      </c>
-      <c r="U149" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
@@ -3890,7 +3899,7 @@
         <v>18.5</v>
       </c>
       <c r="T150" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
@@ -3945,7 +3954,7 @@
         <v>9</v>
       </c>
       <c r="T152" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
@@ -3998,7 +4007,7 @@
       </c>
       <c r="S154" s="4"/>
       <c r="T154" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
@@ -4402,7 +4411,7 @@
         <v>1.3846000000000001</v>
       </c>
       <c r="T171" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
@@ -4632,7 +4641,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="T180" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="U180" s="8"/>
     </row>
@@ -4714,7 +4723,7 @@
         <v>3.3332999999999999</v>
       </c>
       <c r="T183" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
@@ -4765,7 +4774,7 @@
         <v>3.3332999999999999</v>
       </c>
       <c r="T185" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
@@ -4858,10 +4867,10 @@
         <v>65</v>
       </c>
       <c r="T189" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="U189" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
@@ -4937,7 +4946,7 @@
         <v>100</v>
       </c>
       <c r="T192" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
@@ -4963,7 +4972,7 @@
         <v>4.2</v>
       </c>
       <c r="U193" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
@@ -4989,7 +4998,7 @@
         <v>3.3</v>
       </c>
       <c r="U194" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
@@ -5016,7 +5025,7 @@
         <v>3.75</v>
       </c>
       <c r="T195" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
@@ -5164,7 +5173,7 @@
         <v>20</v>
       </c>
       <c r="T201" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
@@ -5250,7 +5259,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -5306,13 +5315,13 @@
       <c r="O208" s="5"/>
       <c r="P208" s="5"/>
       <c r="Q208" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R208" s="5">
         <v>0</v>
       </c>
       <c r="S208" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="T208" s="5" t="s">
         <v>13</v>
@@ -5333,16 +5342,16 @@
       <c r="O209" s="4"/>
       <c r="P209" s="4"/>
       <c r="Q209" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R209">
         <v>35</v>
       </c>
       <c r="T209" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="U209" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
@@ -5360,16 +5369,16 @@
       <c r="O210" s="4"/>
       <c r="P210" s="4"/>
       <c r="Q210" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R210">
         <v>35</v>
       </c>
       <c r="T210" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="U210" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
@@ -5389,16 +5398,16 @@
       <c r="O211" s="4"/>
       <c r="P211" s="4"/>
       <c r="Q211" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R211">
         <v>25</v>
       </c>
       <c r="T211" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U211" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
@@ -5418,16 +5427,16 @@
       <c r="O212" s="4"/>
       <c r="P212" s="4"/>
       <c r="Q212" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R212">
         <v>25</v>
       </c>
       <c r="T212" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="U212" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
@@ -5447,16 +5456,16 @@
       <c r="O213" s="4"/>
       <c r="P213" s="4"/>
       <c r="Q213" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R213">
         <v>40</v>
       </c>
       <c r="T213" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="U213" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
@@ -5476,16 +5485,16 @@
       <c r="O214" s="4"/>
       <c r="P214" s="4"/>
       <c r="Q214" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R214">
         <v>20</v>
       </c>
       <c r="T214" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U214" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
@@ -5505,7 +5514,7 @@
       <c r="O215" s="4"/>
       <c r="P215" s="4"/>
       <c r="Q215" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R215">
         <v>10</v>
@@ -5514,7 +5523,7 @@
         <v>102</v>
       </c>
       <c r="U215" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
@@ -5534,7 +5543,7 @@
       <c r="O216" s="4"/>
       <c r="P216" s="4"/>
       <c r="Q216" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R216">
         <v>10</v>
@@ -5543,7 +5552,7 @@
         <v>102</v>
       </c>
       <c r="U216" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
@@ -5563,7 +5572,7 @@
       <c r="O217" s="4"/>
       <c r="P217" s="4"/>
       <c r="Q217" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R217">
         <v>25</v>
@@ -5586,7 +5595,7 @@
       <c r="O218" s="4"/>
       <c r="P218" s="4"/>
       <c r="Q218" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
@@ -5609,16 +5618,16 @@
       <c r="O219" s="4"/>
       <c r="P219" s="4"/>
       <c r="Q219" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R219" s="6">
         <v>20</v>
       </c>
       <c r="T219" t="s">
+        <v>243</v>
+      </c>
+      <c r="U219" t="s">
         <v>244</v>
-      </c>
-      <c r="U219" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
@@ -5641,7 +5650,7 @@
       <c r="O220" s="4"/>
       <c r="P220" s="4"/>
       <c r="Q220" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R220" s="6">
         <v>40</v>
@@ -5667,7 +5676,7 @@
       <c r="O221" s="4"/>
       <c r="P221" s="4"/>
       <c r="Q221" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R221" s="6">
         <v>10</v>
@@ -5693,7 +5702,7 @@
       <c r="O222" s="4"/>
       <c r="P222" s="4"/>
       <c r="Q222" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R222" s="6">
         <v>20</v>
@@ -5707,7 +5716,7 @@
         <v>148</v>
       </c>
       <c r="Q223" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R223" s="6">
         <v>10</v>
@@ -5721,7 +5730,7 @@
         <v>104</v>
       </c>
       <c r="Q224" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R224" s="6">
         <v>20</v>
@@ -5732,7 +5741,7 @@
         <v>70</v>
       </c>
       <c r="Q225" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R225" s="6">
         <v>40</v>
@@ -5740,44 +5749,44 @@
     </row>
     <row r="226" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q226" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R226" s="4">
         <v>35</v>
       </c>
       <c r="T226" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="227" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q227" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R227" s="4">
         <v>25</v>
       </c>
       <c r="T227" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="228" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q228" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R228" s="4">
         <v>25</v>
       </c>
       <c r="T228" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
@@ -5786,7 +5795,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -5815,34 +5824,34 @@
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4"/>
       <c r="Q232" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R232" s="6">
         <v>40</v>
       </c>
       <c r="S232" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T232" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U232" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="4"/>
       <c r="Q233" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R233" s="6">
         <v>40</v>
       </c>
       <c r="S233" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T233" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
@@ -5850,7 +5859,7 @@
     </row>
     <row r="235" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B235" s="15"/>
       <c r="C235" s="15"/>
@@ -5875,7 +5884,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -5900,27 +5909,27 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B237" s="19"/>
       <c r="C237" s="19"/>
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B238" s="19"/>
       <c r="C238" s="19"/>
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="Q239" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R239" s="5">
         <v>0</v>
       </c>
       <c r="S239" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="T239" s="5" t="s">
         <v>151</v>
@@ -5928,7 +5937,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="Q240" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R240" s="5">
         <v>0</v>
@@ -5942,7 +5951,7 @@
     </row>
     <row r="241" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A241" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B241" s="21"/>
       <c r="C241" s="21"/>
@@ -5956,10 +5965,10 @@
         <v>7</v>
       </c>
       <c r="N242" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q242" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R242">
         <v>3</v>
@@ -5970,10 +5979,10 @@
         <v>7</v>
       </c>
       <c r="N243" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q243" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R243">
         <v>3</v>
@@ -5984,10 +5993,10 @@
         <v>7</v>
       </c>
       <c r="N244" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q244" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R244">
         <v>3</v>
@@ -5998,10 +6007,10 @@
         <v>7</v>
       </c>
       <c r="N245" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q245" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R245">
         <v>3</v>
@@ -6012,10 +6021,10 @@
         <v>7</v>
       </c>
       <c r="N246" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q246" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R246">
         <v>9</v>
@@ -6026,10 +6035,10 @@
         <v>7</v>
       </c>
       <c r="N247" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q247" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R247">
         <v>4</v>
@@ -6040,10 +6049,10 @@
         <v>7</v>
       </c>
       <c r="N248" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q248" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R248">
         <v>-6</v>
@@ -6054,10 +6063,10 @@
         <v>7</v>
       </c>
       <c r="N249" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q249" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R249">
         <v>-16</v>
@@ -6068,10 +6077,10 @@
         <v>25</v>
       </c>
       <c r="N250" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q250" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R250" s="20">
         <f>R242</f>
@@ -6083,10 +6092,10 @@
         <v>25</v>
       </c>
       <c r="N251" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q251" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R251" s="20">
         <f t="shared" ref="R251:R257" si="4">R243</f>
@@ -6098,10 +6107,10 @@
         <v>25</v>
       </c>
       <c r="N252" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q252" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R252" s="20">
         <f t="shared" si="4"/>
@@ -6113,10 +6122,10 @@
         <v>25</v>
       </c>
       <c r="N253" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q253" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R253" s="20">
         <f t="shared" si="4"/>
@@ -6128,10 +6137,10 @@
         <v>25</v>
       </c>
       <c r="N254" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q254" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R254" s="20">
         <f t="shared" si="4"/>
@@ -6143,10 +6152,10 @@
         <v>25</v>
       </c>
       <c r="N255" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q255" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R255" s="20">
         <f t="shared" si="4"/>
@@ -6158,10 +6167,10 @@
         <v>25</v>
       </c>
       <c r="N256" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q256" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R256" s="20">
         <f t="shared" si="4"/>
@@ -6173,10 +6182,10 @@
         <v>25</v>
       </c>
       <c r="N257" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q257" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R257" s="20">
         <f t="shared" si="4"/>
@@ -6188,10 +6197,10 @@
         <v>21</v>
       </c>
       <c r="N258" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q258" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R258" s="20">
         <f>R242</f>
@@ -6203,10 +6212,10 @@
         <v>21</v>
       </c>
       <c r="N259" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q259" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R259" s="20">
         <f t="shared" ref="R259:R265" si="5">R243</f>
@@ -6218,10 +6227,10 @@
         <v>21</v>
       </c>
       <c r="N260" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q260" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R260" s="20">
         <f t="shared" si="5"/>
@@ -6233,10 +6242,10 @@
         <v>21</v>
       </c>
       <c r="N261" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q261" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R261" s="20">
         <f t="shared" si="5"/>
@@ -6248,10 +6257,10 @@
         <v>21</v>
       </c>
       <c r="N262" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q262" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R262" s="20">
         <f t="shared" si="5"/>
@@ -6263,10 +6272,10 @@
         <v>21</v>
       </c>
       <c r="N263" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q263" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R263" s="20">
         <f t="shared" si="5"/>
@@ -6278,10 +6287,10 @@
         <v>21</v>
       </c>
       <c r="N264" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q264" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R264" s="20">
         <f t="shared" si="5"/>
@@ -6293,10 +6302,10 @@
         <v>21</v>
       </c>
       <c r="N265" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q265" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R265" s="20">
         <f t="shared" si="5"/>
@@ -6308,10 +6317,10 @@
         <v>23</v>
       </c>
       <c r="N266" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q266" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R266" s="20">
         <f>R242</f>
@@ -6323,10 +6332,10 @@
         <v>23</v>
       </c>
       <c r="N267" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q267" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R267" s="20">
         <f t="shared" ref="R267:R273" si="6">R243</f>
@@ -6338,10 +6347,10 @@
         <v>23</v>
       </c>
       <c r="N268" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q268" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R268" s="20">
         <f t="shared" si="6"/>
@@ -6353,10 +6362,10 @@
         <v>23</v>
       </c>
       <c r="N269" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q269" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R269" s="20">
         <f t="shared" si="6"/>
@@ -6368,10 +6377,10 @@
         <v>23</v>
       </c>
       <c r="N270" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q270" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R270" s="20">
         <f t="shared" si="6"/>
@@ -6383,10 +6392,10 @@
         <v>23</v>
       </c>
       <c r="N271" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q271" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R271" s="20">
         <f t="shared" si="6"/>
@@ -6398,10 +6407,10 @@
         <v>23</v>
       </c>
       <c r="N272" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q272" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R272" s="20">
         <f t="shared" si="6"/>
@@ -6413,10 +6422,10 @@
         <v>23</v>
       </c>
       <c r="N273" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q273" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R273" s="20">
         <f t="shared" si="6"/>
@@ -6425,7 +6434,7 @@
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B275" s="21"/>
       <c r="C275" s="21"/>
@@ -6435,10 +6444,10 @@
         <v>14</v>
       </c>
       <c r="N276" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q276" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R276">
         <v>3</v>
@@ -6449,10 +6458,10 @@
         <v>14</v>
       </c>
       <c r="N277" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q277" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R277">
         <v>3</v>
@@ -6463,10 +6472,10 @@
         <v>14</v>
       </c>
       <c r="N278" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q278" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R278">
         <v>3</v>
@@ -6477,10 +6486,10 @@
         <v>14</v>
       </c>
       <c r="N279" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q279" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R279">
         <v>3</v>
@@ -6491,10 +6500,10 @@
         <v>14</v>
       </c>
       <c r="N280" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q280" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R280">
         <v>10</v>
@@ -6505,10 +6514,10 @@
         <v>14</v>
       </c>
       <c r="N281" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q281" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R281">
         <v>5</v>
@@ -6519,10 +6528,10 @@
         <v>14</v>
       </c>
       <c r="N282" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q282" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R282">
         <v>0</v>
@@ -6533,10 +6542,10 @@
         <v>14</v>
       </c>
       <c r="N283" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q283" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R283">
         <v>-10</v>
@@ -6547,10 +6556,10 @@
         <v>15</v>
       </c>
       <c r="N284" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q284" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R284" s="20">
         <f>R276</f>
@@ -6562,10 +6571,10 @@
         <v>15</v>
       </c>
       <c r="N285" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q285" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R285" s="20">
         <f t="shared" ref="R285:R291" si="7">R277</f>
@@ -6577,10 +6586,10 @@
         <v>15</v>
       </c>
       <c r="N286" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q286" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R286" s="20">
         <f t="shared" si="7"/>
@@ -6592,10 +6601,10 @@
         <v>15</v>
       </c>
       <c r="N287" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q287" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R287" s="20">
         <f t="shared" si="7"/>
@@ -6607,10 +6616,10 @@
         <v>15</v>
       </c>
       <c r="N288" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q288" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R288" s="20">
         <f t="shared" si="7"/>
@@ -6622,10 +6631,10 @@
         <v>15</v>
       </c>
       <c r="N289" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q289" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R289" s="20">
         <f t="shared" si="7"/>
@@ -6637,10 +6646,10 @@
         <v>15</v>
       </c>
       <c r="N290" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q290" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R290" s="20">
         <f t="shared" si="7"/>
@@ -6652,10 +6661,10 @@
         <v>15</v>
       </c>
       <c r="N291" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q291" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R291" s="20">
         <f t="shared" si="7"/>
@@ -6667,10 +6676,10 @@
         <v>19</v>
       </c>
       <c r="N292" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q292" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R292" s="20">
         <f>R276</f>
@@ -6682,10 +6691,10 @@
         <v>19</v>
       </c>
       <c r="N293" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q293" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R293" s="20">
         <f t="shared" ref="R293:R299" si="8">R277</f>
@@ -6697,10 +6706,10 @@
         <v>19</v>
       </c>
       <c r="N294" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q294" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R294" s="20">
         <f t="shared" si="8"/>
@@ -6712,10 +6721,10 @@
         <v>19</v>
       </c>
       <c r="N295" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q295" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R295" s="20">
         <f t="shared" si="8"/>
@@ -6727,10 +6736,10 @@
         <v>19</v>
       </c>
       <c r="N296" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q296" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R296" s="20">
         <f t="shared" si="8"/>
@@ -6742,10 +6751,10 @@
         <v>19</v>
       </c>
       <c r="N297" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q297" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R297" s="20">
         <f t="shared" si="8"/>
@@ -6757,10 +6766,10 @@
         <v>19</v>
       </c>
       <c r="N298" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q298" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R298" s="20">
         <f t="shared" si="8"/>
@@ -6772,10 +6781,10 @@
         <v>19</v>
       </c>
       <c r="N299" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q299" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R299" s="20">
         <f t="shared" si="8"/>
@@ -6784,13 +6793,13 @@
     </row>
     <row r="300" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N300" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q300" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R300" s="20">
         <f>R276</f>
@@ -6799,13 +6808,13 @@
     </row>
     <row r="301" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N301" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q301" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R301" s="20">
         <f t="shared" ref="R301:R307" si="9">R277</f>
@@ -6814,13 +6823,13 @@
     </row>
     <row r="302" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N302" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q302" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R302" s="20">
         <f t="shared" si="9"/>
@@ -6829,13 +6838,13 @@
     </row>
     <row r="303" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N303" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q303" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R303" s="20">
         <f t="shared" si="9"/>
@@ -6844,13 +6853,13 @@
     </row>
     <row r="304" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N304" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q304" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R304" s="20">
         <f t="shared" si="9"/>
@@ -6859,13 +6868,13 @@
     </row>
     <row r="305" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N305" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q305" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R305" s="20">
         <f t="shared" si="9"/>
@@ -6874,13 +6883,13 @@
     </row>
     <row r="306" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N306" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q306" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R306" s="20">
         <f t="shared" si="9"/>
@@ -6889,13 +6898,13 @@
     </row>
     <row r="307" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N307" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q307" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R307" s="20">
         <f t="shared" si="9"/>
@@ -6907,10 +6916,10 @@
         <v>22</v>
       </c>
       <c r="N308" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q308" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R308" s="20">
         <f t="shared" ref="R308:R315" si="10">R276</f>
@@ -6922,10 +6931,10 @@
         <v>22</v>
       </c>
       <c r="N309" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q309" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R309" s="20">
         <f t="shared" si="10"/>
@@ -6937,10 +6946,10 @@
         <v>22</v>
       </c>
       <c r="N310" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q310" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R310" s="20">
         <f t="shared" si="10"/>
@@ -6952,10 +6961,10 @@
         <v>22</v>
       </c>
       <c r="N311" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q311" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R311" s="20">
         <f t="shared" si="10"/>
@@ -6967,10 +6976,10 @@
         <v>22</v>
       </c>
       <c r="N312" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q312" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R312" s="20">
         <f t="shared" si="10"/>
@@ -6982,10 +6991,10 @@
         <v>22</v>
       </c>
       <c r="N313" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q313" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R313" s="20">
         <f t="shared" si="10"/>
@@ -6997,10 +7006,10 @@
         <v>22</v>
       </c>
       <c r="N314" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q314" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R314" s="20">
         <f t="shared" si="10"/>
@@ -7012,10 +7021,10 @@
         <v>22</v>
       </c>
       <c r="N315" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q315" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R315" s="20">
         <f t="shared" si="10"/>
@@ -7027,10 +7036,10 @@
         <v>27</v>
       </c>
       <c r="N316" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q316" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R316" s="20">
         <f t="shared" ref="R316:R323" si="11">R276</f>
@@ -7042,10 +7051,10 @@
         <v>27</v>
       </c>
       <c r="N317" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q317" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R317" s="20">
         <f t="shared" si="11"/>
@@ -7057,10 +7066,10 @@
         <v>27</v>
       </c>
       <c r="N318" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q318" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R318" s="20">
         <f t="shared" si="11"/>
@@ -7072,10 +7081,10 @@
         <v>27</v>
       </c>
       <c r="N319" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q319" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R319" s="20">
         <f t="shared" si="11"/>
@@ -7087,10 +7096,10 @@
         <v>27</v>
       </c>
       <c r="N320" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q320" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R320" s="20">
         <f t="shared" si="11"/>
@@ -7102,10 +7111,10 @@
         <v>27</v>
       </c>
       <c r="N321" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q321" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R321" s="20">
         <f t="shared" si="11"/>
@@ -7117,10 +7126,10 @@
         <v>27</v>
       </c>
       <c r="N322" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q322" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R322" s="20">
         <f t="shared" si="11"/>
@@ -7132,10 +7141,10 @@
         <v>27</v>
       </c>
       <c r="N323" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q323" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R323" s="20">
         <f t="shared" si="11"/>
@@ -7147,10 +7156,10 @@
         <v>26</v>
       </c>
       <c r="N324" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q324" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R324" s="20">
         <f t="shared" ref="R324:R331" si="12">R276</f>
@@ -7162,10 +7171,10 @@
         <v>26</v>
       </c>
       <c r="N325" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q325" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R325" s="20">
         <f t="shared" si="12"/>
@@ -7177,10 +7186,10 @@
         <v>26</v>
       </c>
       <c r="N326" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q326" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R326" s="20">
         <f t="shared" si="12"/>
@@ -7192,10 +7201,10 @@
         <v>26</v>
       </c>
       <c r="N327" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q327" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R327" s="20">
         <f t="shared" si="12"/>
@@ -7207,10 +7216,10 @@
         <v>26</v>
       </c>
       <c r="N328" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q328" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R328" s="20">
         <f t="shared" si="12"/>
@@ -7222,10 +7231,10 @@
         <v>26</v>
       </c>
       <c r="N329" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q329" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R329" s="20">
         <f t="shared" si="12"/>
@@ -7237,10 +7246,10 @@
         <v>26</v>
       </c>
       <c r="N330" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q330" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R330" s="20">
         <f t="shared" si="12"/>
@@ -7252,10 +7261,10 @@
         <v>26</v>
       </c>
       <c r="N331" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q331" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R331" s="20">
         <f t="shared" si="12"/>
@@ -7269,17 +7278,17 @@
       <c r="B332" s="6"/>
       <c r="C332" s="6"/>
       <c r="N332" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q332" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R332" s="20">
         <f t="shared" ref="R332:R339" si="13">R276</f>
         <v>3</v>
       </c>
       <c r="T332" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="333" spans="1:20" x14ac:dyDescent="0.25">
@@ -7289,10 +7298,10 @@
       <c r="B333" s="6"/>
       <c r="C333" s="6"/>
       <c r="N333" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q333" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R333" s="20">
         <f t="shared" si="13"/>
@@ -7306,10 +7315,10 @@
       <c r="B334" s="6"/>
       <c r="C334" s="6"/>
       <c r="N334" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q334" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R334" s="20">
         <f t="shared" si="13"/>
@@ -7323,10 +7332,10 @@
       <c r="B335" s="6"/>
       <c r="C335" s="6"/>
       <c r="N335" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q335" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R335" s="20">
         <f t="shared" si="13"/>
@@ -7340,10 +7349,10 @@
       <c r="B336" s="6"/>
       <c r="C336" s="6"/>
       <c r="N336" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q336" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R336" s="20">
         <f t="shared" si="13"/>
@@ -7357,10 +7366,10 @@
       <c r="B337" s="6"/>
       <c r="C337" s="6"/>
       <c r="N337" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q337" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R337" s="20">
         <f t="shared" si="13"/>
@@ -7374,10 +7383,10 @@
       <c r="B338" s="6"/>
       <c r="C338" s="6"/>
       <c r="N338" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q338" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R338" s="20">
         <f t="shared" si="13"/>
@@ -7391,10 +7400,10 @@
       <c r="B339" s="6"/>
       <c r="C339" s="6"/>
       <c r="N339" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q339" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R339" s="20">
         <f t="shared" si="13"/>
@@ -7408,17 +7417,17 @@
       <c r="B340" s="6"/>
       <c r="C340" s="6"/>
       <c r="N340" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q340" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R340" s="20">
         <f>R276</f>
         <v>3</v>
       </c>
       <c r="T340" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="341" spans="1:20" x14ac:dyDescent="0.25">
@@ -7428,10 +7437,10 @@
       <c r="B341" s="6"/>
       <c r="C341" s="6"/>
       <c r="N341" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q341" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R341" s="20">
         <f t="shared" ref="R341:R347" si="14">R277</f>
@@ -7445,10 +7454,10 @@
       <c r="B342" s="6"/>
       <c r="C342" s="6"/>
       <c r="N342" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q342" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R342" s="20">
         <f t="shared" si="14"/>
@@ -7462,10 +7471,10 @@
       <c r="B343" s="6"/>
       <c r="C343" s="6"/>
       <c r="N343" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q343" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R343" s="20">
         <f t="shared" si="14"/>
@@ -7479,10 +7488,10 @@
       <c r="B344" s="6"/>
       <c r="C344" s="6"/>
       <c r="N344" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q344" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R344" s="20">
         <f t="shared" si="14"/>
@@ -7496,10 +7505,10 @@
       <c r="B345" s="6"/>
       <c r="C345" s="6"/>
       <c r="N345" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q345" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R345" s="20">
         <f t="shared" si="14"/>
@@ -7511,10 +7520,10 @@
         <v>42</v>
       </c>
       <c r="N346" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q346" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R346" s="20">
         <f t="shared" si="14"/>
@@ -7526,10 +7535,10 @@
         <v>42</v>
       </c>
       <c r="N347" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q347" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R347" s="20">
         <f t="shared" si="14"/>
@@ -7538,7 +7547,7 @@
     </row>
     <row r="348" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A348" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B348" s="21"/>
       <c r="C348" s="21"/>
@@ -7548,10 +7557,10 @@
         <v>32</v>
       </c>
       <c r="N349" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q349" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R349">
         <v>7</v>
@@ -7562,10 +7571,10 @@
         <v>32</v>
       </c>
       <c r="N350" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q350" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R350">
         <v>7</v>
@@ -7576,10 +7585,10 @@
         <v>32</v>
       </c>
       <c r="N351" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q351" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R351">
         <v>7</v>
@@ -7590,10 +7599,10 @@
         <v>32</v>
       </c>
       <c r="N352" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q352" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R352">
         <v>7</v>
@@ -7604,10 +7613,10 @@
         <v>32</v>
       </c>
       <c r="N353" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q353" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R353">
         <v>15.5</v>
@@ -7618,10 +7627,10 @@
         <v>32</v>
       </c>
       <c r="N354" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q354" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R354">
         <v>10.5</v>
@@ -7632,10 +7641,10 @@
         <v>32</v>
       </c>
       <c r="N355" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q355" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R355">
         <v>0.5</v>
@@ -7646,10 +7655,10 @@
         <v>32</v>
       </c>
       <c r="N356" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q356" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R356">
         <v>-9.5</v>
@@ -7660,10 +7669,10 @@
         <v>33</v>
       </c>
       <c r="N357" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q357" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R357">
         <v>7</v>
@@ -7674,10 +7683,10 @@
         <v>33</v>
       </c>
       <c r="N358" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q358" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R358">
         <v>7</v>
@@ -7688,10 +7697,10 @@
         <v>33</v>
       </c>
       <c r="N359" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q359" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R359">
         <v>7</v>
@@ -7702,10 +7711,10 @@
         <v>33</v>
       </c>
       <c r="N360" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q360" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R360">
         <v>7</v>
@@ -7716,10 +7725,10 @@
         <v>33</v>
       </c>
       <c r="N361" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q361" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R361">
         <v>16</v>
@@ -7730,10 +7739,10 @@
         <v>33</v>
       </c>
       <c r="N362" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q362" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R362">
         <v>11</v>
@@ -7744,10 +7753,10 @@
         <v>33</v>
       </c>
       <c r="N363" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q363" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R363">
         <v>1</v>
@@ -7758,10 +7767,10 @@
         <v>33</v>
       </c>
       <c r="N364" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q364" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R364">
         <v>-4</v>
@@ -7779,10 +7788,10 @@
         <v>38</v>
       </c>
       <c r="N367" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q367" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R367">
         <v>3</v>
@@ -7793,10 +7802,10 @@
         <v>38</v>
       </c>
       <c r="N368" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q368" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R368">
         <v>3</v>
@@ -7807,10 +7816,10 @@
         <v>38</v>
       </c>
       <c r="N369" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q369" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R369">
         <v>3</v>
@@ -7821,10 +7830,10 @@
         <v>38</v>
       </c>
       <c r="N370" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q370" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R370">
         <v>7</v>
@@ -7835,10 +7844,10 @@
         <v>38</v>
       </c>
       <c r="N371" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q371" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R371">
         <v>-3</v>
@@ -7849,10 +7858,10 @@
         <v>38</v>
       </c>
       <c r="N372" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q372" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R372">
         <v>-8</v>
@@ -7863,17 +7872,17 @@
         <v>68</v>
       </c>
       <c r="N373" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q373" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R373" s="24">
         <f>R367</f>
         <v>3</v>
       </c>
       <c r="T373" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="374" spans="1:20" x14ac:dyDescent="0.25">
@@ -7881,10 +7890,10 @@
         <v>68</v>
       </c>
       <c r="N374" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q374" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R374" s="24">
         <f t="shared" ref="R374:R378" si="15">R368</f>
@@ -7896,10 +7905,10 @@
         <v>68</v>
       </c>
       <c r="N375" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q375" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R375" s="24">
         <f t="shared" si="15"/>
@@ -7911,10 +7920,10 @@
         <v>68</v>
       </c>
       <c r="N376" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q376" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R376" s="24">
         <f t="shared" si="15"/>
@@ -7926,10 +7935,10 @@
         <v>68</v>
       </c>
       <c r="N377" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q377" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R377" s="24">
         <f t="shared" si="15"/>
@@ -7941,10 +7950,10 @@
         <v>68</v>
       </c>
       <c r="N378" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q378" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R378" s="24">
         <f t="shared" si="15"/>
@@ -7953,7 +7962,7 @@
     </row>
     <row r="380" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A380" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B380" s="21"/>
       <c r="C380" s="21"/>
@@ -7963,10 +7972,10 @@
         <v>40</v>
       </c>
       <c r="N381" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q381" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R381">
         <v>3</v>
@@ -7977,10 +7986,10 @@
         <v>40</v>
       </c>
       <c r="N382" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q382" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R382">
         <v>3</v>
@@ -7991,10 +8000,10 @@
         <v>40</v>
       </c>
       <c r="N383" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q383" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R383">
         <v>3</v>
@@ -8005,10 +8014,10 @@
         <v>40</v>
       </c>
       <c r="N384" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q384" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R384">
         <v>3</v>
@@ -8019,10 +8028,10 @@
         <v>40</v>
       </c>
       <c r="N385" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q385" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R385">
         <v>3</v>
@@ -8033,10 +8042,10 @@
         <v>40</v>
       </c>
       <c r="N386" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q386" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R386">
         <v>3</v>
@@ -8047,10 +8056,10 @@
         <v>40</v>
       </c>
       <c r="N387" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q387" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R387">
         <v>5</v>
@@ -8061,10 +8070,10 @@
         <v>40</v>
       </c>
       <c r="N388" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q388" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R388">
         <v>0</v>
@@ -8075,10 +8084,10 @@
         <v>40</v>
       </c>
       <c r="N389" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q389" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R389">
         <v>-5</v>
@@ -8089,10 +8098,10 @@
         <v>40</v>
       </c>
       <c r="N390" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q390" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R390">
         <v>-10</v>
@@ -8103,10 +8112,10 @@
         <v>40</v>
       </c>
       <c r="N391" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q391" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R391">
         <v>-15</v>
@@ -8117,10 +8126,10 @@
         <v>40</v>
       </c>
       <c r="N392" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q392" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R392">
         <v>-20</v>
@@ -8128,7 +8137,7 @@
     </row>
     <row r="394" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A394" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B394" s="21"/>
       <c r="C394" s="21"/>
@@ -8138,10 +8147,10 @@
         <v>34</v>
       </c>
       <c r="N395" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q395" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R395">
         <v>0.5</v>
@@ -8152,10 +8161,10 @@
         <v>34</v>
       </c>
       <c r="N396" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q396" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R396">
         <v>0.5</v>
@@ -8166,10 +8175,10 @@
         <v>34</v>
       </c>
       <c r="N397" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q397" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R397">
         <v>0.5</v>
@@ -8180,10 +8189,10 @@
         <v>34</v>
       </c>
       <c r="N398" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q398" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R398">
         <v>0.5</v>
@@ -8194,10 +8203,10 @@
         <v>34</v>
       </c>
       <c r="N399" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q399" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R399">
         <v>0.5</v>
@@ -8208,10 +8217,10 @@
         <v>34</v>
       </c>
       <c r="N400" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q400" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R400">
         <v>0.5</v>
@@ -8222,10 +8231,10 @@
         <v>34</v>
       </c>
       <c r="N401" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q401" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R401">
         <v>55</v>
@@ -8236,10 +8245,10 @@
         <v>34</v>
       </c>
       <c r="N402" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q402" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R402">
         <v>35</v>
@@ -8250,10 +8259,10 @@
         <v>34</v>
       </c>
       <c r="N403" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q403" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R403">
         <v>25</v>
@@ -8264,10 +8273,10 @@
         <v>34</v>
       </c>
       <c r="N404" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q404" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R404">
         <v>15</v>
@@ -8278,10 +8287,10 @@
         <v>34</v>
       </c>
       <c r="N405" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q405" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R405">
         <v>0</v>
@@ -8292,10 +8301,10 @@
         <v>34</v>
       </c>
       <c r="N406" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q406" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R406">
         <v>-5</v>
@@ -8306,10 +8315,10 @@
         <v>35</v>
       </c>
       <c r="N407" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q407" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R407" s="20">
         <f>R395</f>
@@ -8321,10 +8330,10 @@
         <v>35</v>
       </c>
       <c r="N408" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q408" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R408" s="20">
         <f t="shared" ref="R408:R418" si="16">R396</f>
@@ -8336,10 +8345,10 @@
         <v>35</v>
       </c>
       <c r="N409" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q409" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R409" s="20">
         <f t="shared" si="16"/>
@@ -8351,10 +8360,10 @@
         <v>35</v>
       </c>
       <c r="N410" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q410" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R410" s="20">
         <f t="shared" si="16"/>
@@ -8366,10 +8375,10 @@
         <v>35</v>
       </c>
       <c r="N411" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q411" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R411" s="20">
         <f t="shared" si="16"/>
@@ -8381,10 +8390,10 @@
         <v>35</v>
       </c>
       <c r="N412" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q412" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R412" s="20">
         <f t="shared" si="16"/>
@@ -8396,10 +8405,10 @@
         <v>35</v>
       </c>
       <c r="N413" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q413" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R413" s="20">
         <f t="shared" si="16"/>
@@ -8411,10 +8420,10 @@
         <v>35</v>
       </c>
       <c r="N414" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q414" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R414" s="20">
         <f t="shared" si="16"/>
@@ -8426,10 +8435,10 @@
         <v>35</v>
       </c>
       <c r="N415" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q415" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R415" s="20">
         <f t="shared" si="16"/>
@@ -8441,10 +8450,10 @@
         <v>35</v>
       </c>
       <c r="N416" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q416" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R416" s="20">
         <f t="shared" si="16"/>
@@ -8456,10 +8465,10 @@
         <v>35</v>
       </c>
       <c r="N417" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q417" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R417" s="20">
         <f t="shared" si="16"/>
@@ -8471,10 +8480,10 @@
         <v>35</v>
       </c>
       <c r="N418" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q418" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R418" s="20">
         <f t="shared" si="16"/>
@@ -8483,7 +8492,7 @@
     </row>
     <row r="420" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A420" s="21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B420" s="21"/>
       <c r="C420" s="21"/>
@@ -8493,10 +8502,10 @@
         <v>28</v>
       </c>
       <c r="N421" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q421" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R421">
         <v>20</v>
@@ -8507,10 +8516,10 @@
         <v>28</v>
       </c>
       <c r="N422" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q422" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R422">
         <v>15</v>
@@ -8521,10 +8530,10 @@
         <v>28</v>
       </c>
       <c r="N423" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q423" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R423">
         <v>10</v>
@@ -8532,31 +8541,31 @@
     </row>
     <row r="424" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N424" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q424" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R424" s="20">
         <f>R421</f>
         <v>20</v>
       </c>
       <c r="T424" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="425" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N425" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q425" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R425" s="20">
         <f t="shared" ref="R425:R426" si="17">R422</f>
@@ -8565,13 +8574,13 @@
     </row>
     <row r="426" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N426" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q426" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R426" s="20">
         <f t="shared" si="17"/>
@@ -8583,10 +8592,10 @@
         <v>30</v>
       </c>
       <c r="N427" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q427" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R427" s="20">
         <f>R421</f>
@@ -8598,10 +8607,10 @@
         <v>30</v>
       </c>
       <c r="N428" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q428" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R428" s="20">
         <f t="shared" ref="R428:R429" si="18">R422</f>
@@ -8613,10 +8622,10 @@
         <v>30</v>
       </c>
       <c r="N429" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q429" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R429" s="20">
         <f t="shared" si="18"/>
@@ -8628,10 +8637,10 @@
         <v>36</v>
       </c>
       <c r="N430" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q430" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R430">
         <v>60</v>
@@ -8642,10 +8651,10 @@
         <v>36</v>
       </c>
       <c r="N431" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q431" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R431">
         <v>45</v>
@@ -8656,10 +8665,10 @@
         <v>36</v>
       </c>
       <c r="N432" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q432" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R432">
         <v>35</v>
@@ -8670,10 +8679,10 @@
         <v>36</v>
       </c>
       <c r="N433" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q433" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R433">
         <v>25</v>
@@ -8684,10 +8693,10 @@
         <v>36</v>
       </c>
       <c r="N434" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q434" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R434">
         <v>10</v>
@@ -8698,10 +8707,10 @@
         <v>39</v>
       </c>
       <c r="N435" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q435" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R435">
         <v>15</v>
@@ -8712,10 +8721,10 @@
         <v>39</v>
       </c>
       <c r="N436" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q436" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R436">
         <v>5</v>
@@ -8728,19 +8737,19 @@
       <c r="B437" s="6"/>
       <c r="C437" s="6"/>
       <c r="N437" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q437" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R437">
         <v>25</v>
       </c>
       <c r="T437" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="U437" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="438" spans="1:21" x14ac:dyDescent="0.25">
@@ -8750,10 +8759,10 @@
       <c r="B438" s="6"/>
       <c r="C438" s="6"/>
       <c r="N438" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q438" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R438">
         <v>25</v>
@@ -8766,10 +8775,10 @@
       <c r="B439" s="6"/>
       <c r="C439" s="6"/>
       <c r="N439" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q439" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R439">
         <v>25</v>
@@ -8777,7 +8786,7 @@
     </row>
     <row r="441" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A441" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B441" s="21"/>
       <c r="C441" s="21"/>
@@ -8787,7 +8796,7 @@
         <v>46</v>
       </c>
       <c r="Q442" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R442">
         <v>0.46200000000000002</v>
@@ -8798,7 +8807,7 @@
         <v>46</v>
       </c>
       <c r="Q443" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R443">
         <v>13.85</v>
@@ -8811,14 +8820,14 @@
       <c r="B444" s="6"/>
       <c r="C444" s="6"/>
       <c r="Q444" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R444" s="20">
         <f>R442</f>
         <v>0.46200000000000002</v>
       </c>
       <c r="T444" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="445" spans="1:21" x14ac:dyDescent="0.25">
@@ -8828,7 +8837,7 @@
       <c r="B445" s="6"/>
       <c r="C445" s="6"/>
       <c r="Q445" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R445" s="20">
         <f>R443</f>
@@ -8840,7 +8849,7 @@
         <v>45</v>
       </c>
       <c r="Q446" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R446">
         <v>2.5</v>
@@ -8851,7 +8860,7 @@
         <v>45</v>
       </c>
       <c r="Q447" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R447">
         <v>-45</v>
@@ -8862,13 +8871,13 @@
         <v>48</v>
       </c>
       <c r="Q448" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R448">
         <v>2.6669999999999998</v>
       </c>
       <c r="T448" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="449" spans="1:20" x14ac:dyDescent="0.25">
@@ -8876,7 +8885,7 @@
         <v>48</v>
       </c>
       <c r="Q449" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R449">
         <v>-33.33</v>
@@ -8889,14 +8898,14 @@
       <c r="B450" s="6"/>
       <c r="C450" s="6"/>
       <c r="Q450" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R450" s="20">
         <f>R448</f>
         <v>2.6669999999999998</v>
       </c>
       <c r="T450" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="451" spans="1:20" x14ac:dyDescent="0.25">
@@ -8906,7 +8915,7 @@
       <c r="B451" s="6"/>
       <c r="C451" s="6"/>
       <c r="Q451" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R451" s="20">
         <f>R449</f>
@@ -8918,14 +8927,14 @@
         <v>53</v>
       </c>
       <c r="Q452" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R452" s="20">
         <f>R450</f>
         <v>2.6669999999999998</v>
       </c>
       <c r="T452" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="453" spans="1:20" x14ac:dyDescent="0.25">
@@ -8933,7 +8942,7 @@
         <v>53</v>
       </c>
       <c r="Q453" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R453" s="20">
         <f>R451</f>
@@ -8945,7 +8954,7 @@
         <v>49</v>
       </c>
       <c r="Q454" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R454">
         <v>0.5</v>
@@ -8956,7 +8965,7 @@
         <v>49</v>
       </c>
       <c r="Q455" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R455">
         <v>15</v>
@@ -8967,7 +8976,7 @@
         <v>50</v>
       </c>
       <c r="Q456" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R456">
         <v>0.66700000000000004</v>
@@ -8978,7 +8987,7 @@
         <v>50</v>
       </c>
       <c r="Q457" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R457">
         <v>-3.33</v>
@@ -8989,7 +8998,7 @@
         <v>51</v>
       </c>
       <c r="Q458" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R458" s="20">
         <f>R456</f>
@@ -9001,7 +9010,7 @@
         <v>51</v>
       </c>
       <c r="Q459" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R459" s="20">
         <f>R457</f>
@@ -9013,13 +9022,13 @@
         <v>67</v>
       </c>
       <c r="Q461" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R461">
         <v>0</v>
       </c>
       <c r="T461" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="462" spans="1:20" x14ac:dyDescent="0.25">
@@ -9027,7 +9036,7 @@
         <v>70</v>
       </c>
       <c r="Q462" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R462">
         <v>0</v>
@@ -9038,7 +9047,7 @@
         <v>71</v>
       </c>
       <c r="Q463" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R463">
         <v>0</v>
@@ -9049,7 +9058,7 @@
         <v>43</v>
       </c>
       <c r="Q464" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R464">
         <v>0</v>
@@ -9060,7 +9069,7 @@
         <v>44</v>
       </c>
       <c r="Q465" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R465">
         <v>0</v>
@@ -9080,13 +9089,13 @@
       <c r="B468" s="6"/>
       <c r="C468" s="6"/>
       <c r="Q468" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R468">
         <v>10</v>
       </c>
       <c r="U468" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="469" spans="1:21" x14ac:dyDescent="0.25">
@@ -9096,16 +9105,16 @@
       <c r="B469" s="6"/>
       <c r="C469" s="6"/>
       <c r="Q469" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R469">
         <v>15</v>
       </c>
       <c r="T469" t="s">
+        <v>254</v>
+      </c>
+      <c r="U469" t="s">
         <v>255</v>
-      </c>
-      <c r="U469" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="470" spans="1:21" x14ac:dyDescent="0.25">
@@ -9136,13 +9145,13 @@
       <c r="B473" s="6"/>
       <c r="C473" s="6"/>
       <c r="Q473" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R473">
         <v>15</v>
       </c>
       <c r="U473" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="474" spans="1:21" x14ac:dyDescent="0.25">
@@ -9152,14 +9161,14 @@
       <c r="B474" s="6"/>
       <c r="C474" s="6"/>
       <c r="Q474" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R474" s="24">
         <f>R473</f>
         <v>15</v>
       </c>
       <c r="T474" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="475" spans="1:21" x14ac:dyDescent="0.25">
@@ -9169,14 +9178,14 @@
       <c r="B475" s="6"/>
       <c r="C475" s="6"/>
       <c r="Q475" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R475" s="24">
         <f>R473</f>
         <v>15</v>
       </c>
       <c r="T475" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="476" spans="1:21" x14ac:dyDescent="0.25">
@@ -9191,13 +9200,13 @@
       <c r="B477" s="6"/>
       <c r="C477" s="6"/>
       <c r="Q477" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R477">
         <v>0.6</v>
       </c>
       <c r="U477" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="478" spans="1:21" x14ac:dyDescent="0.25">
@@ -9207,13 +9216,13 @@
       <c r="B478" s="6"/>
       <c r="C478" s="6"/>
       <c r="Q478" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R478" s="4">
         <v>1.6</v>
       </c>
       <c r="U478" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="479" spans="1:21" x14ac:dyDescent="0.25">
@@ -9223,14 +9232,14 @@
       <c r="B479" s="6"/>
       <c r="C479" s="6"/>
       <c r="Q479" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R479" s="24">
         <f>AVERAGE(R477:R478)</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="T479" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="480" spans="1:21" x14ac:dyDescent="0.25">
@@ -9240,7 +9249,7 @@
       <c r="B480" s="6"/>
       <c r="C480" s="6"/>
       <c r="Q480" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R480" s="24">
         <f>AVERAGE(R477:R478)</f>
@@ -9254,7 +9263,7 @@
       <c r="B481" s="6"/>
       <c r="C481" s="6"/>
       <c r="Q481" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R481" s="24">
         <f>AVERAGE(R477:R478)</f>
@@ -9268,7 +9277,7 @@
       <c r="B482" s="6"/>
       <c r="C482" s="6"/>
       <c r="Q482" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R482" s="24">
         <f>AVERAGE(R477:R478)</f>
@@ -9282,7 +9291,7 @@
       <c r="B483" s="6"/>
       <c r="C483" s="6"/>
       <c r="Q483" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R483" s="24">
         <f>AVERAGE(R477:R478)</f>
@@ -9291,7 +9300,7 @@
     </row>
     <row r="485" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
@@ -9316,28 +9325,28 @@
     </row>
     <row r="486" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A486" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B486" s="18"/>
       <c r="C486" s="18"/>
     </row>
     <row r="487" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A487" s="18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B487" s="18"/>
       <c r="C487" s="18"/>
     </row>
     <row r="488" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A488" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B488" s="18"/>
       <c r="C488" s="18"/>
     </row>
     <row r="489" spans="1:21" x14ac:dyDescent="0.25">
       <c r="Q489" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R489" s="23">
         <v>1</v>
@@ -9349,7 +9358,7 @@
     </row>
     <row r="490" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B490" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C490" s="4"/>
       <c r="D490" s="4"/>
@@ -9366,20 +9375,20 @@
       <c r="O490" s="4"/>
       <c r="P490" s="4"/>
       <c r="Q490" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R490" s="22">
         <v>1.4</v>
       </c>
       <c r="S490" s="4"/>
       <c r="T490" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="U490" s="4"/>
     </row>
     <row r="491" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B491" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C491" s="4"/>
       <c r="D491" s="4"/>
@@ -9396,20 +9405,20 @@
       <c r="O491" s="4"/>
       <c r="P491" s="4"/>
       <c r="Q491" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R491" s="22">
         <v>1.4</v>
       </c>
       <c r="S491" s="4"/>
       <c r="T491" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="U491" s="4"/>
     </row>
     <row r="492" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B492" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D492" s="4"/>
       <c r="E492" s="4"/>
@@ -9425,14 +9434,14 @@
       <c r="O492" s="4"/>
       <c r="P492" s="4"/>
       <c r="Q492" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R492" s="22">
         <v>1.2</v>
       </c>
       <c r="S492" s="4"/>
       <c r="T492" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="U492" s="4"/>
     </row>
@@ -9454,14 +9463,14 @@
       <c r="O493" s="4"/>
       <c r="P493" s="4"/>
       <c r="Q493" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R493" s="22">
         <v>1.25</v>
       </c>
       <c r="S493" s="4"/>
       <c r="T493" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="U493" s="4"/>
     </row>
@@ -9472,7 +9481,7 @@
     </row>
     <row r="495" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B495" s="15"/>
       <c r="C495" s="15"/>
@@ -9497,7 +9506,7 @@
     </row>
     <row r="496" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
@@ -9522,27 +9531,27 @@
     </row>
     <row r="497" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A497" s="19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B497" s="19"/>
       <c r="C497" s="19"/>
     </row>
     <row r="498" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A498" s="19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B498" s="19"/>
       <c r="C498" s="19"/>
     </row>
     <row r="499" spans="1:20" x14ac:dyDescent="0.25">
       <c r="Q499" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R499" s="5">
         <v>0</v>
       </c>
       <c r="S499" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T499" s="5" t="s">
         <v>151</v>
@@ -9550,13 +9559,13 @@
     </row>
     <row r="500" spans="1:20" x14ac:dyDescent="0.25">
       <c r="Q500" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R500" s="5">
         <v>0</v>
       </c>
       <c r="S500" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="T500" s="5" t="s">
         <v>151</v>
@@ -9570,7 +9579,7 @@
     </row>
     <row r="502" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A502" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B502" s="21"/>
       <c r="C502" s="21"/>
@@ -9584,10 +9593,10 @@
         <v>7</v>
       </c>
       <c r="O503" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q503" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R503">
         <v>5</v>
@@ -9598,10 +9607,10 @@
         <v>7</v>
       </c>
       <c r="O504" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q504" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R504" s="4">
         <v>5</v>
@@ -9612,10 +9621,10 @@
         <v>7</v>
       </c>
       <c r="O505" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q505" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R505" s="4">
         <v>5</v>
@@ -9626,10 +9635,10 @@
         <v>7</v>
       </c>
       <c r="O506" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q506" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R506" s="4">
         <v>15</v>
@@ -9640,10 +9649,10 @@
         <v>7</v>
       </c>
       <c r="O507" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q507" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R507" s="4">
         <v>5</v>
@@ -9654,10 +9663,10 @@
         <v>7</v>
       </c>
       <c r="O508" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q508" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R508" s="4">
         <v>-15</v>
@@ -9668,10 +9677,10 @@
         <v>25</v>
       </c>
       <c r="O509" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q509" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R509" s="20">
         <f t="shared" ref="R509:R514" si="19">R503</f>
@@ -9683,10 +9692,10 @@
         <v>25</v>
       </c>
       <c r="O510" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q510" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R510" s="20">
         <f t="shared" si="19"/>
@@ -9698,10 +9707,10 @@
         <v>25</v>
       </c>
       <c r="O511" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q511" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R511" s="20">
         <f t="shared" si="19"/>
@@ -9713,10 +9722,10 @@
         <v>25</v>
       </c>
       <c r="O512" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q512" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R512" s="20">
         <f t="shared" si="19"/>
@@ -9728,10 +9737,10 @@
         <v>25</v>
       </c>
       <c r="O513" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q513" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R513" s="20">
         <f t="shared" si="19"/>
@@ -9743,10 +9752,10 @@
         <v>25</v>
       </c>
       <c r="O514" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q514" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R514" s="20">
         <f t="shared" si="19"/>
@@ -9758,10 +9767,10 @@
         <v>21</v>
       </c>
       <c r="O515" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q515" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R515" s="20">
         <f t="shared" ref="R515:R520" si="20">R503</f>
@@ -9773,10 +9782,10 @@
         <v>21</v>
       </c>
       <c r="O516" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q516" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R516" s="20">
         <f t="shared" si="20"/>
@@ -9788,10 +9797,10 @@
         <v>21</v>
       </c>
       <c r="O517" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q517" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R517" s="20">
         <f t="shared" si="20"/>
@@ -9803,10 +9812,10 @@
         <v>21</v>
       </c>
       <c r="O518" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q518" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R518" s="20">
         <f t="shared" si="20"/>
@@ -9818,10 +9827,10 @@
         <v>21</v>
       </c>
       <c r="O519" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q519" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R519" s="20">
         <f t="shared" si="20"/>
@@ -9833,10 +9842,10 @@
         <v>21</v>
       </c>
       <c r="O520" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q520" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R520" s="20">
         <f t="shared" si="20"/>
@@ -9848,10 +9857,10 @@
         <v>23</v>
       </c>
       <c r="O521" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q521" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R521" s="20">
         <f t="shared" ref="R521:R526" si="21">R503</f>
@@ -9863,10 +9872,10 @@
         <v>23</v>
       </c>
       <c r="O522" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q522" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R522" s="20">
         <f t="shared" si="21"/>
@@ -9878,10 +9887,10 @@
         <v>23</v>
       </c>
       <c r="O523" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q523" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R523" s="20">
         <f t="shared" si="21"/>
@@ -9893,10 +9902,10 @@
         <v>23</v>
       </c>
       <c r="O524" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q524" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R524" s="20">
         <f t="shared" si="21"/>
@@ -9908,10 +9917,10 @@
         <v>23</v>
       </c>
       <c r="O525" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q525" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R525" s="20">
         <f t="shared" si="21"/>
@@ -9923,10 +9932,10 @@
         <v>23</v>
       </c>
       <c r="O526" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q526" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R526" s="20">
         <f t="shared" si="21"/>
@@ -9935,7 +9944,7 @@
     </row>
     <row r="528" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A528" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B528" s="21"/>
       <c r="C528" s="21"/>
@@ -9945,10 +9954,10 @@
         <v>14</v>
       </c>
       <c r="O529" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q529" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R529">
         <v>5</v>
@@ -9959,10 +9968,10 @@
         <v>14</v>
       </c>
       <c r="O530" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q530" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R530">
         <v>5</v>
@@ -9973,10 +9982,10 @@
         <v>14</v>
       </c>
       <c r="O531" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q531" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R531">
         <v>5</v>
@@ -9987,10 +9996,10 @@
         <v>14</v>
       </c>
       <c r="O532" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q532" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R532">
         <v>15</v>
@@ -10001,10 +10010,10 @@
         <v>14</v>
       </c>
       <c r="O533" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q533" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R533">
         <v>5</v>
@@ -10015,10 +10024,10 @@
         <v>14</v>
       </c>
       <c r="O534" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q534" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R534">
         <v>-15</v>
@@ -10029,10 +10038,10 @@
         <v>15</v>
       </c>
       <c r="O535" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q535" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R535" s="20">
         <f t="shared" ref="R535:R540" si="22">R529</f>
@@ -10044,10 +10053,10 @@
         <v>15</v>
       </c>
       <c r="O536" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q536" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R536" s="20">
         <f t="shared" si="22"/>
@@ -10059,10 +10068,10 @@
         <v>15</v>
       </c>
       <c r="O537" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q537" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R537" s="20">
         <f t="shared" si="22"/>
@@ -10074,10 +10083,10 @@
         <v>15</v>
       </c>
       <c r="O538" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q538" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R538" s="20">
         <f t="shared" si="22"/>
@@ -10089,10 +10098,10 @@
         <v>15</v>
       </c>
       <c r="O539" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q539" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R539" s="20">
         <f t="shared" si="22"/>
@@ -10104,10 +10113,10 @@
         <v>15</v>
       </c>
       <c r="O540" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q540" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R540" s="20">
         <f t="shared" si="22"/>
@@ -10119,10 +10128,10 @@
         <v>19</v>
       </c>
       <c r="O541" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q541" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R541" s="20">
         <f t="shared" ref="R541:R546" si="23">R529</f>
@@ -10134,10 +10143,10 @@
         <v>19</v>
       </c>
       <c r="O542" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q542" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R542" s="20">
         <f t="shared" si="23"/>
@@ -10149,10 +10158,10 @@
         <v>19</v>
       </c>
       <c r="O543" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q543" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R543" s="20">
         <f t="shared" si="23"/>
@@ -10164,10 +10173,10 @@
         <v>19</v>
       </c>
       <c r="O544" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q544" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R544" s="20">
         <f t="shared" si="23"/>
@@ -10179,10 +10188,10 @@
         <v>19</v>
       </c>
       <c r="O545" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q545" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R545" s="20">
         <f t="shared" si="23"/>
@@ -10194,10 +10203,10 @@
         <v>19</v>
       </c>
       <c r="O546" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q546" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R546" s="20">
         <f t="shared" si="23"/>
@@ -10206,13 +10215,13 @@
     </row>
     <row r="547" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O547" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q547" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R547" s="20">
         <f t="shared" ref="R547:R552" si="24">R529</f>
@@ -10221,13 +10230,13 @@
     </row>
     <row r="548" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O548" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q548" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R548" s="20">
         <f t="shared" si="24"/>
@@ -10236,13 +10245,13 @@
     </row>
     <row r="549" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O549" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q549" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R549" s="20">
         <f t="shared" si="24"/>
@@ -10251,13 +10260,13 @@
     </row>
     <row r="550" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O550" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q550" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R550" s="20">
         <f t="shared" si="24"/>
@@ -10266,13 +10275,13 @@
     </row>
     <row r="551" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O551" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q551" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R551" s="20">
         <f t="shared" si="24"/>
@@ -10281,13 +10290,13 @@
     </row>
     <row r="552" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O552" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q552" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R552" s="20">
         <f t="shared" si="24"/>
@@ -10299,10 +10308,10 @@
         <v>22</v>
       </c>
       <c r="O553" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q553" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R553" s="20">
         <f t="shared" ref="R553:R558" si="25">R529</f>
@@ -10314,10 +10323,10 @@
         <v>22</v>
       </c>
       <c r="O554" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q554" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R554" s="20">
         <f t="shared" si="25"/>
@@ -10329,10 +10338,10 @@
         <v>22</v>
       </c>
       <c r="O555" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q555" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R555" s="20">
         <f t="shared" si="25"/>
@@ -10344,10 +10353,10 @@
         <v>22</v>
       </c>
       <c r="O556" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q556" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R556" s="20">
         <f t="shared" si="25"/>
@@ -10359,10 +10368,10 @@
         <v>22</v>
       </c>
       <c r="O557" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q557" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R557" s="20">
         <f t="shared" si="25"/>
@@ -10374,10 +10383,10 @@
         <v>22</v>
       </c>
       <c r="O558" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q558" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R558" s="20">
         <f t="shared" si="25"/>
@@ -10389,10 +10398,10 @@
         <v>27</v>
       </c>
       <c r="O559" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q559" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R559" s="20">
         <f t="shared" ref="R559:R564" si="26">R529</f>
@@ -10404,10 +10413,10 @@
         <v>27</v>
       </c>
       <c r="O560" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q560" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R560" s="20">
         <f t="shared" si="26"/>
@@ -10419,10 +10428,10 @@
         <v>27</v>
       </c>
       <c r="O561" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q561" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R561" s="20">
         <f t="shared" si="26"/>
@@ -10434,10 +10443,10 @@
         <v>27</v>
       </c>
       <c r="O562" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q562" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R562" s="20">
         <f t="shared" si="26"/>
@@ -10449,10 +10458,10 @@
         <v>27</v>
       </c>
       <c r="O563" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q563" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R563" s="20">
         <f t="shared" si="26"/>
@@ -10464,10 +10473,10 @@
         <v>27</v>
       </c>
       <c r="O564" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q564" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R564" s="20">
         <f t="shared" si="26"/>
@@ -10479,10 +10488,10 @@
         <v>26</v>
       </c>
       <c r="O565" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q565" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R565" s="20">
         <f t="shared" ref="R565:R570" si="27">R529</f>
@@ -10494,10 +10503,10 @@
         <v>26</v>
       </c>
       <c r="O566" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q566" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R566" s="20">
         <f t="shared" si="27"/>
@@ -10509,10 +10518,10 @@
         <v>26</v>
       </c>
       <c r="O567" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q567" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R567" s="20">
         <f t="shared" si="27"/>
@@ -10524,10 +10533,10 @@
         <v>26</v>
       </c>
       <c r="O568" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q568" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R568" s="20">
         <f t="shared" si="27"/>
@@ -10539,10 +10548,10 @@
         <v>26</v>
       </c>
       <c r="O569" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q569" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R569" s="20">
         <f t="shared" si="27"/>
@@ -10554,10 +10563,10 @@
         <v>26</v>
       </c>
       <c r="O570" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q570" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R570" s="20">
         <f t="shared" si="27"/>
@@ -10571,17 +10580,17 @@
       <c r="B571" s="6"/>
       <c r="C571" s="6"/>
       <c r="O571" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q571" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R571" s="20">
         <f t="shared" ref="R571:R576" si="28">R529</f>
         <v>5</v>
       </c>
       <c r="T571" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="572" spans="1:20" x14ac:dyDescent="0.25">
@@ -10591,10 +10600,10 @@
       <c r="B572" s="6"/>
       <c r="C572" s="6"/>
       <c r="O572" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q572" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R572" s="20">
         <f t="shared" si="28"/>
@@ -10608,10 +10617,10 @@
       <c r="B573" s="6"/>
       <c r="C573" s="6"/>
       <c r="O573" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q573" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R573" s="20">
         <f t="shared" si="28"/>
@@ -10625,10 +10634,10 @@
       <c r="B574" s="6"/>
       <c r="C574" s="6"/>
       <c r="O574" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q574" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R574" s="20">
         <f t="shared" si="28"/>
@@ -10642,10 +10651,10 @@
       <c r="B575" s="6"/>
       <c r="C575" s="6"/>
       <c r="O575" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q575" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R575" s="20">
         <f t="shared" si="28"/>
@@ -10659,10 +10668,10 @@
       <c r="B576" s="6"/>
       <c r="C576" s="6"/>
       <c r="O576" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q576" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R576" s="20">
         <f t="shared" si="28"/>
@@ -10676,17 +10685,17 @@
       <c r="B577" s="6"/>
       <c r="C577" s="6"/>
       <c r="O577" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q577" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R577" s="20">
         <f t="shared" ref="R577:R582" si="29">R529</f>
         <v>5</v>
       </c>
       <c r="T577" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="578" spans="1:20" x14ac:dyDescent="0.25">
@@ -10696,10 +10705,10 @@
       <c r="B578" s="6"/>
       <c r="C578" s="6"/>
       <c r="O578" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q578" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R578" s="20">
         <f t="shared" si="29"/>
@@ -10713,10 +10722,10 @@
       <c r="B579" s="6"/>
       <c r="C579" s="6"/>
       <c r="O579" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q579" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R579" s="20">
         <f t="shared" si="29"/>
@@ -10730,10 +10739,10 @@
       <c r="B580" s="6"/>
       <c r="C580" s="6"/>
       <c r="O580" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q580" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R580" s="20">
         <f t="shared" si="29"/>
@@ -10747,10 +10756,10 @@
       <c r="B581" s="6"/>
       <c r="C581" s="6"/>
       <c r="O581" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q581" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R581" s="20">
         <f t="shared" si="29"/>
@@ -10762,10 +10771,10 @@
         <v>42</v>
       </c>
       <c r="O582" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q582" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R582" s="20">
         <f t="shared" si="29"/>
@@ -10774,7 +10783,7 @@
     </row>
     <row r="583" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A583" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B583" s="21"/>
       <c r="C583" s="21"/>
@@ -10784,10 +10793,10 @@
         <v>32</v>
       </c>
       <c r="O584" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q584" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R584">
         <v>10</v>
@@ -10798,10 +10807,10 @@
         <v>32</v>
       </c>
       <c r="O585" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q585" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R585">
         <v>10</v>
@@ -10812,10 +10821,10 @@
         <v>32</v>
       </c>
       <c r="O586" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q586" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R586">
         <v>10</v>
@@ -10826,10 +10835,10 @@
         <v>32</v>
       </c>
       <c r="O587" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q587" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R587">
         <v>10</v>
@@ -10840,10 +10849,10 @@
         <v>32</v>
       </c>
       <c r="O588" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q588" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R588">
         <v>20</v>
@@ -10854,10 +10863,10 @@
         <v>32</v>
       </c>
       <c r="O589" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q589" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R589">
         <v>10</v>
@@ -10868,10 +10877,10 @@
         <v>32</v>
       </c>
       <c r="O590" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q590" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R590">
         <v>-10</v>
@@ -10882,10 +10891,10 @@
         <v>32</v>
       </c>
       <c r="O591" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q591" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R591">
         <v>-25</v>
@@ -10896,10 +10905,10 @@
         <v>33</v>
       </c>
       <c r="O592" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q592" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R592">
         <v>10</v>
@@ -10910,10 +10919,10 @@
         <v>33</v>
       </c>
       <c r="O593" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q593" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R593">
         <v>10</v>
@@ -10924,10 +10933,10 @@
         <v>33</v>
       </c>
       <c r="O594" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q594" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R594">
         <v>10</v>
@@ -10938,10 +10947,10 @@
         <v>33</v>
       </c>
       <c r="O595" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q595" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R595">
         <v>20</v>
@@ -10952,10 +10961,10 @@
         <v>33</v>
       </c>
       <c r="O596" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q596" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R596">
         <v>10</v>
@@ -10966,10 +10975,10 @@
         <v>33</v>
       </c>
       <c r="O597" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q597" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R597">
         <v>-10</v>
@@ -10987,10 +10996,10 @@
         <v>38</v>
       </c>
       <c r="O600" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q600" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R600">
         <v>10</v>
@@ -11001,10 +11010,10 @@
         <v>38</v>
       </c>
       <c r="O601" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q601" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R601">
         <v>10</v>
@@ -11015,10 +11024,10 @@
         <v>38</v>
       </c>
       <c r="O602" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q602" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R602">
         <v>10</v>
@@ -11029,10 +11038,10 @@
         <v>38</v>
       </c>
       <c r="O603" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q603" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R603">
         <v>10</v>
@@ -11043,10 +11052,10 @@
         <v>38</v>
       </c>
       <c r="O604" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q604" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R604">
         <v>86.7</v>
@@ -11057,10 +11066,10 @@
         <v>38</v>
       </c>
       <c r="O605" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q605" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R605">
         <v>46.7</v>
@@ -11071,10 +11080,10 @@
         <v>38</v>
       </c>
       <c r="O606" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q606" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R606">
         <v>6.7</v>
@@ -11085,10 +11094,10 @@
         <v>38</v>
       </c>
       <c r="O607" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q607" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R607">
         <v>-26.7</v>
@@ -11099,17 +11108,17 @@
         <v>68</v>
       </c>
       <c r="O608" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q608" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R608" s="24">
         <f>R600</f>
         <v>10</v>
       </c>
       <c r="T608" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="609" spans="1:18" x14ac:dyDescent="0.25">
@@ -11117,10 +11126,10 @@
         <v>68</v>
       </c>
       <c r="O609" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q609" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R609" s="24">
         <f t="shared" ref="R609:R615" si="30">R601</f>
@@ -11132,10 +11141,10 @@
         <v>68</v>
       </c>
       <c r="O610" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q610" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R610" s="24">
         <f t="shared" si="30"/>
@@ -11147,10 +11156,10 @@
         <v>68</v>
       </c>
       <c r="O611" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q611" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R611" s="24">
         <f t="shared" si="30"/>
@@ -11162,10 +11171,10 @@
         <v>68</v>
       </c>
       <c r="O612" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q612" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R612" s="24">
         <f t="shared" si="30"/>
@@ -11177,10 +11186,10 @@
         <v>68</v>
       </c>
       <c r="O613" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q613" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R613" s="24">
         <f t="shared" si="30"/>
@@ -11192,10 +11201,10 @@
         <v>68</v>
       </c>
       <c r="O614" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q614" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R614" s="24">
         <f t="shared" si="30"/>
@@ -11207,10 +11216,10 @@
         <v>68</v>
       </c>
       <c r="O615" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q615" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R615" s="24">
         <f t="shared" si="30"/>
@@ -11219,7 +11228,7 @@
     </row>
     <row r="617" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A617" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B617" s="21"/>
       <c r="C617" s="21"/>
@@ -11229,10 +11238,10 @@
         <v>40</v>
       </c>
       <c r="O618" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q618" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R618">
         <v>6.9</v>
@@ -11243,10 +11252,10 @@
         <v>40</v>
       </c>
       <c r="O619" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q619" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R619">
         <v>9.6</v>
@@ -11257,10 +11266,10 @@
         <v>40</v>
       </c>
       <c r="O620" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q620" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R620">
         <v>10</v>
@@ -11271,10 +11280,10 @@
         <v>40</v>
       </c>
       <c r="O621" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q621" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R621">
         <v>10</v>
@@ -11285,10 +11294,10 @@
         <v>40</v>
       </c>
       <c r="O622" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q622" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R622">
         <v>68.400000000000006</v>
@@ -11299,10 +11308,10 @@
         <v>40</v>
       </c>
       <c r="O623" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q623" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R623">
         <v>22.4</v>
@@ -11313,10 +11322,10 @@
         <v>40</v>
       </c>
       <c r="O624" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q624" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R624">
         <v>-20</v>
@@ -11327,10 +11336,10 @@
         <v>40</v>
       </c>
       <c r="O625" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q625" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R625">
         <v>-50</v>
@@ -11338,7 +11347,7 @@
     </row>
     <row r="627" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A627" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B627" s="21"/>
       <c r="C627" s="21"/>
@@ -11348,10 +11357,10 @@
         <v>34</v>
       </c>
       <c r="O628" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q628" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R628">
         <v>4</v>
@@ -11362,10 +11371,10 @@
         <v>34</v>
       </c>
       <c r="O629" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q629" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R629">
         <v>4</v>
@@ -11376,10 +11385,10 @@
         <v>34</v>
       </c>
       <c r="O630" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q630" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R630">
         <v>4</v>
@@ -11390,10 +11399,10 @@
         <v>34</v>
       </c>
       <c r="O631" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q631" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R631">
         <v>4</v>
@@ -11404,10 +11413,10 @@
         <v>34</v>
       </c>
       <c r="O632" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q632" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R632">
         <v>140</v>
@@ -11418,10 +11427,10 @@
         <v>34</v>
       </c>
       <c r="O633" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q633" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R633">
         <v>90</v>
@@ -11432,10 +11441,10 @@
         <v>34</v>
       </c>
       <c r="O634" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q634" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R634">
         <v>40</v>
@@ -11446,10 +11455,10 @@
         <v>34</v>
       </c>
       <c r="O635" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q635" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R635">
         <v>-10</v>
@@ -11460,10 +11469,10 @@
         <v>35</v>
       </c>
       <c r="O636" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q636" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R636" s="20">
         <f t="shared" ref="R636:R643" si="31">R628</f>
@@ -11475,10 +11484,10 @@
         <v>35</v>
       </c>
       <c r="O637" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q637" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R637" s="20">
         <f t="shared" si="31"/>
@@ -11490,10 +11499,10 @@
         <v>35</v>
       </c>
       <c r="O638" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q638" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R638" s="20">
         <f t="shared" si="31"/>
@@ -11505,10 +11514,10 @@
         <v>35</v>
       </c>
       <c r="O639" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q639" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R639" s="20">
         <f t="shared" si="31"/>
@@ -11520,10 +11529,10 @@
         <v>35</v>
       </c>
       <c r="O640" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q640" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R640" s="20">
         <f t="shared" si="31"/>
@@ -11535,10 +11544,10 @@
         <v>35</v>
       </c>
       <c r="O641" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q641" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R641" s="20">
         <f t="shared" si="31"/>
@@ -11550,10 +11559,10 @@
         <v>35</v>
       </c>
       <c r="O642" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q642" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R642" s="20">
         <f t="shared" si="31"/>
@@ -11565,10 +11574,10 @@
         <v>35</v>
       </c>
       <c r="O643" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q643" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R643" s="20">
         <f t="shared" si="31"/>
@@ -11577,7 +11586,7 @@
     </row>
     <row r="645" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A645" s="21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B645" s="21"/>
       <c r="C645" s="21"/>
@@ -11587,10 +11596,10 @@
         <v>28</v>
       </c>
       <c r="O646" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q646" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R646">
         <v>50</v>
@@ -11601,10 +11610,10 @@
         <v>28</v>
       </c>
       <c r="O647" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q647" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R647">
         <v>40</v>
@@ -11615,10 +11624,10 @@
         <v>28</v>
       </c>
       <c r="O648" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q648" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R648">
         <v>20</v>
@@ -11626,31 +11635,31 @@
     </row>
     <row r="649" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O649" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q649" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R649" s="20">
         <f>R646</f>
         <v>50</v>
       </c>
       <c r="T649" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="650" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A650" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O650" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q650" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R650" s="20">
         <f t="shared" ref="R650:R651" si="32">R647</f>
@@ -11659,13 +11668,13 @@
     </row>
     <row r="651" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A651" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O651" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q651" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R651" s="20">
         <f t="shared" si="32"/>
@@ -11677,10 +11686,10 @@
         <v>30</v>
       </c>
       <c r="O652" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q652" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R652" s="20">
         <f>R646</f>
@@ -11692,10 +11701,10 @@
         <v>30</v>
       </c>
       <c r="O653" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q653" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R653" s="20">
         <f t="shared" ref="R653:R654" si="33">R647</f>
@@ -11707,10 +11716,10 @@
         <v>30</v>
       </c>
       <c r="O654" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q654" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R654" s="20">
         <f t="shared" si="33"/>
@@ -11722,10 +11731,10 @@
         <v>36</v>
       </c>
       <c r="O655" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q655" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R655">
         <v>120</v>
@@ -11736,10 +11745,10 @@
         <v>36</v>
       </c>
       <c r="O656" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q656" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R656">
         <v>90</v>
@@ -11750,10 +11759,10 @@
         <v>36</v>
       </c>
       <c r="O657" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q657" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R657">
         <v>50</v>
@@ -11764,10 +11773,10 @@
         <v>36</v>
       </c>
       <c r="O658" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q658" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R658">
         <v>30</v>
@@ -11778,10 +11787,10 @@
         <v>39</v>
       </c>
       <c r="O659" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q659" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R659">
         <v>40</v>
@@ -11792,10 +11801,10 @@
         <v>39</v>
       </c>
       <c r="O660" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q660" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R660">
         <v>20</v>
@@ -11808,19 +11817,19 @@
       <c r="B661" s="6"/>
       <c r="C661" s="6"/>
       <c r="O661" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q661" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R661">
         <v>155</v>
       </c>
       <c r="T661" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="U661" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="662" spans="1:21" x14ac:dyDescent="0.25">
@@ -11830,10 +11839,10 @@
       <c r="B662" s="6"/>
       <c r="C662" s="6"/>
       <c r="O662" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q662" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R662">
         <v>155</v>
@@ -11846,10 +11855,10 @@
       <c r="B663" s="6"/>
       <c r="C663" s="6"/>
       <c r="O663" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q663" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R663">
         <v>155</v>
@@ -11857,7 +11866,7 @@
     </row>
     <row r="665" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A665" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B665" s="21"/>
       <c r="C665" s="21"/>
@@ -11867,7 +11876,7 @@
         <v>46</v>
       </c>
       <c r="Q666" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R666">
         <v>3.4</v>
@@ -11878,7 +11887,7 @@
         <v>46</v>
       </c>
       <c r="Q667" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R667">
         <v>62</v>
@@ -11891,14 +11900,14 @@
       <c r="B668" s="6"/>
       <c r="C668" s="6"/>
       <c r="Q668" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R668" s="20">
         <f>R666</f>
         <v>3.4</v>
       </c>
       <c r="T668" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="669" spans="1:21" x14ac:dyDescent="0.25">
@@ -11908,7 +11917,7 @@
       <c r="B669" s="6"/>
       <c r="C669" s="6"/>
       <c r="Q669" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R669" s="20">
         <f>R667</f>
@@ -11920,7 +11929,7 @@
         <v>45</v>
       </c>
       <c r="Q670" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R670">
         <v>0.31</v>
@@ -11931,7 +11940,7 @@
         <v>45</v>
       </c>
       <c r="Q671" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R671">
         <v>129</v>
@@ -11942,13 +11951,13 @@
         <v>48</v>
       </c>
       <c r="Q672" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R672">
         <v>0.62</v>
       </c>
       <c r="T672" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="673" spans="1:20" x14ac:dyDescent="0.25">
@@ -11956,7 +11965,7 @@
         <v>48</v>
       </c>
       <c r="Q673" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R673">
         <v>98</v>
@@ -11969,14 +11978,14 @@
       <c r="B674" s="6"/>
       <c r="C674" s="6"/>
       <c r="Q674" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R674" s="20">
         <f>R672</f>
         <v>0.62</v>
       </c>
       <c r="T674" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="675" spans="1:20" x14ac:dyDescent="0.25">
@@ -11986,7 +11995,7 @@
       <c r="B675" s="6"/>
       <c r="C675" s="6"/>
       <c r="Q675" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R675" s="20">
         <f>R673</f>
@@ -11998,14 +12007,14 @@
         <v>53</v>
       </c>
       <c r="Q676" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R676" s="20">
         <f>R674</f>
         <v>0.62</v>
       </c>
       <c r="T676" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="677" spans="1:20" x14ac:dyDescent="0.25">
@@ -12013,7 +12022,7 @@
         <v>53</v>
       </c>
       <c r="Q677" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R677" s="20">
         <f>R675</f>
@@ -12025,7 +12034,7 @@
         <v>49</v>
       </c>
       <c r="Q678" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R678">
         <v>2</v>
@@ -12036,7 +12045,7 @@
         <v>49</v>
       </c>
       <c r="Q679" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R679">
         <v>120</v>
@@ -12047,7 +12056,7 @@
         <v>50</v>
       </c>
       <c r="Q680" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="681" spans="1:20" x14ac:dyDescent="0.25">
@@ -12055,7 +12064,7 @@
         <v>50</v>
       </c>
       <c r="Q681" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="682" spans="1:20" x14ac:dyDescent="0.25">
@@ -12063,7 +12072,7 @@
         <v>51</v>
       </c>
       <c r="Q682" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R682" s="20">
         <f>R680</f>
@@ -12075,7 +12084,7 @@
         <v>51</v>
       </c>
       <c r="Q683" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R683" s="20">
         <f>R681</f>
@@ -12087,13 +12096,13 @@
         <v>67</v>
       </c>
       <c r="Q685" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R685">
         <v>0</v>
       </c>
       <c r="T685" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="686" spans="1:20" x14ac:dyDescent="0.25">
@@ -12101,7 +12110,7 @@
         <v>70</v>
       </c>
       <c r="Q686" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R686">
         <v>0</v>
@@ -12112,7 +12121,7 @@
         <v>71</v>
       </c>
       <c r="Q687" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R687">
         <v>0</v>
@@ -12123,7 +12132,7 @@
         <v>43</v>
       </c>
       <c r="Q688" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R688">
         <v>0</v>
@@ -12134,7 +12143,7 @@
         <v>44</v>
       </c>
       <c r="Q689" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R689">
         <v>0</v>
@@ -12154,13 +12163,13 @@
       <c r="B692" s="6"/>
       <c r="C692" s="6"/>
       <c r="Q692" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R692">
         <v>20</v>
       </c>
       <c r="U692" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="693" spans="1:21" x14ac:dyDescent="0.25">
@@ -12170,16 +12179,16 @@
       <c r="B693" s="6"/>
       <c r="C693" s="6"/>
       <c r="Q693" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R693">
         <v>22.5</v>
       </c>
       <c r="T693" t="s">
+        <v>254</v>
+      </c>
+      <c r="U693" t="s">
         <v>255</v>
-      </c>
-      <c r="U693" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="694" spans="1:21" x14ac:dyDescent="0.25">
@@ -12210,13 +12219,13 @@
       <c r="B697" s="6"/>
       <c r="C697" s="6"/>
       <c r="Q697" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R697">
         <v>105</v>
       </c>
       <c r="U697" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="698" spans="1:21" x14ac:dyDescent="0.25">
@@ -12226,14 +12235,14 @@
       <c r="B698" s="6"/>
       <c r="C698" s="6"/>
       <c r="Q698" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R698" s="24">
         <f>R697</f>
         <v>105</v>
       </c>
       <c r="T698" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="699" spans="1:21" x14ac:dyDescent="0.25">
@@ -12243,14 +12252,14 @@
       <c r="B699" s="6"/>
       <c r="C699" s="6"/>
       <c r="Q699" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R699" s="24">
         <f>R697</f>
         <v>105</v>
       </c>
       <c r="T699" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="700" spans="1:21" x14ac:dyDescent="0.25">
@@ -12265,13 +12274,13 @@
       <c r="B701" s="6"/>
       <c r="C701" s="6"/>
       <c r="Q701" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R701">
         <v>5.6</v>
       </c>
       <c r="U701" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="702" spans="1:21" x14ac:dyDescent="0.25">
@@ -12281,13 +12290,13 @@
       <c r="B702" s="6"/>
       <c r="C702" s="6"/>
       <c r="Q702" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R702" s="26">
         <v>3</v>
       </c>
       <c r="U702" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="703" spans="1:21" x14ac:dyDescent="0.25">
@@ -12297,14 +12306,14 @@
       <c r="B703" s="6"/>
       <c r="C703" s="6"/>
       <c r="Q703" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R703" s="24">
         <f>AVERAGE(R701:R702)</f>
         <v>4.3</v>
       </c>
       <c r="T703" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="704" spans="1:21" x14ac:dyDescent="0.25">
@@ -12314,7 +12323,7 @@
       <c r="B704" s="6"/>
       <c r="C704" s="6"/>
       <c r="Q704" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R704" s="24">
         <f>AVERAGE(R701:R702)</f>
@@ -12328,7 +12337,7 @@
       <c r="B705" s="6"/>
       <c r="C705" s="6"/>
       <c r="Q705" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R705" s="24">
         <f>AVERAGE(R701:R702)</f>
@@ -12342,7 +12351,7 @@
       <c r="B706" s="6"/>
       <c r="C706" s="6"/>
       <c r="Q706" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R706" s="24">
         <f>AVERAGE(R701:R702)</f>
@@ -12356,7 +12365,7 @@
       <c r="B707" s="6"/>
       <c r="C707" s="6"/>
       <c r="Q707" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R707" s="24">
         <f>AVERAGE(R701:R702)</f>
@@ -12370,7 +12379,7 @@
     </row>
     <row r="709" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B709" s="2"/>
       <c r="C709" s="2"/>
@@ -12395,19 +12404,19 @@
     </row>
     <row r="711" spans="1:21" x14ac:dyDescent="0.25">
       <c r="Q711" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R711" s="23">
         <v>1.2</v>
       </c>
       <c r="S711" s="5"/>
       <c r="T711" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="713" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B713" s="2"/>
       <c r="C713" s="2"/>
@@ -12449,7 +12458,7 @@
     </row>
     <row r="715" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
-        <v>152</v>
+        <v>338</v>
       </c>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -12481,7 +12490,7 @@
         <v>121</v>
       </c>
       <c r="U716" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="717" spans="1:21" x14ac:dyDescent="0.25">
@@ -12502,12 +12511,12 @@
         <v>120</v>
       </c>
       <c r="U717" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="718" spans="1:21" x14ac:dyDescent="0.25">
       <c r="H718" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P718" t="s">
         <v>119</v>
@@ -12523,142 +12532,29 @@
         <v>120</v>
       </c>
       <c r="U718" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="719" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A719" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B719" s="1"/>
-      <c r="C719" s="1"/>
-      <c r="D719" s="1"/>
-      <c r="E719" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="720" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="J720" t="s">
-        <v>126</v>
-      </c>
-      <c r="K720" t="s">
-        <v>127</v>
-      </c>
-      <c r="L720" t="s">
-        <v>128</v>
-      </c>
-      <c r="M720" t="s">
-        <v>138</v>
-      </c>
-      <c r="P720" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q720" t="s">
-        <v>147</v>
-      </c>
-      <c r="R720">
-        <v>33</v>
-      </c>
-      <c r="S720" t="s">
-        <v>120</v>
-      </c>
-      <c r="U720" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="721" spans="10:21" x14ac:dyDescent="0.25">
-      <c r="J721" t="s">
-        <v>126</v>
-      </c>
-      <c r="K721" t="s">
-        <v>127</v>
-      </c>
-      <c r="L721" t="s">
-        <v>128</v>
-      </c>
-      <c r="M721" t="s">
-        <v>139</v>
-      </c>
-      <c r="P721" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q721" t="s">
-        <v>147</v>
-      </c>
-      <c r="R721">
-        <v>38</v>
-      </c>
-      <c r="S721" t="s">
-        <v>120</v>
-      </c>
-      <c r="U721" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="722" spans="10:21" x14ac:dyDescent="0.25">
-      <c r="J722" t="s">
-        <v>126</v>
-      </c>
-      <c r="K722" t="s">
-        <v>127</v>
-      </c>
-      <c r="L722" t="s">
-        <v>128</v>
-      </c>
-      <c r="M722" t="s">
-        <v>140</v>
-      </c>
-      <c r="P722" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q722" t="s">
-        <v>147</v>
-      </c>
-      <c r="R722">
-        <v>41</v>
-      </c>
-      <c r="S722" t="s">
-        <v>120</v>
-      </c>
-      <c r="U722" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="723" spans="10:21" x14ac:dyDescent="0.25">
-      <c r="J723" t="s">
-        <v>126</v>
-      </c>
-      <c r="K723" t="s">
-        <v>127</v>
-      </c>
-      <c r="L723" t="s">
-        <v>128</v>
-      </c>
-      <c r="M723" t="s">
-        <v>187</v>
-      </c>
-      <c r="P723" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q723" t="s">
-        <v>147</v>
-      </c>
-      <c r="R723">
-        <v>33</v>
-      </c>
-      <c r="S723" t="s">
-        <v>120</v>
-      </c>
-      <c r="U723" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="724" spans="10:21" x14ac:dyDescent="0.25">
+      <c r="R719" s="11"/>
+    </row>
+    <row r="723" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A723" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B723" s="1"/>
+      <c r="C723" s="1"/>
+      <c r="D723" s="1"/>
+      <c r="E723" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="724" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J724" t="s">
         <v>126</v>
       </c>
       <c r="K724" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L724" t="s">
         <v>128</v>
@@ -12673,21 +12569,21 @@
         <v>147</v>
       </c>
       <c r="R724">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S724" t="s">
         <v>120</v>
       </c>
       <c r="U724" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="725" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="725" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J725" t="s">
         <v>126</v>
       </c>
       <c r="K725" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L725" t="s">
         <v>128</v>
@@ -12702,21 +12598,21 @@
         <v>147</v>
       </c>
       <c r="R725">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S725" t="s">
         <v>120</v>
       </c>
       <c r="U725" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="726" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="726" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J726" t="s">
         <v>126</v>
       </c>
       <c r="K726" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L726" t="s">
         <v>128</v>
@@ -12731,27 +12627,27 @@
         <v>147</v>
       </c>
       <c r="R726">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S726" t="s">
         <v>120</v>
       </c>
       <c r="U726" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="727" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="727" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J727" t="s">
         <v>126</v>
       </c>
       <c r="K727" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L727" t="s">
         <v>128</v>
       </c>
       <c r="M727" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P727" t="s">
         <v>119</v>
@@ -12760,21 +12656,24 @@
         <v>147</v>
       </c>
       <c r="R727">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S727" t="s">
         <v>120</v>
       </c>
       <c r="U727" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="728" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="728" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J728" t="s">
         <v>126</v>
       </c>
+      <c r="K728" t="s">
+        <v>129</v>
+      </c>
       <c r="L728" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M728" t="s">
         <v>138</v>
@@ -12792,15 +12691,18 @@
         <v>120</v>
       </c>
       <c r="U728" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="729" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="729" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J729" t="s">
         <v>126</v>
       </c>
+      <c r="K729" t="s">
+        <v>129</v>
+      </c>
       <c r="L729" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M729" t="s">
         <v>139</v>
@@ -12812,21 +12714,24 @@
         <v>147</v>
       </c>
       <c r="R729">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S729" t="s">
         <v>120</v>
       </c>
       <c r="U729" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="730" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="730" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J730" t="s">
         <v>126</v>
       </c>
+      <c r="K730" t="s">
+        <v>129</v>
+      </c>
       <c r="L730" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M730" t="s">
         <v>140</v>
@@ -12838,24 +12743,27 @@
         <v>147</v>
       </c>
       <c r="R730">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S730" t="s">
         <v>120</v>
       </c>
       <c r="U730" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="731" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="731" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J731" t="s">
         <v>126</v>
       </c>
+      <c r="K731" t="s">
+        <v>129</v>
+      </c>
       <c r="L731" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M731" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P731" t="s">
         <v>119</v>
@@ -12870,15 +12778,15 @@
         <v>120</v>
       </c>
       <c r="U731" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="732" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="732" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J732" t="s">
         <v>126</v>
       </c>
       <c r="L732" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M732" t="s">
         <v>138</v>
@@ -12890,21 +12798,21 @@
         <v>147</v>
       </c>
       <c r="R732">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S732" t="s">
         <v>120</v>
       </c>
       <c r="U732" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="733" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="733" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J733" t="s">
         <v>126</v>
       </c>
       <c r="L733" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M733" t="s">
         <v>139</v>
@@ -12916,21 +12824,21 @@
         <v>147</v>
       </c>
       <c r="R733">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S733" t="s">
         <v>120</v>
       </c>
       <c r="U733" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="734" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="734" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J734" t="s">
         <v>126</v>
       </c>
       <c r="L734" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M734" t="s">
         <v>140</v>
@@ -12948,18 +12856,18 @@
         <v>120</v>
       </c>
       <c r="U734" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="735" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="735" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J735" t="s">
         <v>126</v>
       </c>
       <c r="L735" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M735" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P735" t="s">
         <v>119</v>
@@ -12968,19 +12876,22 @@
         <v>147</v>
       </c>
       <c r="R735">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S735" t="s">
         <v>120</v>
       </c>
       <c r="U735" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="736" spans="10:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="736" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J736" t="s">
         <v>126</v>
       </c>
+      <c r="L736" t="s">
+        <v>131</v>
+      </c>
       <c r="M736" t="s">
         <v>138</v>
       </c>
@@ -12991,22 +12902,22 @@
         <v>147</v>
       </c>
       <c r="R736">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S736" t="s">
         <v>120</v>
       </c>
-      <c r="T736" t="s">
-        <v>141</v>
-      </c>
       <c r="U736" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="737" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J737" t="s">
         <v>126</v>
       </c>
+      <c r="L737" t="s">
+        <v>131</v>
+      </c>
       <c r="M737" t="s">
         <v>139</v>
       </c>
@@ -13022,17 +12933,17 @@
       <c r="S737" t="s">
         <v>120</v>
       </c>
-      <c r="T737" t="s">
-        <v>141</v>
-      </c>
       <c r="U737" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="738" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J738" t="s">
         <v>126</v>
       </c>
+      <c r="L738" t="s">
+        <v>131</v>
+      </c>
       <c r="M738" t="s">
         <v>140</v>
       </c>
@@ -13043,24 +12954,24 @@
         <v>147</v>
       </c>
       <c r="R738">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S738" t="s">
         <v>120</v>
       </c>
-      <c r="T738" t="s">
-        <v>141</v>
-      </c>
       <c r="U738" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="739" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J739" t="s">
         <v>126</v>
       </c>
+      <c r="L739" t="s">
+        <v>131</v>
+      </c>
       <c r="M739" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P739" t="s">
         <v>119</v>
@@ -13069,16 +12980,13 @@
         <v>147</v>
       </c>
       <c r="R739">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S739" t="s">
         <v>120</v>
       </c>
-      <c r="T739" t="s">
-        <v>141</v>
-      </c>
       <c r="U739" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="740" spans="10:21" x14ac:dyDescent="0.25">
@@ -13086,7 +12994,7 @@
         <v>126</v>
       </c>
       <c r="M740" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="P740" t="s">
         <v>119</v>
@@ -13095,18 +13003,21 @@
         <v>147</v>
       </c>
       <c r="R740">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="S740" t="s">
         <v>120</v>
       </c>
+      <c r="T740" t="s">
+        <v>141</v>
+      </c>
       <c r="U740" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
     </row>
     <row r="741" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J741" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="M741" t="s">
         <v>139</v>
@@ -13118,18 +13029,21 @@
         <v>147</v>
       </c>
       <c r="R741">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S741" t="s">
         <v>120</v>
       </c>
+      <c r="T741" t="s">
+        <v>141</v>
+      </c>
       <c r="U741" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="742" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J742" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="M742" t="s">
         <v>140</v>
@@ -13141,21 +13055,24 @@
         <v>147</v>
       </c>
       <c r="R742">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S742" t="s">
         <v>120</v>
       </c>
+      <c r="T742" t="s">
+        <v>141</v>
+      </c>
       <c r="U742" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="743" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J743" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="M743" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="P743" t="s">
         <v>119</v>
@@ -13164,21 +13081,24 @@
         <v>147</v>
       </c>
       <c r="R743">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="S743" t="s">
         <v>120</v>
       </c>
+      <c r="T743" t="s">
+        <v>141</v>
+      </c>
       <c r="U743" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="744" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J744" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="M744" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P744" t="s">
         <v>119</v>
@@ -13187,18 +13107,18 @@
         <v>147</v>
       </c>
       <c r="R744">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="S744" t="s">
         <v>120</v>
       </c>
       <c r="U744" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="745" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J745" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="M745" t="s">
         <v>139</v>
@@ -13216,15 +13136,15 @@
         <v>120</v>
       </c>
       <c r="U745" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="746" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J746" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="M746" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="P746" t="s">
         <v>119</v>
@@ -13233,24 +13153,21 @@
         <v>147</v>
       </c>
       <c r="R746">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="S746" t="s">
         <v>120</v>
       </c>
       <c r="U746" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
     </row>
     <row r="747" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J747" t="s">
-        <v>132</v>
-      </c>
-      <c r="L747" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="M747" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="P747" t="s">
         <v>119</v>
@@ -13259,24 +13176,21 @@
         <v>147</v>
       </c>
       <c r="R747">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="S747" t="s">
         <v>120</v>
       </c>
       <c r="U747" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="748" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J748" t="s">
-        <v>132</v>
-      </c>
-      <c r="L748" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="M748" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="P748" t="s">
         <v>119</v>
@@ -13291,18 +13205,15 @@
         <v>120</v>
       </c>
       <c r="U748" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
     </row>
     <row r="749" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J749" t="s">
-        <v>132</v>
-      </c>
-      <c r="L749" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="M749" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P749" t="s">
         <v>119</v>
@@ -13311,24 +13222,21 @@
         <v>147</v>
       </c>
       <c r="R749">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="S749" t="s">
         <v>120</v>
       </c>
       <c r="U749" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="750" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J750" t="s">
-        <v>132</v>
-      </c>
-      <c r="L750" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="M750" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="P750" t="s">
         <v>119</v>
@@ -13337,13 +13245,13 @@
         <v>147</v>
       </c>
       <c r="R750">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="S750" t="s">
         <v>120</v>
       </c>
       <c r="U750" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
     </row>
     <row r="751" spans="10:21" x14ac:dyDescent="0.25">
@@ -13351,7 +13259,7 @@
         <v>132</v>
       </c>
       <c r="L751" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M751" t="s">
         <v>138</v>
@@ -13362,15 +13270,14 @@
       <c r="Q751" t="s">
         <v>147</v>
       </c>
-      <c r="R751" s="12">
-        <f>R747</f>
+      <c r="R751">
         <v>30</v>
       </c>
       <c r="S751" t="s">
         <v>120</v>
       </c>
-      <c r="T751" t="s">
-        <v>143</v>
+      <c r="U751" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="752" spans="10:21" x14ac:dyDescent="0.25">
@@ -13378,7 +13285,7 @@
         <v>132</v>
       </c>
       <c r="L752" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M752" t="s">
         <v>139</v>
@@ -13389,15 +13296,14 @@
       <c r="Q752" t="s">
         <v>147</v>
       </c>
-      <c r="R752" s="12">
-        <f>R748</f>
+      <c r="R752">
         <v>35</v>
       </c>
       <c r="S752" t="s">
         <v>120</v>
       </c>
-      <c r="T752" t="s">
-        <v>143</v>
+      <c r="U752" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="753" spans="10:21" x14ac:dyDescent="0.25">
@@ -13405,7 +13311,7 @@
         <v>132</v>
       </c>
       <c r="L753" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M753" t="s">
         <v>140</v>
@@ -13416,15 +13322,14 @@
       <c r="Q753" t="s">
         <v>147</v>
       </c>
-      <c r="R753" s="12">
-        <f>R749</f>
+      <c r="R753">
         <v>48</v>
       </c>
       <c r="S753" t="s">
         <v>120</v>
       </c>
-      <c r="T753" t="s">
-        <v>143</v>
+      <c r="U753" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="754" spans="10:21" x14ac:dyDescent="0.25">
@@ -13432,10 +13337,10 @@
         <v>132</v>
       </c>
       <c r="L754" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M754" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P754" t="s">
         <v>119</v>
@@ -13443,15 +13348,14 @@
       <c r="Q754" t="s">
         <v>147</v>
       </c>
-      <c r="R754" s="12">
-        <f>R750</f>
+      <c r="R754">
         <v>30</v>
       </c>
       <c r="S754" t="s">
         <v>120</v>
       </c>
-      <c r="T754" t="s">
-        <v>143</v>
+      <c r="U754" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="755" spans="10:21" x14ac:dyDescent="0.25">
@@ -13459,7 +13363,7 @@
         <v>132</v>
       </c>
       <c r="L755" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M755" t="s">
         <v>138</v>
@@ -13470,14 +13374,15 @@
       <c r="Q755" t="s">
         <v>147</v>
       </c>
-      <c r="R755">
-        <v>29</v>
+      <c r="R755" s="12">
+        <f>R751</f>
+        <v>30</v>
       </c>
       <c r="S755" t="s">
         <v>120</v>
       </c>
-      <c r="U755" t="s">
-        <v>154</v>
+      <c r="T755" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="756" spans="10:21" x14ac:dyDescent="0.25">
@@ -13485,7 +13390,7 @@
         <v>132</v>
       </c>
       <c r="L756" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M756" t="s">
         <v>139</v>
@@ -13496,14 +13401,15 @@
       <c r="Q756" t="s">
         <v>147</v>
       </c>
-      <c r="R756">
-        <v>34</v>
+      <c r="R756" s="12">
+        <f>R752</f>
+        <v>35</v>
       </c>
       <c r="S756" t="s">
         <v>120</v>
       </c>
-      <c r="U756" t="s">
-        <v>154</v>
+      <c r="T756" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="757" spans="10:21" x14ac:dyDescent="0.25">
@@ -13511,7 +13417,7 @@
         <v>132</v>
       </c>
       <c r="L757" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M757" t="s">
         <v>140</v>
@@ -13522,14 +13428,15 @@
       <c r="Q757" t="s">
         <v>147</v>
       </c>
-      <c r="R757">
-        <v>46</v>
+      <c r="R757" s="12">
+        <f>R753</f>
+        <v>48</v>
       </c>
       <c r="S757" t="s">
         <v>120</v>
       </c>
-      <c r="U757" t="s">
-        <v>154</v>
+      <c r="T757" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="758" spans="10:21" x14ac:dyDescent="0.25">
@@ -13537,10 +13444,10 @@
         <v>132</v>
       </c>
       <c r="L758" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M758" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P758" t="s">
         <v>119</v>
@@ -13548,14 +13455,15 @@
       <c r="Q758" t="s">
         <v>147</v>
       </c>
-      <c r="R758">
-        <v>29</v>
+      <c r="R758" s="12">
+        <f>R754</f>
+        <v>30</v>
       </c>
       <c r="S758" t="s">
         <v>120</v>
       </c>
-      <c r="U758" t="s">
-        <v>154</v>
+      <c r="T758" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="759" spans="10:21" x14ac:dyDescent="0.25">
@@ -13563,7 +13471,7 @@
         <v>132</v>
       </c>
       <c r="L759" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M759" t="s">
         <v>138</v>
@@ -13581,7 +13489,7 @@
         <v>120</v>
       </c>
       <c r="U759" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="760" spans="10:21" x14ac:dyDescent="0.25">
@@ -13589,7 +13497,7 @@
         <v>132</v>
       </c>
       <c r="L760" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M760" t="s">
         <v>139</v>
@@ -13601,13 +13509,13 @@
         <v>147</v>
       </c>
       <c r="R760">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S760" t="s">
         <v>120</v>
       </c>
       <c r="U760" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="761" spans="10:21" x14ac:dyDescent="0.25">
@@ -13615,7 +13523,7 @@
         <v>132</v>
       </c>
       <c r="L761" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M761" t="s">
         <v>140</v>
@@ -13627,13 +13535,13 @@
         <v>147</v>
       </c>
       <c r="R761">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S761" t="s">
         <v>120</v>
       </c>
       <c r="U761" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="762" spans="10:21" x14ac:dyDescent="0.25">
@@ -13641,10 +13549,10 @@
         <v>132</v>
       </c>
       <c r="L762" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M762" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P762" t="s">
         <v>119</v>
@@ -13659,13 +13567,16 @@
         <v>120</v>
       </c>
       <c r="U762" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="763" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J763" t="s">
         <v>132</v>
       </c>
+      <c r="L763" t="s">
+        <v>135</v>
+      </c>
       <c r="M763" t="s">
         <v>138</v>
       </c>
@@ -13681,17 +13592,17 @@
       <c r="S763" t="s">
         <v>120</v>
       </c>
-      <c r="T763" t="s">
-        <v>142</v>
-      </c>
       <c r="U763" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="764" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J764" t="s">
         <v>132</v>
       </c>
+      <c r="L764" t="s">
+        <v>135</v>
+      </c>
       <c r="M764" t="s">
         <v>139</v>
       </c>
@@ -13707,17 +13618,17 @@
       <c r="S764" t="s">
         <v>120</v>
       </c>
-      <c r="T764" t="s">
-        <v>142</v>
-      </c>
       <c r="U764" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="765" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J765" t="s">
         <v>132</v>
       </c>
+      <c r="L765" t="s">
+        <v>135</v>
+      </c>
       <c r="M765" t="s">
         <v>140</v>
       </c>
@@ -13728,24 +13639,24 @@
         <v>147</v>
       </c>
       <c r="R765">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="S765" t="s">
         <v>120</v>
       </c>
-      <c r="T765" t="s">
-        <v>142</v>
-      </c>
       <c r="U765" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="766" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J766" t="s">
         <v>132</v>
       </c>
+      <c r="L766" t="s">
+        <v>135</v>
+      </c>
       <c r="M766" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P766" t="s">
         <v>119</v>
@@ -13759,16 +13670,13 @@
       <c r="S766" t="s">
         <v>120</v>
       </c>
-      <c r="T766" t="s">
-        <v>142</v>
-      </c>
       <c r="U766" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="767" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J767" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="M767" t="s">
         <v>138</v>
@@ -13785,13 +13693,16 @@
       <c r="S767" t="s">
         <v>120</v>
       </c>
+      <c r="T767" t="s">
+        <v>142</v>
+      </c>
       <c r="U767" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="768" spans="10:21" x14ac:dyDescent="0.25">
       <c r="J768" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="M768" t="s">
         <v>139</v>
@@ -13803,18 +13714,21 @@
         <v>147</v>
       </c>
       <c r="R768">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S768" t="s">
         <v>120</v>
       </c>
+      <c r="T768" t="s">
+        <v>142</v>
+      </c>
       <c r="U768" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="769" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J769" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="M769" t="s">
         <v>140</v>
@@ -13826,24 +13740,24 @@
         <v>147</v>
       </c>
       <c r="R769">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="S769" t="s">
         <v>120</v>
       </c>
+      <c r="T769" t="s">
+        <v>142</v>
+      </c>
       <c r="U769" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="770" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J770" t="s">
-        <v>137</v>
-      </c>
-      <c r="L770" t="s">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="M770" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="P770" t="s">
         <v>119</v>
@@ -13852,24 +13766,24 @@
         <v>147</v>
       </c>
       <c r="R770">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S770" t="s">
         <v>120</v>
       </c>
+      <c r="T770" t="s">
+        <v>142</v>
+      </c>
       <c r="U770" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="771" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J771" t="s">
         <v>137</v>
       </c>
-      <c r="L771" t="s">
-        <v>190</v>
-      </c>
       <c r="M771" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P771" t="s">
         <v>119</v>
@@ -13878,24 +13792,21 @@
         <v>147</v>
       </c>
       <c r="R771">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="S771" t="s">
         <v>120</v>
       </c>
       <c r="U771" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="772" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J772" t="s">
         <v>137</v>
       </c>
-      <c r="L772" t="s">
-        <v>190</v>
-      </c>
       <c r="M772" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P772" t="s">
         <v>119</v>
@@ -13904,24 +13815,21 @@
         <v>147</v>
       </c>
       <c r="R772">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="S772" t="s">
         <v>120</v>
       </c>
       <c r="U772" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="773" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J773" t="s">
         <v>137</v>
       </c>
-      <c r="L773" t="s">
-        <v>191</v>
-      </c>
       <c r="M773" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P773" t="s">
         <v>119</v>
@@ -13930,13 +13838,13 @@
         <v>147</v>
       </c>
       <c r="R773">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="S773" t="s">
         <v>120</v>
       </c>
       <c r="U773" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="774" spans="1:21" x14ac:dyDescent="0.25">
@@ -13944,10 +13852,10 @@
         <v>137</v>
       </c>
       <c r="L774" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M774" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P774" t="s">
         <v>119</v>
@@ -13956,23 +13864,76 @@
         <v>147</v>
       </c>
       <c r="R774">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="S774" t="s">
         <v>120</v>
       </c>
       <c r="U774" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="775" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="J775" t="s">
+        <v>137</v>
+      </c>
+      <c r="L775" t="s">
+        <v>189</v>
+      </c>
+      <c r="M775" t="s">
+        <v>139</v>
+      </c>
+      <c r="P775" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q775" t="s">
+        <v>147</v>
+      </c>
+      <c r="R775">
+        <v>41</v>
+      </c>
+      <c r="S775" t="s">
+        <v>120</v>
+      </c>
+      <c r="U775" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="776" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A776" s="1" t="s">
-        <v>262</v>
+      <c r="J776" t="s">
+        <v>137</v>
+      </c>
+      <c r="L776" t="s">
+        <v>189</v>
+      </c>
+      <c r="M776" t="s">
+        <v>140</v>
+      </c>
+      <c r="P776" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q776" t="s">
+        <v>147</v>
+      </c>
+      <c r="R776">
+        <v>56</v>
+      </c>
+      <c r="S776" t="s">
+        <v>120</v>
+      </c>
+      <c r="U776" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="777" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="I777" t="s">
-        <v>187</v>
+      <c r="J777" t="s">
+        <v>137</v>
+      </c>
+      <c r="L777" t="s">
+        <v>190</v>
+      </c>
+      <c r="M777" t="s">
+        <v>139</v>
       </c>
       <c r="P777" t="s">
         <v>119</v>
@@ -13980,136 +13941,98 @@
       <c r="Q777" t="s">
         <v>147</v>
       </c>
-      <c r="R777" s="6">
-        <v>30</v>
+      <c r="R777">
+        <v>41</v>
       </c>
       <c r="S777" t="s">
         <v>120</v>
       </c>
-      <c r="T777" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="779" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A779" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B779" s="2"/>
-      <c r="C779" s="2"/>
-      <c r="D779" s="2"/>
-      <c r="E779" s="2"/>
-      <c r="F779" s="2"/>
-      <c r="G779" s="2"/>
-      <c r="H779" s="2"/>
-      <c r="I779" s="2"/>
-      <c r="J779" s="2"/>
-      <c r="K779" s="2"/>
-      <c r="L779" s="2"/>
-      <c r="M779" s="2"/>
-      <c r="N779" s="2"/>
-      <c r="O779" s="2"/>
-      <c r="P779" s="2"/>
-      <c r="Q779" s="2"/>
-      <c r="R779" s="2"/>
-      <c r="S779" s="2"/>
-      <c r="T779" s="2"/>
-      <c r="U779" s="2"/>
+      <c r="U777" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="778" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="J778" t="s">
+        <v>137</v>
+      </c>
+      <c r="L778" t="s">
+        <v>190</v>
+      </c>
+      <c r="M778" t="s">
+        <v>140</v>
+      </c>
+      <c r="P778" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q778" t="s">
+        <v>147</v>
+      </c>
+      <c r="R778">
+        <v>41</v>
+      </c>
+      <c r="S778" t="s">
+        <v>120</v>
+      </c>
+      <c r="U778" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="780" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A780" s="1" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="781" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="I781" t="s">
+        <v>186</v>
+      </c>
       <c r="P781" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="Q781" t="s">
-        <v>166</v>
-      </c>
-      <c r="R781">
-        <v>1</v>
+        <v>147</v>
+      </c>
+      <c r="R781" s="6">
+        <v>30</v>
       </c>
       <c r="S781" t="s">
-        <v>115</v>
-      </c>
-      <c r="T781" t="s">
-        <v>162</v>
-      </c>
-      <c r="U781" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="782" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="P782" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q782" t="s">
-        <v>168</v>
-      </c>
-      <c r="R782">
-        <v>1</v>
-      </c>
-      <c r="S782" t="s">
-        <v>115</v>
-      </c>
-      <c r="T782" t="s">
-        <v>163</v>
-      </c>
-      <c r="U782" t="s">
-        <v>158</v>
+        <v>120</v>
+      </c>
+      <c r="T781" s="6" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="783" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="J783" t="s">
-        <v>126</v>
-      </c>
-      <c r="M783" t="s">
-        <v>156</v>
-      </c>
-      <c r="P783" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q783" t="s">
-        <v>168</v>
-      </c>
-      <c r="R783">
-        <v>2</v>
-      </c>
-      <c r="S783" t="s">
-        <v>115</v>
-      </c>
-      <c r="T783" t="s">
-        <v>159</v>
-      </c>
-      <c r="U783" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="784" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="M784" t="s">
-        <v>156</v>
-      </c>
-      <c r="P784" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q784" t="s">
-        <v>168</v>
-      </c>
-      <c r="R784">
-        <v>1</v>
-      </c>
-      <c r="S784" t="s">
-        <v>115</v>
-      </c>
-      <c r="T784" t="s">
-        <v>160</v>
-      </c>
-      <c r="U784" t="s">
-        <v>157</v>
-      </c>
+      <c r="A783" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B783" s="2"/>
+      <c r="C783" s="2"/>
+      <c r="D783" s="2"/>
+      <c r="E783" s="2"/>
+      <c r="F783" s="2"/>
+      <c r="G783" s="2"/>
+      <c r="H783" s="2"/>
+      <c r="I783" s="2"/>
+      <c r="J783" s="2"/>
+      <c r="K783" s="2"/>
+      <c r="L783" s="2"/>
+      <c r="M783" s="2"/>
+      <c r="N783" s="2"/>
+      <c r="O783" s="2"/>
+      <c r="P783" s="2"/>
+      <c r="Q783" s="2"/>
+      <c r="R783" s="2"/>
+      <c r="S783" s="2"/>
+      <c r="T783" s="2"/>
+      <c r="U783" s="2"/>
     </row>
     <row r="785" spans="1:21" x14ac:dyDescent="0.25">
       <c r="P785" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q785" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R785">
         <v>1</v>
@@ -14118,18 +14041,18 @@
         <v>115</v>
       </c>
       <c r="T785" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="U785" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="786" spans="1:21" x14ac:dyDescent="0.25">
       <c r="P786" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q786" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R786">
         <v>1</v>
@@ -14138,445 +14061,573 @@
         <v>115</v>
       </c>
       <c r="T786" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U786" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="787" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="J787" t="s">
+        <v>126</v>
+      </c>
+      <c r="M787" t="s">
+        <v>155</v>
+      </c>
+      <c r="P787" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q787" t="s">
+        <v>167</v>
+      </c>
+      <c r="R787">
+        <v>2</v>
+      </c>
+      <c r="S787" t="s">
+        <v>115</v>
+      </c>
+      <c r="T787" t="s">
         <v>158</v>
       </c>
+      <c r="U787" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="788" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M788" t="s">
+        <v>155</v>
+      </c>
       <c r="P788" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q788" t="s">
+        <v>167</v>
+      </c>
+      <c r="R788">
+        <v>1</v>
+      </c>
+      <c r="S788" t="s">
+        <v>115</v>
+      </c>
+      <c r="T788" t="s">
+        <v>159</v>
+      </c>
+      <c r="U788" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="789" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="P789" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q789" t="s">
+        <v>166</v>
+      </c>
+      <c r="R789">
+        <v>1</v>
+      </c>
+      <c r="S789" t="s">
+        <v>115</v>
+      </c>
+      <c r="T789" t="s">
+        <v>169</v>
+      </c>
+      <c r="U789" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="790" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="P790" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q790" t="s">
+        <v>168</v>
+      </c>
+      <c r="R790">
+        <v>1</v>
+      </c>
+      <c r="S790" t="s">
+        <v>115</v>
+      </c>
+      <c r="T790" t="s">
+        <v>160</v>
+      </c>
+      <c r="U790" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="792" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="P792" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q792" t="s">
+        <v>172</v>
+      </c>
+      <c r="R792">
+        <v>0</v>
+      </c>
+      <c r="S792" t="s">
         <v>173</v>
       </c>
-      <c r="R788">
-        <v>0</v>
-      </c>
-      <c r="S788" t="s">
-        <v>174</v>
-      </c>
-      <c r="T788" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="789" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D789" t="s">
-        <v>182</v>
-      </c>
-      <c r="P789" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q789" t="s">
-        <v>173</v>
-      </c>
-      <c r="R789">
-        <v>13</v>
-      </c>
-      <c r="S789" t="s">
-        <v>174</v>
-      </c>
-      <c r="U789" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="791" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A791" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B791" s="2"/>
-      <c r="C791" s="2"/>
-      <c r="D791" s="2"/>
-      <c r="E791" s="2"/>
-      <c r="F791" s="2"/>
-      <c r="G791" s="2"/>
-      <c r="H791" s="2"/>
-      <c r="I791" s="2"/>
-      <c r="J791" s="2"/>
-      <c r="K791" s="2"/>
-      <c r="L791" s="2"/>
-      <c r="M791" s="2"/>
-      <c r="N791" s="2"/>
-      <c r="O791" s="2"/>
-      <c r="P791" s="2"/>
-      <c r="Q791" s="2"/>
-      <c r="R791" s="2"/>
-      <c r="S791" s="2"/>
-      <c r="T791" s="2"/>
-      <c r="U791" s="2"/>
+      <c r="T792" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="793" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D793" t="s">
+        <v>181</v>
+      </c>
+      <c r="P793" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q793" t="s">
+        <v>172</v>
+      </c>
+      <c r="R793">
+        <v>13</v>
+      </c>
+      <c r="S793" t="s">
+        <v>173</v>
+      </c>
+      <c r="U793" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="795" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A795" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B795" s="2"/>
+      <c r="C795" s="2"/>
+      <c r="D795" s="2"/>
+      <c r="E795" s="2"/>
+      <c r="F795" s="2"/>
+      <c r="G795" s="2"/>
+      <c r="H795" s="2"/>
+      <c r="I795" s="2"/>
+      <c r="J795" s="2"/>
+      <c r="K795" s="2"/>
+      <c r="L795" s="2"/>
+      <c r="M795" s="2"/>
+      <c r="N795" s="2"/>
+      <c r="O795" s="2"/>
+      <c r="P795" s="2"/>
+      <c r="Q795" s="2"/>
+      <c r="R795" s="2"/>
+      <c r="S795" s="2"/>
+      <c r="T795" s="2"/>
+      <c r="U795" s="2"/>
+    </row>
+    <row r="797" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D797" t="s">
+        <v>181</v>
+      </c>
+      <c r="P797" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q797" t="s">
+        <v>176</v>
+      </c>
+      <c r="R797">
+        <v>0.24</v>
+      </c>
+      <c r="S797" t="s">
+        <v>178</v>
+      </c>
+      <c r="U797" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="798" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D798" t="s">
         <v>182</v>
       </c>
-      <c r="P793" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q793" t="s">
+      <c r="P798" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q798" t="s">
+        <v>176</v>
+      </c>
+      <c r="R798">
+        <v>0.24</v>
+      </c>
+      <c r="S798" t="s">
+        <v>178</v>
+      </c>
+      <c r="U798" t="s">
         <v>177</v>
       </c>
-      <c r="R793">
-        <v>0.24</v>
-      </c>
-      <c r="S793" t="s">
+    </row>
+    <row r="799" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D799" t="s">
+        <v>183</v>
+      </c>
+      <c r="P799" t="s">
         <v>179</v>
       </c>
-      <c r="U793" t="s">
+      <c r="Q799" t="s">
+        <v>176</v>
+      </c>
+      <c r="R799">
+        <v>0</v>
+      </c>
+      <c r="S799" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="794" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D794" t="s">
-        <v>183</v>
-      </c>
-      <c r="P794" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q794" t="s">
-        <v>177</v>
-      </c>
-      <c r="R794">
-        <v>0.24</v>
-      </c>
-      <c r="S794" t="s">
-        <v>179</v>
-      </c>
-      <c r="U794" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="795" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D795" t="s">
+      <c r="T799" t="s">
         <v>184</v>
       </c>
-      <c r="P795" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q795" t="s">
-        <v>177</v>
-      </c>
-      <c r="R795">
-        <v>0</v>
-      </c>
-      <c r="S795" t="s">
-        <v>179</v>
-      </c>
-      <c r="T795" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="797" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A797" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="B797" s="28"/>
-      <c r="C797" s="28"/>
-      <c r="D797" s="28"/>
-      <c r="E797" s="28"/>
-      <c r="F797" s="28"/>
-      <c r="G797" s="28"/>
-      <c r="H797" s="28"/>
-      <c r="I797" s="28"/>
-      <c r="J797" s="28"/>
-      <c r="K797" s="28"/>
-      <c r="L797" s="28"/>
-      <c r="M797" s="28"/>
-      <c r="N797" s="28"/>
-      <c r="O797" s="28"/>
-      <c r="P797" s="28"/>
-      <c r="Q797" s="28"/>
-      <c r="R797" s="28"/>
-      <c r="S797" s="28"/>
-      <c r="T797" s="28"/>
-      <c r="U797" s="28"/>
-    </row>
-    <row r="799" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="H799" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q799" t="s">
-        <v>333</v>
-      </c>
-      <c r="R799" s="11">
+    </row>
+    <row r="801" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A801" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="B801" s="28"/>
+      <c r="C801" s="28"/>
+      <c r="D801" s="28"/>
+      <c r="E801" s="28"/>
+      <c r="F801" s="28"/>
+      <c r="G801" s="28"/>
+      <c r="H801" s="28"/>
+      <c r="I801" s="28"/>
+      <c r="J801" s="28"/>
+      <c r="K801" s="28"/>
+      <c r="L801" s="28"/>
+      <c r="M801" s="28"/>
+      <c r="N801" s="28"/>
+      <c r="O801" s="28"/>
+      <c r="P801" s="28"/>
+      <c r="Q801" s="28"/>
+      <c r="R801" s="28"/>
+      <c r="S801" s="28"/>
+      <c r="T801" s="28"/>
+      <c r="U801" s="28"/>
+    </row>
+    <row r="803" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="H803" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q803" t="s">
+        <v>332</v>
+      </c>
+      <c r="R803" s="11">
         <f>213/(213 + 60)*100</f>
         <v>78.021978021978029</v>
       </c>
-      <c r="S799" t="s">
+      <c r="S803" t="s">
         <v>103</v>
       </c>
-      <c r="U799" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="800" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="H800" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q800" t="s">
+      <c r="U803" t="s">
         <v>333</v>
       </c>
-      <c r="R800" s="11">
+    </row>
+    <row r="804" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="H804" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q804" t="s">
+        <v>332</v>
+      </c>
+      <c r="R804" s="11">
         <f>60/(213 + 60)*100</f>
         <v>21.978021978021978</v>
       </c>
-      <c r="S800" t="s">
+      <c r="S804" t="s">
         <v>103</v>
       </c>
-      <c r="U800" t="s">
+      <c r="U804" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="806" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="H806" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="802" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="H802" t="s">
+      <c r="Q806" t="s">
+        <v>336</v>
+      </c>
+      <c r="R806">
+        <v>45</v>
+      </c>
+      <c r="S806" t="s">
+        <v>103</v>
+      </c>
+      <c r="U806" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="807" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="H807" t="s">
         <v>335</v>
       </c>
-      <c r="Q802" t="s">
+      <c r="Q807" t="s">
+        <v>336</v>
+      </c>
+      <c r="R807">
+        <v>48</v>
+      </c>
+      <c r="S807" t="s">
+        <v>103</v>
+      </c>
+      <c r="U807" t="s">
         <v>337</v>
       </c>
-      <c r="R802">
-        <v>45</v>
-      </c>
-      <c r="S802" t="s">
-        <v>103</v>
-      </c>
-      <c r="U802" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="803" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="H803" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q803" t="s">
-        <v>337</v>
-      </c>
-      <c r="R803">
-        <v>48</v>
-      </c>
-      <c r="S803" t="s">
-        <v>103</v>
-      </c>
-      <c r="U803" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="805" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="Q805" t="s">
-        <v>316</v>
-      </c>
-      <c r="R805" s="32">
-        <f>R811</f>
+    </row>
+    <row r="809" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q809" t="s">
+        <v>315</v>
+      </c>
+      <c r="R809" s="32">
+        <f>R815</f>
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="S805" t="s">
-        <v>319</v>
-      </c>
-      <c r="T805" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="806" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="R806" s="32"/>
-    </row>
-    <row r="807" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A807" t="s">
+      <c r="S809" t="s">
+        <v>318</v>
+      </c>
+      <c r="T809" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="810" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="R810" s="32"/>
+    </row>
+    <row r="811" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A811" t="s">
         <v>38</v>
       </c>
-      <c r="Q807" t="s">
-        <v>316</v>
-      </c>
-      <c r="R807" s="29">
+      <c r="Q811" t="s">
+        <v>315</v>
+      </c>
+      <c r="R811" s="29">
         <f>-(45.5*0.2+10.7*0.8)/1000</f>
         <v>-1.7659999999999999E-2</v>
       </c>
-      <c r="S807" t="s">
-        <v>319</v>
-      </c>
-      <c r="U807" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="808" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A808" t="s">
+      <c r="S811" t="s">
+        <v>318</v>
+      </c>
+      <c r="U811" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="812" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A812" t="s">
         <v>39</v>
       </c>
-      <c r="Q808" t="s">
-        <v>316</v>
-      </c>
-      <c r="R808" s="29">
-        <f>R807</f>
+      <c r="Q812" t="s">
+        <v>315</v>
+      </c>
+      <c r="R812" s="29">
+        <f>R811</f>
         <v>-1.7659999999999999E-2</v>
       </c>
-      <c r="S808" t="s">
-        <v>319</v>
-      </c>
-      <c r="U808" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="809" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A809" s="4" t="s">
+      <c r="S812" t="s">
+        <v>318</v>
+      </c>
+      <c r="U812" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="813" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A813" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="Q809" t="s">
-        <v>316</v>
-      </c>
-      <c r="R809" s="6">
+      <c r="Q813" t="s">
+        <v>315</v>
+      </c>
+      <c r="R813" s="6">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
-      <c r="S809" t="s">
-        <v>319</v>
-      </c>
-      <c r="T809" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="810" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A810" s="4" t="s">
+      <c r="S813" t="s">
+        <v>318</v>
+      </c>
+      <c r="T813" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="814" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A814" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="Q810" t="s">
-        <v>316</v>
-      </c>
-      <c r="R810" s="6">
+      <c r="Q814" t="s">
+        <v>315</v>
+      </c>
+      <c r="R814" s="6">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
-      <c r="S810" t="s">
-        <v>319</v>
-      </c>
-      <c r="T810" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="811" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B811" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q811" t="s">
-        <v>316</v>
-      </c>
-      <c r="R811">
+      <c r="S814" t="s">
+        <v>318</v>
+      </c>
+      <c r="T814" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="815" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B815" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q815" t="s">
+        <v>315</v>
+      </c>
+      <c r="R815">
         <f>-0.6/1000</f>
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="S811" t="s">
-        <v>319</v>
-      </c>
-      <c r="U811" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="813" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C813" t="s">
+      <c r="S815" t="s">
+        <v>318</v>
+      </c>
+      <c r="U815" t="s">
         <v>322</v>
       </c>
-      <c r="Q813" t="s">
-        <v>317</v>
-      </c>
-      <c r="R813">
+    </row>
+    <row r="817" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C817" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q817" t="s">
+        <v>316</v>
+      </c>
+      <c r="R817">
         <f>-9.2/1000</f>
         <v>-9.1999999999999998E-3</v>
       </c>
-      <c r="S813" t="s">
+      <c r="S817" t="s">
+        <v>318</v>
+      </c>
+      <c r="U817" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="820" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="H820" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q820" t="s">
+        <v>324</v>
+      </c>
+      <c r="R820" s="33">
+        <v>-0.5</v>
+      </c>
+      <c r="S820" t="s">
         <v>319</v>
       </c>
-      <c r="U813" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="816" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="H816" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q816" t="s">
+      <c r="U820" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="821" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="H821" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q821" t="s">
+        <v>324</v>
+      </c>
+      <c r="R821" s="33">
+        <v>-1</v>
+      </c>
+      <c r="S821" t="s">
+        <v>319</v>
+      </c>
+      <c r="U821" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="822" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="H822" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q822" t="s">
+        <v>324</v>
+      </c>
+      <c r="R822" s="31">
+        <v>-1</v>
+      </c>
+      <c r="S822" t="s">
+        <v>319</v>
+      </c>
+      <c r="T822" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="824" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="Q824" t="s">
+        <v>326</v>
+      </c>
+      <c r="R824" s="30">
+        <v>0</v>
+      </c>
+      <c r="S824" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="826" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="Q826" t="s">
         <v>325</v>
       </c>
-      <c r="R816" s="33">
-        <v>-0.5</v>
-      </c>
-      <c r="S816" t="s">
-        <v>320</v>
-      </c>
-      <c r="U816" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="817" spans="8:21" x14ac:dyDescent="0.25">
-      <c r="H817" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q817" t="s">
-        <v>325</v>
-      </c>
-      <c r="R817" s="33">
-        <v>-1</v>
-      </c>
-      <c r="S817" t="s">
-        <v>320</v>
-      </c>
-      <c r="U817" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="818" spans="8:21" x14ac:dyDescent="0.25">
-      <c r="H818" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q818" t="s">
-        <v>325</v>
-      </c>
-      <c r="R818" s="31">
-        <v>-1</v>
-      </c>
-      <c r="S818" t="s">
-        <v>320</v>
-      </c>
-      <c r="T818" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="820" spans="8:21" x14ac:dyDescent="0.25">
-      <c r="Q820" t="s">
+      <c r="R826" s="30">
+        <v>0</v>
+      </c>
+      <c r="S826" t="s">
         <v>327</v>
       </c>
-      <c r="R820" s="30">
-        <v>0</v>
-      </c>
-      <c r="S820" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="822" spans="8:21" x14ac:dyDescent="0.25">
-      <c r="Q822" t="s">
-        <v>326</v>
-      </c>
-      <c r="R822" s="30">
-        <v>0</v>
-      </c>
-      <c r="S822" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="824" spans="8:21" x14ac:dyDescent="0.25">
-      <c r="Q824" t="s">
-        <v>318</v>
-      </c>
-      <c r="R824" s="33">
+    </row>
+    <row r="828" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="Q828" t="s">
+        <v>317</v>
+      </c>
+      <c r="R828" s="33">
         <f>3/5</f>
         <v>0.6</v>
       </c>
-      <c r="S824" t="s">
-        <v>320</v>
-      </c>
-      <c r="T824" t="s">
-        <v>324</v>
-      </c>
-      <c r="U824" t="s">
+      <c r="S828" t="s">
+        <v>319</v>
+      </c>
+      <c r="T828" t="s">
         <v>323</v>
       </c>
+      <c r="U828" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="830" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="H830" t="s">
+        <v>334</v>
+      </c>
+      <c r="P830" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q830" t="s">
+        <v>341</v>
+      </c>
+      <c r="R830" s="33">
+        <f>0.12*(44/12)</f>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="S830" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="831" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="H831" t="s">
+        <v>335</v>
+      </c>
+      <c r="P831" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q831" t="s">
+        <v>341</v>
+      </c>
+      <c r="R831" s="33">
+        <f>0.13*(44/12)</f>
+        <v>0.47666666666666668</v>
+      </c>
+      <c r="S831" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="832" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="R832" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -903,9 +903,6 @@
     <t>"Jordbruksverket (2023) Rekommendationer för gödsling och kalkning 2023"</t>
   </si>
   <si>
-    <t>grass clover ley (40% clover) and three harvest</t>
-  </si>
-  <si>
     <t>grass ley and three harvest</t>
   </si>
   <si>
@@ -1081,6 +1078,9 @@
   </si>
   <si>
     <t>Assume that some 'Fallow' is used as green manure</t>
+  </si>
+  <si>
+    <t>grass clover ley (avg. 20/40% clover) and three harvest</t>
   </si>
 </sst>
 </file>
@@ -1580,13 +1580,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>174</v>
@@ -1845,7 +1845,7 @@
         <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R15" s="4" t="s">
         <v>211</v>
@@ -1857,7 +1857,7 @@
         <v>210</v>
       </c>
       <c r="U15" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -1899,7 +1899,7 @@
         <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R19" s="4" t="s">
         <v>212</v>
@@ -1911,7 +1911,7 @@
         <v>213</v>
       </c>
       <c r="U19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -1938,7 +1938,7 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S24">
         <v>66</v>
@@ -1973,10 +1973,10 @@
         <v>97</v>
       </c>
       <c r="U24" t="s">
+        <v>299</v>
+      </c>
+      <c r="V24" t="s">
         <v>300</v>
-      </c>
-      <c r="V24" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4004,7 +4004,7 @@
         <v>18.5</v>
       </c>
       <c r="U153" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.25">
@@ -4058,10 +4058,10 @@
         <v>10</v>
       </c>
       <c r="S155">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U155" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
@@ -4088,7 +4088,7 @@
         <v>11</v>
       </c>
       <c r="S156">
-        <v>13</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.25">
@@ -5116,7 +5116,7 @@
         <v>4.2</v>
       </c>
       <c r="V196" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.25">
@@ -5143,7 +5143,7 @@
         <v>3.3</v>
       </c>
       <c r="V197" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="198" spans="1:22" x14ac:dyDescent="0.25">
@@ -5171,7 +5171,7 @@
         <v>3.75</v>
       </c>
       <c r="U198" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.25">
@@ -5325,7 +5325,7 @@
         <v>20</v>
       </c>
       <c r="U204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="205" spans="1:22" x14ac:dyDescent="0.25">
@@ -5917,10 +5917,10 @@
         <v>60</v>
       </c>
       <c r="U228" t="s">
+        <v>343</v>
+      </c>
+      <c r="V228" t="s">
         <v>344</v>
-      </c>
-      <c r="V228" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="229" spans="1:22" x14ac:dyDescent="0.25">
@@ -5939,7 +5939,7 @@
         <v>30</v>
       </c>
       <c r="U229" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="230" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -6017,19 +6017,19 @@
     </row>
     <row r="235" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A235" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B235" s="4"/>
     </row>
     <row r="236" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A236" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B236" s="4"/>
     </row>
     <row r="237" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A237" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B237" s="4"/>
     </row>
@@ -6046,7 +6046,7 @@
         <v>245</v>
       </c>
       <c r="U238" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="V238" t="s">
         <v>250</v>
@@ -7510,7 +7510,7 @@
         <v>3</v>
       </c>
       <c r="U338" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="339" spans="1:21" x14ac:dyDescent="0.25">
@@ -7657,7 +7657,7 @@
         <v>3</v>
       </c>
       <c r="U346" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="347" spans="1:21" x14ac:dyDescent="0.25">
@@ -8121,7 +8121,7 @@
         <v>3</v>
       </c>
       <c r="U379" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="380" spans="1:21" x14ac:dyDescent="0.25">
@@ -9469,7 +9469,7 @@
         <v>0.6</v>
       </c>
       <c r="V483" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="484" spans="1:22" x14ac:dyDescent="0.25">
@@ -9486,7 +9486,7 @@
         <v>1.6</v>
       </c>
       <c r="V484" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="485" spans="1:22" x14ac:dyDescent="0.25">
@@ -9504,7 +9504,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="U485" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="486" spans="1:22" x14ac:dyDescent="0.25">
@@ -10871,7 +10871,7 @@
         <v>5</v>
       </c>
       <c r="U577" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="578" spans="1:21" x14ac:dyDescent="0.25">
@@ -10982,7 +10982,7 @@
         <v>5</v>
       </c>
       <c r="U583" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="584" spans="1:21" x14ac:dyDescent="0.25">
@@ -11412,7 +11412,7 @@
         <v>10</v>
       </c>
       <c r="U614" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="615" spans="1:21" x14ac:dyDescent="0.25">
@@ -12600,7 +12600,7 @@
         <v>5.6</v>
       </c>
       <c r="V707" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="708" spans="1:22" x14ac:dyDescent="0.25">
@@ -12617,7 +12617,7 @@
         <v>3</v>
       </c>
       <c r="V708" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="709" spans="1:22" x14ac:dyDescent="0.25">
@@ -12635,7 +12635,7 @@
         <v>4.3</v>
       </c>
       <c r="U709" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="710" spans="1:22" x14ac:dyDescent="0.25">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="T717" s="5"/>
       <c r="U717" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="719" spans="1:22" x14ac:dyDescent="0.25">
@@ -12787,7 +12787,7 @@
     </row>
     <row r="721" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -14503,7 +14503,7 @@
         <v>167</v>
       </c>
       <c r="U798" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="799" spans="1:22" x14ac:dyDescent="0.25">
@@ -14614,7 +14614,7 @@
     </row>
     <row r="807" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A807" s="27" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B807" s="27"/>
       <c r="C807" s="28"/>
@@ -14640,10 +14640,10 @@
     </row>
     <row r="809" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I809" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="R809" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="S809" s="11">
         <f>213/(213 + 60)*100</f>
@@ -14653,15 +14653,15 @@
         <v>97</v>
       </c>
       <c r="V809" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="810" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I810" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R810" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="S810" s="11">
         <f>60/(213 + 60)*100</f>
@@ -14671,15 +14671,15 @@
         <v>97</v>
       </c>
       <c r="V810" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="812" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I812" t="s">
+        <v>326</v>
+      </c>
+      <c r="R812" t="s">
         <v>327</v>
-      </c>
-      <c r="R812" t="s">
-        <v>328</v>
       </c>
       <c r="S812">
         <v>45</v>
@@ -14688,15 +14688,15 @@
         <v>97</v>
       </c>
       <c r="V812" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="813" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I813" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R813" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S813">
         <v>48</v>
@@ -14705,25 +14705,25 @@
         <v>97</v>
       </c>
       <c r="V813" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="815" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R815" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S815" s="30">
         <f>S822</f>
         <v>-5.9999999999999995E-4</v>
       </c>
       <c r="T815" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="U815" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="V815" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="816" spans="1:22" x14ac:dyDescent="0.25">
@@ -14734,20 +14734,20 @@
         <v>142</v>
       </c>
       <c r="R816" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S816" s="29">
         <f>-(45.5*0.1+10.7*0.9)/1000</f>
         <v>-1.418E-2</v>
       </c>
       <c r="T816" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="U816" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="V816" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="817" spans="1:22" x14ac:dyDescent="0.25">
@@ -14758,14 +14758,14 @@
         <v>142</v>
       </c>
       <c r="R817" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S817" s="33">
         <f>S816</f>
         <v>-1.418E-2</v>
       </c>
       <c r="T817" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="818" spans="1:22" x14ac:dyDescent="0.25">
@@ -14776,20 +14776,20 @@
         <v>98</v>
       </c>
       <c r="R818" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S818" s="29">
         <f>-(45.5*0.4+10.7*0.6)/1000</f>
         <v>-2.4619999999999996E-2</v>
       </c>
       <c r="T818" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="U818" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="V818" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="819" spans="1:22" x14ac:dyDescent="0.25">
@@ -14800,14 +14800,14 @@
         <v>98</v>
       </c>
       <c r="R819" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S819" s="33">
         <f>S818</f>
         <v>-2.4619999999999996E-2</v>
       </c>
       <c r="T819" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="820" spans="1:22" x14ac:dyDescent="0.25">
@@ -14816,20 +14816,20 @@
       </c>
       <c r="B820" s="4"/>
       <c r="R820" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S820" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="T820" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="U820" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="V820" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="821" spans="1:22" x14ac:dyDescent="0.25">
@@ -14838,20 +14838,20 @@
       </c>
       <c r="B821" s="4"/>
       <c r="R821" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S821" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="T821" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="U821" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="V821" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="822" spans="1:22" x14ac:dyDescent="0.25">
@@ -14859,56 +14859,56 @@
         <v>226</v>
       </c>
       <c r="R822" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S822">
         <f>-0.6/1000</f>
         <v>-5.9999999999999995E-4</v>
       </c>
       <c r="T822" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="V822" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="823" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B823" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R823" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S823" s="29">
         <f>-20*0.45/0.85/1000</f>
         <v>-1.0588235294117647E-2</v>
       </c>
       <c r="T823" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="U823" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="V823" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="825" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D825" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="R825" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S825">
         <f>-9.2/1000</f>
         <v>-9.1999999999999998E-3</v>
       </c>
       <c r="T825" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="V825" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="827" spans="1:22" x14ac:dyDescent="0.25">
@@ -14916,16 +14916,16 @@
         <v>107</v>
       </c>
       <c r="R827" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S827" s="31">
         <v>-0.5</v>
       </c>
       <c r="T827" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="V827" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="828" spans="1:22" x14ac:dyDescent="0.25">
@@ -14933,16 +14933,16 @@
         <v>108</v>
       </c>
       <c r="R828" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S828" s="31">
         <v>-1</v>
       </c>
       <c r="T828" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="V828" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="829" spans="1:22" x14ac:dyDescent="0.25">
@@ -14950,106 +14950,106 @@
         <v>208</v>
       </c>
       <c r="R829" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S829" s="22">
         <v>-1</v>
       </c>
       <c r="T829" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="U829" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="830" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R830" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="S830" s="22">
         <f>-0.4 / ( (2*30.97) / (2*30.97 + 5*16) )</f>
         <v>-0.91662899580238943</v>
       </c>
       <c r="T830" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="U830" s="32" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="V830" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="831" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R831" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="S831" s="22">
         <f>0.6 / ( (2*39.1) / (2*39.1 + 16) )</f>
         <v>0.72276214833759589</v>
       </c>
       <c r="T831" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="U831" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="V831" t="s">
         <v>336</v>
-      </c>
-      <c r="V831" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="833" spans="9:22" x14ac:dyDescent="0.25">
       <c r="R833" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S833" s="31">
         <f>3/5</f>
         <v>0.6</v>
       </c>
       <c r="T833" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="U833" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V833" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="835" spans="9:22" x14ac:dyDescent="0.25">
       <c r="I835" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q835" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R835" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="S835" s="31">
         <f>0.12*(44/12)</f>
         <v>0.43999999999999995</v>
       </c>
       <c r="T835" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="836" spans="9:22" x14ac:dyDescent="0.25">
       <c r="I836" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q836" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R836" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="S836" s="31">
         <f>0.13*(44/12)</f>
         <v>0.47666666666666668</v>
       </c>
       <c r="T836" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="837" spans="9:22" x14ac:dyDescent="0.25">

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="355">
   <si>
     <t>f_crop</t>
   </si>
@@ -936,9 +936,6 @@
     <t>Set to match K/ha in stat.</t>
   </si>
   <si>
-    <t>zero for all non-cropland</t>
-  </si>
-  <si>
     <t>Liming</t>
   </si>
   <si>
@@ -1081,6 +1078,12 @@
   </si>
   <si>
     <t>grass clover ley (avg. 20/40% clover) and three harvest</t>
+  </si>
+  <si>
+    <t>Not included in NIR, reported under forest</t>
+  </si>
+  <si>
+    <t>Pers. comm. Mattias Lindblad (2024-11-14)</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V837"/>
+  <dimension ref="A1:V838"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="21" customWidth="1"/>
@@ -1580,13 +1583,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>174</v>
@@ -1845,7 +1848,7 @@
         <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R15" s="4" t="s">
         <v>211</v>
@@ -1857,7 +1860,7 @@
         <v>210</v>
       </c>
       <c r="U15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -1899,7 +1902,7 @@
         <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R19" s="4" t="s">
         <v>212</v>
@@ -1911,7 +1914,7 @@
         <v>213</v>
       </c>
       <c r="U19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -4061,7 +4064,7 @@
         <v>12</v>
       </c>
       <c r="U155" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
@@ -5917,10 +5920,10 @@
         <v>60</v>
       </c>
       <c r="U228" t="s">
+        <v>342</v>
+      </c>
+      <c r="V228" t="s">
         <v>343</v>
-      </c>
-      <c r="V228" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="229" spans="1:22" x14ac:dyDescent="0.25">
@@ -5939,7 +5942,7 @@
         <v>30</v>
       </c>
       <c r="U229" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="230" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -6017,19 +6020,19 @@
     </row>
     <row r="235" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A235" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B235" s="4"/>
     </row>
     <row r="236" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A236" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B236" s="4"/>
     </row>
     <row r="237" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A237" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B237" s="4"/>
     </row>
@@ -6046,7 +6049,7 @@
         <v>245</v>
       </c>
       <c r="U238" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="V238" t="s">
         <v>250</v>
@@ -12787,7 +12790,7 @@
     </row>
     <row r="721" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -14502,9 +14505,6 @@
       <c r="T798" t="s">
         <v>167</v>
       </c>
-      <c r="U798" t="s">
-        <v>305</v>
-      </c>
     </row>
     <row r="799" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E799" t="s">
@@ -14526,55 +14526,58 @@
         <v>151</v>
       </c>
     </row>
-    <row r="801" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A801" s="2" t="s">
+    <row r="800" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E800" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q800" t="s">
+        <v>148</v>
+      </c>
+      <c r="R800" t="s">
+        <v>166</v>
+      </c>
+      <c r="S800">
+        <v>13</v>
+      </c>
+      <c r="T800" t="s">
+        <v>167</v>
+      </c>
+      <c r="U800" t="s">
+        <v>353</v>
+      </c>
+      <c r="V800" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="802" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A802" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B801" s="2"/>
-      <c r="C801" s="2"/>
-      <c r="D801" s="2"/>
-      <c r="E801" s="2"/>
-      <c r="F801" s="2"/>
-      <c r="G801" s="2"/>
-      <c r="H801" s="2"/>
-      <c r="I801" s="2"/>
-      <c r="J801" s="2"/>
-      <c r="K801" s="2"/>
-      <c r="L801" s="2"/>
-      <c r="M801" s="2"/>
-      <c r="N801" s="2"/>
-      <c r="O801" s="2"/>
-      <c r="P801" s="2"/>
-      <c r="Q801" s="2"/>
-      <c r="R801" s="2"/>
-      <c r="S801" s="2"/>
-      <c r="T801" s="2"/>
-      <c r="U801" s="2"/>
-      <c r="V801" s="2"/>
-    </row>
-    <row r="803" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="E803" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q803" t="s">
-        <v>173</v>
-      </c>
-      <c r="R803" t="s">
-        <v>170</v>
-      </c>
-      <c r="S803">
-        <v>0.24</v>
-      </c>
-      <c r="T803" t="s">
-        <v>172</v>
-      </c>
-      <c r="V803" t="s">
-        <v>171</v>
-      </c>
+      <c r="B802" s="2"/>
+      <c r="C802" s="2"/>
+      <c r="D802" s="2"/>
+      <c r="E802" s="2"/>
+      <c r="F802" s="2"/>
+      <c r="G802" s="2"/>
+      <c r="H802" s="2"/>
+      <c r="I802" s="2"/>
+      <c r="J802" s="2"/>
+      <c r="K802" s="2"/>
+      <c r="L802" s="2"/>
+      <c r="M802" s="2"/>
+      <c r="N802" s="2"/>
+      <c r="O802" s="2"/>
+      <c r="P802" s="2"/>
+      <c r="Q802" s="2"/>
+      <c r="R802" s="2"/>
+      <c r="S802" s="2"/>
+      <c r="T802" s="2"/>
+      <c r="U802" s="2"/>
+      <c r="V802" s="2"/>
     </row>
     <row r="804" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E804" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q804" t="s">
         <v>173</v>
@@ -14594,7 +14597,7 @@
     </row>
     <row r="805" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E805" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q805" t="s">
         <v>173</v>
@@ -14603,381 +14606,383 @@
         <v>170</v>
       </c>
       <c r="S805">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="T805" t="s">
         <v>172</v>
       </c>
-      <c r="U805" t="s">
+      <c r="V805" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="806" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E806" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q806" t="s">
+        <v>173</v>
+      </c>
+      <c r="R806" t="s">
+        <v>170</v>
+      </c>
+      <c r="S806">
+        <v>0</v>
+      </c>
+      <c r="T806" t="s">
+        <v>172</v>
+      </c>
+      <c r="U806" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="807" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A807" s="27" t="s">
-        <v>306</v>
-      </c>
-      <c r="B807" s="27"/>
-      <c r="C807" s="28"/>
-      <c r="D807" s="28"/>
-      <c r="E807" s="28"/>
-      <c r="F807" s="28"/>
-      <c r="G807" s="28"/>
-      <c r="H807" s="28"/>
-      <c r="I807" s="28"/>
-      <c r="J807" s="28"/>
-      <c r="K807" s="28"/>
-      <c r="L807" s="28"/>
-      <c r="M807" s="28"/>
-      <c r="N807" s="28"/>
-      <c r="O807" s="28"/>
-      <c r="P807" s="28"/>
-      <c r="Q807" s="28"/>
-      <c r="R807" s="28"/>
-      <c r="S807" s="28"/>
-      <c r="T807" s="28"/>
-      <c r="U807" s="28"/>
-      <c r="V807" s="28"/>
-    </row>
-    <row r="809" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I809" t="s">
-        <v>326</v>
-      </c>
-      <c r="R809" t="s">
-        <v>324</v>
-      </c>
-      <c r="S809" s="11">
+    <row r="808" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A808" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="B808" s="27"/>
+      <c r="C808" s="28"/>
+      <c r="D808" s="28"/>
+      <c r="E808" s="28"/>
+      <c r="F808" s="28"/>
+      <c r="G808" s="28"/>
+      <c r="H808" s="28"/>
+      <c r="I808" s="28"/>
+      <c r="J808" s="28"/>
+      <c r="K808" s="28"/>
+      <c r="L808" s="28"/>
+      <c r="M808" s="28"/>
+      <c r="N808" s="28"/>
+      <c r="O808" s="28"/>
+      <c r="P808" s="28"/>
+      <c r="Q808" s="28"/>
+      <c r="R808" s="28"/>
+      <c r="S808" s="28"/>
+      <c r="T808" s="28"/>
+      <c r="U808" s="28"/>
+      <c r="V808" s="28"/>
+    </row>
+    <row r="810" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I810" t="s">
+        <v>325</v>
+      </c>
+      <c r="R810" t="s">
+        <v>323</v>
+      </c>
+      <c r="S810" s="11">
         <f>213/(213 + 60)*100</f>
         <v>78.021978021978029</v>
       </c>
-      <c r="T809" t="s">
+      <c r="T810" t="s">
         <v>97</v>
       </c>
-      <c r="V809" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="810" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I810" t="s">
-        <v>340</v>
-      </c>
-      <c r="R810" t="s">
+      <c r="V810" t="s">
         <v>324</v>
       </c>
-      <c r="S810" s="11">
+    </row>
+    <row r="811" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I811" t="s">
+        <v>339</v>
+      </c>
+      <c r="R811" t="s">
+        <v>323</v>
+      </c>
+      <c r="S811" s="11">
         <f>60/(213 + 60)*100</f>
         <v>21.978021978021978</v>
       </c>
-      <c r="T810" t="s">
+      <c r="T811" t="s">
         <v>97</v>
       </c>
-      <c r="V810" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="812" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I812" t="s">
-        <v>326</v>
-      </c>
-      <c r="R812" t="s">
-        <v>327</v>
-      </c>
-      <c r="S812">
-        <v>45</v>
-      </c>
-      <c r="T812" t="s">
-        <v>97</v>
-      </c>
-      <c r="V812" t="s">
-        <v>328</v>
+      <c r="V811" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="813" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I813" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="R813" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="S813">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="T813" t="s">
         <v>97</v>
       </c>
       <c r="V813" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="815" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R815" t="s">
-        <v>307</v>
-      </c>
-      <c r="S815" s="30">
-        <f>S822</f>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="814" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I814" t="s">
+        <v>339</v>
+      </c>
+      <c r="R814" t="s">
+        <v>326</v>
+      </c>
+      <c r="S814">
+        <v>48</v>
+      </c>
+      <c r="T814" t="s">
+        <v>97</v>
+      </c>
+      <c r="V814" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="816" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R816" t="s">
+        <v>306</v>
+      </c>
+      <c r="S816" s="30">
+        <f>S823</f>
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="T815" t="s">
-        <v>310</v>
-      </c>
-      <c r="U815" t="s">
-        <v>323</v>
-      </c>
-      <c r="V815" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="816" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A816" t="s">
+      <c r="T816" t="s">
+        <v>309</v>
+      </c>
+      <c r="U816" t="s">
+        <v>322</v>
+      </c>
+      <c r="V816" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="817" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A817" t="s">
         <v>37</v>
       </c>
-      <c r="G816" t="s">
+      <c r="G817" t="s">
         <v>142</v>
       </c>
-      <c r="R816" t="s">
-        <v>307</v>
-      </c>
-      <c r="S816" s="29">
+      <c r="R817" t="s">
+        <v>306</v>
+      </c>
+      <c r="S817" s="29">
         <f>-(45.5*0.1+10.7*0.9)/1000</f>
         <v>-1.418E-2</v>
       </c>
-      <c r="T816" t="s">
-        <v>310</v>
-      </c>
-      <c r="U816" t="s">
-        <v>341</v>
-      </c>
-      <c r="V816" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="817" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A817" t="s">
-        <v>38</v>
-      </c>
-      <c r="G817" t="s">
-        <v>142</v>
-      </c>
-      <c r="R817" t="s">
-        <v>307</v>
-      </c>
-      <c r="S817" s="33">
-        <f>S816</f>
-        <v>-1.418E-2</v>
-      </c>
       <c r="T817" t="s">
-        <v>310</v>
+        <v>309</v>
+      </c>
+      <c r="U817" t="s">
+        <v>340</v>
+      </c>
+      <c r="V817" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="818" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
+        <v>38</v>
+      </c>
+      <c r="G818" t="s">
+        <v>142</v>
+      </c>
+      <c r="R818" t="s">
+        <v>306</v>
+      </c>
+      <c r="S818" s="33">
+        <f>S817</f>
+        <v>-1.418E-2</v>
+      </c>
+      <c r="T818" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="819" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A819" t="s">
         <v>37</v>
       </c>
-      <c r="G818" t="s">
+      <c r="G819" t="s">
         <v>98</v>
       </c>
-      <c r="R818" t="s">
-        <v>307</v>
-      </c>
-      <c r="S818" s="29">
+      <c r="R819" t="s">
+        <v>306</v>
+      </c>
+      <c r="S819" s="29">
         <f>-(45.5*0.4+10.7*0.6)/1000</f>
         <v>-2.4619999999999996E-2</v>
       </c>
-      <c r="T818" t="s">
-        <v>310</v>
-      </c>
-      <c r="U818" t="s">
-        <v>342</v>
-      </c>
-      <c r="V818" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="819" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A819" t="s">
+      <c r="T819" t="s">
+        <v>309</v>
+      </c>
+      <c r="U819" t="s">
+        <v>341</v>
+      </c>
+      <c r="V819" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="820" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A820" t="s">
         <v>38</v>
       </c>
-      <c r="G819" t="s">
+      <c r="G820" t="s">
         <v>98</v>
       </c>
-      <c r="R819" t="s">
-        <v>307</v>
-      </c>
-      <c r="S819" s="33">
-        <f>S818</f>
+      <c r="R820" t="s">
+        <v>306</v>
+      </c>
+      <c r="S820" s="33">
+        <f>S819</f>
         <v>-2.4619999999999996E-2</v>
       </c>
-      <c r="T819" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="820" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A820" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B820" s="4"/>
-      <c r="R820" t="s">
-        <v>307</v>
-      </c>
-      <c r="S820" s="4">
-        <f>-10.7/1000</f>
-        <v>-1.0699999999999999E-2</v>
-      </c>
       <c r="T820" t="s">
-        <v>310</v>
-      </c>
-      <c r="U820" t="s">
-        <v>321</v>
-      </c>
-      <c r="V820" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="821" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A821" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B821" s="4"/>
       <c r="R821" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S821" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="T821" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="U821" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="V821" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="822" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C822" t="s">
+      <c r="A822" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B822" s="4"/>
+      <c r="R822" t="s">
+        <v>306</v>
+      </c>
+      <c r="S822" s="4">
+        <f>-10.7/1000</f>
+        <v>-1.0699999999999999E-2</v>
+      </c>
+      <c r="T822" t="s">
+        <v>309</v>
+      </c>
+      <c r="U822" t="s">
+        <v>320</v>
+      </c>
+      <c r="V822" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="823" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C823" t="s">
         <v>226</v>
       </c>
-      <c r="R822" t="s">
-        <v>307</v>
-      </c>
-      <c r="S822">
+      <c r="R823" t="s">
+        <v>306</v>
+      </c>
+      <c r="S823">
         <f>-0.6/1000</f>
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="T822" t="s">
-        <v>310</v>
-      </c>
-      <c r="V822" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="823" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B823" t="s">
-        <v>337</v>
-      </c>
-      <c r="R823" t="s">
-        <v>307</v>
-      </c>
-      <c r="S823" s="29">
+      <c r="T823" t="s">
+        <v>309</v>
+      </c>
+      <c r="V823" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="824" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B824" t="s">
+        <v>336</v>
+      </c>
+      <c r="R824" t="s">
+        <v>306</v>
+      </c>
+      <c r="S824" s="29">
         <f>-20*0.45/0.85/1000</f>
         <v>-1.0588235294117647E-2</v>
       </c>
-      <c r="T823" t="s">
-        <v>310</v>
-      </c>
-      <c r="U823" t="s">
-        <v>339</v>
-      </c>
-      <c r="V823" t="s">
+      <c r="T824" t="s">
+        <v>309</v>
+      </c>
+      <c r="U824" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="825" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D825" t="s">
-        <v>313</v>
-      </c>
-      <c r="R825" t="s">
-        <v>308</v>
-      </c>
-      <c r="S825">
+      <c r="V824" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="826" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D826" t="s">
+        <v>312</v>
+      </c>
+      <c r="R826" t="s">
+        <v>307</v>
+      </c>
+      <c r="S826">
         <f>-9.2/1000</f>
         <v>-9.1999999999999998E-3</v>
       </c>
-      <c r="T825" t="s">
-        <v>310</v>
-      </c>
-      <c r="V825" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="827" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I827" t="s">
-        <v>107</v>
-      </c>
-      <c r="R827" t="s">
-        <v>316</v>
-      </c>
-      <c r="S827" s="31">
-        <v>-0.5</v>
-      </c>
-      <c r="T827" t="s">
-        <v>311</v>
-      </c>
-      <c r="V827" t="s">
-        <v>320</v>
+      <c r="T826" t="s">
+        <v>309</v>
+      </c>
+      <c r="V826" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="828" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I828" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R828" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="S828" s="31">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="T828" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="V828" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="829" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I829" t="s">
+        <v>108</v>
+      </c>
+      <c r="R829" t="s">
+        <v>315</v>
+      </c>
+      <c r="S829" s="31">
+        <v>-1</v>
+      </c>
+      <c r="T829" t="s">
+        <v>310</v>
+      </c>
+      <c r="V829" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="830" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I830" t="s">
         <v>208</v>
       </c>
-      <c r="R829" t="s">
-        <v>316</v>
-      </c>
-      <c r="S829" s="22">
+      <c r="R830" t="s">
+        <v>315</v>
+      </c>
+      <c r="S830" s="22">
         <v>-1</v>
       </c>
-      <c r="T829" t="s">
-        <v>311</v>
-      </c>
-      <c r="U829" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="830" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R830" t="s">
-        <v>318</v>
-      </c>
-      <c r="S830" s="22">
-        <f>-0.4 / ( (2*30.97) / (2*30.97 + 5*16) )</f>
-        <v>-0.91662899580238943</v>
-      </c>
       <c r="T830" t="s">
-        <v>319</v>
-      </c>
-      <c r="U830" s="32" t="s">
-        <v>334</v>
-      </c>
-      <c r="V830" t="s">
-        <v>336</v>
+        <v>310</v>
+      </c>
+      <c r="U830" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="831" spans="1:22" x14ac:dyDescent="0.25">
@@ -14985,75 +14990,93 @@
         <v>317</v>
       </c>
       <c r="S831" s="22">
+        <f>-0.4 / ( (2*30.97) / (2*30.97 + 5*16) )</f>
+        <v>-0.91662899580238943</v>
+      </c>
+      <c r="T831" t="s">
+        <v>318</v>
+      </c>
+      <c r="U831" s="32" t="s">
+        <v>333</v>
+      </c>
+      <c r="V831" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="832" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R832" t="s">
+        <v>316</v>
+      </c>
+      <c r="S832" s="22">
         <f>0.6 / ( (2*39.1) / (2*39.1 + 16) )</f>
         <v>0.72276214833759589</v>
       </c>
-      <c r="T831" t="s">
-        <v>319</v>
-      </c>
-      <c r="U831" s="32" t="s">
+      <c r="T832" t="s">
+        <v>318</v>
+      </c>
+      <c r="U832" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="V832" t="s">
         <v>335</v>
       </c>
-      <c r="V831" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="833" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="R833" t="s">
-        <v>309</v>
-      </c>
-      <c r="S833" s="31">
+    </row>
+    <row r="834" spans="9:22" x14ac:dyDescent="0.25">
+      <c r="R834" t="s">
+        <v>308</v>
+      </c>
+      <c r="S834" s="31">
         <f>3/5</f>
         <v>0.6</v>
       </c>
-      <c r="T833" t="s">
-        <v>311</v>
-      </c>
-      <c r="U833" t="s">
-        <v>315</v>
-      </c>
-      <c r="V833" t="s">
+      <c r="T834" t="s">
+        <v>310</v>
+      </c>
+      <c r="U834" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="835" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I835" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q835" t="s">
-        <v>330</v>
-      </c>
-      <c r="R835" t="s">
-        <v>332</v>
-      </c>
-      <c r="S835" s="31">
+      <c r="V834" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="836" spans="9:22" x14ac:dyDescent="0.25">
+      <c r="I836" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q836" t="s">
+        <v>329</v>
+      </c>
+      <c r="R836" t="s">
+        <v>331</v>
+      </c>
+      <c r="S836" s="31">
         <f>0.12*(44/12)</f>
         <v>0.43999999999999995</v>
       </c>
-      <c r="T835" t="s">
+      <c r="T836" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="837" spans="9:22" x14ac:dyDescent="0.25">
+      <c r="I837" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q837" t="s">
+        <v>329</v>
+      </c>
+      <c r="R837" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="836" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I836" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q836" t="s">
-        <v>330</v>
-      </c>
-      <c r="R836" t="s">
-        <v>332</v>
-      </c>
-      <c r="S836" s="31">
+      <c r="S837" s="31">
         <f>0.13*(44/12)</f>
         <v>0.47666666666666668</v>
       </c>
-      <c r="T836" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="837" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="S837" s="11"/>
+      <c r="T837" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="838" spans="9:22" x14ac:dyDescent="0.25">
+      <c r="S838" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="360">
   <si>
     <t>f_crop</t>
   </si>
@@ -1080,10 +1080,25 @@
     <t>grass clover ley (avg. 20/40% clover) and three harvest</t>
   </si>
   <si>
-    <t>Not included in NIR, reported under forest</t>
-  </si>
-  <si>
-    <t>Pers. comm. Mattias Lindblad (2024-11-14)</t>
+    <t>kg/ha</t>
+  </si>
+  <si>
+    <t>kg CO2/ha</t>
+  </si>
+  <si>
+    <t>Not included in NIR under Agriculture, reported under forest</t>
+  </si>
+  <si>
+    <t>Lindgren &amp; Lundblad (2014) Towards new reporting of drained organic soils under the UNFCCC - assessment of emission factors and areas in Sweden.</t>
+  </si>
+  <si>
+    <t>Soil losses organic soils</t>
+  </si>
+  <si>
+    <t>CH4bio</t>
+  </si>
+  <si>
+    <t>kg CH4/ha</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1255,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1277,6 +1292,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1558,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V838"/>
+  <dimension ref="A1:V845"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="21" customWidth="1"/>
@@ -14493,106 +14509,105 @@
       </c>
     </row>
     <row r="798" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="Q798" t="s">
+      <c r="A798" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B798" s="2"/>
+      <c r="C798" s="2"/>
+      <c r="D798" s="2"/>
+      <c r="E798" s="2"/>
+      <c r="F798" s="2"/>
+      <c r="G798" s="2"/>
+      <c r="H798" s="2"/>
+      <c r="I798" s="2"/>
+      <c r="J798" s="2"/>
+      <c r="K798" s="2"/>
+      <c r="L798" s="2"/>
+      <c r="M798" s="2"/>
+      <c r="N798" s="2"/>
+      <c r="O798" s="2"/>
+      <c r="P798" s="2"/>
+      <c r="Q798" s="2"/>
+      <c r="R798" s="2"/>
+      <c r="S798" s="2"/>
+      <c r="T798" s="2"/>
+      <c r="U798" s="2"/>
+      <c r="V798" s="2"/>
+    </row>
+    <row r="799" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R799" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="S799" s="5">
+        <v>0</v>
+      </c>
+      <c r="T799" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="U799" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="801" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E801" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q801" t="s">
         <v>148</v>
       </c>
-      <c r="R798" t="s">
+      <c r="R801" t="s">
         <v>166</v>
       </c>
-      <c r="S798">
-        <v>0</v>
-      </c>
-      <c r="T798" t="s">
+      <c r="S801">
+        <v>13</v>
+      </c>
+      <c r="T801" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="799" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="E799" t="s">
+      <c r="V801" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="802" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E802" t="s">
         <v>175</v>
       </c>
-      <c r="Q799" t="s">
-        <v>148</v>
-      </c>
-      <c r="R799" t="s">
+      <c r="Q802" t="s">
+        <v>329</v>
+      </c>
+      <c r="R802" t="s">
         <v>166</v>
       </c>
-      <c r="S799">
-        <v>13</v>
-      </c>
-      <c r="T799" t="s">
-        <v>167</v>
-      </c>
-      <c r="V799" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="800" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="E800" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q800" t="s">
-        <v>148</v>
-      </c>
-      <c r="R800" t="s">
+      <c r="S802" s="34">
+        <f>6.1*(44/12)*1000</f>
+        <v>22366.666666666664</v>
+      </c>
+      <c r="T802" t="s">
+        <v>354</v>
+      </c>
+      <c r="V802" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="803" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E803" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q803" t="s">
+        <v>358</v>
+      </c>
+      <c r="R803" t="s">
         <v>166</v>
       </c>
-      <c r="S800">
-        <v>13</v>
-      </c>
-      <c r="T800" t="s">
-        <v>167</v>
-      </c>
-      <c r="U800" t="s">
-        <v>353</v>
-      </c>
-      <c r="V800" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="802" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A802" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B802" s="2"/>
-      <c r="C802" s="2"/>
-      <c r="D802" s="2"/>
-      <c r="E802" s="2"/>
-      <c r="F802" s="2"/>
-      <c r="G802" s="2"/>
-      <c r="H802" s="2"/>
-      <c r="I802" s="2"/>
-      <c r="J802" s="2"/>
-      <c r="K802" s="2"/>
-      <c r="L802" s="2"/>
-      <c r="M802" s="2"/>
-      <c r="N802" s="2"/>
-      <c r="O802" s="2"/>
-      <c r="P802" s="2"/>
-      <c r="Q802" s="2"/>
-      <c r="R802" s="2"/>
-      <c r="S802" s="2"/>
-      <c r="T802" s="2"/>
-      <c r="U802" s="2"/>
-      <c r="V802" s="2"/>
-    </row>
-    <row r="804" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="E804" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q804" t="s">
-        <v>173</v>
-      </c>
-      <c r="R804" t="s">
-        <v>170</v>
-      </c>
-      <c r="S804">
-        <v>0.24</v>
-      </c>
-      <c r="T804" t="s">
-        <v>172</v>
-      </c>
-      <c r="V804" t="s">
-        <v>171</v>
+      <c r="S803">
+        <f>0+58.3</f>
+        <v>58.3</v>
+      </c>
+      <c r="T803" t="s">
+        <v>359</v>
+      </c>
+      <c r="V803" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="805" spans="1:22" x14ac:dyDescent="0.25">
@@ -14600,483 +14615,594 @@
         <v>176</v>
       </c>
       <c r="Q805" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="R805" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="S805">
-        <v>0.24</v>
+        <v>2.8</v>
       </c>
       <c r="T805" t="s">
-        <v>172</v>
+        <v>167</v>
+      </c>
+      <c r="U805" t="s">
+        <v>355</v>
       </c>
       <c r="V805" t="s">
-        <v>171</v>
+        <v>356</v>
       </c>
     </row>
     <row r="806" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E806" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q806" t="s">
+        <v>329</v>
+      </c>
+      <c r="R806" t="s">
+        <v>166</v>
+      </c>
+      <c r="S806" s="34">
+        <f>2.6*(44/12)*1000</f>
+        <v>9533.3333333333339</v>
+      </c>
+      <c r="T806" t="s">
+        <v>354</v>
+      </c>
+      <c r="V806" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="807" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E807" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q807" t="s">
+        <v>358</v>
+      </c>
+      <c r="R807" t="s">
+        <v>166</v>
+      </c>
+      <c r="S807">
+        <f>2.5+5.4</f>
+        <v>7.9</v>
+      </c>
+      <c r="T807" t="s">
+        <v>359</v>
+      </c>
+      <c r="V807" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="809" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A809" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B809" s="2"/>
+      <c r="C809" s="2"/>
+      <c r="D809" s="2"/>
+      <c r="E809" s="2"/>
+      <c r="F809" s="2"/>
+      <c r="G809" s="2"/>
+      <c r="H809" s="2"/>
+      <c r="I809" s="2"/>
+      <c r="J809" s="2"/>
+      <c r="K809" s="2"/>
+      <c r="L809" s="2"/>
+      <c r="M809" s="2"/>
+      <c r="N809" s="2"/>
+      <c r="O809" s="2"/>
+      <c r="P809" s="2"/>
+      <c r="Q809" s="2"/>
+      <c r="R809" s="2"/>
+      <c r="S809" s="2"/>
+      <c r="T809" s="2"/>
+      <c r="U809" s="2"/>
+      <c r="V809" s="2"/>
+    </row>
+    <row r="811" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E811" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q811" t="s">
+        <v>173</v>
+      </c>
+      <c r="R811" t="s">
+        <v>170</v>
+      </c>
+      <c r="S811">
+        <v>0.24</v>
+      </c>
+      <c r="T811" t="s">
+        <v>172</v>
+      </c>
+      <c r="V811" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="812" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E812" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q812" t="s">
+        <v>173</v>
+      </c>
+      <c r="R812" t="s">
+        <v>170</v>
+      </c>
+      <c r="S812">
+        <v>0.24</v>
+      </c>
+      <c r="T812" t="s">
+        <v>172</v>
+      </c>
+      <c r="V812" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="813" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E813" t="s">
         <v>177</v>
       </c>
-      <c r="Q806" t="s">
+      <c r="Q813" t="s">
         <v>173</v>
       </c>
-      <c r="R806" t="s">
+      <c r="R813" t="s">
         <v>170</v>
       </c>
-      <c r="S806">
+      <c r="S813">
         <v>0</v>
       </c>
-      <c r="T806" t="s">
+      <c r="T813" t="s">
         <v>172</v>
       </c>
-      <c r="U806" t="s">
+      <c r="U813" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="808" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A808" s="27" t="s">
+    <row r="815" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A815" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="B808" s="27"/>
-      <c r="C808" s="28"/>
-      <c r="D808" s="28"/>
-      <c r="E808" s="28"/>
-      <c r="F808" s="28"/>
-      <c r="G808" s="28"/>
-      <c r="H808" s="28"/>
-      <c r="I808" s="28"/>
-      <c r="J808" s="28"/>
-      <c r="K808" s="28"/>
-      <c r="L808" s="28"/>
-      <c r="M808" s="28"/>
-      <c r="N808" s="28"/>
-      <c r="O808" s="28"/>
-      <c r="P808" s="28"/>
-      <c r="Q808" s="28"/>
-      <c r="R808" s="28"/>
-      <c r="S808" s="28"/>
-      <c r="T808" s="28"/>
-      <c r="U808" s="28"/>
-      <c r="V808" s="28"/>
-    </row>
-    <row r="810" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I810" t="s">
+      <c r="B815" s="27"/>
+      <c r="C815" s="28"/>
+      <c r="D815" s="28"/>
+      <c r="E815" s="28"/>
+      <c r="F815" s="28"/>
+      <c r="G815" s="28"/>
+      <c r="H815" s="28"/>
+      <c r="I815" s="28"/>
+      <c r="J815" s="28"/>
+      <c r="K815" s="28"/>
+      <c r="L815" s="28"/>
+      <c r="M815" s="28"/>
+      <c r="N815" s="28"/>
+      <c r="O815" s="28"/>
+      <c r="P815" s="28"/>
+      <c r="Q815" s="28"/>
+      <c r="R815" s="28"/>
+      <c r="S815" s="28"/>
+      <c r="T815" s="28"/>
+      <c r="U815" s="28"/>
+      <c r="V815" s="28"/>
+    </row>
+    <row r="817" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I817" t="s">
         <v>325</v>
       </c>
-      <c r="R810" t="s">
+      <c r="R817" t="s">
         <v>323</v>
       </c>
-      <c r="S810" s="11">
+      <c r="S817" s="11">
         <f>213/(213 + 60)*100</f>
         <v>78.021978021978029</v>
       </c>
-      <c r="T810" t="s">
+      <c r="T817" t="s">
         <v>97</v>
       </c>
-      <c r="V810" t="s">
+      <c r="V817" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="811" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I811" t="s">
+    <row r="818" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I818" t="s">
         <v>339</v>
       </c>
-      <c r="R811" t="s">
+      <c r="R818" t="s">
         <v>323</v>
       </c>
-      <c r="S811" s="11">
+      <c r="S818" s="11">
         <f>60/(213 + 60)*100</f>
         <v>21.978021978021978</v>
       </c>
-      <c r="T811" t="s">
+      <c r="T818" t="s">
         <v>97</v>
       </c>
-      <c r="V811" t="s">
+      <c r="V818" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="813" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I813" t="s">
+    <row r="820" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I820" t="s">
         <v>325</v>
       </c>
-      <c r="R813" t="s">
+      <c r="R820" t="s">
         <v>326</v>
       </c>
-      <c r="S813">
+      <c r="S820">
         <v>45</v>
       </c>
-      <c r="T813" t="s">
+      <c r="T820" t="s">
         <v>97</v>
       </c>
-      <c r="V813" t="s">
+      <c r="V820" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="814" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I814" t="s">
+    <row r="821" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I821" t="s">
         <v>339</v>
       </c>
-      <c r="R814" t="s">
+      <c r="R821" t="s">
         <v>326</v>
       </c>
-      <c r="S814">
+      <c r="S821">
         <v>48</v>
       </c>
-      <c r="T814" t="s">
+      <c r="T821" t="s">
         <v>97</v>
       </c>
-      <c r="V814" t="s">
+      <c r="V821" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="816" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R816" t="s">
+    <row r="823" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R823" t="s">
         <v>306</v>
       </c>
-      <c r="S816" s="30">
-        <f>S823</f>
+      <c r="S823" s="30">
+        <f>S830</f>
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="T816" t="s">
+      <c r="T823" t="s">
         <v>309</v>
       </c>
-      <c r="U816" t="s">
+      <c r="U823" t="s">
         <v>322</v>
       </c>
-      <c r="V816" t="s">
+      <c r="V823" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="817" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A817" t="s">
+    <row r="824" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A824" t="s">
         <v>37</v>
       </c>
-      <c r="G817" t="s">
+      <c r="G824" t="s">
         <v>142</v>
       </c>
-      <c r="R817" t="s">
+      <c r="R824" t="s">
         <v>306</v>
       </c>
-      <c r="S817" s="29">
+      <c r="S824" s="29">
         <f>-(45.5*0.1+10.7*0.9)/1000</f>
         <v>-1.418E-2</v>
       </c>
-      <c r="T817" t="s">
+      <c r="T824" t="s">
         <v>309</v>
       </c>
-      <c r="U817" t="s">
+      <c r="U824" t="s">
         <v>340</v>
       </c>
-      <c r="V817" t="s">
+      <c r="V824" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="818" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A818" t="s">
+    <row r="825" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A825" t="s">
         <v>38</v>
       </c>
-      <c r="G818" t="s">
+      <c r="G825" t="s">
         <v>142</v>
       </c>
-      <c r="R818" t="s">
+      <c r="R825" t="s">
         <v>306</v>
       </c>
-      <c r="S818" s="33">
-        <f>S817</f>
+      <c r="S825" s="33">
+        <f>S824</f>
         <v>-1.418E-2</v>
       </c>
-      <c r="T818" t="s">
+      <c r="T825" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="819" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A819" t="s">
+    <row r="826" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A826" t="s">
         <v>37</v>
       </c>
-      <c r="G819" t="s">
+      <c r="G826" t="s">
         <v>98</v>
       </c>
-      <c r="R819" t="s">
+      <c r="R826" t="s">
         <v>306</v>
       </c>
-      <c r="S819" s="29">
+      <c r="S826" s="29">
         <f>-(45.5*0.4+10.7*0.6)/1000</f>
         <v>-2.4619999999999996E-2</v>
       </c>
-      <c r="T819" t="s">
+      <c r="T826" t="s">
         <v>309</v>
       </c>
-      <c r="U819" t="s">
+      <c r="U826" t="s">
         <v>341</v>
       </c>
-      <c r="V819" t="s">
+      <c r="V826" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="820" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A820" t="s">
+    <row r="827" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A827" t="s">
         <v>38</v>
       </c>
-      <c r="G820" t="s">
+      <c r="G827" t="s">
         <v>98</v>
       </c>
-      <c r="R820" t="s">
+      <c r="R827" t="s">
         <v>306</v>
       </c>
-      <c r="S820" s="33">
-        <f>S819</f>
+      <c r="S827" s="33">
+        <f>S826</f>
         <v>-2.4619999999999996E-2</v>
       </c>
-      <c r="T820" t="s">
+      <c r="T827" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="821" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A821" s="4" t="s">
+    <row r="828" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A828" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B821" s="4"/>
-      <c r="R821" t="s">
+      <c r="B828" s="4"/>
+      <c r="R828" t="s">
         <v>306</v>
       </c>
-      <c r="S821" s="4">
+      <c r="S828" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
-      <c r="T821" t="s">
+      <c r="T828" t="s">
         <v>309</v>
       </c>
-      <c r="U821" t="s">
+      <c r="U828" t="s">
         <v>320</v>
       </c>
-      <c r="V821" t="s">
+      <c r="V828" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="822" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A822" s="4" t="s">
+    <row r="829" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A829" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B822" s="4"/>
-      <c r="R822" t="s">
+      <c r="B829" s="4"/>
+      <c r="R829" t="s">
         <v>306</v>
       </c>
-      <c r="S822" s="4">
+      <c r="S829" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
-      <c r="T822" t="s">
+      <c r="T829" t="s">
         <v>309</v>
       </c>
-      <c r="U822" t="s">
+      <c r="U829" t="s">
         <v>320</v>
       </c>
-      <c r="V822" t="s">
+      <c r="V829" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="823" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C823" t="s">
+    <row r="830" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C830" t="s">
         <v>226</v>
       </c>
-      <c r="R823" t="s">
+      <c r="R830" t="s">
         <v>306</v>
       </c>
-      <c r="S823">
+      <c r="S830">
         <f>-0.6/1000</f>
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="T823" t="s">
+      <c r="T830" t="s">
         <v>309</v>
       </c>
-      <c r="V823" t="s">
+      <c r="V830" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="824" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B824" t="s">
+    <row r="831" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B831" t="s">
         <v>336</v>
       </c>
-      <c r="R824" t="s">
+      <c r="R831" t="s">
         <v>306</v>
       </c>
-      <c r="S824" s="29">
+      <c r="S831" s="29">
         <f>-20*0.45/0.85/1000</f>
         <v>-1.0588235294117647E-2</v>
       </c>
-      <c r="T824" t="s">
+      <c r="T831" t="s">
         <v>309</v>
       </c>
-      <c r="U824" t="s">
+      <c r="U831" t="s">
         <v>338</v>
       </c>
-      <c r="V824" t="s">
+      <c r="V831" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="826" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D826" t="s">
+    <row r="833" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="D833" t="s">
         <v>312</v>
       </c>
-      <c r="R826" t="s">
+      <c r="R833" t="s">
         <v>307</v>
       </c>
-      <c r="S826">
+      <c r="S833">
         <f>-9.2/1000</f>
         <v>-9.1999999999999998E-3</v>
       </c>
-      <c r="T826" t="s">
+      <c r="T833" t="s">
         <v>309</v>
       </c>
-      <c r="V826" t="s">
+      <c r="V833" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="828" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I828" t="s">
+    <row r="835" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="I835" t="s">
         <v>107</v>
       </c>
-      <c r="R828" t="s">
+      <c r="R835" t="s">
         <v>315</v>
       </c>
-      <c r="S828" s="31">
+      <c r="S835" s="31">
         <v>-0.5</v>
       </c>
-      <c r="T828" t="s">
+      <c r="T835" t="s">
         <v>310</v>
       </c>
-      <c r="V828" t="s">
+      <c r="V835" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="829" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I829" t="s">
+    <row r="836" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="I836" t="s">
         <v>108</v>
       </c>
-      <c r="R829" t="s">
+      <c r="R836" t="s">
         <v>315</v>
       </c>
-      <c r="S829" s="31">
+      <c r="S836" s="31">
         <v>-1</v>
       </c>
-      <c r="T829" t="s">
+      <c r="T836" t="s">
         <v>310</v>
       </c>
-      <c r="V829" t="s">
+      <c r="V836" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="830" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I830" t="s">
+    <row r="837" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="I837" t="s">
         <v>208</v>
       </c>
-      <c r="R830" t="s">
+      <c r="R837" t="s">
         <v>315</v>
       </c>
-      <c r="S830" s="22">
+      <c r="S837" s="22">
         <v>-1</v>
       </c>
-      <c r="T830" t="s">
+      <c r="T837" t="s">
         <v>310</v>
       </c>
-      <c r="U830" t="s">
+      <c r="U837" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="831" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R831" t="s">
+    <row r="838" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="R838" t="s">
         <v>317</v>
       </c>
-      <c r="S831" s="22">
+      <c r="S838" s="22">
         <f>-0.4 / ( (2*30.97) / (2*30.97 + 5*16) )</f>
         <v>-0.91662899580238943</v>
       </c>
-      <c r="T831" t="s">
+      <c r="T838" t="s">
         <v>318</v>
       </c>
-      <c r="U831" s="32" t="s">
+      <c r="U838" s="32" t="s">
         <v>333</v>
       </c>
-      <c r="V831" t="s">
+      <c r="V838" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="832" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R832" t="s">
+    <row r="839" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="R839" t="s">
         <v>316</v>
       </c>
-      <c r="S832" s="22">
+      <c r="S839" s="22">
         <f>0.6 / ( (2*39.1) / (2*39.1 + 16) )</f>
         <v>0.72276214833759589</v>
       </c>
-      <c r="T832" t="s">
+      <c r="T839" t="s">
         <v>318</v>
       </c>
-      <c r="U832" s="32" t="s">
+      <c r="U839" s="32" t="s">
         <v>334</v>
       </c>
-      <c r="V832" t="s">
+      <c r="V839" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="834" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="R834" t="s">
+    <row r="841" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="R841" t="s">
         <v>308</v>
       </c>
-      <c r="S834" s="31">
+      <c r="S841" s="31">
         <f>3/5</f>
         <v>0.6</v>
       </c>
-      <c r="T834" t="s">
+      <c r="T841" t="s">
         <v>310</v>
       </c>
-      <c r="U834" t="s">
+      <c r="U841" t="s">
         <v>314</v>
       </c>
-      <c r="V834" t="s">
+      <c r="V841" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="836" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I836" t="s">
+    <row r="843" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="I843" t="s">
         <v>325</v>
       </c>
-      <c r="Q836" t="s">
+      <c r="Q843" t="s">
         <v>329</v>
       </c>
-      <c r="R836" t="s">
+      <c r="R843" t="s">
         <v>331</v>
       </c>
-      <c r="S836" s="31">
+      <c r="S843" s="31">
         <f>0.12*(44/12)</f>
         <v>0.43999999999999995</v>
       </c>
-      <c r="T836" t="s">
+      <c r="T843" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="837" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I837" t="s">
+    <row r="844" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="I844" t="s">
         <v>339</v>
       </c>
-      <c r="Q837" t="s">
+      <c r="Q844" t="s">
         <v>329</v>
       </c>
-      <c r="R837" t="s">
+      <c r="R844" t="s">
         <v>331</v>
       </c>
-      <c r="S837" s="31">
+      <c r="S844" s="31">
         <f>0.13*(44/12)</f>
         <v>0.47666666666666668</v>
       </c>
-      <c r="T837" t="s">
+      <c r="T844" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="838" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="S838" s="11"/>
+    <row r="845" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="S845" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="362">
   <si>
     <t>f_crop</t>
   </si>
@@ -1099,6 +1099,12 @@
   </si>
   <si>
     <t>kg CH4/ha</t>
+  </si>
+  <si>
+    <t>soil_losses_cover_crop_residues</t>
+  </si>
+  <si>
+    <t>cover crop residues</t>
   </si>
 </sst>
 </file>
@@ -1110,7 +1116,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1215,6 +1221,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1255,7 +1268,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1293,6 +1306,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1574,7 +1588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V845"/>
+  <dimension ref="A1:V846"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="21" customWidth="1"/>
@@ -14508,64 +14522,62 @@
         <v>151</v>
       </c>
     </row>
-    <row r="798" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A798" s="2" t="s">
+    <row r="797" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Q797" t="s">
+        <v>148</v>
+      </c>
+      <c r="R797" t="s">
+        <v>360</v>
+      </c>
+      <c r="S797" s="35">
+        <f>S796</f>
+        <v>1</v>
+      </c>
+      <c r="T797" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="U797" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="799" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A799" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B798" s="2"/>
-      <c r="C798" s="2"/>
-      <c r="D798" s="2"/>
-      <c r="E798" s="2"/>
-      <c r="F798" s="2"/>
-      <c r="G798" s="2"/>
-      <c r="H798" s="2"/>
-      <c r="I798" s="2"/>
-      <c r="J798" s="2"/>
-      <c r="K798" s="2"/>
-      <c r="L798" s="2"/>
-      <c r="M798" s="2"/>
-      <c r="N798" s="2"/>
-      <c r="O798" s="2"/>
-      <c r="P798" s="2"/>
-      <c r="Q798" s="2"/>
-      <c r="R798" s="2"/>
-      <c r="S798" s="2"/>
-      <c r="T798" s="2"/>
-      <c r="U798" s="2"/>
-      <c r="V798" s="2"/>
-    </row>
-    <row r="799" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R799" s="5" t="s">
+      <c r="B799" s="2"/>
+      <c r="C799" s="2"/>
+      <c r="D799" s="2"/>
+      <c r="E799" s="2"/>
+      <c r="F799" s="2"/>
+      <c r="G799" s="2"/>
+      <c r="H799" s="2"/>
+      <c r="I799" s="2"/>
+      <c r="J799" s="2"/>
+      <c r="K799" s="2"/>
+      <c r="L799" s="2"/>
+      <c r="M799" s="2"/>
+      <c r="N799" s="2"/>
+      <c r="O799" s="2"/>
+      <c r="P799" s="2"/>
+      <c r="Q799" s="2"/>
+      <c r="R799" s="2"/>
+      <c r="S799" s="2"/>
+      <c r="T799" s="2"/>
+      <c r="U799" s="2"/>
+      <c r="V799" s="2"/>
+    </row>
+    <row r="800" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R800" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="S799" s="5">
+      <c r="S800" s="5">
         <v>0</v>
       </c>
-      <c r="T799" s="5" t="s">
+      <c r="T800" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="U799" s="5" t="s">
+      <c r="U800" s="5" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="801" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="E801" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q801" t="s">
-        <v>148</v>
-      </c>
-      <c r="R801" t="s">
-        <v>166</v>
-      </c>
-      <c r="S801">
-        <v>13</v>
-      </c>
-      <c r="T801" t="s">
-        <v>167</v>
-      </c>
-      <c r="V801" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="802" spans="1:22" x14ac:dyDescent="0.25">
@@ -14573,20 +14585,19 @@
         <v>175</v>
       </c>
       <c r="Q802" t="s">
-        <v>329</v>
+        <v>148</v>
       </c>
       <c r="R802" t="s">
         <v>166</v>
       </c>
-      <c r="S802" s="34">
-        <f>6.1*(44/12)*1000</f>
-        <v>22366.666666666664</v>
+      <c r="S802">
+        <v>13</v>
       </c>
       <c r="T802" t="s">
-        <v>354</v>
+        <v>167</v>
       </c>
       <c r="V802" t="s">
-        <v>356</v>
+        <v>151</v>
       </c>
     </row>
     <row r="803" spans="1:22" x14ac:dyDescent="0.25">
@@ -14594,42 +14605,40 @@
         <v>175</v>
       </c>
       <c r="Q803" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="R803" t="s">
         <v>166</v>
       </c>
-      <c r="S803">
+      <c r="S803" s="34">
+        <f>6.1*(44/12)*1000</f>
+        <v>22366.666666666664</v>
+      </c>
+      <c r="T803" t="s">
+        <v>354</v>
+      </c>
+      <c r="V803" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="804" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E804" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q804" t="s">
+        <v>358</v>
+      </c>
+      <c r="R804" t="s">
+        <v>166</v>
+      </c>
+      <c r="S804">
         <f>0+58.3</f>
         <v>58.3</v>
       </c>
-      <c r="T803" t="s">
+      <c r="T804" t="s">
         <v>359</v>
       </c>
-      <c r="V803" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="805" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="E805" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q805" t="s">
-        <v>148</v>
-      </c>
-      <c r="R805" t="s">
-        <v>166</v>
-      </c>
-      <c r="S805">
-        <v>2.8</v>
-      </c>
-      <c r="T805" t="s">
-        <v>167</v>
-      </c>
-      <c r="U805" t="s">
-        <v>355</v>
-      </c>
-      <c r="V805" t="s">
+      <c r="V804" t="s">
         <v>356</v>
       </c>
     </row>
@@ -14638,17 +14647,19 @@
         <v>176</v>
       </c>
       <c r="Q806" t="s">
-        <v>329</v>
+        <v>148</v>
       </c>
       <c r="R806" t="s">
         <v>166</v>
       </c>
-      <c r="S806" s="34">
-        <f>2.6*(44/12)*1000</f>
-        <v>9533.3333333333339</v>
+      <c r="S806">
+        <v>2.8</v>
       </c>
       <c r="T806" t="s">
-        <v>354</v>
+        <v>167</v>
+      </c>
+      <c r="U806" t="s">
+        <v>355</v>
       </c>
       <c r="V806" t="s">
         <v>356</v>
@@ -14659,71 +14670,72 @@
         <v>176</v>
       </c>
       <c r="Q807" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="R807" t="s">
         <v>166</v>
       </c>
-      <c r="S807">
+      <c r="S807" s="34">
+        <f>2.6*(44/12)*1000</f>
+        <v>9533.3333333333339</v>
+      </c>
+      <c r="T807" t="s">
+        <v>354</v>
+      </c>
+      <c r="V807" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="808" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E808" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q808" t="s">
+        <v>358</v>
+      </c>
+      <c r="R808" t="s">
+        <v>166</v>
+      </c>
+      <c r="S808">
         <f>2.5+5.4</f>
         <v>7.9</v>
       </c>
-      <c r="T807" t="s">
+      <c r="T808" t="s">
         <v>359</v>
       </c>
-      <c r="V807" t="s">
+      <c r="V808" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="809" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A809" s="2" t="s">
+    <row r="810" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A810" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B809" s="2"/>
-      <c r="C809" s="2"/>
-      <c r="D809" s="2"/>
-      <c r="E809" s="2"/>
-      <c r="F809" s="2"/>
-      <c r="G809" s="2"/>
-      <c r="H809" s="2"/>
-      <c r="I809" s="2"/>
-      <c r="J809" s="2"/>
-      <c r="K809" s="2"/>
-      <c r="L809" s="2"/>
-      <c r="M809" s="2"/>
-      <c r="N809" s="2"/>
-      <c r="O809" s="2"/>
-      <c r="P809" s="2"/>
-      <c r="Q809" s="2"/>
-      <c r="R809" s="2"/>
-      <c r="S809" s="2"/>
-      <c r="T809" s="2"/>
-      <c r="U809" s="2"/>
-      <c r="V809" s="2"/>
-    </row>
-    <row r="811" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="E811" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q811" t="s">
-        <v>173</v>
-      </c>
-      <c r="R811" t="s">
-        <v>170</v>
-      </c>
-      <c r="S811">
-        <v>0.24</v>
-      </c>
-      <c r="T811" t="s">
-        <v>172</v>
-      </c>
-      <c r="V811" t="s">
-        <v>171</v>
-      </c>
+      <c r="B810" s="2"/>
+      <c r="C810" s="2"/>
+      <c r="D810" s="2"/>
+      <c r="E810" s="2"/>
+      <c r="F810" s="2"/>
+      <c r="G810" s="2"/>
+      <c r="H810" s="2"/>
+      <c r="I810" s="2"/>
+      <c r="J810" s="2"/>
+      <c r="K810" s="2"/>
+      <c r="L810" s="2"/>
+      <c r="M810" s="2"/>
+      <c r="N810" s="2"/>
+      <c r="O810" s="2"/>
+      <c r="P810" s="2"/>
+      <c r="Q810" s="2"/>
+      <c r="R810" s="2"/>
+      <c r="S810" s="2"/>
+      <c r="T810" s="2"/>
+      <c r="U810" s="2"/>
+      <c r="V810" s="2"/>
     </row>
     <row r="812" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E812" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q812" t="s">
         <v>173</v>
@@ -14743,7 +14755,7 @@
     </row>
     <row r="813" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E813" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q813" t="s">
         <v>173</v>
@@ -14752,103 +14764,106 @@
         <v>170</v>
       </c>
       <c r="S813">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="T813" t="s">
         <v>172</v>
       </c>
-      <c r="U813" t="s">
+      <c r="V813" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="814" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="E814" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q814" t="s">
+        <v>173</v>
+      </c>
+      <c r="R814" t="s">
+        <v>170</v>
+      </c>
+      <c r="S814">
+        <v>0</v>
+      </c>
+      <c r="T814" t="s">
+        <v>172</v>
+      </c>
+      <c r="U814" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="815" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A815" s="27" t="s">
+    <row r="816" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A816" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="B815" s="27"/>
-      <c r="C815" s="28"/>
-      <c r="D815" s="28"/>
-      <c r="E815" s="28"/>
-      <c r="F815" s="28"/>
-      <c r="G815" s="28"/>
-      <c r="H815" s="28"/>
-      <c r="I815" s="28"/>
-      <c r="J815" s="28"/>
-      <c r="K815" s="28"/>
-      <c r="L815" s="28"/>
-      <c r="M815" s="28"/>
-      <c r="N815" s="28"/>
-      <c r="O815" s="28"/>
-      <c r="P815" s="28"/>
-      <c r="Q815" s="28"/>
-      <c r="R815" s="28"/>
-      <c r="S815" s="28"/>
-      <c r="T815" s="28"/>
-      <c r="U815" s="28"/>
-      <c r="V815" s="28"/>
-    </row>
-    <row r="817" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I817" t="s">
+      <c r="B816" s="27"/>
+      <c r="C816" s="28"/>
+      <c r="D816" s="28"/>
+      <c r="E816" s="28"/>
+      <c r="F816" s="28"/>
+      <c r="G816" s="28"/>
+      <c r="H816" s="28"/>
+      <c r="I816" s="28"/>
+      <c r="J816" s="28"/>
+      <c r="K816" s="28"/>
+      <c r="L816" s="28"/>
+      <c r="M816" s="28"/>
+      <c r="N816" s="28"/>
+      <c r="O816" s="28"/>
+      <c r="P816" s="28"/>
+      <c r="Q816" s="28"/>
+      <c r="R816" s="28"/>
+      <c r="S816" s="28"/>
+      <c r="T816" s="28"/>
+      <c r="U816" s="28"/>
+      <c r="V816" s="28"/>
+    </row>
+    <row r="818" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I818" t="s">
         <v>325</v>
       </c>
-      <c r="R817" t="s">
+      <c r="R818" t="s">
         <v>323</v>
       </c>
-      <c r="S817" s="11">
+      <c r="S818" s="11">
         <f>213/(213 + 60)*100</f>
         <v>78.021978021978029</v>
       </c>
-      <c r="T817" t="s">
+      <c r="T818" t="s">
         <v>97</v>
       </c>
-      <c r="V817" t="s">
+      <c r="V818" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="818" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I818" t="s">
+    <row r="819" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I819" t="s">
         <v>339</v>
       </c>
-      <c r="R818" t="s">
+      <c r="R819" t="s">
         <v>323</v>
       </c>
-      <c r="S818" s="11">
+      <c r="S819" s="11">
         <f>60/(213 + 60)*100</f>
         <v>21.978021978021978</v>
       </c>
-      <c r="T818" t="s">
+      <c r="T819" t="s">
         <v>97</v>
       </c>
-      <c r="V818" t="s">
+      <c r="V819" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="820" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I820" t="s">
-        <v>325</v>
-      </c>
-      <c r="R820" t="s">
-        <v>326</v>
-      </c>
-      <c r="S820">
-        <v>45</v>
-      </c>
-      <c r="T820" t="s">
-        <v>97</v>
-      </c>
-      <c r="V820" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="821" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I821" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="R821" t="s">
         <v>326</v>
       </c>
       <c r="S821">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="T821" t="s">
         <v>97</v>
@@ -14857,133 +14872,128 @@
         <v>327</v>
       </c>
     </row>
-    <row r="823" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R823" t="s">
-        <v>306</v>
-      </c>
-      <c r="S823" s="30">
-        <f>S830</f>
-        <v>-5.9999999999999995E-4</v>
-      </c>
-      <c r="T823" t="s">
-        <v>309</v>
-      </c>
-      <c r="U823" t="s">
-        <v>322</v>
-      </c>
-      <c r="V823" t="s">
-        <v>313</v>
+    <row r="822" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I822" t="s">
+        <v>339</v>
+      </c>
+      <c r="R822" t="s">
+        <v>326</v>
+      </c>
+      <c r="S822">
+        <v>48</v>
+      </c>
+      <c r="T822" t="s">
+        <v>97</v>
+      </c>
+      <c r="V822" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="824" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A824" t="s">
-        <v>37</v>
-      </c>
-      <c r="G824" t="s">
-        <v>142</v>
-      </c>
       <c r="R824" t="s">
         <v>306</v>
       </c>
-      <c r="S824" s="29">
+      <c r="S824" s="30">
+        <f>S831</f>
+        <v>-5.9999999999999995E-4</v>
+      </c>
+      <c r="T824" t="s">
+        <v>309</v>
+      </c>
+      <c r="U824" t="s">
+        <v>322</v>
+      </c>
+      <c r="V824" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="825" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A825" t="s">
+        <v>37</v>
+      </c>
+      <c r="G825" t="s">
+        <v>142</v>
+      </c>
+      <c r="R825" t="s">
+        <v>306</v>
+      </c>
+      <c r="S825" s="29">
         <f>-(45.5*0.1+10.7*0.9)/1000</f>
         <v>-1.418E-2</v>
       </c>
-      <c r="T824" t="s">
-        <v>309</v>
-      </c>
-      <c r="U824" t="s">
-        <v>340</v>
-      </c>
-      <c r="V824" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="825" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A825" t="s">
-        <v>38</v>
-      </c>
-      <c r="G825" t="s">
-        <v>142</v>
-      </c>
-      <c r="R825" t="s">
-        <v>306</v>
-      </c>
-      <c r="S825" s="33">
-        <f>S824</f>
-        <v>-1.418E-2</v>
-      </c>
       <c r="T825" t="s">
         <v>309</v>
       </c>
+      <c r="U825" t="s">
+        <v>340</v>
+      </c>
+      <c r="V825" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="826" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G826" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="R826" t="s">
         <v>306</v>
       </c>
-      <c r="S826" s="29">
+      <c r="S826" s="33">
+        <f>S825</f>
+        <v>-1.418E-2</v>
+      </c>
+      <c r="T826" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="827" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A827" t="s">
+        <v>37</v>
+      </c>
+      <c r="G827" t="s">
+        <v>98</v>
+      </c>
+      <c r="R827" t="s">
+        <v>306</v>
+      </c>
+      <c r="S827" s="29">
         <f>-(45.5*0.4+10.7*0.6)/1000</f>
         <v>-2.4619999999999996E-2</v>
       </c>
-      <c r="T826" t="s">
-        <v>309</v>
-      </c>
-      <c r="U826" t="s">
-        <v>341</v>
-      </c>
-      <c r="V826" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="827" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A827" t="s">
-        <v>38</v>
-      </c>
-      <c r="G827" t="s">
-        <v>98</v>
-      </c>
-      <c r="R827" t="s">
-        <v>306</v>
-      </c>
-      <c r="S827" s="33">
-        <f>S826</f>
-        <v>-2.4619999999999996E-2</v>
-      </c>
       <c r="T827" t="s">
         <v>309</v>
       </c>
+      <c r="U827" t="s">
+        <v>341</v>
+      </c>
+      <c r="V827" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="828" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A828" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B828" s="4"/>
+      <c r="A828" t="s">
+        <v>38</v>
+      </c>
+      <c r="G828" t="s">
+        <v>98</v>
+      </c>
       <c r="R828" t="s">
         <v>306</v>
       </c>
-      <c r="S828" s="4">
-        <f>-10.7/1000</f>
-        <v>-1.0699999999999999E-2</v>
+      <c r="S828" s="33">
+        <f>S827</f>
+        <v>-2.4619999999999996E-2</v>
       </c>
       <c r="T828" t="s">
         <v>309</v>
       </c>
-      <c r="U828" t="s">
-        <v>320</v>
-      </c>
-      <c r="V828" t="s">
-        <v>313</v>
-      </c>
     </row>
     <row r="829" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A829" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B829" s="4"/>
       <c r="R829" t="s">
@@ -15004,88 +15014,93 @@
       </c>
     </row>
     <row r="830" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C830" t="s">
-        <v>226</v>
-      </c>
+      <c r="A830" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B830" s="4"/>
       <c r="R830" t="s">
         <v>306</v>
       </c>
-      <c r="S830">
+      <c r="S830" s="4">
+        <f>-10.7/1000</f>
+        <v>-1.0699999999999999E-2</v>
+      </c>
+      <c r="T830" t="s">
+        <v>309</v>
+      </c>
+      <c r="U830" t="s">
+        <v>320</v>
+      </c>
+      <c r="V830" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="831" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C831" t="s">
+        <v>226</v>
+      </c>
+      <c r="R831" t="s">
+        <v>306</v>
+      </c>
+      <c r="S831">
         <f>-0.6/1000</f>
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="T830" t="s">
+      <c r="T831" t="s">
         <v>309</v>
       </c>
-      <c r="V830" t="s">
+      <c r="V831" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="831" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B831" t="s">
+    <row r="832" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B832" t="s">
         <v>336</v>
       </c>
-      <c r="R831" t="s">
+      <c r="R832" t="s">
         <v>306</v>
       </c>
-      <c r="S831" s="29">
+      <c r="S832" s="29">
         <f>-20*0.45/0.85/1000</f>
         <v>-1.0588235294117647E-2</v>
       </c>
-      <c r="T831" t="s">
+      <c r="T832" t="s">
         <v>309</v>
       </c>
-      <c r="U831" t="s">
+      <c r="U832" t="s">
         <v>338</v>
       </c>
-      <c r="V831" t="s">
+      <c r="V832" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="833" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="D833" t="s">
+    <row r="834" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="D834" t="s">
         <v>312</v>
       </c>
-      <c r="R833" t="s">
+      <c r="R834" t="s">
         <v>307</v>
       </c>
-      <c r="S833">
+      <c r="S834">
         <f>-9.2/1000</f>
         <v>-9.1999999999999998E-3</v>
       </c>
-      <c r="T833" t="s">
+      <c r="T834" t="s">
         <v>309</v>
       </c>
-      <c r="V833" t="s">
+      <c r="V834" t="s">
         <v>313</v>
-      </c>
-    </row>
-    <row r="835" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="I835" t="s">
-        <v>107</v>
-      </c>
-      <c r="R835" t="s">
-        <v>315</v>
-      </c>
-      <c r="S835" s="31">
-        <v>-0.5</v>
-      </c>
-      <c r="T835" t="s">
-        <v>310</v>
-      </c>
-      <c r="V835" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="836" spans="4:22" x14ac:dyDescent="0.25">
       <c r="I836" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R836" t="s">
         <v>315</v>
       </c>
       <c r="S836" s="31">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="T836" t="s">
         <v>310</v>
@@ -15096,113 +15111,130 @@
     </row>
     <row r="837" spans="4:22" x14ac:dyDescent="0.25">
       <c r="I837" t="s">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="R837" t="s">
         <v>315</v>
       </c>
-      <c r="S837" s="22">
+      <c r="S837" s="31">
         <v>-1</v>
       </c>
       <c r="T837" t="s">
         <v>310</v>
       </c>
-      <c r="U837" t="s">
+      <c r="V837" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="838" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="I838" t="s">
+        <v>208</v>
+      </c>
+      <c r="R838" t="s">
+        <v>315</v>
+      </c>
+      <c r="S838" s="22">
+        <v>-1</v>
+      </c>
+      <c r="T838" t="s">
+        <v>310</v>
+      </c>
+      <c r="U838" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="838" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="R838" t="s">
+    <row r="839" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="R839" t="s">
         <v>317</v>
       </c>
-      <c r="S838" s="22">
+      <c r="S839" s="22">
         <f>-0.4 / ( (2*30.97) / (2*30.97 + 5*16) )</f>
         <v>-0.91662899580238943</v>
       </c>
-      <c r="T838" t="s">
+      <c r="T839" t="s">
         <v>318</v>
       </c>
-      <c r="U838" s="32" t="s">
+      <c r="U839" s="32" t="s">
         <v>333</v>
       </c>
-      <c r="V838" t="s">
+      <c r="V839" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="839" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="R839" t="s">
+    <row r="840" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="R840" t="s">
         <v>316</v>
       </c>
-      <c r="S839" s="22">
+      <c r="S840" s="22">
         <f>0.6 / ( (2*39.1) / (2*39.1 + 16) )</f>
         <v>0.72276214833759589</v>
       </c>
-      <c r="T839" t="s">
+      <c r="T840" t="s">
         <v>318</v>
       </c>
-      <c r="U839" s="32" t="s">
+      <c r="U840" s="32" t="s">
         <v>334</v>
       </c>
-      <c r="V839" t="s">
+      <c r="V840" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="841" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="R841" t="s">
+    <row r="842" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="R842" t="s">
         <v>308</v>
       </c>
-      <c r="S841" s="31">
+      <c r="S842" s="31">
         <f>3/5</f>
         <v>0.6</v>
       </c>
-      <c r="T841" t="s">
+      <c r="T842" t="s">
         <v>310</v>
       </c>
-      <c r="U841" t="s">
+      <c r="U842" t="s">
         <v>314</v>
       </c>
-      <c r="V841" t="s">
+      <c r="V842" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="843" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="I843" t="s">
+    <row r="844" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="I844" t="s">
         <v>325</v>
       </c>
-      <c r="Q843" t="s">
+      <c r="Q844" t="s">
         <v>329</v>
       </c>
-      <c r="R843" t="s">
+      <c r="R844" t="s">
         <v>331</v>
       </c>
-      <c r="S843" s="31">
+      <c r="S844" s="31">
         <f>0.12*(44/12)</f>
         <v>0.43999999999999995</v>
       </c>
-      <c r="T843" t="s">
+      <c r="T844" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="844" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="I844" t="s">
+    <row r="845" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="I845" t="s">
         <v>339</v>
       </c>
-      <c r="Q844" t="s">
+      <c r="Q845" t="s">
         <v>329</v>
       </c>
-      <c r="R844" t="s">
+      <c r="R845" t="s">
         <v>331</v>
       </c>
-      <c r="S844" s="31">
+      <c r="S845" s="31">
         <f>0.13*(44/12)</f>
         <v>0.47666666666666668</v>
       </c>
-      <c r="T844" t="s">
+      <c r="T845" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="845" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="S845" s="11"/>
+    <row r="846" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="S846" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="361">
   <si>
     <t>f_crop</t>
   </si>
@@ -820,9 +820,6 @@
   </si>
   <si>
     <t>same as pea</t>
-  </si>
-  <si>
-    <t>Lentils</t>
   </si>
   <si>
     <t>assumed to be the same as "åkerbönor"</t>
@@ -1613,13 +1610,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>174</v>
@@ -1655,7 +1652,7 @@
         <v>189</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>112</v>
@@ -1878,7 +1875,7 @@
         <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R15" s="4" t="s">
         <v>211</v>
@@ -1890,7 +1887,7 @@
         <v>210</v>
       </c>
       <c r="U15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -1932,7 +1929,7 @@
         <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R19" s="4" t="s">
         <v>212</v>
@@ -1944,7 +1941,7 @@
         <v>213</v>
       </c>
       <c r="U19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -1971,7 +1968,7 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1997,7 +1994,7 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R24" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S24">
         <v>66</v>
@@ -2006,15 +2003,15 @@
         <v>97</v>
       </c>
       <c r="U24" t="s">
+        <v>298</v>
+      </c>
+      <c r="V24" t="s">
         <v>299</v>
-      </c>
-      <c r="V24" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -2040,7 +2037,7 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -2066,7 +2063,7 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -2092,7 +2089,7 @@
     </row>
     <row r="29" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -2118,7 +2115,7 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -4037,7 +4034,7 @@
         <v>18.5</v>
       </c>
       <c r="U153" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.25">
@@ -4094,7 +4091,7 @@
         <v>12</v>
       </c>
       <c r="U155" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
@@ -4566,7 +4563,7 @@
         <v>1.3846000000000001</v>
       </c>
       <c r="U174" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.25">
@@ -4805,7 +4802,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="U183" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="V183" s="8"/>
     </row>
@@ -4890,7 +4887,7 @@
         <v>3.3332999999999999</v>
       </c>
       <c r="U186" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="187" spans="1:22" x14ac:dyDescent="0.25">
@@ -4943,7 +4940,7 @@
         <v>3.3332999999999999</v>
       </c>
       <c r="U188" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.25">
@@ -5040,10 +5037,10 @@
         <v>65</v>
       </c>
       <c r="U192" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="V192" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="193" spans="1:22" x14ac:dyDescent="0.25">
@@ -5149,7 +5146,7 @@
         <v>4.2</v>
       </c>
       <c r="V196" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.25">
@@ -5176,7 +5173,7 @@
         <v>3.3</v>
       </c>
       <c r="V197" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="198" spans="1:22" x14ac:dyDescent="0.25">
@@ -5204,7 +5201,7 @@
         <v>3.75</v>
       </c>
       <c r="U198" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.25">
@@ -5358,7 +5355,7 @@
         <v>20</v>
       </c>
       <c r="U204" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="205" spans="1:22" x14ac:dyDescent="0.25">
@@ -5950,10 +5947,10 @@
         <v>60</v>
       </c>
       <c r="U228" t="s">
+        <v>341</v>
+      </c>
+      <c r="V228" t="s">
         <v>342</v>
-      </c>
-      <c r="V228" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="229" spans="1:22" x14ac:dyDescent="0.25">
@@ -5972,7 +5969,7 @@
         <v>30</v>
       </c>
       <c r="U229" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="230" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -5991,7 +5988,7 @@
     </row>
     <row r="231" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="R231" s="4" t="s">
         <v>243</v>
@@ -6000,7 +5997,7 @@
         <v>25</v>
       </c>
       <c r="U231" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="232" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -6014,7 +6011,7 @@
         <v>25</v>
       </c>
       <c r="U232" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="233" spans="1:22" x14ac:dyDescent="0.25">
@@ -6050,19 +6047,19 @@
     </row>
     <row r="235" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A235" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B235" s="4"/>
     </row>
     <row r="236" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A236" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B236" s="4"/>
     </row>
     <row r="237" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A237" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B237" s="4"/>
     </row>
@@ -6079,7 +6076,7 @@
         <v>245</v>
       </c>
       <c r="U238" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V238" t="s">
         <v>250</v>
@@ -6107,7 +6104,7 @@
     </row>
     <row r="241" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B241" s="15"/>
       <c r="C241" s="15"/>
@@ -7543,7 +7540,7 @@
         <v>3</v>
       </c>
       <c r="U338" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="339" spans="1:21" x14ac:dyDescent="0.25">
@@ -7690,7 +7687,7 @@
         <v>3</v>
       </c>
       <c r="U346" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="347" spans="1:21" x14ac:dyDescent="0.25">
@@ -8154,7 +8151,7 @@
         <v>3</v>
       </c>
       <c r="U379" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="380" spans="1:21" x14ac:dyDescent="0.25">
@@ -8829,7 +8826,7 @@
         <v>20</v>
       </c>
       <c r="U430" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="431" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9022,10 +9019,10 @@
         <v>25</v>
       </c>
       <c r="U443" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="V443" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="444" spans="1:22" x14ac:dyDescent="0.25">
@@ -9382,7 +9379,7 @@
         <v>10</v>
       </c>
       <c r="V474" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="475" spans="1:22" x14ac:dyDescent="0.25">
@@ -9443,7 +9440,7 @@
         <v>15</v>
       </c>
       <c r="V479" s="25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="480" spans="1:22" x14ac:dyDescent="0.25">
@@ -9461,7 +9458,7 @@
         <v>15</v>
       </c>
       <c r="U480" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="481" spans="1:22" x14ac:dyDescent="0.25">
@@ -9479,7 +9476,7 @@
         <v>15</v>
       </c>
       <c r="U481" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="482" spans="1:22" x14ac:dyDescent="0.25">
@@ -9502,7 +9499,7 @@
         <v>0.6</v>
       </c>
       <c r="V483" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="484" spans="1:22" x14ac:dyDescent="0.25">
@@ -9519,7 +9516,7 @@
         <v>1.6</v>
       </c>
       <c r="V484" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="485" spans="1:22" x14ac:dyDescent="0.25">
@@ -9537,7 +9534,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="U485" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="486" spans="1:22" x14ac:dyDescent="0.25">
@@ -9788,7 +9785,7 @@
     </row>
     <row r="501" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B501" s="15"/>
       <c r="C501" s="15"/>
@@ -9814,7 +9811,7 @@
     </row>
     <row r="502" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
@@ -9840,7 +9837,7 @@
     </row>
     <row r="503" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A503" s="19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B503" s="19"/>
       <c r="C503" s="19"/>
@@ -9848,7 +9845,7 @@
     </row>
     <row r="504" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A504" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B504" s="19"/>
       <c r="C504" s="19"/>
@@ -10904,7 +10901,7 @@
         <v>5</v>
       </c>
       <c r="U577" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="578" spans="1:21" x14ac:dyDescent="0.25">
@@ -11015,7 +11012,7 @@
         <v>5</v>
       </c>
       <c r="U583" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="584" spans="1:21" x14ac:dyDescent="0.25">
@@ -11365,7 +11362,7 @@
         <v>37</v>
       </c>
       <c r="P609" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R609" t="s">
         <v>205</v>
@@ -11421,7 +11418,7 @@
         <v>37</v>
       </c>
       <c r="P613" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R613" t="s">
         <v>206</v>
@@ -11445,7 +11442,7 @@
         <v>10</v>
       </c>
       <c r="U614" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="615" spans="1:21" x14ac:dyDescent="0.25">
@@ -11483,7 +11480,7 @@
         <v>67</v>
       </c>
       <c r="P617" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R617" t="s">
         <v>205</v>
@@ -11543,7 +11540,7 @@
         <v>67</v>
       </c>
       <c r="P621" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R621" t="s">
         <v>206</v>
@@ -11608,7 +11605,7 @@
         <v>39</v>
       </c>
       <c r="P627" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R627" t="s">
         <v>205</v>
@@ -11664,7 +11661,7 @@
         <v>39</v>
       </c>
       <c r="P631" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R631" t="s">
         <v>206</v>
@@ -11728,7 +11725,7 @@
         <v>33</v>
       </c>
       <c r="P637" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R637" t="s">
         <v>205</v>
@@ -11784,7 +11781,7 @@
         <v>33</v>
       </c>
       <c r="P641" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R641" t="s">
         <v>206</v>
@@ -11843,7 +11840,7 @@
         <v>34</v>
       </c>
       <c r="P645" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R645" t="s">
         <v>205</v>
@@ -11903,7 +11900,7 @@
         <v>34</v>
       </c>
       <c r="P649" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R649" t="s">
         <v>206</v>
@@ -11915,7 +11912,7 @@
     </row>
     <row r="651" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A651" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B651" s="21"/>
       <c r="C651" s="21"/>
@@ -11978,7 +11975,7 @@
         <v>50</v>
       </c>
       <c r="U655" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="656" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12103,7 +12100,7 @@
         <v>35</v>
       </c>
       <c r="P664" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R664" t="s">
         <v>206</v>
@@ -12157,10 +12154,10 @@
         <v>155</v>
       </c>
       <c r="U667" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="V667" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="668" spans="1:22" x14ac:dyDescent="0.25">
@@ -12513,7 +12510,7 @@
         <v>20</v>
       </c>
       <c r="V698" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="699" spans="1:22" x14ac:dyDescent="0.25">
@@ -12574,7 +12571,7 @@
         <v>105</v>
       </c>
       <c r="V703" s="25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="704" spans="1:22" x14ac:dyDescent="0.25">
@@ -12592,7 +12589,7 @@
         <v>105</v>
       </c>
       <c r="U704" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="705" spans="1:22" x14ac:dyDescent="0.25">
@@ -12610,7 +12607,7 @@
         <v>105</v>
       </c>
       <c r="U705" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="706" spans="1:22" x14ac:dyDescent="0.25">
@@ -12633,7 +12630,7 @@
         <v>5.6</v>
       </c>
       <c r="V707" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="708" spans="1:22" x14ac:dyDescent="0.25">
@@ -12650,7 +12647,7 @@
         <v>3</v>
       </c>
       <c r="V708" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="709" spans="1:22" x14ac:dyDescent="0.25">
@@ -12668,7 +12665,7 @@
         <v>4.3</v>
       </c>
       <c r="U709" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="710" spans="1:22" x14ac:dyDescent="0.25">
@@ -12739,7 +12736,7 @@
     </row>
     <row r="715" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B715" s="2"/>
       <c r="C715" s="2"/>
@@ -12772,7 +12769,7 @@
       </c>
       <c r="T717" s="5"/>
       <c r="U717" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="719" spans="1:22" x14ac:dyDescent="0.25">
@@ -12820,7 +12817,7 @@
     </row>
     <row r="721" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -14527,7 +14524,7 @@
         <v>148</v>
       </c>
       <c r="R797" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="S797" s="35">
         <f>S796</f>
@@ -14537,12 +14534,12 @@
         <v>109</v>
       </c>
       <c r="U797" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="799" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B799" s="2"/>
       <c r="C799" s="2"/>
@@ -14574,7 +14571,7 @@
         <v>0</v>
       </c>
       <c r="T800" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="U800" s="5" t="s">
         <v>12</v>
@@ -14605,7 +14602,7 @@
         <v>175</v>
       </c>
       <c r="Q803" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="R803" t="s">
         <v>166</v>
@@ -14615,10 +14612,10 @@
         <v>22366.666666666664</v>
       </c>
       <c r="T803" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="V803" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="804" spans="1:22" x14ac:dyDescent="0.25">
@@ -14626,7 +14623,7 @@
         <v>175</v>
       </c>
       <c r="Q804" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R804" t="s">
         <v>166</v>
@@ -14636,10 +14633,10 @@
         <v>58.3</v>
       </c>
       <c r="T804" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="V804" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="806" spans="1:22" x14ac:dyDescent="0.25">
@@ -14659,10 +14656,10 @@
         <v>167</v>
       </c>
       <c r="U806" t="s">
+        <v>354</v>
+      </c>
+      <c r="V806" t="s">
         <v>355</v>
-      </c>
-      <c r="V806" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="807" spans="1:22" x14ac:dyDescent="0.25">
@@ -14670,7 +14667,7 @@
         <v>176</v>
       </c>
       <c r="Q807" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="R807" t="s">
         <v>166</v>
@@ -14680,10 +14677,10 @@
         <v>9533.3333333333339</v>
       </c>
       <c r="T807" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="V807" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="808" spans="1:22" x14ac:dyDescent="0.25">
@@ -14691,7 +14688,7 @@
         <v>176</v>
       </c>
       <c r="Q808" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R808" t="s">
         <v>166</v>
@@ -14701,10 +14698,10 @@
         <v>7.9</v>
       </c>
       <c r="T808" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="V808" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="810" spans="1:22" x14ac:dyDescent="0.25">
@@ -14795,7 +14792,7 @@
     </row>
     <row r="816" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A816" s="27" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B816" s="27"/>
       <c r="C816" s="28"/>
@@ -14821,10 +14818,10 @@
     </row>
     <row r="818" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I818" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R818" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="S818" s="11">
         <f>213/(213 + 60)*100</f>
@@ -14834,15 +14831,15 @@
         <v>97</v>
       </c>
       <c r="V818" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="819" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I819" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R819" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="S819" s="11">
         <f>60/(213 + 60)*100</f>
@@ -14852,15 +14849,15 @@
         <v>97</v>
       </c>
       <c r="V819" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="821" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I821" t="s">
+        <v>324</v>
+      </c>
+      <c r="R821" t="s">
         <v>325</v>
-      </c>
-      <c r="R821" t="s">
-        <v>326</v>
       </c>
       <c r="S821">
         <v>45</v>
@@ -14869,15 +14866,15 @@
         <v>97</v>
       </c>
       <c r="V821" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="822" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I822" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R822" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="S822">
         <v>48</v>
@@ -14886,25 +14883,25 @@
         <v>97</v>
       </c>
       <c r="V822" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="824" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R824" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S824" s="30">
         <f>S831</f>
         <v>-5.9999999999999995E-4</v>
       </c>
       <c r="T824" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U824" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="V824" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="825" spans="1:22" x14ac:dyDescent="0.25">
@@ -14915,20 +14912,20 @@
         <v>142</v>
       </c>
       <c r="R825" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S825" s="29">
         <f>-(45.5*0.1+10.7*0.9)/1000</f>
         <v>-1.418E-2</v>
       </c>
       <c r="T825" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U825" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="V825" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="826" spans="1:22" x14ac:dyDescent="0.25">
@@ -14939,14 +14936,14 @@
         <v>142</v>
       </c>
       <c r="R826" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S826" s="33">
         <f>S825</f>
         <v>-1.418E-2</v>
       </c>
       <c r="T826" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="827" spans="1:22" x14ac:dyDescent="0.25">
@@ -14957,20 +14954,20 @@
         <v>98</v>
       </c>
       <c r="R827" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S827" s="29">
         <f>-(45.5*0.4+10.7*0.6)/1000</f>
         <v>-2.4619999999999996E-2</v>
       </c>
       <c r="T827" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U827" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="V827" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="828" spans="1:22" x14ac:dyDescent="0.25">
@@ -14981,14 +14978,14 @@
         <v>98</v>
       </c>
       <c r="R828" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S828" s="33">
         <f>S827</f>
         <v>-2.4619999999999996E-2</v>
       </c>
       <c r="T828" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="829" spans="1:22" x14ac:dyDescent="0.25">
@@ -14997,20 +14994,20 @@
       </c>
       <c r="B829" s="4"/>
       <c r="R829" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S829" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="T829" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U829" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="V829" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="830" spans="1:22" x14ac:dyDescent="0.25">
@@ -15019,20 +15016,20 @@
       </c>
       <c r="B830" s="4"/>
       <c r="R830" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S830" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="T830" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U830" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="V830" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="831" spans="1:22" x14ac:dyDescent="0.25">
@@ -15040,56 +15037,56 @@
         <v>226</v>
       </c>
       <c r="R831" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S831">
         <f>-0.6/1000</f>
         <v>-5.9999999999999995E-4</v>
       </c>
       <c r="T831" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="V831" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="832" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B832" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="R832" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S832" s="29">
         <f>-20*0.45/0.85/1000</f>
         <v>-1.0588235294117647E-2</v>
       </c>
       <c r="T832" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U832" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="V832" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="834" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D834" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="R834" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S834">
         <f>-9.2/1000</f>
         <v>-9.1999999999999998E-3</v>
       </c>
       <c r="T834" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="V834" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="836" spans="4:22" x14ac:dyDescent="0.25">
@@ -15097,16 +15094,16 @@
         <v>107</v>
       </c>
       <c r="R836" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S836" s="31">
         <v>-0.5</v>
       </c>
       <c r="T836" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="V836" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="837" spans="4:22" x14ac:dyDescent="0.25">
@@ -15114,16 +15111,16 @@
         <v>108</v>
       </c>
       <c r="R837" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S837" s="31">
         <v>-1</v>
       </c>
       <c r="T837" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="V837" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="838" spans="4:22" x14ac:dyDescent="0.25">
@@ -15131,106 +15128,106 @@
         <v>208</v>
       </c>
       <c r="R838" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S838" s="22">
         <v>-1</v>
       </c>
       <c r="T838" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="U838" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="839" spans="4:22" x14ac:dyDescent="0.25">
       <c r="R839" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S839" s="22">
         <f>-0.4 / ( (2*30.97) / (2*30.97 + 5*16) )</f>
         <v>-0.91662899580238943</v>
       </c>
       <c r="T839" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="U839" s="32" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="V839" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="840" spans="4:22" x14ac:dyDescent="0.25">
       <c r="R840" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="S840" s="22">
         <f>0.6 / ( (2*39.1) / (2*39.1 + 16) )</f>
         <v>0.72276214833759589</v>
       </c>
       <c r="T840" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="U840" s="32" t="s">
+        <v>333</v>
+      </c>
+      <c r="V840" t="s">
         <v>334</v>
-      </c>
-      <c r="V840" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="842" spans="4:22" x14ac:dyDescent="0.25">
       <c r="R842" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S842" s="31">
         <f>3/5</f>
         <v>0.6</v>
       </c>
       <c r="T842" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="U842" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="V842" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="844" spans="4:22" x14ac:dyDescent="0.25">
       <c r="I844" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q844" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="R844" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="S844" s="31">
         <f>0.12*(44/12)</f>
         <v>0.43999999999999995</v>
       </c>
       <c r="T844" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="845" spans="4:22" x14ac:dyDescent="0.25">
       <c r="I845" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q845" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="R845" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="S845" s="31">
         <f>0.13*(44/12)</f>
         <v>0.47666666666666668</v>
       </c>
       <c r="T845" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="846" spans="4:22" x14ac:dyDescent="0.25">

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D849481-FAFA-4D35-9359-07E2CC878DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18240" windowHeight="10650"/>
+    <workbookView xWindow="-35805" yWindow="2595" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="360">
   <si>
     <t>f_crop</t>
   </si>
@@ -525,9 +537,6 @@
     <t>N_leaching_frac</t>
   </si>
   <si>
-    <t>IPCC Guidelines 2019</t>
-  </si>
-  <si>
     <t>kg N leached/kg N added</t>
   </si>
   <si>
@@ -1096,12 +1105,18 @@
   </si>
   <si>
     <t>chickens</t>
+  </si>
+  <si>
+    <t>Finland’s NIR 2023. Table 5.4-9</t>
+  </si>
+  <si>
+    <t>Use factor from Finland. Sweden uses a more sophisticated model for N leaching</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0E+00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -1252,7 +1267,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1262,17 +1277,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1570,7 +1581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V842"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1598,16 +1609,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>165</v>
@@ -1622,7 +1633,7 @@
         <v>137</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>116</v>
@@ -1631,16 +1642,16 @@
         <v>117</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>118</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>112</v>
@@ -1829,7 +1840,7 @@
         <v>139</v>
       </c>
       <c r="I12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R12" t="s">
         <v>136</v>
@@ -1846,13 +1857,13 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R14" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="S14" s="5">
         <v>0</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U14" s="5" t="s">
         <v>12</v>
@@ -1863,19 +1874,19 @@
         <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="S15" s="4">
         <v>100</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -1883,30 +1894,30 @@
         <v>139</v>
       </c>
       <c r="I16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R18" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S18" s="5">
         <v>0</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="U18" s="5" t="s">
         <v>12</v>
@@ -1917,19 +1928,19 @@
         <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S19" s="4">
         <v>100</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="U19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -1937,16 +1948,16 @@
         <v>139</v>
       </c>
       <c r="I20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S20" s="4">
         <v>100</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -1956,7 +1967,7 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1982,7 +1993,7 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R24" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="S24">
         <v>66</v>
@@ -1991,119 +2002,115 @@
         <v>97</v>
       </c>
       <c r="U24" t="s">
+        <v>293</v>
+      </c>
+      <c r="V24" t="s">
         <v>294</v>
       </c>
-      <c r="V24" t="s">
-        <v>295</v>
-      </c>
     </row>
     <row r="26" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
-      <c r="S26" s="13"/>
-      <c r="T26" s="13"/>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
+      <c r="A26" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="11"/>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="13"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="15"/>
-      <c r="S28" s="15"/>
-      <c r="T28" s="15"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="13"/>
     </row>
     <row r="29" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13"/>
+      <c r="A29" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2128,56 +2135,52 @@
       <c r="V30" s="3"/>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="13"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
-      <c r="T31" s="15"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="15"/>
-      <c r="S32" s="15"/>
-      <c r="T32" s="15"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="R33" s="5" t="s">
@@ -3299,7 +3302,7 @@
     </row>
     <row r="106" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R106" s="4" t="s">
         <v>9</v>
@@ -3313,7 +3316,7 @@
     </row>
     <row r="107" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R107" s="4" t="s">
         <v>10</v>
@@ -3324,7 +3327,7 @@
     </row>
     <row r="108" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R108" s="4" t="s">
         <v>11</v>
@@ -3335,7 +3338,7 @@
     </row>
     <row r="109" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>85</v>
@@ -3352,7 +3355,7 @@
     </row>
     <row r="110" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>85</v>
@@ -3366,7 +3369,7 @@
     </row>
     <row r="111" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>85</v>
@@ -3380,7 +3383,7 @@
     </row>
     <row r="112" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>84</v>
@@ -3399,7 +3402,7 @@
     </row>
     <row r="113" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>84</v>
@@ -3414,7 +3417,7 @@
     </row>
     <row r="114" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>84</v>
@@ -3749,7 +3752,7 @@
     </row>
     <row r="135" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R135" s="4" t="s">
         <v>11</v>
@@ -3758,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="U135" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.25">
@@ -3791,7 +3794,7 @@
     </row>
     <row r="138" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R138" s="4" t="s">
         <v>11</v>
@@ -3800,12 +3803,12 @@
         <v>30</v>
       </c>
       <c r="U138" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="139" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R139" s="4" t="s">
         <v>11</v>
@@ -3814,12 +3817,12 @@
         <v>30</v>
       </c>
       <c r="U139" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="140" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R140" s="4" t="s">
         <v>11</v>
@@ -3828,7 +3831,7 @@
         <v>75</v>
       </c>
       <c r="V140" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="141" spans="1:22" x14ac:dyDescent="0.25">
@@ -3989,32 +3992,32 @@
         <v>75</v>
       </c>
       <c r="U152" t="s">
+        <v>242</v>
+      </c>
+      <c r="V152" t="s">
         <v>243</v>
       </c>
-      <c r="V152" t="s">
-        <v>244</v>
-      </c>
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A153" s="9" t="s">
+      <c r="A153" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B153" s="9"/>
-      <c r="C153" s="9"/>
-      <c r="D153" s="9"/>
-      <c r="E153" s="9"/>
+      <c r="B153" s="4"/>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
       <c r="G153" t="s">
         <v>139</v>
       </c>
-      <c r="I153" s="9"/>
-      <c r="J153" s="9"/>
-      <c r="K153" s="9"/>
-      <c r="L153" s="9"/>
-      <c r="M153" s="9"/>
-      <c r="N153" s="9"/>
-      <c r="O153" s="9"/>
-      <c r="P153" s="9"/>
-      <c r="Q153" s="9"/>
+      <c r="I153" s="4"/>
+      <c r="J153" s="4"/>
+      <c r="K153" s="4"/>
+      <c r="L153" s="4"/>
+      <c r="M153" s="4"/>
+      <c r="N153" s="4"/>
+      <c r="O153" s="4"/>
+      <c r="P153" s="4"/>
+      <c r="Q153" s="4"/>
       <c r="R153" t="s">
         <v>10</v>
       </c>
@@ -4022,29 +4025,29 @@
         <v>18.5</v>
       </c>
       <c r="U153" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A154" s="9" t="s">
+      <c r="A154" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B154" s="9"/>
-      <c r="C154" s="9"/>
-      <c r="D154" s="9"/>
-      <c r="E154" s="9"/>
+      <c r="B154" s="4"/>
+      <c r="C154" s="4"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4"/>
       <c r="G154" t="s">
         <v>139</v>
       </c>
-      <c r="I154" s="9"/>
-      <c r="J154" s="9"/>
-      <c r="K154" s="9"/>
-      <c r="L154" s="9"/>
-      <c r="M154" s="9"/>
-      <c r="N154" s="9"/>
-      <c r="O154" s="9"/>
-      <c r="P154" s="9"/>
-      <c r="Q154" s="9"/>
+      <c r="I154" s="4"/>
+      <c r="J154" s="4"/>
+      <c r="K154" s="4"/>
+      <c r="L154" s="4"/>
+      <c r="M154" s="4"/>
+      <c r="N154" s="4"/>
+      <c r="O154" s="4"/>
+      <c r="P154" s="4"/>
+      <c r="Q154" s="4"/>
       <c r="R154" t="s">
         <v>11</v>
       </c>
@@ -4053,25 +4056,25 @@
       </c>
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A155" s="9" t="s">
+      <c r="A155" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B155" s="9"/>
-      <c r="C155" s="9"/>
-      <c r="D155" s="9"/>
-      <c r="E155" s="9"/>
+      <c r="B155" s="4"/>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
       <c r="G155" t="s">
         <v>98</v>
       </c>
-      <c r="I155" s="9"/>
-      <c r="J155" s="9"/>
-      <c r="K155" s="9"/>
-      <c r="L155" s="9"/>
-      <c r="M155" s="9"/>
-      <c r="N155" s="9"/>
-      <c r="O155" s="9"/>
-      <c r="P155" s="9"/>
-      <c r="Q155" s="9"/>
+      <c r="I155" s="4"/>
+      <c r="J155" s="4"/>
+      <c r="K155" s="4"/>
+      <c r="L155" s="4"/>
+      <c r="M155" s="4"/>
+      <c r="N155" s="4"/>
+      <c r="O155" s="4"/>
+      <c r="P155" s="4"/>
+      <c r="Q155" s="4"/>
       <c r="R155" t="s">
         <v>10</v>
       </c>
@@ -4079,29 +4082,29 @@
         <v>12</v>
       </c>
       <c r="U155" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A156" s="9" t="s">
+      <c r="A156" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B156" s="9"/>
-      <c r="C156" s="9"/>
-      <c r="D156" s="9"/>
-      <c r="E156" s="9"/>
+      <c r="B156" s="4"/>
+      <c r="C156" s="4"/>
+      <c r="D156" s="4"/>
+      <c r="E156" s="4"/>
       <c r="G156" t="s">
         <v>98</v>
       </c>
-      <c r="I156" s="9"/>
-      <c r="J156" s="9"/>
-      <c r="K156" s="9"/>
-      <c r="L156" s="9"/>
-      <c r="M156" s="9"/>
-      <c r="N156" s="9"/>
-      <c r="O156" s="9"/>
-      <c r="P156" s="9"/>
-      <c r="Q156" s="9"/>
+      <c r="I156" s="4"/>
+      <c r="J156" s="4"/>
+      <c r="K156" s="4"/>
+      <c r="L156" s="4"/>
+      <c r="M156" s="4"/>
+      <c r="N156" s="4"/>
+      <c r="O156" s="4"/>
+      <c r="P156" s="4"/>
+      <c r="Q156" s="4"/>
       <c r="R156" t="s">
         <v>11</v>
       </c>
@@ -4110,22 +4113,22 @@
       </c>
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A157" s="9" t="s">
+      <c r="A157" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B157" s="9"/>
-      <c r="C157" s="9"/>
-      <c r="D157" s="9"/>
-      <c r="E157" s="10"/>
-      <c r="I157" s="10"/>
-      <c r="J157" s="10"/>
-      <c r="K157" s="10"/>
-      <c r="L157" s="10"/>
-      <c r="M157" s="10"/>
-      <c r="N157" s="10"/>
-      <c r="O157" s="10"/>
-      <c r="P157" s="10"/>
-      <c r="Q157" s="10"/>
+      <c r="B157" s="4"/>
+      <c r="C157" s="4"/>
+      <c r="D157" s="4"/>
+      <c r="E157" s="6"/>
+      <c r="I157" s="6"/>
+      <c r="J157" s="6"/>
+      <c r="K157" s="6"/>
+      <c r="L157" s="6"/>
+      <c r="M157" s="6"/>
+      <c r="N157" s="6"/>
+      <c r="O157" s="6"/>
+      <c r="P157" s="6"/>
+      <c r="Q157" s="6"/>
       <c r="R157" t="s">
         <v>11</v>
       </c>
@@ -4134,7 +4137,7 @@
       </c>
       <c r="T157" s="4"/>
       <c r="U157" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.25">
@@ -4249,190 +4252,190 @@
       <c r="U161" s="6"/>
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A162" s="9" t="s">
+      <c r="A162" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B162" s="9"/>
-      <c r="C162" s="10"/>
-      <c r="D162" s="10"/>
-      <c r="E162" s="10"/>
-      <c r="I162" s="10"/>
-      <c r="J162" s="10"/>
-      <c r="K162" s="10"/>
-      <c r="L162" s="10"/>
-      <c r="M162" s="10"/>
-      <c r="N162" s="10"/>
-      <c r="O162" s="10"/>
-      <c r="P162" s="10"/>
-      <c r="Q162" s="10"/>
+      <c r="B162" s="4"/>
+      <c r="C162" s="6"/>
+      <c r="D162" s="6"/>
+      <c r="E162" s="6"/>
+      <c r="I162" s="6"/>
+      <c r="J162" s="6"/>
+      <c r="K162" s="6"/>
+      <c r="L162" s="6"/>
+      <c r="M162" s="6"/>
+      <c r="N162" s="6"/>
+      <c r="O162" s="6"/>
+      <c r="P162" s="6"/>
+      <c r="Q162" s="6"/>
       <c r="R162" t="s">
         <v>9</v>
       </c>
-      <c r="S162" s="23">
+      <c r="S162" s="19">
         <f>S67</f>
         <v>-1.0713999999999999</v>
       </c>
-      <c r="T162" s="23"/>
-      <c r="U162" s="23" t="str">
+      <c r="T162" s="19"/>
+      <c r="U162" s="19" t="str">
         <f>U67</f>
         <v>Korn, foder, norra götaland och svealand</v>
       </c>
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A163" s="9" t="s">
+      <c r="A163" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B163" s="9"/>
-      <c r="C163" s="10"/>
-      <c r="D163" s="10"/>
-      <c r="E163" s="10"/>
-      <c r="I163" s="10"/>
-      <c r="J163" s="10"/>
-      <c r="K163" s="10"/>
-      <c r="L163" s="10"/>
-      <c r="M163" s="10"/>
-      <c r="N163" s="10"/>
-      <c r="O163" s="10"/>
-      <c r="P163" s="10"/>
-      <c r="Q163" s="10"/>
+      <c r="B163" s="4"/>
+      <c r="C163" s="6"/>
+      <c r="D163" s="6"/>
+      <c r="E163" s="6"/>
+      <c r="I163" s="6"/>
+      <c r="J163" s="6"/>
+      <c r="K163" s="6"/>
+      <c r="L163" s="6"/>
+      <c r="M163" s="6"/>
+      <c r="N163" s="6"/>
+      <c r="O163" s="6"/>
+      <c r="P163" s="6"/>
+      <c r="Q163" s="6"/>
       <c r="R163" t="s">
         <v>10</v>
       </c>
-      <c r="S163" s="23">
+      <c r="S163" s="19">
         <f>S68</f>
         <v>23.928999999999998</v>
       </c>
-      <c r="T163" s="23"/>
-      <c r="U163" s="23"/>
+      <c r="T163" s="19"/>
+      <c r="U163" s="19"/>
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A164" s="9" t="s">
+      <c r="A164" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B164" s="9"/>
-      <c r="C164" s="10"/>
-      <c r="D164" s="10"/>
-      <c r="E164" s="10"/>
-      <c r="I164" s="10"/>
-      <c r="J164" s="10"/>
-      <c r="K164" s="10"/>
-      <c r="L164" s="10"/>
-      <c r="M164" s="10"/>
-      <c r="N164" s="10"/>
-      <c r="O164" s="10"/>
-      <c r="P164" s="10"/>
-      <c r="Q164" s="10"/>
+      <c r="B164" s="4"/>
+      <c r="C164" s="6"/>
+      <c r="D164" s="6"/>
+      <c r="E164" s="6"/>
+      <c r="I164" s="6"/>
+      <c r="J164" s="6"/>
+      <c r="K164" s="6"/>
+      <c r="L164" s="6"/>
+      <c r="M164" s="6"/>
+      <c r="N164" s="6"/>
+      <c r="O164" s="6"/>
+      <c r="P164" s="6"/>
+      <c r="Q164" s="6"/>
       <c r="R164" t="s">
         <v>11</v>
       </c>
-      <c r="S164" s="23">
+      <c r="S164" s="19">
         <f>S69</f>
         <v>32</v>
       </c>
-      <c r="T164" s="23"/>
-      <c r="U164" s="23"/>
+      <c r="T164" s="19"/>
+      <c r="U164" s="19"/>
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A165" s="9" t="s">
+      <c r="A165" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B165" s="9"/>
-      <c r="C165" s="10"/>
-      <c r="D165" s="10"/>
-      <c r="E165" s="10"/>
-      <c r="I165" s="10"/>
-      <c r="J165" s="10"/>
-      <c r="K165" s="10"/>
-      <c r="L165" s="10"/>
-      <c r="M165" s="10"/>
-      <c r="N165" s="10"/>
-      <c r="O165" s="10"/>
-      <c r="P165" s="10"/>
-      <c r="Q165" s="10"/>
+      <c r="B165" s="4"/>
+      <c r="C165" s="6"/>
+      <c r="D165" s="6"/>
+      <c r="E165" s="6"/>
+      <c r="I165" s="6"/>
+      <c r="J165" s="6"/>
+      <c r="K165" s="6"/>
+      <c r="L165" s="6"/>
+      <c r="M165" s="6"/>
+      <c r="N165" s="6"/>
+      <c r="O165" s="6"/>
+      <c r="P165" s="6"/>
+      <c r="Q165" s="6"/>
       <c r="R165" t="s">
         <v>9</v>
       </c>
-      <c r="S165" s="23">
+      <c r="S165" s="19">
         <f>S67</f>
         <v>-1.0713999999999999</v>
       </c>
-      <c r="T165" s="23"/>
-      <c r="U165" s="23" t="str">
+      <c r="T165" s="19"/>
+      <c r="U165" s="19" t="str">
         <f>U67</f>
         <v>Korn, foder, norra götaland och svealand</v>
       </c>
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A166" s="9" t="s">
+      <c r="A166" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B166" s="9"/>
-      <c r="C166" s="10"/>
-      <c r="D166" s="10"/>
-      <c r="E166" s="10"/>
-      <c r="I166" s="10"/>
-      <c r="J166" s="10"/>
-      <c r="K166" s="10"/>
-      <c r="L166" s="10"/>
-      <c r="M166" s="10"/>
-      <c r="N166" s="10"/>
-      <c r="O166" s="10"/>
-      <c r="P166" s="10"/>
-      <c r="Q166" s="10"/>
+      <c r="B166" s="4"/>
+      <c r="C166" s="6"/>
+      <c r="D166" s="6"/>
+      <c r="E166" s="6"/>
+      <c r="I166" s="6"/>
+      <c r="J166" s="6"/>
+      <c r="K166" s="6"/>
+      <c r="L166" s="6"/>
+      <c r="M166" s="6"/>
+      <c r="N166" s="6"/>
+      <c r="O166" s="6"/>
+      <c r="P166" s="6"/>
+      <c r="Q166" s="6"/>
       <c r="R166" t="s">
         <v>10</v>
       </c>
-      <c r="S166" s="23">
+      <c r="S166" s="19">
         <f>S68</f>
         <v>23.928999999999998</v>
       </c>
-      <c r="T166" s="23"/>
-      <c r="U166" s="23"/>
+      <c r="T166" s="19"/>
+      <c r="U166" s="19"/>
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A167" s="9" t="s">
+      <c r="A167" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B167" s="9"/>
-      <c r="C167" s="10"/>
-      <c r="D167" s="10"/>
-      <c r="E167" s="10"/>
-      <c r="I167" s="10"/>
-      <c r="J167" s="10"/>
-      <c r="K167" s="10"/>
-      <c r="L167" s="10"/>
-      <c r="M167" s="10"/>
-      <c r="N167" s="10"/>
-      <c r="O167" s="10"/>
-      <c r="P167" s="10"/>
-      <c r="Q167" s="10"/>
+      <c r="B167" s="4"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="6"/>
+      <c r="E167" s="6"/>
+      <c r="I167" s="6"/>
+      <c r="J167" s="6"/>
+      <c r="K167" s="6"/>
+      <c r="L167" s="6"/>
+      <c r="M167" s="6"/>
+      <c r="N167" s="6"/>
+      <c r="O167" s="6"/>
+      <c r="P167" s="6"/>
+      <c r="Q167" s="6"/>
       <c r="R167" t="s">
         <v>11</v>
       </c>
-      <c r="S167" s="23">
+      <c r="S167" s="19">
         <f>S69</f>
         <v>32</v>
       </c>
-      <c r="T167" s="23"/>
-      <c r="U167" s="23"/>
+      <c r="T167" s="19"/>
+      <c r="U167" s="19"/>
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A168" s="9" t="s">
+      <c r="A168" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B168" s="9"/>
-      <c r="C168" s="9"/>
-      <c r="D168" s="9"/>
-      <c r="E168" s="9"/>
-      <c r="I168" s="9"/>
-      <c r="J168" s="9"/>
-      <c r="K168" s="9"/>
-      <c r="L168" s="9"/>
-      <c r="M168" s="9"/>
-      <c r="N168" s="9"/>
-      <c r="O168" s="9"/>
-      <c r="P168" s="9"/>
-      <c r="Q168" s="9"/>
+      <c r="B168" s="4"/>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="I168" s="4"/>
+      <c r="J168" s="4"/>
+      <c r="K168" s="4"/>
+      <c r="L168" s="4"/>
+      <c r="M168" s="4"/>
+      <c r="N168" s="4"/>
+      <c r="O168" s="4"/>
+      <c r="P168" s="4"/>
+      <c r="Q168" s="4"/>
       <c r="R168" t="s">
         <v>11</v>
       </c>
@@ -4444,22 +4447,22 @@
       </c>
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A169" s="9" t="s">
+      <c r="A169" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B169" s="9"/>
-      <c r="C169" s="9"/>
-      <c r="D169" s="9"/>
-      <c r="E169" s="9"/>
-      <c r="I169" s="9"/>
-      <c r="J169" s="9"/>
-      <c r="K169" s="9"/>
-      <c r="L169" s="9"/>
-      <c r="M169" s="9"/>
-      <c r="N169" s="9"/>
-      <c r="O169" s="9"/>
-      <c r="P169" s="9"/>
-      <c r="Q169" s="9"/>
+      <c r="B169" s="4"/>
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="I169" s="4"/>
+      <c r="J169" s="4"/>
+      <c r="K169" s="4"/>
+      <c r="L169" s="4"/>
+      <c r="M169" s="4"/>
+      <c r="N169" s="4"/>
+      <c r="O169" s="4"/>
+      <c r="P169" s="4"/>
+      <c r="Q169" s="4"/>
       <c r="R169" t="s">
         <v>11</v>
       </c>
@@ -4551,7 +4554,7 @@
         <v>1.3846000000000001</v>
       </c>
       <c r="U174" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.25">
@@ -4790,7 +4793,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="U183" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="V183" s="8"/>
     </row>
@@ -4875,7 +4878,7 @@
         <v>3.3332999999999999</v>
       </c>
       <c r="U186" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="187" spans="1:22" x14ac:dyDescent="0.25">
@@ -4928,7 +4931,7 @@
         <v>3.3332999999999999</v>
       </c>
       <c r="U188" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.25">
@@ -5025,10 +5028,10 @@
         <v>65</v>
       </c>
       <c r="U192" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="V192" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="193" spans="1:22" x14ac:dyDescent="0.25">
@@ -5107,7 +5110,7 @@
         <v>100</v>
       </c>
       <c r="U195" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:22" x14ac:dyDescent="0.25">
@@ -5134,7 +5137,7 @@
         <v>4.2</v>
       </c>
       <c r="V196" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.25">
@@ -5161,7 +5164,7 @@
         <v>3.3</v>
       </c>
       <c r="V197" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="198" spans="1:22" x14ac:dyDescent="0.25">
@@ -5184,12 +5187,12 @@
       <c r="R198" t="s">
         <v>10</v>
       </c>
-      <c r="S198" s="23">
+      <c r="S198" s="19">
         <f>AVERAGE(S196:S197)</f>
         <v>3.75</v>
       </c>
       <c r="U198" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.25">
@@ -5212,7 +5215,7 @@
       <c r="R199" t="s">
         <v>10</v>
       </c>
-      <c r="S199" s="23">
+      <c r="S199" s="19">
         <f>AVERAGE(S196:S197)</f>
         <v>3.75</v>
       </c>
@@ -5237,7 +5240,7 @@
       <c r="R200" t="s">
         <v>10</v>
       </c>
-      <c r="S200" s="23">
+      <c r="S200" s="19">
         <f>AVERAGE(S196:S197)</f>
         <v>3.75</v>
       </c>
@@ -5262,7 +5265,7 @@
       <c r="R201" t="s">
         <v>10</v>
       </c>
-      <c r="S201" s="23">
+      <c r="S201" s="19">
         <f>AVERAGE(S196:S197)</f>
         <v>3.75</v>
       </c>
@@ -5287,7 +5290,7 @@
       <c r="R202" t="s">
         <v>10</v>
       </c>
-      <c r="S202" s="23">
+      <c r="S202" s="19">
         <f>AVERAGE(S196:S197)</f>
         <v>3.75</v>
       </c>
@@ -5343,7 +5346,7 @@
         <v>20</v>
       </c>
       <c r="U204" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="205" spans="1:22" x14ac:dyDescent="0.25">
@@ -5433,7 +5436,7 @@
     </row>
     <row r="209" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -5492,13 +5495,13 @@
       <c r="P211" s="5"/>
       <c r="Q211" s="5"/>
       <c r="R211" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S211" s="5">
         <v>0</v>
       </c>
       <c r="T211" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U211" s="5" t="s">
         <v>12</v>
@@ -5519,16 +5522,16 @@
       <c r="P212" s="4"/>
       <c r="Q212" s="4"/>
       <c r="R212" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S212">
         <v>35</v>
       </c>
       <c r="U212" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="V212" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="213" spans="1:22" x14ac:dyDescent="0.25">
@@ -5546,16 +5549,16 @@
       <c r="P213" s="4"/>
       <c r="Q213" s="4"/>
       <c r="R213" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S213">
         <v>35</v>
       </c>
       <c r="U213" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V213" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="214" spans="1:22" x14ac:dyDescent="0.25">
@@ -5575,16 +5578,16 @@
       <c r="P214" s="4"/>
       <c r="Q214" s="4"/>
       <c r="R214" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S214">
         <v>25</v>
       </c>
       <c r="U214" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="V214" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="215" spans="1:22" x14ac:dyDescent="0.25">
@@ -5604,16 +5607,16 @@
       <c r="P215" s="4"/>
       <c r="Q215" s="4"/>
       <c r="R215" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S215">
         <v>25</v>
       </c>
       <c r="U215" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="V215" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="216" spans="1:22" x14ac:dyDescent="0.25">
@@ -5633,16 +5636,16 @@
       <c r="P216" s="4"/>
       <c r="Q216" s="4"/>
       <c r="R216" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S216">
         <v>40</v>
       </c>
       <c r="U216" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="V216" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="217" spans="1:22" x14ac:dyDescent="0.25">
@@ -5662,16 +5665,16 @@
       <c r="P217" s="4"/>
       <c r="Q217" s="4"/>
       <c r="R217" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S217">
         <v>20</v>
       </c>
       <c r="U217" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="V217" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="218" spans="1:22" x14ac:dyDescent="0.25">
@@ -5691,7 +5694,7 @@
       <c r="P218" s="4"/>
       <c r="Q218" s="4"/>
       <c r="R218" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S218">
         <v>10</v>
@@ -5700,7 +5703,7 @@
         <v>96</v>
       </c>
       <c r="V218" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="219" spans="1:22" x14ac:dyDescent="0.25">
@@ -5720,7 +5723,7 @@
       <c r="P219" s="4"/>
       <c r="Q219" s="4"/>
       <c r="R219" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S219">
         <v>10</v>
@@ -5729,7 +5732,7 @@
         <v>96</v>
       </c>
       <c r="V219" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="220" spans="1:22" x14ac:dyDescent="0.25">
@@ -5749,13 +5752,13 @@
       <c r="P220" s="4"/>
       <c r="Q220" s="4"/>
       <c r="R220" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S220">
         <v>25</v>
       </c>
       <c r="V220" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="221" spans="1:22" x14ac:dyDescent="0.25">
@@ -5776,14 +5779,14 @@
       <c r="P221" s="4"/>
       <c r="Q221" s="4"/>
       <c r="R221" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="222" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A222" s="9" t="s">
+      <c r="A222" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B222" s="9"/>
+      <c r="B222" s="4"/>
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
@@ -5800,23 +5803,23 @@
       <c r="P222" s="4"/>
       <c r="Q222" s="4"/>
       <c r="R222" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S222" s="6">
         <v>10</v>
       </c>
       <c r="U222" t="s">
+        <v>232</v>
+      </c>
+      <c r="V222" t="s">
         <v>233</v>
       </c>
-      <c r="V222" t="s">
-        <v>234</v>
-      </c>
     </row>
     <row r="223" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A223" s="9" t="s">
+      <c r="A223" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B223" s="9"/>
+      <c r="B223" s="4"/>
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
@@ -5833,17 +5836,17 @@
       <c r="P223" s="4"/>
       <c r="Q223" s="4"/>
       <c r="R223" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S223" s="6">
         <v>40</v>
       </c>
     </row>
     <row r="224" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A224" s="9" t="s">
+      <c r="A224" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B224" s="9"/>
+      <c r="B224" s="4"/>
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
@@ -5860,17 +5863,17 @@
       <c r="P224" s="4"/>
       <c r="Q224" s="4"/>
       <c r="R224" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S224" s="6">
         <v>10</v>
       </c>
     </row>
     <row r="225" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A225" s="9" t="s">
+      <c r="A225" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B225" s="9"/>
+      <c r="B225" s="4"/>
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
@@ -5887,7 +5890,7 @@
       <c r="P225" s="4"/>
       <c r="Q225" s="4"/>
       <c r="R225" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S225" s="6">
         <v>40</v>
@@ -5902,7 +5905,7 @@
         <v>139</v>
       </c>
       <c r="R226" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S226" s="6">
         <v>10</v>
@@ -5917,7 +5920,7 @@
         <v>98</v>
       </c>
       <c r="R227" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S227" s="6">
         <v>40</v>
@@ -5929,16 +5932,16 @@
       </c>
       <c r="B228" s="4"/>
       <c r="R228" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S228" s="4">
         <v>60</v>
       </c>
       <c r="U228" t="s">
+        <v>336</v>
+      </c>
+      <c r="V228" t="s">
         <v>337</v>
-      </c>
-      <c r="V228" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="229" spans="1:22" x14ac:dyDescent="0.25">
@@ -5950,56 +5953,56 @@
         <v>98</v>
       </c>
       <c r="R229" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S229" s="4">
         <f>60*0.5</f>
         <v>30</v>
       </c>
       <c r="U229" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="230" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R230" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S230" s="4">
         <v>35</v>
       </c>
       <c r="U230" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="231" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R231" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S231" s="4">
         <v>25</v>
       </c>
       <c r="U231" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="232" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R232" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S232" s="4">
         <v>25</v>
       </c>
       <c r="U232" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="233" spans="1:22" x14ac:dyDescent="0.25">
@@ -6009,7 +6012,7 @@
     </row>
     <row r="234" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -6034,20 +6037,20 @@
       <c r="V234" s="3"/>
     </row>
     <row r="235" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A235" s="18" t="s">
-        <v>344</v>
+      <c r="A235" s="14" t="s">
+        <v>343</v>
       </c>
       <c r="B235" s="4"/>
     </row>
     <row r="236" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A236" s="18" t="s">
-        <v>343</v>
+      <c r="A236" s="14" t="s">
+        <v>342</v>
       </c>
       <c r="B236" s="4"/>
     </row>
     <row r="237" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A237" s="18" t="s">
-        <v>342</v>
+      <c r="A237" s="14" t="s">
+        <v>341</v>
       </c>
       <c r="B237" s="4"/>
     </row>
@@ -6055,35 +6058,35 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="R238" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S238" s="6">
         <v>40</v>
       </c>
       <c r="T238" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="U238" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="V238" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="239" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="R239" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S239" s="6">
         <v>40</v>
       </c>
       <c r="T239" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="U239" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="240" spans="1:22" x14ac:dyDescent="0.25">
@@ -6091,34 +6094,34 @@
       <c r="B240" s="4"/>
     </row>
     <row r="241" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="B241" s="14"/>
-      <c r="C241" s="14"/>
-      <c r="D241" s="14"/>
-      <c r="E241" s="13"/>
-      <c r="F241" s="13"/>
-      <c r="G241" s="13"/>
-      <c r="H241" s="13"/>
-      <c r="I241" s="13"/>
-      <c r="J241" s="13"/>
-      <c r="K241" s="13"/>
-      <c r="L241" s="13"/>
-      <c r="M241" s="13"/>
-      <c r="N241" s="13"/>
-      <c r="O241" s="13"/>
-      <c r="P241" s="13"/>
-      <c r="Q241" s="13"/>
-      <c r="R241" s="13"/>
-      <c r="S241" s="13"/>
-      <c r="T241" s="13"/>
-      <c r="U241" s="13"/>
-      <c r="V241" s="13"/>
+      <c r="A241" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B241" s="12"/>
+      <c r="C241" s="12"/>
+      <c r="D241" s="12"/>
+      <c r="E241" s="11"/>
+      <c r="F241" s="11"/>
+      <c r="G241" s="11"/>
+      <c r="H241" s="11"/>
+      <c r="I241" s="11"/>
+      <c r="J241" s="11"/>
+      <c r="K241" s="11"/>
+      <c r="L241" s="11"/>
+      <c r="M241" s="11"/>
+      <c r="N241" s="11"/>
+      <c r="O241" s="11"/>
+      <c r="P241" s="11"/>
+      <c r="Q241" s="11"/>
+      <c r="R241" s="11"/>
+      <c r="S241" s="11"/>
+      <c r="T241" s="11"/>
+      <c r="U241" s="11"/>
+      <c r="V241" s="11"/>
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -6143,30 +6146,30 @@
       <c r="V242" s="3"/>
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A243" s="18" t="s">
+      <c r="A243" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B243" s="14"/>
+      <c r="C243" s="14"/>
+      <c r="D243" s="14"/>
+    </row>
+    <row r="244" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A244" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="B243" s="18"/>
-      <c r="C243" s="18"/>
-      <c r="D243" s="18"/>
-    </row>
-    <row r="244" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A244" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B244" s="18"/>
-      <c r="C244" s="18"/>
-      <c r="D244" s="18"/>
+      <c r="B244" s="14"/>
+      <c r="C244" s="14"/>
+      <c r="D244" s="14"/>
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R245" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S245" s="5">
         <v>0</v>
       </c>
       <c r="T245" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="U245" s="5" t="s">
         <v>142</v>
@@ -6174,7 +6177,7 @@
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R246" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S246" s="5">
         <v>0</v>
@@ -6187,12 +6190,12 @@
       </c>
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A247" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="B247" s="20"/>
-      <c r="C247" s="20"/>
-      <c r="D247" s="20"/>
+      <c r="A247" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B247" s="16"/>
+      <c r="C247" s="16"/>
+      <c r="D247" s="16"/>
       <c r="R247" s="5"/>
       <c r="S247" s="5"/>
       <c r="T247" s="5"/>
@@ -6203,10 +6206,10 @@
         <v>6</v>
       </c>
       <c r="O248" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R248" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S248">
         <v>3</v>
@@ -6217,10 +6220,10 @@
         <v>6</v>
       </c>
       <c r="O249" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R249" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S249">
         <v>3</v>
@@ -6231,10 +6234,10 @@
         <v>6</v>
       </c>
       <c r="O250" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R250" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S250">
         <v>3</v>
@@ -6245,10 +6248,10 @@
         <v>6</v>
       </c>
       <c r="O251" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R251" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S251">
         <v>3</v>
@@ -6259,10 +6262,10 @@
         <v>6</v>
       </c>
       <c r="O252" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R252" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S252">
         <v>9</v>
@@ -6273,10 +6276,10 @@
         <v>6</v>
       </c>
       <c r="O253" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R253" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S253">
         <v>4</v>
@@ -6287,10 +6290,10 @@
         <v>6</v>
       </c>
       <c r="O254" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R254" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S254">
         <v>-6</v>
@@ -6301,10 +6304,10 @@
         <v>6</v>
       </c>
       <c r="O255" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R255" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S255">
         <v>-16</v>
@@ -6315,12 +6318,12 @@
         <v>24</v>
       </c>
       <c r="O256" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R256" t="s">
-        <v>183</v>
-      </c>
-      <c r="S256" s="19">
+        <v>182</v>
+      </c>
+      <c r="S256" s="15">
         <f>S248</f>
         <v>3</v>
       </c>
@@ -6330,12 +6333,12 @@
         <v>24</v>
       </c>
       <c r="O257" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R257" t="s">
-        <v>183</v>
-      </c>
-      <c r="S257" s="19">
+        <v>182</v>
+      </c>
+      <c r="S257" s="15">
         <f t="shared" ref="S257:S263" si="4">S249</f>
         <v>3</v>
       </c>
@@ -6345,12 +6348,12 @@
         <v>24</v>
       </c>
       <c r="O258" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R258" t="s">
-        <v>183</v>
-      </c>
-      <c r="S258" s="19">
+        <v>182</v>
+      </c>
+      <c r="S258" s="15">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
@@ -6360,12 +6363,12 @@
         <v>24</v>
       </c>
       <c r="O259" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R259" t="s">
-        <v>183</v>
-      </c>
-      <c r="S259" s="19">
+        <v>182</v>
+      </c>
+      <c r="S259" s="15">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
@@ -6375,12 +6378,12 @@
         <v>24</v>
       </c>
       <c r="O260" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R260" t="s">
-        <v>184</v>
-      </c>
-      <c r="S260" s="19">
+        <v>183</v>
+      </c>
+      <c r="S260" s="15">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
@@ -6390,12 +6393,12 @@
         <v>24</v>
       </c>
       <c r="O261" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R261" t="s">
-        <v>184</v>
-      </c>
-      <c r="S261" s="19">
+        <v>183</v>
+      </c>
+      <c r="S261" s="15">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
@@ -6405,12 +6408,12 @@
         <v>24</v>
       </c>
       <c r="O262" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R262" t="s">
-        <v>184</v>
-      </c>
-      <c r="S262" s="19">
+        <v>183</v>
+      </c>
+      <c r="S262" s="15">
         <f t="shared" si="4"/>
         <v>-6</v>
       </c>
@@ -6420,12 +6423,12 @@
         <v>24</v>
       </c>
       <c r="O263" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R263" t="s">
-        <v>184</v>
-      </c>
-      <c r="S263" s="19">
+        <v>183</v>
+      </c>
+      <c r="S263" s="15">
         <f t="shared" si="4"/>
         <v>-16</v>
       </c>
@@ -6435,12 +6438,12 @@
         <v>20</v>
       </c>
       <c r="O264" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R264" t="s">
-        <v>183</v>
-      </c>
-      <c r="S264" s="19">
+        <v>182</v>
+      </c>
+      <c r="S264" s="15">
         <f>S248</f>
         <v>3</v>
       </c>
@@ -6450,12 +6453,12 @@
         <v>20</v>
       </c>
       <c r="O265" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R265" t="s">
-        <v>183</v>
-      </c>
-      <c r="S265" s="19">
+        <v>182</v>
+      </c>
+      <c r="S265" s="15">
         <f t="shared" ref="S265:S271" si="5">S249</f>
         <v>3</v>
       </c>
@@ -6465,12 +6468,12 @@
         <v>20</v>
       </c>
       <c r="O266" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R266" t="s">
-        <v>183</v>
-      </c>
-      <c r="S266" s="19">
+        <v>182</v>
+      </c>
+      <c r="S266" s="15">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -6480,12 +6483,12 @@
         <v>20</v>
       </c>
       <c r="O267" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R267" t="s">
-        <v>183</v>
-      </c>
-      <c r="S267" s="19">
+        <v>182</v>
+      </c>
+      <c r="S267" s="15">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -6495,12 +6498,12 @@
         <v>20</v>
       </c>
       <c r="O268" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R268" t="s">
-        <v>184</v>
-      </c>
-      <c r="S268" s="19">
+        <v>183</v>
+      </c>
+      <c r="S268" s="15">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
@@ -6510,12 +6513,12 @@
         <v>20</v>
       </c>
       <c r="O269" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R269" t="s">
-        <v>184</v>
-      </c>
-      <c r="S269" s="19">
+        <v>183</v>
+      </c>
+      <c r="S269" s="15">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
@@ -6525,12 +6528,12 @@
         <v>20</v>
       </c>
       <c r="O270" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R270" t="s">
-        <v>184</v>
-      </c>
-      <c r="S270" s="19">
+        <v>183</v>
+      </c>
+      <c r="S270" s="15">
         <f t="shared" si="5"/>
         <v>-6</v>
       </c>
@@ -6540,12 +6543,12 @@
         <v>20</v>
       </c>
       <c r="O271" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R271" t="s">
-        <v>184</v>
-      </c>
-      <c r="S271" s="19">
+        <v>183</v>
+      </c>
+      <c r="S271" s="15">
         <f t="shared" si="5"/>
         <v>-16</v>
       </c>
@@ -6555,12 +6558,12 @@
         <v>22</v>
       </c>
       <c r="O272" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R272" t="s">
-        <v>183</v>
-      </c>
-      <c r="S272" s="19">
+        <v>182</v>
+      </c>
+      <c r="S272" s="15">
         <f>S248</f>
         <v>3</v>
       </c>
@@ -6570,12 +6573,12 @@
         <v>22</v>
       </c>
       <c r="O273" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R273" t="s">
-        <v>183</v>
-      </c>
-      <c r="S273" s="19">
+        <v>182</v>
+      </c>
+      <c r="S273" s="15">
         <f t="shared" ref="S273:S279" si="6">S249</f>
         <v>3</v>
       </c>
@@ -6585,12 +6588,12 @@
         <v>22</v>
       </c>
       <c r="O274" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R274" t="s">
-        <v>183</v>
-      </c>
-      <c r="S274" s="19">
+        <v>182</v>
+      </c>
+      <c r="S274" s="15">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
@@ -6600,12 +6603,12 @@
         <v>22</v>
       </c>
       <c r="O275" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R275" t="s">
-        <v>183</v>
-      </c>
-      <c r="S275" s="19">
+        <v>182</v>
+      </c>
+      <c r="S275" s="15">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
@@ -6615,12 +6618,12 @@
         <v>22</v>
       </c>
       <c r="O276" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R276" t="s">
-        <v>184</v>
-      </c>
-      <c r="S276" s="19">
+        <v>183</v>
+      </c>
+      <c r="S276" s="15">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
@@ -6630,12 +6633,12 @@
         <v>22</v>
       </c>
       <c r="O277" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R277" t="s">
-        <v>184</v>
-      </c>
-      <c r="S277" s="19">
+        <v>183</v>
+      </c>
+      <c r="S277" s="15">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
@@ -6645,12 +6648,12 @@
         <v>22</v>
       </c>
       <c r="O278" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R278" t="s">
-        <v>184</v>
-      </c>
-      <c r="S278" s="19">
+        <v>183</v>
+      </c>
+      <c r="S278" s="15">
         <f t="shared" si="6"/>
         <v>-6</v>
       </c>
@@ -6660,33 +6663,33 @@
         <v>22</v>
       </c>
       <c r="O279" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R279" t="s">
-        <v>184</v>
-      </c>
-      <c r="S279" s="19">
+        <v>183</v>
+      </c>
+      <c r="S279" s="15">
         <f t="shared" si="6"/>
         <v>-16</v>
       </c>
     </row>
     <row r="281" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A281" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B281" s="20"/>
-      <c r="C281" s="20"/>
-      <c r="D281" s="20"/>
+      <c r="A281" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B281" s="16"/>
+      <c r="C281" s="16"/>
+      <c r="D281" s="16"/>
     </row>
     <row r="282" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>13</v>
       </c>
       <c r="O282" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R282" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S282">
         <v>3</v>
@@ -6697,10 +6700,10 @@
         <v>13</v>
       </c>
       <c r="O283" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R283" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S283">
         <v>3</v>
@@ -6711,10 +6714,10 @@
         <v>13</v>
       </c>
       <c r="O284" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R284" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S284">
         <v>3</v>
@@ -6725,10 +6728,10 @@
         <v>13</v>
       </c>
       <c r="O285" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R285" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S285">
         <v>3</v>
@@ -6739,10 +6742,10 @@
         <v>13</v>
       </c>
       <c r="O286" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R286" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S286">
         <v>10</v>
@@ -6753,10 +6756,10 @@
         <v>13</v>
       </c>
       <c r="O287" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R287" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S287">
         <v>5</v>
@@ -6767,10 +6770,10 @@
         <v>13</v>
       </c>
       <c r="O288" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R288" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S288">
         <v>0</v>
@@ -6781,10 +6784,10 @@
         <v>13</v>
       </c>
       <c r="O289" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R289" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S289">
         <v>-10</v>
@@ -6795,12 +6798,12 @@
         <v>14</v>
       </c>
       <c r="O290" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R290" t="s">
-        <v>183</v>
-      </c>
-      <c r="S290" s="19">
+        <v>182</v>
+      </c>
+      <c r="S290" s="15">
         <f>S282</f>
         <v>3</v>
       </c>
@@ -6810,12 +6813,12 @@
         <v>14</v>
       </c>
       <c r="O291" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R291" t="s">
-        <v>183</v>
-      </c>
-      <c r="S291" s="19">
+        <v>182</v>
+      </c>
+      <c r="S291" s="15">
         <f t="shared" ref="S291:S297" si="7">S283</f>
         <v>3</v>
       </c>
@@ -6825,12 +6828,12 @@
         <v>14</v>
       </c>
       <c r="O292" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R292" t="s">
-        <v>183</v>
-      </c>
-      <c r="S292" s="19">
+        <v>182</v>
+      </c>
+      <c r="S292" s="15">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
@@ -6840,12 +6843,12 @@
         <v>14</v>
       </c>
       <c r="O293" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R293" t="s">
-        <v>183</v>
-      </c>
-      <c r="S293" s="19">
+        <v>182</v>
+      </c>
+      <c r="S293" s="15">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
@@ -6855,12 +6858,12 @@
         <v>14</v>
       </c>
       <c r="O294" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R294" t="s">
-        <v>184</v>
-      </c>
-      <c r="S294" s="19">
+        <v>183</v>
+      </c>
+      <c r="S294" s="15">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
@@ -6870,12 +6873,12 @@
         <v>14</v>
       </c>
       <c r="O295" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R295" t="s">
-        <v>184</v>
-      </c>
-      <c r="S295" s="19">
+        <v>183</v>
+      </c>
+      <c r="S295" s="15">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
@@ -6885,12 +6888,12 @@
         <v>14</v>
       </c>
       <c r="O296" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R296" t="s">
-        <v>184</v>
-      </c>
-      <c r="S296" s="19">
+        <v>183</v>
+      </c>
+      <c r="S296" s="15">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6900,12 +6903,12 @@
         <v>14</v>
       </c>
       <c r="O297" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R297" t="s">
-        <v>184</v>
-      </c>
-      <c r="S297" s="19">
+        <v>183</v>
+      </c>
+      <c r="S297" s="15">
         <f t="shared" si="7"/>
         <v>-10</v>
       </c>
@@ -6915,12 +6918,12 @@
         <v>18</v>
       </c>
       <c r="O298" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R298" t="s">
-        <v>183</v>
-      </c>
-      <c r="S298" s="19">
+        <v>182</v>
+      </c>
+      <c r="S298" s="15">
         <f>S282</f>
         <v>3</v>
       </c>
@@ -6930,12 +6933,12 @@
         <v>18</v>
       </c>
       <c r="O299" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R299" t="s">
-        <v>183</v>
-      </c>
-      <c r="S299" s="19">
+        <v>182</v>
+      </c>
+      <c r="S299" s="15">
         <f t="shared" ref="S299:S305" si="8">S283</f>
         <v>3</v>
       </c>
@@ -6945,12 +6948,12 @@
         <v>18</v>
       </c>
       <c r="O300" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R300" t="s">
-        <v>183</v>
-      </c>
-      <c r="S300" s="19">
+        <v>182</v>
+      </c>
+      <c r="S300" s="15">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
@@ -6960,12 +6963,12 @@
         <v>18</v>
       </c>
       <c r="O301" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R301" t="s">
-        <v>183</v>
-      </c>
-      <c r="S301" s="19">
+        <v>182</v>
+      </c>
+      <c r="S301" s="15">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
@@ -6975,12 +6978,12 @@
         <v>18</v>
       </c>
       <c r="O302" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R302" t="s">
-        <v>184</v>
-      </c>
-      <c r="S302" s="19">
+        <v>183</v>
+      </c>
+      <c r="S302" s="15">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
@@ -6990,12 +6993,12 @@
         <v>18</v>
       </c>
       <c r="O303" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R303" t="s">
-        <v>184</v>
-      </c>
-      <c r="S303" s="19">
+        <v>183</v>
+      </c>
+      <c r="S303" s="15">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
@@ -7005,12 +7008,12 @@
         <v>18</v>
       </c>
       <c r="O304" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R304" t="s">
-        <v>184</v>
-      </c>
-      <c r="S304" s="19">
+        <v>183</v>
+      </c>
+      <c r="S304" s="15">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -7020,132 +7023,132 @@
         <v>18</v>
       </c>
       <c r="O305" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R305" t="s">
-        <v>184</v>
-      </c>
-      <c r="S305" s="19">
+        <v>183</v>
+      </c>
+      <c r="S305" s="15">
         <f t="shared" si="8"/>
         <v>-10</v>
       </c>
     </row>
     <row r="306" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O306" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R306" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="S306" s="19">
+        <v>182</v>
+      </c>
+      <c r="S306" s="15">
         <f>S282</f>
         <v>3</v>
       </c>
     </row>
     <row r="307" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O307" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R307" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="S307" s="19">
+        <v>182</v>
+      </c>
+      <c r="S307" s="15">
         <f t="shared" ref="S307:S313" si="9">S283</f>
         <v>3</v>
       </c>
     </row>
     <row r="308" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O308" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R308" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="S308" s="19">
+        <v>182</v>
+      </c>
+      <c r="S308" s="15">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
     <row r="309" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O309" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R309" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="S309" s="19">
+        <v>182</v>
+      </c>
+      <c r="S309" s="15">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
     <row r="310" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O310" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R310" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="S310" s="19">
+        <v>183</v>
+      </c>
+      <c r="S310" s="15">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
     </row>
     <row r="311" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O311" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R311" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="S311" s="19">
+        <v>183</v>
+      </c>
+      <c r="S311" s="15">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O312" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R312" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="S312" s="19">
+        <v>183</v>
+      </c>
+      <c r="S312" s="15">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O313" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R313" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="S313" s="19">
+        <v>183</v>
+      </c>
+      <c r="S313" s="15">
         <f t="shared" si="9"/>
         <v>-10</v>
       </c>
@@ -7155,12 +7158,12 @@
         <v>21</v>
       </c>
       <c r="O314" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R314" t="s">
-        <v>183</v>
-      </c>
-      <c r="S314" s="19">
+        <v>182</v>
+      </c>
+      <c r="S314" s="15">
         <f t="shared" ref="S314:S321" si="10">S282</f>
         <v>3</v>
       </c>
@@ -7170,12 +7173,12 @@
         <v>21</v>
       </c>
       <c r="O315" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R315" t="s">
-        <v>183</v>
-      </c>
-      <c r="S315" s="19">
+        <v>182</v>
+      </c>
+      <c r="S315" s="15">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -7185,12 +7188,12 @@
         <v>21</v>
       </c>
       <c r="O316" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R316" t="s">
-        <v>183</v>
-      </c>
-      <c r="S316" s="19">
+        <v>182</v>
+      </c>
+      <c r="S316" s="15">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -7200,12 +7203,12 @@
         <v>21</v>
       </c>
       <c r="O317" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R317" t="s">
-        <v>183</v>
-      </c>
-      <c r="S317" s="19">
+        <v>182</v>
+      </c>
+      <c r="S317" s="15">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -7215,12 +7218,12 @@
         <v>21</v>
       </c>
       <c r="O318" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R318" t="s">
-        <v>184</v>
-      </c>
-      <c r="S318" s="19">
+        <v>183</v>
+      </c>
+      <c r="S318" s="15">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
@@ -7230,12 +7233,12 @@
         <v>21</v>
       </c>
       <c r="O319" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R319" t="s">
-        <v>184</v>
-      </c>
-      <c r="S319" s="19">
+        <v>183</v>
+      </c>
+      <c r="S319" s="15">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
@@ -7245,12 +7248,12 @@
         <v>21</v>
       </c>
       <c r="O320" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R320" t="s">
-        <v>184</v>
-      </c>
-      <c r="S320" s="19">
+        <v>183</v>
+      </c>
+      <c r="S320" s="15">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -7260,12 +7263,12 @@
         <v>21</v>
       </c>
       <c r="O321" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R321" t="s">
-        <v>184</v>
-      </c>
-      <c r="S321" s="19">
+        <v>183</v>
+      </c>
+      <c r="S321" s="15">
         <f t="shared" si="10"/>
         <v>-10</v>
       </c>
@@ -7275,12 +7278,12 @@
         <v>26</v>
       </c>
       <c r="O322" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R322" t="s">
-        <v>183</v>
-      </c>
-      <c r="S322" s="19">
+        <v>182</v>
+      </c>
+      <c r="S322" s="15">
         <f t="shared" ref="S322:S329" si="11">S282</f>
         <v>3</v>
       </c>
@@ -7290,12 +7293,12 @@
         <v>26</v>
       </c>
       <c r="O323" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R323" t="s">
-        <v>183</v>
-      </c>
-      <c r="S323" s="19">
+        <v>182</v>
+      </c>
+      <c r="S323" s="15">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -7305,12 +7308,12 @@
         <v>26</v>
       </c>
       <c r="O324" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R324" t="s">
-        <v>183</v>
-      </c>
-      <c r="S324" s="19">
+        <v>182</v>
+      </c>
+      <c r="S324" s="15">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -7320,12 +7323,12 @@
         <v>26</v>
       </c>
       <c r="O325" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R325" t="s">
-        <v>183</v>
-      </c>
-      <c r="S325" s="19">
+        <v>182</v>
+      </c>
+      <c r="S325" s="15">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -7335,12 +7338,12 @@
         <v>26</v>
       </c>
       <c r="O326" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R326" t="s">
-        <v>184</v>
-      </c>
-      <c r="S326" s="19">
+        <v>183</v>
+      </c>
+      <c r="S326" s="15">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
@@ -7350,12 +7353,12 @@
         <v>26</v>
       </c>
       <c r="O327" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R327" t="s">
-        <v>184</v>
-      </c>
-      <c r="S327" s="19">
+        <v>183</v>
+      </c>
+      <c r="S327" s="15">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
@@ -7365,12 +7368,12 @@
         <v>26</v>
       </c>
       <c r="O328" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R328" t="s">
-        <v>184</v>
-      </c>
-      <c r="S328" s="19">
+        <v>183</v>
+      </c>
+      <c r="S328" s="15">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -7380,12 +7383,12 @@
         <v>26</v>
       </c>
       <c r="O329" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R329" t="s">
-        <v>184</v>
-      </c>
-      <c r="S329" s="19">
+        <v>183</v>
+      </c>
+      <c r="S329" s="15">
         <f t="shared" si="11"/>
         <v>-10</v>
       </c>
@@ -7395,12 +7398,12 @@
         <v>25</v>
       </c>
       <c r="O330" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R330" t="s">
-        <v>183</v>
-      </c>
-      <c r="S330" s="19">
+        <v>182</v>
+      </c>
+      <c r="S330" s="15">
         <f t="shared" ref="S330:S337" si="12">S282</f>
         <v>3</v>
       </c>
@@ -7410,12 +7413,12 @@
         <v>25</v>
       </c>
       <c r="O331" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R331" t="s">
-        <v>183</v>
-      </c>
-      <c r="S331" s="19">
+        <v>182</v>
+      </c>
+      <c r="S331" s="15">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
@@ -7425,12 +7428,12 @@
         <v>25</v>
       </c>
       <c r="O332" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R332" t="s">
-        <v>183</v>
-      </c>
-      <c r="S332" s="19">
+        <v>182</v>
+      </c>
+      <c r="S332" s="15">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
@@ -7440,12 +7443,12 @@
         <v>25</v>
       </c>
       <c r="O333" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R333" t="s">
-        <v>183</v>
-      </c>
-      <c r="S333" s="19">
+        <v>182</v>
+      </c>
+      <c r="S333" s="15">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
@@ -7455,12 +7458,12 @@
         <v>25</v>
       </c>
       <c r="O334" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R334" t="s">
-        <v>184</v>
-      </c>
-      <c r="S334" s="19">
+        <v>183</v>
+      </c>
+      <c r="S334" s="15">
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
@@ -7470,12 +7473,12 @@
         <v>25</v>
       </c>
       <c r="O335" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R335" t="s">
-        <v>184</v>
-      </c>
-      <c r="S335" s="19">
+        <v>183</v>
+      </c>
+      <c r="S335" s="15">
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
@@ -7485,12 +7488,12 @@
         <v>25</v>
       </c>
       <c r="O336" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R336" t="s">
-        <v>184</v>
-      </c>
-      <c r="S336" s="19">
+        <v>183</v>
+      </c>
+      <c r="S336" s="15">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7500,12 +7503,12 @@
         <v>25</v>
       </c>
       <c r="O337" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R337" t="s">
-        <v>184</v>
-      </c>
-      <c r="S337" s="19">
+        <v>183</v>
+      </c>
+      <c r="S337" s="15">
         <f t="shared" si="12"/>
         <v>-10</v>
       </c>
@@ -7518,17 +7521,17 @@
       <c r="C338" s="6"/>
       <c r="D338" s="6"/>
       <c r="O338" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R338" t="s">
-        <v>183</v>
-      </c>
-      <c r="S338" s="19">
+        <v>182</v>
+      </c>
+      <c r="S338" s="15">
         <f t="shared" ref="S338:S345" si="13">S282</f>
         <v>3</v>
       </c>
       <c r="U338" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="339" spans="1:21" x14ac:dyDescent="0.25">
@@ -7539,12 +7542,12 @@
       <c r="C339" s="6"/>
       <c r="D339" s="6"/>
       <c r="O339" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R339" t="s">
-        <v>183</v>
-      </c>
-      <c r="S339" s="19">
+        <v>182</v>
+      </c>
+      <c r="S339" s="15">
         <f t="shared" si="13"/>
         <v>3</v>
       </c>
@@ -7557,12 +7560,12 @@
       <c r="C340" s="6"/>
       <c r="D340" s="6"/>
       <c r="O340" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R340" t="s">
-        <v>183</v>
-      </c>
-      <c r="S340" s="19">
+        <v>182</v>
+      </c>
+      <c r="S340" s="15">
         <f t="shared" si="13"/>
         <v>3</v>
       </c>
@@ -7575,12 +7578,12 @@
       <c r="C341" s="6"/>
       <c r="D341" s="6"/>
       <c r="O341" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R341" t="s">
-        <v>183</v>
-      </c>
-      <c r="S341" s="19">
+        <v>182</v>
+      </c>
+      <c r="S341" s="15">
         <f t="shared" si="13"/>
         <v>3</v>
       </c>
@@ -7593,12 +7596,12 @@
       <c r="C342" s="6"/>
       <c r="D342" s="6"/>
       <c r="O342" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R342" t="s">
-        <v>184</v>
-      </c>
-      <c r="S342" s="19">
+        <v>183</v>
+      </c>
+      <c r="S342" s="15">
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
@@ -7611,12 +7614,12 @@
       <c r="C343" s="6"/>
       <c r="D343" s="6"/>
       <c r="O343" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R343" t="s">
-        <v>184</v>
-      </c>
-      <c r="S343" s="19">
+        <v>183</v>
+      </c>
+      <c r="S343" s="15">
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
@@ -7629,12 +7632,12 @@
       <c r="C344" s="6"/>
       <c r="D344" s="6"/>
       <c r="O344" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R344" t="s">
-        <v>184</v>
-      </c>
-      <c r="S344" s="19">
+        <v>183</v>
+      </c>
+      <c r="S344" s="15">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -7647,12 +7650,12 @@
       <c r="C345" s="6"/>
       <c r="D345" s="6"/>
       <c r="O345" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R345" t="s">
-        <v>184</v>
-      </c>
-      <c r="S345" s="19">
+        <v>183</v>
+      </c>
+      <c r="S345" s="15">
         <f t="shared" si="13"/>
         <v>-10</v>
       </c>
@@ -7665,17 +7668,17 @@
       <c r="C346" s="6"/>
       <c r="D346" s="6"/>
       <c r="O346" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R346" t="s">
-        <v>183</v>
-      </c>
-      <c r="S346" s="19">
+        <v>182</v>
+      </c>
+      <c r="S346" s="15">
         <f>S282</f>
         <v>3</v>
       </c>
       <c r="U346" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="347" spans="1:21" x14ac:dyDescent="0.25">
@@ -7686,12 +7689,12 @@
       <c r="C347" s="6"/>
       <c r="D347" s="6"/>
       <c r="O347" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R347" t="s">
-        <v>183</v>
-      </c>
-      <c r="S347" s="19">
+        <v>182</v>
+      </c>
+      <c r="S347" s="15">
         <f t="shared" ref="S347:S353" si="14">S283</f>
         <v>3</v>
       </c>
@@ -7704,12 +7707,12 @@
       <c r="C348" s="6"/>
       <c r="D348" s="6"/>
       <c r="O348" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R348" t="s">
-        <v>183</v>
-      </c>
-      <c r="S348" s="19">
+        <v>182</v>
+      </c>
+      <c r="S348" s="15">
         <f t="shared" si="14"/>
         <v>3</v>
       </c>
@@ -7722,12 +7725,12 @@
       <c r="C349" s="6"/>
       <c r="D349" s="6"/>
       <c r="O349" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R349" t="s">
-        <v>183</v>
-      </c>
-      <c r="S349" s="19">
+        <v>182</v>
+      </c>
+      <c r="S349" s="15">
         <f t="shared" si="14"/>
         <v>3</v>
       </c>
@@ -7740,12 +7743,12 @@
       <c r="C350" s="6"/>
       <c r="D350" s="6"/>
       <c r="O350" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R350" t="s">
-        <v>184</v>
-      </c>
-      <c r="S350" s="19">
+        <v>183</v>
+      </c>
+      <c r="S350" s="15">
         <f t="shared" si="14"/>
         <v>10</v>
       </c>
@@ -7758,12 +7761,12 @@
       <c r="C351" s="6"/>
       <c r="D351" s="6"/>
       <c r="O351" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R351" t="s">
-        <v>184</v>
-      </c>
-      <c r="S351" s="19">
+        <v>183</v>
+      </c>
+      <c r="S351" s="15">
         <f t="shared" si="14"/>
         <v>5</v>
       </c>
@@ -7774,12 +7777,12 @@
       </c>
       <c r="B352" s="4"/>
       <c r="O352" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R352" t="s">
-        <v>184</v>
-      </c>
-      <c r="S352" s="19">
+        <v>183</v>
+      </c>
+      <c r="S352" s="15">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -7790,33 +7793,33 @@
       </c>
       <c r="B353" s="4"/>
       <c r="O353" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R353" t="s">
-        <v>184</v>
-      </c>
-      <c r="S353" s="19">
+        <v>183</v>
+      </c>
+      <c r="S353" s="15">
         <f t="shared" si="14"/>
         <v>-10</v>
       </c>
     </row>
     <row r="354" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A354" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="B354" s="20"/>
-      <c r="C354" s="20"/>
-      <c r="D354" s="20"/>
+      <c r="A354" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B354" s="16"/>
+      <c r="C354" s="16"/>
+      <c r="D354" s="16"/>
     </row>
     <row r="355" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>31</v>
       </c>
       <c r="O355" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R355" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S355">
         <v>7</v>
@@ -7827,10 +7830,10 @@
         <v>31</v>
       </c>
       <c r="O356" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R356" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S356">
         <v>7</v>
@@ -7841,10 +7844,10 @@
         <v>31</v>
       </c>
       <c r="O357" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R357" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S357">
         <v>7</v>
@@ -7855,10 +7858,10 @@
         <v>31</v>
       </c>
       <c r="O358" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R358" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S358">
         <v>7</v>
@@ -7869,10 +7872,10 @@
         <v>31</v>
       </c>
       <c r="O359" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R359" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S359">
         <v>15.5</v>
@@ -7883,10 +7886,10 @@
         <v>31</v>
       </c>
       <c r="O360" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R360" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S360">
         <v>10.5</v>
@@ -7897,10 +7900,10 @@
         <v>31</v>
       </c>
       <c r="O361" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R361" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S361">
         <v>0.5</v>
@@ -7911,10 +7914,10 @@
         <v>31</v>
       </c>
       <c r="O362" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R362" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S362">
         <v>-9.5</v>
@@ -7925,10 +7928,10 @@
         <v>32</v>
       </c>
       <c r="O363" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R363" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S363">
         <v>7</v>
@@ -7939,10 +7942,10 @@
         <v>32</v>
       </c>
       <c r="O364" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R364" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S364">
         <v>7</v>
@@ -7953,10 +7956,10 @@
         <v>32</v>
       </c>
       <c r="O365" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R365" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S365">
         <v>7</v>
@@ -7967,10 +7970,10 @@
         <v>32</v>
       </c>
       <c r="O366" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R366" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S366">
         <v>7</v>
@@ -7981,10 +7984,10 @@
         <v>32</v>
       </c>
       <c r="O367" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R367" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S367">
         <v>16</v>
@@ -7995,10 +7998,10 @@
         <v>32</v>
       </c>
       <c r="O368" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R368" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S368">
         <v>11</v>
@@ -8009,10 +8012,10 @@
         <v>32</v>
       </c>
       <c r="O369" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R369" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S369">
         <v>1</v>
@@ -8023,32 +8026,32 @@
         <v>32</v>
       </c>
       <c r="O370" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R370" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S370">
         <v>-4</v>
       </c>
     </row>
     <row r="372" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A372" s="20" t="s">
+      <c r="A372" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B372" s="20"/>
-      <c r="C372" s="20"/>
-      <c r="D372" s="20"/>
+      <c r="B372" s="16"/>
+      <c r="C372" s="16"/>
+      <c r="D372" s="16"/>
     </row>
     <row r="373" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>37</v>
       </c>
       <c r="O373" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R373" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S373">
         <v>3</v>
@@ -8059,10 +8062,10 @@
         <v>37</v>
       </c>
       <c r="O374" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R374" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S374">
         <v>3</v>
@@ -8073,10 +8076,10 @@
         <v>37</v>
       </c>
       <c r="O375" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R375" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S375">
         <v>3</v>
@@ -8087,10 +8090,10 @@
         <v>37</v>
       </c>
       <c r="O376" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R376" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S376">
         <v>7</v>
@@ -8101,10 +8104,10 @@
         <v>37</v>
       </c>
       <c r="O377" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R377" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S377">
         <v>-3</v>
@@ -8115,10 +8118,10 @@
         <v>37</v>
       </c>
       <c r="O378" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R378" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S378">
         <v>-8</v>
@@ -8129,17 +8132,17 @@
         <v>67</v>
       </c>
       <c r="O379" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R379" t="s">
-        <v>183</v>
-      </c>
-      <c r="S379" s="23">
+        <v>182</v>
+      </c>
+      <c r="S379" s="19">
         <f>S373</f>
         <v>3</v>
       </c>
       <c r="U379" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="380" spans="1:21" x14ac:dyDescent="0.25">
@@ -8147,12 +8150,12 @@
         <v>67</v>
       </c>
       <c r="O380" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R380" t="s">
-        <v>183</v>
-      </c>
-      <c r="S380" s="23">
+        <v>182</v>
+      </c>
+      <c r="S380" s="19">
         <f t="shared" ref="S380:S384" si="15">S374</f>
         <v>3</v>
       </c>
@@ -8162,12 +8165,12 @@
         <v>67</v>
       </c>
       <c r="O381" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R381" t="s">
-        <v>183</v>
-      </c>
-      <c r="S381" s="23">
+        <v>182</v>
+      </c>
+      <c r="S381" s="19">
         <f t="shared" si="15"/>
         <v>3</v>
       </c>
@@ -8177,12 +8180,12 @@
         <v>67</v>
       </c>
       <c r="O382" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R382" t="s">
-        <v>184</v>
-      </c>
-      <c r="S382" s="23">
+        <v>183</v>
+      </c>
+      <c r="S382" s="19">
         <f t="shared" si="15"/>
         <v>7</v>
       </c>
@@ -8192,12 +8195,12 @@
         <v>67</v>
       </c>
       <c r="O383" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R383" t="s">
-        <v>184</v>
-      </c>
-      <c r="S383" s="23">
+        <v>183</v>
+      </c>
+      <c r="S383" s="19">
         <f t="shared" si="15"/>
         <v>-3</v>
       </c>
@@ -8207,33 +8210,33 @@
         <v>67</v>
       </c>
       <c r="O384" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R384" t="s">
-        <v>184</v>
-      </c>
-      <c r="S384" s="23">
+        <v>183</v>
+      </c>
+      <c r="S384" s="19">
         <f t="shared" si="15"/>
         <v>-8</v>
       </c>
     </row>
     <row r="386" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A386" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="B386" s="20"/>
-      <c r="C386" s="20"/>
-      <c r="D386" s="20"/>
+      <c r="A386" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B386" s="16"/>
+      <c r="C386" s="16"/>
+      <c r="D386" s="16"/>
     </row>
     <row r="387" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>39</v>
       </c>
       <c r="O387" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R387" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S387">
         <v>3</v>
@@ -8244,10 +8247,10 @@
         <v>39</v>
       </c>
       <c r="O388" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R388" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S388">
         <v>3</v>
@@ -8258,10 +8261,10 @@
         <v>39</v>
       </c>
       <c r="O389" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R389" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S389">
         <v>3</v>
@@ -8272,10 +8275,10 @@
         <v>39</v>
       </c>
       <c r="O390" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R390" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S390">
         <v>3</v>
@@ -8286,10 +8289,10 @@
         <v>39</v>
       </c>
       <c r="O391" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R391" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S391">
         <v>3</v>
@@ -8300,10 +8303,10 @@
         <v>39</v>
       </c>
       <c r="O392" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R392" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S392">
         <v>3</v>
@@ -8314,10 +8317,10 @@
         <v>39</v>
       </c>
       <c r="O393" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R393" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S393">
         <v>5</v>
@@ -8328,10 +8331,10 @@
         <v>39</v>
       </c>
       <c r="O394" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R394" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S394">
         <v>0</v>
@@ -8342,10 +8345,10 @@
         <v>39</v>
       </c>
       <c r="O395" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R395" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S395">
         <v>-5</v>
@@ -8356,10 +8359,10 @@
         <v>39</v>
       </c>
       <c r="O396" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R396" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S396">
         <v>-10</v>
@@ -8370,10 +8373,10 @@
         <v>39</v>
       </c>
       <c r="O397" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R397" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S397">
         <v>-15</v>
@@ -8384,32 +8387,32 @@
         <v>39</v>
       </c>
       <c r="O398" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R398" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S398">
         <v>-20</v>
       </c>
     </row>
     <row r="400" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A400" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="B400" s="20"/>
-      <c r="C400" s="20"/>
-      <c r="D400" s="20"/>
+      <c r="A400" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B400" s="16"/>
+      <c r="C400" s="16"/>
+      <c r="D400" s="16"/>
     </row>
     <row r="401" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>33</v>
       </c>
       <c r="O401" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R401" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S401">
         <v>0.5</v>
@@ -8420,10 +8423,10 @@
         <v>33</v>
       </c>
       <c r="O402" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R402" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S402">
         <v>0.5</v>
@@ -8434,10 +8437,10 @@
         <v>33</v>
       </c>
       <c r="O403" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R403" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S403">
         <v>0.5</v>
@@ -8448,10 +8451,10 @@
         <v>33</v>
       </c>
       <c r="O404" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R404" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S404">
         <v>0.5</v>
@@ -8462,10 +8465,10 @@
         <v>33</v>
       </c>
       <c r="O405" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R405" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S405">
         <v>0.5</v>
@@ -8476,10 +8479,10 @@
         <v>33</v>
       </c>
       <c r="O406" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R406" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S406">
         <v>0.5</v>
@@ -8490,10 +8493,10 @@
         <v>33</v>
       </c>
       <c r="O407" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R407" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S407">
         <v>55</v>
@@ -8504,10 +8507,10 @@
         <v>33</v>
       </c>
       <c r="O408" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R408" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S408">
         <v>35</v>
@@ -8518,10 +8521,10 @@
         <v>33</v>
       </c>
       <c r="O409" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R409" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S409">
         <v>25</v>
@@ -8532,10 +8535,10 @@
         <v>33</v>
       </c>
       <c r="O410" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R410" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S410">
         <v>15</v>
@@ -8546,10 +8549,10 @@
         <v>33</v>
       </c>
       <c r="O411" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R411" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S411">
         <v>0</v>
@@ -8560,10 +8563,10 @@
         <v>33</v>
       </c>
       <c r="O412" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R412" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S412">
         <v>-5</v>
@@ -8574,12 +8577,12 @@
         <v>34</v>
       </c>
       <c r="O413" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R413" t="s">
-        <v>183</v>
-      </c>
-      <c r="S413" s="19">
+        <v>182</v>
+      </c>
+      <c r="S413" s="15">
         <f>S401</f>
         <v>0.5</v>
       </c>
@@ -8589,12 +8592,12 @@
         <v>34</v>
       </c>
       <c r="O414" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R414" t="s">
-        <v>183</v>
-      </c>
-      <c r="S414" s="19">
+        <v>182</v>
+      </c>
+      <c r="S414" s="15">
         <f t="shared" ref="S414:S424" si="16">S402</f>
         <v>0.5</v>
       </c>
@@ -8604,12 +8607,12 @@
         <v>34</v>
       </c>
       <c r="O415" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R415" t="s">
-        <v>183</v>
-      </c>
-      <c r="S415" s="19">
+        <v>182</v>
+      </c>
+      <c r="S415" s="15">
         <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
@@ -8619,12 +8622,12 @@
         <v>34</v>
       </c>
       <c r="O416" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R416" t="s">
-        <v>183</v>
-      </c>
-      <c r="S416" s="19">
+        <v>182</v>
+      </c>
+      <c r="S416" s="15">
         <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
@@ -8634,12 +8637,12 @@
         <v>34</v>
       </c>
       <c r="O417" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R417" t="s">
-        <v>183</v>
-      </c>
-      <c r="S417" s="19">
+        <v>182</v>
+      </c>
+      <c r="S417" s="15">
         <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
@@ -8649,12 +8652,12 @@
         <v>34</v>
       </c>
       <c r="O418" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R418" t="s">
-        <v>183</v>
-      </c>
-      <c r="S418" s="19">
+        <v>182</v>
+      </c>
+      <c r="S418" s="15">
         <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
@@ -8664,12 +8667,12 @@
         <v>34</v>
       </c>
       <c r="O419" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R419" t="s">
-        <v>184</v>
-      </c>
-      <c r="S419" s="19">
+        <v>183</v>
+      </c>
+      <c r="S419" s="15">
         <f t="shared" si="16"/>
         <v>55</v>
       </c>
@@ -8679,12 +8682,12 @@
         <v>34</v>
       </c>
       <c r="O420" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R420" t="s">
-        <v>184</v>
-      </c>
-      <c r="S420" s="19">
+        <v>183</v>
+      </c>
+      <c r="S420" s="15">
         <f t="shared" si="16"/>
         <v>35</v>
       </c>
@@ -8694,12 +8697,12 @@
         <v>34</v>
       </c>
       <c r="O421" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R421" t="s">
-        <v>184</v>
-      </c>
-      <c r="S421" s="19">
+        <v>183</v>
+      </c>
+      <c r="S421" s="15">
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
@@ -8709,12 +8712,12 @@
         <v>34</v>
       </c>
       <c r="O422" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R422" t="s">
-        <v>184</v>
-      </c>
-      <c r="S422" s="19">
+        <v>183</v>
+      </c>
+      <c r="S422" s="15">
         <f t="shared" si="16"/>
         <v>15</v>
       </c>
@@ -8724,12 +8727,12 @@
         <v>34</v>
       </c>
       <c r="O423" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R423" t="s">
-        <v>184</v>
-      </c>
-      <c r="S423" s="19">
+        <v>183</v>
+      </c>
+      <c r="S423" s="15">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -8739,33 +8742,33 @@
         <v>34</v>
       </c>
       <c r="O424" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R424" t="s">
-        <v>184</v>
-      </c>
-      <c r="S424" s="19">
+        <v>183</v>
+      </c>
+      <c r="S424" s="15">
         <f t="shared" si="16"/>
         <v>-5</v>
       </c>
     </row>
     <row r="426" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A426" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="B426" s="20"/>
-      <c r="C426" s="20"/>
-      <c r="D426" s="20"/>
+      <c r="A426" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B426" s="16"/>
+      <c r="C426" s="16"/>
+      <c r="D426" s="16"/>
     </row>
     <row r="427" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>27</v>
       </c>
       <c r="O427" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R427" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S427">
         <v>20</v>
@@ -8776,10 +8779,10 @@
         <v>27</v>
       </c>
       <c r="O428" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R428" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S428">
         <v>15</v>
@@ -8790,10 +8793,10 @@
         <v>27</v>
       </c>
       <c r="O429" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R429" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S429">
         <v>10</v>
@@ -8801,48 +8804,48 @@
     </row>
     <row r="430" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O430" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R430" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="S430" s="19">
+        <v>183</v>
+      </c>
+      <c r="S430" s="15">
         <f>S427</f>
         <v>20</v>
       </c>
       <c r="U430" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="431" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O431" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R431" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="S431" s="19">
+        <v>183</v>
+      </c>
+      <c r="S431" s="15">
         <f t="shared" ref="S431:S432" si="17">S428</f>
         <v>15</v>
       </c>
     </row>
     <row r="432" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O432" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R432" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="S432" s="19">
+        <v>183</v>
+      </c>
+      <c r="S432" s="15">
         <f t="shared" si="17"/>
         <v>10</v>
       </c>
@@ -8852,12 +8855,12 @@
         <v>29</v>
       </c>
       <c r="O433" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R433" t="s">
-        <v>184</v>
-      </c>
-      <c r="S433" s="19">
+        <v>183</v>
+      </c>
+      <c r="S433" s="15">
         <f>S427</f>
         <v>20</v>
       </c>
@@ -8867,12 +8870,12 @@
         <v>29</v>
       </c>
       <c r="O434" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R434" t="s">
-        <v>184</v>
-      </c>
-      <c r="S434" s="19">
+        <v>183</v>
+      </c>
+      <c r="S434" s="15">
         <f t="shared" ref="S434:S435" si="18">S428</f>
         <v>15</v>
       </c>
@@ -8882,12 +8885,12 @@
         <v>29</v>
       </c>
       <c r="O435" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R435" t="s">
-        <v>184</v>
-      </c>
-      <c r="S435" s="19">
+        <v>183</v>
+      </c>
+      <c r="S435" s="15">
         <f t="shared" si="18"/>
         <v>10</v>
       </c>
@@ -8897,10 +8900,10 @@
         <v>35</v>
       </c>
       <c r="O436" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R436" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S436">
         <v>60</v>
@@ -8911,10 +8914,10 @@
         <v>35</v>
       </c>
       <c r="O437" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R437" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S437">
         <v>45</v>
@@ -8925,10 +8928,10 @@
         <v>35</v>
       </c>
       <c r="O438" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R438" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S438">
         <v>35</v>
@@ -8939,10 +8942,10 @@
         <v>35</v>
       </c>
       <c r="O439" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R439" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S439">
         <v>25</v>
@@ -8953,10 +8956,10 @@
         <v>35</v>
       </c>
       <c r="O440" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R440" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S440">
         <v>10</v>
@@ -8967,10 +8970,10 @@
         <v>38</v>
       </c>
       <c r="O441" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R441" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S441">
         <v>15</v>
@@ -8981,10 +8984,10 @@
         <v>38</v>
       </c>
       <c r="O442" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R442" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S442">
         <v>5</v>
@@ -8998,19 +9001,19 @@
       <c r="C443" s="6"/>
       <c r="D443" s="6"/>
       <c r="O443" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R443" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S443">
         <v>25</v>
       </c>
       <c r="U443" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V443" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="444" spans="1:22" x14ac:dyDescent="0.25">
@@ -9021,10 +9024,10 @@
       <c r="C444" s="6"/>
       <c r="D444" s="6"/>
       <c r="O444" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R444" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S444">
         <v>25</v>
@@ -9038,29 +9041,29 @@
       <c r="C445" s="6"/>
       <c r="D445" s="6"/>
       <c r="O445" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R445" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S445">
         <v>25</v>
       </c>
     </row>
     <row r="447" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A447" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="B447" s="20"/>
-      <c r="C447" s="20"/>
-      <c r="D447" s="20"/>
+      <c r="A447" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B447" s="16"/>
+      <c r="C447" s="16"/>
+      <c r="D447" s="16"/>
     </row>
     <row r="448" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>45</v>
       </c>
       <c r="R448" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S448">
         <v>0.46200000000000002</v>
@@ -9071,7 +9074,7 @@
         <v>45</v>
       </c>
       <c r="R449" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S449">
         <v>13.85</v>
@@ -9085,14 +9088,14 @@
       <c r="C450" s="6"/>
       <c r="D450" s="6"/>
       <c r="R450" t="s">
-        <v>183</v>
-      </c>
-      <c r="S450" s="19">
+        <v>182</v>
+      </c>
+      <c r="S450" s="15">
         <f>S448</f>
         <v>0.46200000000000002</v>
       </c>
       <c r="U450" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="451" spans="1:21" x14ac:dyDescent="0.25">
@@ -9103,9 +9106,9 @@
       <c r="C451" s="6"/>
       <c r="D451" s="6"/>
       <c r="R451" t="s">
-        <v>184</v>
-      </c>
-      <c r="S451" s="19">
+        <v>183</v>
+      </c>
+      <c r="S451" s="15">
         <f>S449</f>
         <v>13.85</v>
       </c>
@@ -9115,7 +9118,7 @@
         <v>44</v>
       </c>
       <c r="R452" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S452">
         <v>2.5</v>
@@ -9126,7 +9129,7 @@
         <v>44</v>
       </c>
       <c r="R453" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S453">
         <v>-45</v>
@@ -9137,13 +9140,13 @@
         <v>47</v>
       </c>
       <c r="R454" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S454">
         <v>2.6669999999999998</v>
       </c>
       <c r="U454" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="455" spans="1:21" x14ac:dyDescent="0.25">
@@ -9151,7 +9154,7 @@
         <v>47</v>
       </c>
       <c r="R455" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S455">
         <v>-33.33</v>
@@ -9165,14 +9168,14 @@
       <c r="C456" s="6"/>
       <c r="D456" s="6"/>
       <c r="R456" t="s">
-        <v>183</v>
-      </c>
-      <c r="S456" s="19">
+        <v>182</v>
+      </c>
+      <c r="S456" s="15">
         <f>S454</f>
         <v>2.6669999999999998</v>
       </c>
       <c r="U456" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="457" spans="1:21" x14ac:dyDescent="0.25">
@@ -9183,9 +9186,9 @@
       <c r="C457" s="6"/>
       <c r="D457" s="6"/>
       <c r="R457" t="s">
-        <v>184</v>
-      </c>
-      <c r="S457" s="19">
+        <v>183</v>
+      </c>
+      <c r="S457" s="15">
         <f>S455</f>
         <v>-33.33</v>
       </c>
@@ -9196,14 +9199,14 @@
       </c>
       <c r="B458" s="4"/>
       <c r="R458" t="s">
-        <v>183</v>
-      </c>
-      <c r="S458" s="19">
+        <v>182</v>
+      </c>
+      <c r="S458" s="15">
         <f>S456</f>
         <v>2.6669999999999998</v>
       </c>
       <c r="U458" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="459" spans="1:21" x14ac:dyDescent="0.25">
@@ -9212,9 +9215,9 @@
       </c>
       <c r="B459" s="4"/>
       <c r="R459" t="s">
-        <v>184</v>
-      </c>
-      <c r="S459" s="19">
+        <v>183</v>
+      </c>
+      <c r="S459" s="15">
         <f>S457</f>
         <v>-33.33</v>
       </c>
@@ -9224,7 +9227,7 @@
         <v>48</v>
       </c>
       <c r="R460" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S460">
         <v>0.5</v>
@@ -9235,7 +9238,7 @@
         <v>48</v>
       </c>
       <c r="R461" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S461">
         <v>15</v>
@@ -9246,7 +9249,7 @@
         <v>49</v>
       </c>
       <c r="R462" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S462">
         <v>0.66700000000000004</v>
@@ -9257,7 +9260,7 @@
         <v>49</v>
       </c>
       <c r="R463" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S463">
         <v>-3.33</v>
@@ -9268,9 +9271,9 @@
         <v>50</v>
       </c>
       <c r="R464" t="s">
-        <v>183</v>
-      </c>
-      <c r="S464" s="19">
+        <v>182</v>
+      </c>
+      <c r="S464" s="15">
         <f>S462</f>
         <v>0.66700000000000004</v>
       </c>
@@ -9280,9 +9283,9 @@
         <v>50</v>
       </c>
       <c r="R465" t="s">
-        <v>184</v>
-      </c>
-      <c r="S465" s="19">
+        <v>183</v>
+      </c>
+      <c r="S465" s="15">
         <f>S463</f>
         <v>-3.33</v>
       </c>
@@ -9292,13 +9295,13 @@
         <v>66</v>
       </c>
       <c r="R467" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S467">
         <v>0</v>
       </c>
       <c r="U467" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="468" spans="1:22" x14ac:dyDescent="0.25">
@@ -9306,7 +9309,7 @@
         <v>69</v>
       </c>
       <c r="R468" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S468">
         <v>0</v>
@@ -9317,7 +9320,7 @@
         <v>70</v>
       </c>
       <c r="R469" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S469">
         <v>0</v>
@@ -9328,7 +9331,7 @@
         <v>42</v>
       </c>
       <c r="R470" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S470">
         <v>0</v>
@@ -9339,7 +9342,7 @@
         <v>43</v>
       </c>
       <c r="R471" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S471">
         <v>0</v>
@@ -9361,13 +9364,13 @@
       <c r="C474" s="6"/>
       <c r="D474" s="6"/>
       <c r="R474" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S474">
         <v>10</v>
       </c>
       <c r="V474" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="475" spans="1:22" x14ac:dyDescent="0.25">
@@ -9378,16 +9381,16 @@
       <c r="C475" s="6"/>
       <c r="D475" s="6"/>
       <c r="R475" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S475">
         <v>15</v>
       </c>
       <c r="U475" t="s">
+        <v>242</v>
+      </c>
+      <c r="V475" t="s">
         <v>243</v>
-      </c>
-      <c r="V475" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="476" spans="1:22" x14ac:dyDescent="0.25">
@@ -9422,13 +9425,13 @@
       <c r="C479" s="6"/>
       <c r="D479" s="6"/>
       <c r="R479" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S479">
         <v>15</v>
       </c>
-      <c r="V479" s="24" t="s">
-        <v>272</v>
+      <c r="V479" s="20" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="480" spans="1:22" x14ac:dyDescent="0.25">
@@ -9439,14 +9442,14 @@
       <c r="C480" s="6"/>
       <c r="D480" s="6"/>
       <c r="R480" t="s">
-        <v>184</v>
-      </c>
-      <c r="S480" s="23">
+        <v>183</v>
+      </c>
+      <c r="S480" s="19">
         <f>S479</f>
         <v>15</v>
       </c>
       <c r="U480" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="481" spans="1:22" x14ac:dyDescent="0.25">
@@ -9457,14 +9460,14 @@
       <c r="C481" s="6"/>
       <c r="D481" s="6"/>
       <c r="R481" t="s">
-        <v>184</v>
-      </c>
-      <c r="S481" s="23">
+        <v>183</v>
+      </c>
+      <c r="S481" s="19">
         <f>S479</f>
         <v>15</v>
       </c>
       <c r="U481" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="482" spans="1:22" x14ac:dyDescent="0.25">
@@ -9481,13 +9484,13 @@
       <c r="C483" s="6"/>
       <c r="D483" s="6"/>
       <c r="R483" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S483">
         <v>0.6</v>
       </c>
       <c r="V483" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="484" spans="1:22" x14ac:dyDescent="0.25">
@@ -9498,13 +9501,13 @@
       <c r="C484" s="6"/>
       <c r="D484" s="6"/>
       <c r="R484" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S484" s="4">
         <v>1.6</v>
       </c>
       <c r="V484" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="485" spans="1:22" x14ac:dyDescent="0.25">
@@ -9515,14 +9518,14 @@
       <c r="C485" s="6"/>
       <c r="D485" s="6"/>
       <c r="R485" t="s">
-        <v>183</v>
-      </c>
-      <c r="S485" s="23">
+        <v>182</v>
+      </c>
+      <c r="S485" s="19">
         <f>AVERAGE(S483:S484)</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="U485" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="486" spans="1:22" x14ac:dyDescent="0.25">
@@ -9533,9 +9536,9 @@
       <c r="C486" s="6"/>
       <c r="D486" s="6"/>
       <c r="R486" t="s">
-        <v>183</v>
-      </c>
-      <c r="S486" s="23">
+        <v>182</v>
+      </c>
+      <c r="S486" s="19">
         <f>AVERAGE(S483:S484)</f>
         <v>1.1000000000000001</v>
       </c>
@@ -9548,9 +9551,9 @@
       <c r="C487" s="6"/>
       <c r="D487" s="6"/>
       <c r="R487" t="s">
-        <v>183</v>
-      </c>
-      <c r="S487" s="23">
+        <v>182</v>
+      </c>
+      <c r="S487" s="19">
         <f>AVERAGE(S483:S484)</f>
         <v>1.1000000000000001</v>
       </c>
@@ -9563,9 +9566,9 @@
       <c r="C488" s="6"/>
       <c r="D488" s="6"/>
       <c r="R488" t="s">
-        <v>183</v>
-      </c>
-      <c r="S488" s="23">
+        <v>182</v>
+      </c>
+      <c r="S488" s="19">
         <f>AVERAGE(S483:S484)</f>
         <v>1.1000000000000001</v>
       </c>
@@ -9578,16 +9581,16 @@
       <c r="C489" s="6"/>
       <c r="D489" s="6"/>
       <c r="R489" t="s">
-        <v>183</v>
-      </c>
-      <c r="S489" s="23">
+        <v>182</v>
+      </c>
+      <c r="S489" s="19">
         <f>AVERAGE(S483:S484)</f>
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="491" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
@@ -9612,34 +9615,34 @@
       <c r="V491" s="3"/>
     </row>
     <row r="492" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A492" s="17" t="s">
+      <c r="A492" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B492" s="14"/>
+      <c r="C492" s="14"/>
+      <c r="D492" s="14"/>
+    </row>
+    <row r="493" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A493" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="B492" s="17"/>
-      <c r="C492" s="17"/>
-      <c r="D492" s="17"/>
-    </row>
-    <row r="493" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A493" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="B493" s="17"/>
-      <c r="C493" s="17"/>
-      <c r="D493" s="17"/>
+      <c r="B493" s="14"/>
+      <c r="C493" s="14"/>
+      <c r="D493" s="14"/>
     </row>
     <row r="494" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A494" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="B494" s="17"/>
-      <c r="C494" s="17"/>
-      <c r="D494" s="17"/>
+      <c r="A494" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B494" s="14"/>
+      <c r="C494" s="14"/>
+      <c r="D494" s="14"/>
     </row>
     <row r="495" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R495" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="S495" s="22">
+        <v>214</v>
+      </c>
+      <c r="S495" s="18">
         <v>1</v>
       </c>
       <c r="T495" s="5"/>
@@ -9649,7 +9652,7 @@
     </row>
     <row r="496" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C496" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D496" s="4"/>
       <c r="E496" s="4"/>
@@ -9666,20 +9669,20 @@
       <c r="P496" s="4"/>
       <c r="Q496" s="4"/>
       <c r="R496" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="S496" s="21">
+        <v>214</v>
+      </c>
+      <c r="S496" s="17">
         <v>1.4</v>
       </c>
       <c r="T496" s="4"/>
       <c r="U496" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V496" s="4"/>
     </row>
     <row r="497" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C497" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D497" s="4"/>
       <c r="E497" s="4"/>
@@ -9696,20 +9699,20 @@
       <c r="P497" s="4"/>
       <c r="Q497" s="4"/>
       <c r="R497" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="S497" s="21">
+        <v>214</v>
+      </c>
+      <c r="S497" s="17">
         <v>1.4</v>
       </c>
       <c r="T497" s="4"/>
       <c r="U497" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V497" s="4"/>
     </row>
     <row r="498" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C498" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E498" s="4"/>
       <c r="F498" s="4"/>
@@ -9725,14 +9728,14 @@
       <c r="P498" s="4"/>
       <c r="Q498" s="4"/>
       <c r="R498" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="S498" s="21">
+        <v>214</v>
+      </c>
+      <c r="S498" s="17">
         <v>1.2</v>
       </c>
       <c r="T498" s="4"/>
       <c r="U498" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V498" s="4"/>
     </row>
@@ -9754,14 +9757,14 @@
       <c r="P499" s="4"/>
       <c r="Q499" s="4"/>
       <c r="R499" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="S499" s="21">
+        <v>214</v>
+      </c>
+      <c r="S499" s="17">
         <v>1.25</v>
       </c>
       <c r="T499" s="4"/>
       <c r="U499" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V499" s="4"/>
     </row>
@@ -9772,34 +9775,34 @@
       <c r="D500" s="6"/>
     </row>
     <row r="501" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A501" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="B501" s="14"/>
-      <c r="C501" s="14"/>
-      <c r="D501" s="14"/>
-      <c r="E501" s="13"/>
-      <c r="F501" s="13"/>
-      <c r="G501" s="13"/>
-      <c r="H501" s="13"/>
-      <c r="I501" s="13"/>
-      <c r="J501" s="13"/>
-      <c r="K501" s="13"/>
-      <c r="L501" s="13"/>
-      <c r="M501" s="13"/>
-      <c r="N501" s="13"/>
-      <c r="O501" s="13"/>
-      <c r="P501" s="13"/>
-      <c r="Q501" s="13"/>
-      <c r="R501" s="13"/>
-      <c r="S501" s="13"/>
-      <c r="T501" s="13"/>
-      <c r="U501" s="13"/>
-      <c r="V501" s="13"/>
+      <c r="A501" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B501" s="12"/>
+      <c r="C501" s="12"/>
+      <c r="D501" s="12"/>
+      <c r="E501" s="11"/>
+      <c r="F501" s="11"/>
+      <c r="G501" s="11"/>
+      <c r="H501" s="11"/>
+      <c r="I501" s="11"/>
+      <c r="J501" s="11"/>
+      <c r="K501" s="11"/>
+      <c r="L501" s="11"/>
+      <c r="M501" s="11"/>
+      <c r="N501" s="11"/>
+      <c r="O501" s="11"/>
+      <c r="P501" s="11"/>
+      <c r="Q501" s="11"/>
+      <c r="R501" s="11"/>
+      <c r="S501" s="11"/>
+      <c r="T501" s="11"/>
+      <c r="U501" s="11"/>
+      <c r="V501" s="11"/>
     </row>
     <row r="502" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
@@ -9824,30 +9827,30 @@
       <c r="V502" s="3"/>
     </row>
     <row r="503" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A503" s="18" t="s">
+      <c r="A503" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B503" s="14"/>
+      <c r="C503" s="14"/>
+      <c r="D503" s="14"/>
+    </row>
+    <row r="504" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A504" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="B503" s="18"/>
-      <c r="C503" s="18"/>
-      <c r="D503" s="18"/>
-    </row>
-    <row r="504" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A504" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="B504" s="18"/>
-      <c r="C504" s="18"/>
-      <c r="D504" s="18"/>
+      <c r="B504" s="14"/>
+      <c r="C504" s="14"/>
+      <c r="D504" s="14"/>
     </row>
     <row r="505" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R505" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S505" s="5">
         <v>0</v>
       </c>
       <c r="T505" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U505" s="5" t="s">
         <v>142</v>
@@ -9855,13 +9858,13 @@
     </row>
     <row r="506" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R506" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S506" s="5">
         <v>0</v>
       </c>
       <c r="T506" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="U506" s="5" t="s">
         <v>142</v>
@@ -9874,12 +9877,12 @@
       <c r="U507" s="5"/>
     </row>
     <row r="508" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A508" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="B508" s="20"/>
-      <c r="C508" s="20"/>
-      <c r="D508" s="20"/>
+      <c r="A508" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B508" s="16"/>
+      <c r="C508" s="16"/>
+      <c r="D508" s="16"/>
       <c r="R508" s="5"/>
       <c r="S508" s="5"/>
       <c r="T508" s="5"/>
@@ -9890,10 +9893,10 @@
         <v>6</v>
       </c>
       <c r="P509" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R509" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S509">
         <v>5</v>
@@ -9904,10 +9907,10 @@
         <v>6</v>
       </c>
       <c r="P510" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R510" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S510" s="4">
         <v>5</v>
@@ -9918,10 +9921,10 @@
         <v>6</v>
       </c>
       <c r="P511" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R511" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S511" s="4">
         <v>5</v>
@@ -9932,10 +9935,10 @@
         <v>6</v>
       </c>
       <c r="P512" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R512" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S512" s="4">
         <v>15</v>
@@ -9946,10 +9949,10 @@
         <v>6</v>
       </c>
       <c r="P513" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R513" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S513" s="4">
         <v>5</v>
@@ -9960,10 +9963,10 @@
         <v>6</v>
       </c>
       <c r="P514" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R514" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S514" s="4">
         <v>-15</v>
@@ -9974,12 +9977,12 @@
         <v>24</v>
       </c>
       <c r="P515" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R515" t="s">
-        <v>201</v>
-      </c>
-      <c r="S515" s="19">
+        <v>200</v>
+      </c>
+      <c r="S515" s="15">
         <f t="shared" ref="S515:S520" si="19">S509</f>
         <v>5</v>
       </c>
@@ -9989,12 +9992,12 @@
         <v>24</v>
       </c>
       <c r="P516" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R516" t="s">
-        <v>201</v>
-      </c>
-      <c r="S516" s="19">
+        <v>200</v>
+      </c>
+      <c r="S516" s="15">
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
@@ -10004,12 +10007,12 @@
         <v>24</v>
       </c>
       <c r="P517" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R517" t="s">
-        <v>201</v>
-      </c>
-      <c r="S517" s="19">
+        <v>200</v>
+      </c>
+      <c r="S517" s="15">
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
@@ -10019,12 +10022,12 @@
         <v>24</v>
       </c>
       <c r="P518" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R518" t="s">
-        <v>202</v>
-      </c>
-      <c r="S518" s="19">
+        <v>201</v>
+      </c>
+      <c r="S518" s="15">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
@@ -10034,12 +10037,12 @@
         <v>24</v>
       </c>
       <c r="P519" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R519" t="s">
-        <v>202</v>
-      </c>
-      <c r="S519" s="19">
+        <v>201</v>
+      </c>
+      <c r="S519" s="15">
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
@@ -10049,12 +10052,12 @@
         <v>24</v>
       </c>
       <c r="P520" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R520" t="s">
-        <v>202</v>
-      </c>
-      <c r="S520" s="19">
+        <v>201</v>
+      </c>
+      <c r="S520" s="15">
         <f t="shared" si="19"/>
         <v>-15</v>
       </c>
@@ -10064,12 +10067,12 @@
         <v>20</v>
       </c>
       <c r="P521" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R521" t="s">
-        <v>201</v>
-      </c>
-      <c r="S521" s="19">
+        <v>200</v>
+      </c>
+      <c r="S521" s="15">
         <f t="shared" ref="S521:S526" si="20">S509</f>
         <v>5</v>
       </c>
@@ -10079,12 +10082,12 @@
         <v>20</v>
       </c>
       <c r="P522" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R522" t="s">
-        <v>201</v>
-      </c>
-      <c r="S522" s="19">
+        <v>200</v>
+      </c>
+      <c r="S522" s="15">
         <f t="shared" si="20"/>
         <v>5</v>
       </c>
@@ -10094,12 +10097,12 @@
         <v>20</v>
       </c>
       <c r="P523" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R523" t="s">
-        <v>201</v>
-      </c>
-      <c r="S523" s="19">
+        <v>200</v>
+      </c>
+      <c r="S523" s="15">
         <f t="shared" si="20"/>
         <v>5</v>
       </c>
@@ -10109,12 +10112,12 @@
         <v>20</v>
       </c>
       <c r="P524" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R524" t="s">
-        <v>202</v>
-      </c>
-      <c r="S524" s="19">
+        <v>201</v>
+      </c>
+      <c r="S524" s="15">
         <f t="shared" si="20"/>
         <v>15</v>
       </c>
@@ -10124,12 +10127,12 @@
         <v>20</v>
       </c>
       <c r="P525" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R525" t="s">
-        <v>202</v>
-      </c>
-      <c r="S525" s="19">
+        <v>201</v>
+      </c>
+      <c r="S525" s="15">
         <f t="shared" si="20"/>
         <v>5</v>
       </c>
@@ -10139,12 +10142,12 @@
         <v>20</v>
       </c>
       <c r="P526" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R526" t="s">
-        <v>202</v>
-      </c>
-      <c r="S526" s="19">
+        <v>201</v>
+      </c>
+      <c r="S526" s="15">
         <f t="shared" si="20"/>
         <v>-15</v>
       </c>
@@ -10154,12 +10157,12 @@
         <v>22</v>
       </c>
       <c r="P527" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R527" t="s">
-        <v>201</v>
-      </c>
-      <c r="S527" s="19">
+        <v>200</v>
+      </c>
+      <c r="S527" s="15">
         <f t="shared" ref="S527:S532" si="21">S509</f>
         <v>5</v>
       </c>
@@ -10169,12 +10172,12 @@
         <v>22</v>
       </c>
       <c r="P528" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R528" t="s">
-        <v>201</v>
-      </c>
-      <c r="S528" s="19">
+        <v>200</v>
+      </c>
+      <c r="S528" s="15">
         <f t="shared" si="21"/>
         <v>5</v>
       </c>
@@ -10184,12 +10187,12 @@
         <v>22</v>
       </c>
       <c r="P529" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R529" t="s">
-        <v>201</v>
-      </c>
-      <c r="S529" s="19">
+        <v>200</v>
+      </c>
+      <c r="S529" s="15">
         <f t="shared" si="21"/>
         <v>5</v>
       </c>
@@ -10199,12 +10202,12 @@
         <v>22</v>
       </c>
       <c r="P530" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R530" t="s">
-        <v>202</v>
-      </c>
-      <c r="S530" s="19">
+        <v>201</v>
+      </c>
+      <c r="S530" s="15">
         <f t="shared" si="21"/>
         <v>15</v>
       </c>
@@ -10214,12 +10217,12 @@
         <v>22</v>
       </c>
       <c r="P531" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R531" t="s">
-        <v>202</v>
-      </c>
-      <c r="S531" s="19">
+        <v>201</v>
+      </c>
+      <c r="S531" s="15">
         <f t="shared" si="21"/>
         <v>5</v>
       </c>
@@ -10229,33 +10232,33 @@
         <v>22</v>
       </c>
       <c r="P532" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R532" t="s">
-        <v>202</v>
-      </c>
-      <c r="S532" s="19">
+        <v>201</v>
+      </c>
+      <c r="S532" s="15">
         <f t="shared" si="21"/>
         <v>-15</v>
       </c>
     </row>
     <row r="534" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A534" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B534" s="20"/>
-      <c r="C534" s="20"/>
-      <c r="D534" s="20"/>
+      <c r="A534" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B534" s="16"/>
+      <c r="C534" s="16"/>
+      <c r="D534" s="16"/>
     </row>
     <row r="535" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>13</v>
       </c>
       <c r="P535" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R535" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S535">
         <v>5</v>
@@ -10266,10 +10269,10 @@
         <v>13</v>
       </c>
       <c r="P536" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R536" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S536">
         <v>5</v>
@@ -10280,10 +10283,10 @@
         <v>13</v>
       </c>
       <c r="P537" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R537" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S537">
         <v>5</v>
@@ -10294,10 +10297,10 @@
         <v>13</v>
       </c>
       <c r="P538" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R538" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S538">
         <v>15</v>
@@ -10308,10 +10311,10 @@
         <v>13</v>
       </c>
       <c r="P539" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R539" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S539">
         <v>5</v>
@@ -10322,10 +10325,10 @@
         <v>13</v>
       </c>
       <c r="P540" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R540" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S540">
         <v>-15</v>
@@ -10336,12 +10339,12 @@
         <v>14</v>
       </c>
       <c r="P541" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R541" t="s">
-        <v>201</v>
-      </c>
-      <c r="S541" s="19">
+        <v>200</v>
+      </c>
+      <c r="S541" s="15">
         <f t="shared" ref="S541:S546" si="22">S535</f>
         <v>5</v>
       </c>
@@ -10351,12 +10354,12 @@
         <v>14</v>
       </c>
       <c r="P542" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R542" t="s">
-        <v>201</v>
-      </c>
-      <c r="S542" s="19">
+        <v>200</v>
+      </c>
+      <c r="S542" s="15">
         <f t="shared" si="22"/>
         <v>5</v>
       </c>
@@ -10366,12 +10369,12 @@
         <v>14</v>
       </c>
       <c r="P543" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R543" t="s">
-        <v>201</v>
-      </c>
-      <c r="S543" s="19">
+        <v>200</v>
+      </c>
+      <c r="S543" s="15">
         <f t="shared" si="22"/>
         <v>5</v>
       </c>
@@ -10381,12 +10384,12 @@
         <v>14</v>
       </c>
       <c r="P544" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R544" t="s">
-        <v>202</v>
-      </c>
-      <c r="S544" s="19">
+        <v>201</v>
+      </c>
+      <c r="S544" s="15">
         <f t="shared" si="22"/>
         <v>15</v>
       </c>
@@ -10396,12 +10399,12 @@
         <v>14</v>
       </c>
       <c r="P545" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R545" t="s">
-        <v>202</v>
-      </c>
-      <c r="S545" s="19">
+        <v>201</v>
+      </c>
+      <c r="S545" s="15">
         <f t="shared" si="22"/>
         <v>5</v>
       </c>
@@ -10411,12 +10414,12 @@
         <v>14</v>
       </c>
       <c r="P546" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R546" t="s">
-        <v>202</v>
-      </c>
-      <c r="S546" s="19">
+        <v>201</v>
+      </c>
+      <c r="S546" s="15">
         <f t="shared" si="22"/>
         <v>-15</v>
       </c>
@@ -10426,12 +10429,12 @@
         <v>18</v>
       </c>
       <c r="P547" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R547" t="s">
-        <v>201</v>
-      </c>
-      <c r="S547" s="19">
+        <v>200</v>
+      </c>
+      <c r="S547" s="15">
         <f t="shared" ref="S547:S552" si="23">S535</f>
         <v>5</v>
       </c>
@@ -10441,12 +10444,12 @@
         <v>18</v>
       </c>
       <c r="P548" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R548" t="s">
-        <v>201</v>
-      </c>
-      <c r="S548" s="19">
+        <v>200</v>
+      </c>
+      <c r="S548" s="15">
         <f t="shared" si="23"/>
         <v>5</v>
       </c>
@@ -10456,12 +10459,12 @@
         <v>18</v>
       </c>
       <c r="P549" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R549" t="s">
-        <v>201</v>
-      </c>
-      <c r="S549" s="19">
+        <v>200</v>
+      </c>
+      <c r="S549" s="15">
         <f t="shared" si="23"/>
         <v>5</v>
       </c>
@@ -10471,12 +10474,12 @@
         <v>18</v>
       </c>
       <c r="P550" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R550" t="s">
-        <v>202</v>
-      </c>
-      <c r="S550" s="19">
+        <v>201</v>
+      </c>
+      <c r="S550" s="15">
         <f t="shared" si="23"/>
         <v>15</v>
       </c>
@@ -10486,12 +10489,12 @@
         <v>18</v>
       </c>
       <c r="P551" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R551" t="s">
-        <v>202</v>
-      </c>
-      <c r="S551" s="19">
+        <v>201</v>
+      </c>
+      <c r="S551" s="15">
         <f t="shared" si="23"/>
         <v>5</v>
       </c>
@@ -10501,102 +10504,102 @@
         <v>18</v>
       </c>
       <c r="P552" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R552" t="s">
-        <v>202</v>
-      </c>
-      <c r="S552" s="19">
+        <v>201</v>
+      </c>
+      <c r="S552" s="15">
         <f t="shared" si="23"/>
         <v>-15</v>
       </c>
     </row>
     <row r="553" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P553" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R553" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="S553" s="19">
+        <v>200</v>
+      </c>
+      <c r="S553" s="15">
         <f t="shared" ref="S553:S558" si="24">S535</f>
         <v>5</v>
       </c>
     </row>
     <row r="554" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P554" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R554" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="S554" s="19">
+        <v>200</v>
+      </c>
+      <c r="S554" s="15">
         <f t="shared" si="24"/>
         <v>5</v>
       </c>
     </row>
     <row r="555" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A555" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P555" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R555" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="S555" s="19">
+        <v>200</v>
+      </c>
+      <c r="S555" s="15">
         <f t="shared" si="24"/>
         <v>5</v>
       </c>
     </row>
     <row r="556" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A556" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P556" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R556" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="S556" s="19">
+        <v>201</v>
+      </c>
+      <c r="S556" s="15">
         <f t="shared" si="24"/>
         <v>15</v>
       </c>
     </row>
     <row r="557" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A557" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P557" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R557" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="S557" s="19">
+        <v>201</v>
+      </c>
+      <c r="S557" s="15">
         <f t="shared" si="24"/>
         <v>5</v>
       </c>
     </row>
     <row r="558" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P558" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R558" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="S558" s="19">
+        <v>201</v>
+      </c>
+      <c r="S558" s="15">
         <f t="shared" si="24"/>
         <v>-15</v>
       </c>
@@ -10606,12 +10609,12 @@
         <v>21</v>
       </c>
       <c r="P559" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R559" t="s">
-        <v>201</v>
-      </c>
-      <c r="S559" s="19">
+        <v>200</v>
+      </c>
+      <c r="S559" s="15">
         <f t="shared" ref="S559:S564" si="25">S535</f>
         <v>5</v>
       </c>
@@ -10621,12 +10624,12 @@
         <v>21</v>
       </c>
       <c r="P560" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R560" t="s">
-        <v>201</v>
-      </c>
-      <c r="S560" s="19">
+        <v>200</v>
+      </c>
+      <c r="S560" s="15">
         <f t="shared" si="25"/>
         <v>5</v>
       </c>
@@ -10636,12 +10639,12 @@
         <v>21</v>
       </c>
       <c r="P561" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R561" t="s">
-        <v>201</v>
-      </c>
-      <c r="S561" s="19">
+        <v>200</v>
+      </c>
+      <c r="S561" s="15">
         <f t="shared" si="25"/>
         <v>5</v>
       </c>
@@ -10651,12 +10654,12 @@
         <v>21</v>
       </c>
       <c r="P562" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R562" t="s">
-        <v>202</v>
-      </c>
-      <c r="S562" s="19">
+        <v>201</v>
+      </c>
+      <c r="S562" s="15">
         <f t="shared" si="25"/>
         <v>15</v>
       </c>
@@ -10666,12 +10669,12 @@
         <v>21</v>
       </c>
       <c r="P563" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R563" t="s">
-        <v>202</v>
-      </c>
-      <c r="S563" s="19">
+        <v>201</v>
+      </c>
+      <c r="S563" s="15">
         <f t="shared" si="25"/>
         <v>5</v>
       </c>
@@ -10681,12 +10684,12 @@
         <v>21</v>
       </c>
       <c r="P564" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R564" t="s">
-        <v>202</v>
-      </c>
-      <c r="S564" s="19">
+        <v>201</v>
+      </c>
+      <c r="S564" s="15">
         <f t="shared" si="25"/>
         <v>-15</v>
       </c>
@@ -10696,12 +10699,12 @@
         <v>26</v>
       </c>
       <c r="P565" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R565" t="s">
-        <v>201</v>
-      </c>
-      <c r="S565" s="19">
+        <v>200</v>
+      </c>
+      <c r="S565" s="15">
         <f t="shared" ref="S565:S570" si="26">S535</f>
         <v>5</v>
       </c>
@@ -10711,12 +10714,12 @@
         <v>26</v>
       </c>
       <c r="P566" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R566" t="s">
-        <v>201</v>
-      </c>
-      <c r="S566" s="19">
+        <v>200</v>
+      </c>
+      <c r="S566" s="15">
         <f t="shared" si="26"/>
         <v>5</v>
       </c>
@@ -10726,12 +10729,12 @@
         <v>26</v>
       </c>
       <c r="P567" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R567" t="s">
-        <v>201</v>
-      </c>
-      <c r="S567" s="19">
+        <v>200</v>
+      </c>
+      <c r="S567" s="15">
         <f t="shared" si="26"/>
         <v>5</v>
       </c>
@@ -10741,12 +10744,12 @@
         <v>26</v>
       </c>
       <c r="P568" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R568" t="s">
-        <v>202</v>
-      </c>
-      <c r="S568" s="19">
+        <v>201</v>
+      </c>
+      <c r="S568" s="15">
         <f t="shared" si="26"/>
         <v>15</v>
       </c>
@@ -10756,12 +10759,12 @@
         <v>26</v>
       </c>
       <c r="P569" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R569" t="s">
-        <v>202</v>
-      </c>
-      <c r="S569" s="19">
+        <v>201</v>
+      </c>
+      <c r="S569" s="15">
         <f t="shared" si="26"/>
         <v>5</v>
       </c>
@@ -10771,12 +10774,12 @@
         <v>26</v>
       </c>
       <c r="P570" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R570" t="s">
-        <v>202</v>
-      </c>
-      <c r="S570" s="19">
+        <v>201</v>
+      </c>
+      <c r="S570" s="15">
         <f t="shared" si="26"/>
         <v>-15</v>
       </c>
@@ -10786,12 +10789,12 @@
         <v>25</v>
       </c>
       <c r="P571" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R571" t="s">
-        <v>201</v>
-      </c>
-      <c r="S571" s="19">
+        <v>200</v>
+      </c>
+      <c r="S571" s="15">
         <f t="shared" ref="S571:S576" si="27">S535</f>
         <v>5</v>
       </c>
@@ -10801,12 +10804,12 @@
         <v>25</v>
       </c>
       <c r="P572" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R572" t="s">
-        <v>201</v>
-      </c>
-      <c r="S572" s="19">
+        <v>200</v>
+      </c>
+      <c r="S572" s="15">
         <f t="shared" si="27"/>
         <v>5</v>
       </c>
@@ -10816,12 +10819,12 @@
         <v>25</v>
       </c>
       <c r="P573" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R573" t="s">
-        <v>201</v>
-      </c>
-      <c r="S573" s="19">
+        <v>200</v>
+      </c>
+      <c r="S573" s="15">
         <f t="shared" si="27"/>
         <v>5</v>
       </c>
@@ -10831,12 +10834,12 @@
         <v>25</v>
       </c>
       <c r="P574" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R574" t="s">
-        <v>202</v>
-      </c>
-      <c r="S574" s="19">
+        <v>201</v>
+      </c>
+      <c r="S574" s="15">
         <f t="shared" si="27"/>
         <v>15</v>
       </c>
@@ -10846,12 +10849,12 @@
         <v>25</v>
       </c>
       <c r="P575" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R575" t="s">
-        <v>202</v>
-      </c>
-      <c r="S575" s="19">
+        <v>201</v>
+      </c>
+      <c r="S575" s="15">
         <f t="shared" si="27"/>
         <v>5</v>
       </c>
@@ -10861,12 +10864,12 @@
         <v>25</v>
       </c>
       <c r="P576" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R576" t="s">
-        <v>202</v>
-      </c>
-      <c r="S576" s="19">
+        <v>201</v>
+      </c>
+      <c r="S576" s="15">
         <f t="shared" si="27"/>
         <v>-15</v>
       </c>
@@ -10879,17 +10882,17 @@
       <c r="C577" s="6"/>
       <c r="D577" s="6"/>
       <c r="P577" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R577" t="s">
-        <v>201</v>
-      </c>
-      <c r="S577" s="19">
+        <v>200</v>
+      </c>
+      <c r="S577" s="15">
         <f t="shared" ref="S577:S582" si="28">S535</f>
         <v>5</v>
       </c>
       <c r="U577" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="578" spans="1:21" x14ac:dyDescent="0.25">
@@ -10900,12 +10903,12 @@
       <c r="C578" s="6"/>
       <c r="D578" s="6"/>
       <c r="P578" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R578" t="s">
-        <v>201</v>
-      </c>
-      <c r="S578" s="19">
+        <v>200</v>
+      </c>
+      <c r="S578" s="15">
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
@@ -10918,12 +10921,12 @@
       <c r="C579" s="6"/>
       <c r="D579" s="6"/>
       <c r="P579" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R579" t="s">
-        <v>201</v>
-      </c>
-      <c r="S579" s="19">
+        <v>200</v>
+      </c>
+      <c r="S579" s="15">
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
@@ -10936,12 +10939,12 @@
       <c r="C580" s="6"/>
       <c r="D580" s="6"/>
       <c r="P580" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R580" t="s">
-        <v>202</v>
-      </c>
-      <c r="S580" s="19">
+        <v>201</v>
+      </c>
+      <c r="S580" s="15">
         <f t="shared" si="28"/>
         <v>15</v>
       </c>
@@ -10954,12 +10957,12 @@
       <c r="C581" s="6"/>
       <c r="D581" s="6"/>
       <c r="P581" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R581" t="s">
-        <v>202</v>
-      </c>
-      <c r="S581" s="19">
+        <v>201</v>
+      </c>
+      <c r="S581" s="15">
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
@@ -10972,12 +10975,12 @@
       <c r="C582" s="6"/>
       <c r="D582" s="6"/>
       <c r="P582" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R582" t="s">
-        <v>202</v>
-      </c>
-      <c r="S582" s="19">
+        <v>201</v>
+      </c>
+      <c r="S582" s="15">
         <f t="shared" si="28"/>
         <v>-15</v>
       </c>
@@ -10990,17 +10993,17 @@
       <c r="C583" s="6"/>
       <c r="D583" s="6"/>
       <c r="P583" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R583" t="s">
-        <v>201</v>
-      </c>
-      <c r="S583" s="19">
+        <v>200</v>
+      </c>
+      <c r="S583" s="15">
         <f t="shared" ref="S583:S588" si="29">S535</f>
         <v>5</v>
       </c>
       <c r="U583" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="584" spans="1:21" x14ac:dyDescent="0.25">
@@ -11011,12 +11014,12 @@
       <c r="C584" s="6"/>
       <c r="D584" s="6"/>
       <c r="P584" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R584" t="s">
-        <v>201</v>
-      </c>
-      <c r="S584" s="19">
+        <v>200</v>
+      </c>
+      <c r="S584" s="15">
         <f t="shared" si="29"/>
         <v>5</v>
       </c>
@@ -11029,12 +11032,12 @@
       <c r="C585" s="6"/>
       <c r="D585" s="6"/>
       <c r="P585" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R585" t="s">
-        <v>201</v>
-      </c>
-      <c r="S585" s="19">
+        <v>200</v>
+      </c>
+      <c r="S585" s="15">
         <f t="shared" si="29"/>
         <v>5</v>
       </c>
@@ -11047,12 +11050,12 @@
       <c r="C586" s="6"/>
       <c r="D586" s="6"/>
       <c r="P586" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R586" t="s">
-        <v>202</v>
-      </c>
-      <c r="S586" s="19">
+        <v>201</v>
+      </c>
+      <c r="S586" s="15">
         <f t="shared" si="29"/>
         <v>15</v>
       </c>
@@ -11065,12 +11068,12 @@
       <c r="C587" s="6"/>
       <c r="D587" s="6"/>
       <c r="P587" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R587" t="s">
-        <v>202</v>
-      </c>
-      <c r="S587" s="19">
+        <v>201</v>
+      </c>
+      <c r="S587" s="15">
         <f t="shared" si="29"/>
         <v>5</v>
       </c>
@@ -11081,33 +11084,33 @@
       </c>
       <c r="B588" s="4"/>
       <c r="P588" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R588" t="s">
-        <v>202</v>
-      </c>
-      <c r="S588" s="19">
+        <v>201</v>
+      </c>
+      <c r="S588" s="15">
         <f t="shared" si="29"/>
         <v>-15</v>
       </c>
     </row>
     <row r="589" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A589" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="B589" s="20"/>
-      <c r="C589" s="20"/>
-      <c r="D589" s="20"/>
+      <c r="A589" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B589" s="16"/>
+      <c r="C589" s="16"/>
+      <c r="D589" s="16"/>
     </row>
     <row r="590" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>31</v>
       </c>
       <c r="P590" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R590" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S590">
         <v>10</v>
@@ -11118,10 +11121,10 @@
         <v>31</v>
       </c>
       <c r="P591" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R591" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S591">
         <v>10</v>
@@ -11132,10 +11135,10 @@
         <v>31</v>
       </c>
       <c r="P592" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R592" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S592">
         <v>10</v>
@@ -11146,10 +11149,10 @@
         <v>31</v>
       </c>
       <c r="P593" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R593" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S593">
         <v>10</v>
@@ -11160,10 +11163,10 @@
         <v>31</v>
       </c>
       <c r="P594" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R594" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S594">
         <v>20</v>
@@ -11174,10 +11177,10 @@
         <v>31</v>
       </c>
       <c r="P595" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R595" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S595">
         <v>10</v>
@@ -11188,10 +11191,10 @@
         <v>31</v>
       </c>
       <c r="P596" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R596" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S596">
         <v>-10</v>
@@ -11202,10 +11205,10 @@
         <v>31</v>
       </c>
       <c r="P597" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R597" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S597">
         <v>-25</v>
@@ -11216,10 +11219,10 @@
         <v>32</v>
       </c>
       <c r="P598" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R598" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S598">
         <v>10</v>
@@ -11230,10 +11233,10 @@
         <v>32</v>
       </c>
       <c r="P599" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R599" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S599">
         <v>10</v>
@@ -11244,10 +11247,10 @@
         <v>32</v>
       </c>
       <c r="P600" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R600" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S600">
         <v>10</v>
@@ -11258,10 +11261,10 @@
         <v>32</v>
       </c>
       <c r="P601" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R601" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S601">
         <v>20</v>
@@ -11272,10 +11275,10 @@
         <v>32</v>
       </c>
       <c r="P602" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R602" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S602">
         <v>10</v>
@@ -11286,32 +11289,32 @@
         <v>32</v>
       </c>
       <c r="P603" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R603" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S603">
         <v>-10</v>
       </c>
     </row>
     <row r="605" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A605" s="20" t="s">
+      <c r="A605" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B605" s="20"/>
-      <c r="C605" s="20"/>
-      <c r="D605" s="20"/>
+      <c r="B605" s="16"/>
+      <c r="C605" s="16"/>
+      <c r="D605" s="16"/>
     </row>
     <row r="606" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>37</v>
       </c>
       <c r="P606" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R606" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S606">
         <v>10</v>
@@ -11322,10 +11325,10 @@
         <v>37</v>
       </c>
       <c r="P607" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R607" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S607">
         <v>10</v>
@@ -11336,10 +11339,10 @@
         <v>37</v>
       </c>
       <c r="P608" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R608" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S608">
         <v>10</v>
@@ -11350,10 +11353,10 @@
         <v>37</v>
       </c>
       <c r="P609" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R609" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S609">
         <v>10</v>
@@ -11364,10 +11367,10 @@
         <v>37</v>
       </c>
       <c r="P610" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R610" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S610">
         <v>86.7</v>
@@ -11378,10 +11381,10 @@
         <v>37</v>
       </c>
       <c r="P611" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R611" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S611">
         <v>46.7</v>
@@ -11392,10 +11395,10 @@
         <v>37</v>
       </c>
       <c r="P612" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R612" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S612">
         <v>6.7</v>
@@ -11406,10 +11409,10 @@
         <v>37</v>
       </c>
       <c r="P613" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R613" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S613">
         <v>-26.7</v>
@@ -11420,17 +11423,17 @@
         <v>67</v>
       </c>
       <c r="P614" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R614" t="s">
-        <v>201</v>
-      </c>
-      <c r="S614" s="23">
+        <v>200</v>
+      </c>
+      <c r="S614" s="19">
         <f>S606</f>
         <v>10</v>
       </c>
       <c r="U614" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="615" spans="1:21" x14ac:dyDescent="0.25">
@@ -11438,12 +11441,12 @@
         <v>67</v>
       </c>
       <c r="P615" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R615" t="s">
-        <v>201</v>
-      </c>
-      <c r="S615" s="23">
+        <v>200</v>
+      </c>
+      <c r="S615" s="19">
         <f t="shared" ref="S615:S621" si="30">S607</f>
         <v>10</v>
       </c>
@@ -11453,12 +11456,12 @@
         <v>67</v>
       </c>
       <c r="P616" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R616" t="s">
-        <v>201</v>
-      </c>
-      <c r="S616" s="23">
+        <v>200</v>
+      </c>
+      <c r="S616" s="19">
         <f t="shared" si="30"/>
         <v>10</v>
       </c>
@@ -11468,12 +11471,12 @@
         <v>67</v>
       </c>
       <c r="P617" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R617" t="s">
-        <v>201</v>
-      </c>
-      <c r="S617" s="23">
+        <v>200</v>
+      </c>
+      <c r="S617" s="19">
         <f t="shared" si="30"/>
         <v>10</v>
       </c>
@@ -11483,12 +11486,12 @@
         <v>67</v>
       </c>
       <c r="P618" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R618" t="s">
-        <v>202</v>
-      </c>
-      <c r="S618" s="23">
+        <v>201</v>
+      </c>
+      <c r="S618" s="19">
         <f t="shared" si="30"/>
         <v>86.7</v>
       </c>
@@ -11498,12 +11501,12 @@
         <v>67</v>
       </c>
       <c r="P619" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R619" t="s">
-        <v>202</v>
-      </c>
-      <c r="S619" s="23">
+        <v>201</v>
+      </c>
+      <c r="S619" s="19">
         <f t="shared" si="30"/>
         <v>46.7</v>
       </c>
@@ -11513,12 +11516,12 @@
         <v>67</v>
       </c>
       <c r="P620" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R620" t="s">
-        <v>202</v>
-      </c>
-      <c r="S620" s="23">
+        <v>201</v>
+      </c>
+      <c r="S620" s="19">
         <f t="shared" si="30"/>
         <v>6.7</v>
       </c>
@@ -11528,33 +11531,33 @@
         <v>67</v>
       </c>
       <c r="P621" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R621" t="s">
-        <v>202</v>
-      </c>
-      <c r="S621" s="23">
+        <v>201</v>
+      </c>
+      <c r="S621" s="19">
         <f t="shared" si="30"/>
         <v>-26.7</v>
       </c>
     </row>
     <row r="623" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A623" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="B623" s="20"/>
-      <c r="C623" s="20"/>
-      <c r="D623" s="20"/>
+      <c r="A623" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B623" s="16"/>
+      <c r="C623" s="16"/>
+      <c r="D623" s="16"/>
     </row>
     <row r="624" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>39</v>
       </c>
       <c r="P624" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R624" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S624">
         <v>6.9</v>
@@ -11565,10 +11568,10 @@
         <v>39</v>
       </c>
       <c r="P625" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R625" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S625">
         <v>9.6</v>
@@ -11579,10 +11582,10 @@
         <v>39</v>
       </c>
       <c r="P626" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R626" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S626">
         <v>10</v>
@@ -11593,10 +11596,10 @@
         <v>39</v>
       </c>
       <c r="P627" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R627" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S627">
         <v>10</v>
@@ -11607,10 +11610,10 @@
         <v>39</v>
       </c>
       <c r="P628" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R628" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S628">
         <v>68.400000000000006</v>
@@ -11621,10 +11624,10 @@
         <v>39</v>
       </c>
       <c r="P629" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R629" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S629">
         <v>22.4</v>
@@ -11635,10 +11638,10 @@
         <v>39</v>
       </c>
       <c r="P630" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R630" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S630">
         <v>-20</v>
@@ -11649,32 +11652,32 @@
         <v>39</v>
       </c>
       <c r="P631" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R631" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S631">
         <v>-50</v>
       </c>
     </row>
     <row r="633" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A633" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="B633" s="20"/>
-      <c r="C633" s="20"/>
-      <c r="D633" s="20"/>
+      <c r="A633" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B633" s="16"/>
+      <c r="C633" s="16"/>
+      <c r="D633" s="16"/>
     </row>
     <row r="634" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>33</v>
       </c>
       <c r="P634" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R634" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S634">
         <v>4</v>
@@ -11685,10 +11688,10 @@
         <v>33</v>
       </c>
       <c r="P635" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R635" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S635">
         <v>4</v>
@@ -11699,10 +11702,10 @@
         <v>33</v>
       </c>
       <c r="P636" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R636" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S636">
         <v>4</v>
@@ -11713,10 +11716,10 @@
         <v>33</v>
       </c>
       <c r="P637" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R637" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S637">
         <v>4</v>
@@ -11727,10 +11730,10 @@
         <v>33</v>
       </c>
       <c r="P638" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R638" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S638">
         <v>140</v>
@@ -11741,10 +11744,10 @@
         <v>33</v>
       </c>
       <c r="P639" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R639" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S639">
         <v>90</v>
@@ -11755,10 +11758,10 @@
         <v>33</v>
       </c>
       <c r="P640" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R640" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S640">
         <v>40</v>
@@ -11769,10 +11772,10 @@
         <v>33</v>
       </c>
       <c r="P641" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R641" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S641">
         <v>-10</v>
@@ -11783,12 +11786,12 @@
         <v>34</v>
       </c>
       <c r="P642" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R642" t="s">
-        <v>201</v>
-      </c>
-      <c r="S642" s="19">
+        <v>200</v>
+      </c>
+      <c r="S642" s="15">
         <f t="shared" ref="S642:S649" si="31">S634</f>
         <v>4</v>
       </c>
@@ -11798,12 +11801,12 @@
         <v>34</v>
       </c>
       <c r="P643" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R643" t="s">
-        <v>201</v>
-      </c>
-      <c r="S643" s="19">
+        <v>200</v>
+      </c>
+      <c r="S643" s="15">
         <f t="shared" si="31"/>
         <v>4</v>
       </c>
@@ -11813,12 +11816,12 @@
         <v>34</v>
       </c>
       <c r="P644" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R644" t="s">
-        <v>201</v>
-      </c>
-      <c r="S644" s="19">
+        <v>200</v>
+      </c>
+      <c r="S644" s="15">
         <f t="shared" si="31"/>
         <v>4</v>
       </c>
@@ -11828,12 +11831,12 @@
         <v>34</v>
       </c>
       <c r="P645" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R645" t="s">
-        <v>201</v>
-      </c>
-      <c r="S645" s="19">
+        <v>200</v>
+      </c>
+      <c r="S645" s="15">
         <f t="shared" si="31"/>
         <v>4</v>
       </c>
@@ -11843,12 +11846,12 @@
         <v>34</v>
       </c>
       <c r="P646" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R646" t="s">
-        <v>202</v>
-      </c>
-      <c r="S646" s="19">
+        <v>201</v>
+      </c>
+      <c r="S646" s="15">
         <f t="shared" si="31"/>
         <v>140</v>
       </c>
@@ -11858,12 +11861,12 @@
         <v>34</v>
       </c>
       <c r="P647" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R647" t="s">
-        <v>202</v>
-      </c>
-      <c r="S647" s="19">
+        <v>201</v>
+      </c>
+      <c r="S647" s="15">
         <f t="shared" si="31"/>
         <v>90</v>
       </c>
@@ -11873,12 +11876,12 @@
         <v>34</v>
       </c>
       <c r="P648" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R648" t="s">
-        <v>202</v>
-      </c>
-      <c r="S648" s="19">
+        <v>201</v>
+      </c>
+      <c r="S648" s="15">
         <f t="shared" si="31"/>
         <v>40</v>
       </c>
@@ -11888,33 +11891,33 @@
         <v>34</v>
       </c>
       <c r="P649" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R649" t="s">
-        <v>202</v>
-      </c>
-      <c r="S649" s="19">
+        <v>201</v>
+      </c>
+      <c r="S649" s="15">
         <f t="shared" si="31"/>
         <v>-10</v>
       </c>
     </row>
     <row r="651" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A651" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="B651" s="20"/>
-      <c r="C651" s="20"/>
-      <c r="D651" s="20"/>
+      <c r="A651" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="B651" s="16"/>
+      <c r="C651" s="16"/>
+      <c r="D651" s="16"/>
     </row>
     <row r="652" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>27</v>
       </c>
       <c r="P652" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R652" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S652">
         <v>50</v>
@@ -11925,10 +11928,10 @@
         <v>27</v>
       </c>
       <c r="P653" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R653" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S653">
         <v>40</v>
@@ -11939,10 +11942,10 @@
         <v>27</v>
       </c>
       <c r="P654" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R654" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S654">
         <v>20</v>
@@ -11950,48 +11953,48 @@
     </row>
     <row r="655" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A655" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P655" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R655" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="S655" s="19">
+        <v>201</v>
+      </c>
+      <c r="S655" s="15">
         <f>S652</f>
         <v>50</v>
       </c>
       <c r="U655" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="656" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A656" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P656" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R656" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="S656" s="19">
+        <v>201</v>
+      </c>
+      <c r="S656" s="15">
         <f t="shared" ref="S656:S657" si="32">S653</f>
         <v>40</v>
       </c>
     </row>
     <row r="657" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A657" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P657" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R657" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="S657" s="19">
+        <v>201</v>
+      </c>
+      <c r="S657" s="15">
         <f t="shared" si="32"/>
         <v>20</v>
       </c>
@@ -12001,12 +12004,12 @@
         <v>29</v>
       </c>
       <c r="P658" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R658" t="s">
-        <v>202</v>
-      </c>
-      <c r="S658" s="19">
+        <v>201</v>
+      </c>
+      <c r="S658" s="15">
         <f>S652</f>
         <v>50</v>
       </c>
@@ -12016,12 +12019,12 @@
         <v>29</v>
       </c>
       <c r="P659" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R659" t="s">
-        <v>202</v>
-      </c>
-      <c r="S659" s="19">
+        <v>201</v>
+      </c>
+      <c r="S659" s="15">
         <f t="shared" ref="S659:S660" si="33">S653</f>
         <v>40</v>
       </c>
@@ -12031,12 +12034,12 @@
         <v>29</v>
       </c>
       <c r="P660" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R660" t="s">
-        <v>202</v>
-      </c>
-      <c r="S660" s="19">
+        <v>201</v>
+      </c>
+      <c r="S660" s="15">
         <f t="shared" si="33"/>
         <v>20</v>
       </c>
@@ -12046,10 +12049,10 @@
         <v>35</v>
       </c>
       <c r="P661" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R661" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S661">
         <v>120</v>
@@ -12060,10 +12063,10 @@
         <v>35</v>
       </c>
       <c r="P662" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R662" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S662">
         <v>90</v>
@@ -12074,10 +12077,10 @@
         <v>35</v>
       </c>
       <c r="P663" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R663" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S663">
         <v>50</v>
@@ -12088,10 +12091,10 @@
         <v>35</v>
       </c>
       <c r="P664" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R664" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S664">
         <v>30</v>
@@ -12102,10 +12105,10 @@
         <v>38</v>
       </c>
       <c r="P665" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R665" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S665">
         <v>40</v>
@@ -12116,10 +12119,10 @@
         <v>38</v>
       </c>
       <c r="P666" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R666" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S666">
         <v>20</v>
@@ -12133,19 +12136,19 @@
       <c r="C667" s="6"/>
       <c r="D667" s="6"/>
       <c r="P667" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R667" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S667">
         <v>155</v>
       </c>
       <c r="U667" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V667" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="668" spans="1:22" x14ac:dyDescent="0.25">
@@ -12156,10 +12159,10 @@
       <c r="C668" s="6"/>
       <c r="D668" s="6"/>
       <c r="P668" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R668" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S668">
         <v>155</v>
@@ -12173,29 +12176,29 @@
       <c r="C669" s="6"/>
       <c r="D669" s="6"/>
       <c r="P669" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R669" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S669">
         <v>155</v>
       </c>
     </row>
     <row r="671" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A671" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="B671" s="20"/>
-      <c r="C671" s="20"/>
-      <c r="D671" s="20"/>
+      <c r="A671" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B671" s="16"/>
+      <c r="C671" s="16"/>
+      <c r="D671" s="16"/>
     </row>
     <row r="672" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>45</v>
       </c>
       <c r="R672" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S672">
         <v>3.4</v>
@@ -12206,7 +12209,7 @@
         <v>45</v>
       </c>
       <c r="R673" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S673">
         <v>62</v>
@@ -12220,14 +12223,14 @@
       <c r="C674" s="6"/>
       <c r="D674" s="6"/>
       <c r="R674" t="s">
-        <v>201</v>
-      </c>
-      <c r="S674" s="19">
+        <v>200</v>
+      </c>
+      <c r="S674" s="15">
         <f>S672</f>
         <v>3.4</v>
       </c>
       <c r="U674" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="675" spans="1:21" x14ac:dyDescent="0.25">
@@ -12238,9 +12241,9 @@
       <c r="C675" s="6"/>
       <c r="D675" s="6"/>
       <c r="R675" t="s">
-        <v>202</v>
-      </c>
-      <c r="S675" s="19">
+        <v>201</v>
+      </c>
+      <c r="S675" s="15">
         <f>S673</f>
         <v>62</v>
       </c>
@@ -12250,7 +12253,7 @@
         <v>44</v>
       </c>
       <c r="R676" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S676">
         <v>0.31</v>
@@ -12261,7 +12264,7 @@
         <v>44</v>
       </c>
       <c r="R677" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S677">
         <v>129</v>
@@ -12272,13 +12275,13 @@
         <v>47</v>
       </c>
       <c r="R678" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S678">
         <v>0.62</v>
       </c>
       <c r="U678" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="679" spans="1:21" x14ac:dyDescent="0.25">
@@ -12286,7 +12289,7 @@
         <v>47</v>
       </c>
       <c r="R679" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S679">
         <v>98</v>
@@ -12300,14 +12303,14 @@
       <c r="C680" s="6"/>
       <c r="D680" s="6"/>
       <c r="R680" t="s">
-        <v>201</v>
-      </c>
-      <c r="S680" s="19">
+        <v>200</v>
+      </c>
+      <c r="S680" s="15">
         <f>S678</f>
         <v>0.62</v>
       </c>
       <c r="U680" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="681" spans="1:21" x14ac:dyDescent="0.25">
@@ -12318,9 +12321,9 @@
       <c r="C681" s="6"/>
       <c r="D681" s="6"/>
       <c r="R681" t="s">
-        <v>202</v>
-      </c>
-      <c r="S681" s="19">
+        <v>201</v>
+      </c>
+      <c r="S681" s="15">
         <f>S679</f>
         <v>98</v>
       </c>
@@ -12331,14 +12334,14 @@
       </c>
       <c r="B682" s="4"/>
       <c r="R682" t="s">
-        <v>201</v>
-      </c>
-      <c r="S682" s="19">
+        <v>200</v>
+      </c>
+      <c r="S682" s="15">
         <f>S680</f>
         <v>0.62</v>
       </c>
       <c r="U682" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="683" spans="1:21" x14ac:dyDescent="0.25">
@@ -12347,9 +12350,9 @@
       </c>
       <c r="B683" s="4"/>
       <c r="R683" t="s">
-        <v>202</v>
-      </c>
-      <c r="S683" s="19">
+        <v>201</v>
+      </c>
+      <c r="S683" s="15">
         <f>S681</f>
         <v>98</v>
       </c>
@@ -12359,7 +12362,7 @@
         <v>48</v>
       </c>
       <c r="R684" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S684">
         <v>2</v>
@@ -12370,7 +12373,7 @@
         <v>48</v>
       </c>
       <c r="R685" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S685">
         <v>120</v>
@@ -12382,7 +12385,7 @@
       </c>
       <c r="B686" s="6"/>
       <c r="R686" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="687" spans="1:21" x14ac:dyDescent="0.25">
@@ -12391,7 +12394,7 @@
       </c>
       <c r="B687" s="6"/>
       <c r="R687" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="688" spans="1:21" x14ac:dyDescent="0.25">
@@ -12399,9 +12402,9 @@
         <v>50</v>
       </c>
       <c r="R688" t="s">
-        <v>201</v>
-      </c>
-      <c r="S688" s="19">
+        <v>200</v>
+      </c>
+      <c r="S688" s="15">
         <f>S686</f>
         <v>0</v>
       </c>
@@ -12411,9 +12414,9 @@
         <v>50</v>
       </c>
       <c r="R689" t="s">
-        <v>202</v>
-      </c>
-      <c r="S689" s="19">
+        <v>201</v>
+      </c>
+      <c r="S689" s="15">
         <f>S687</f>
         <v>0</v>
       </c>
@@ -12423,13 +12426,13 @@
         <v>66</v>
       </c>
       <c r="R691" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S691">
         <v>0</v>
       </c>
       <c r="U691" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="692" spans="1:22" x14ac:dyDescent="0.25">
@@ -12437,7 +12440,7 @@
         <v>69</v>
       </c>
       <c r="R692" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S692">
         <v>0</v>
@@ -12448,7 +12451,7 @@
         <v>70</v>
       </c>
       <c r="R693" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S693">
         <v>0</v>
@@ -12459,7 +12462,7 @@
         <v>42</v>
       </c>
       <c r="R694" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S694">
         <v>0</v>
@@ -12470,7 +12473,7 @@
         <v>43</v>
       </c>
       <c r="R695" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S695">
         <v>0</v>
@@ -12492,13 +12495,13 @@
       <c r="C698" s="6"/>
       <c r="D698" s="6"/>
       <c r="R698" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S698">
         <v>20</v>
       </c>
       <c r="V698" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="699" spans="1:22" x14ac:dyDescent="0.25">
@@ -12509,16 +12512,16 @@
       <c r="C699" s="6"/>
       <c r="D699" s="6"/>
       <c r="R699" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S699">
         <v>22.5</v>
       </c>
       <c r="U699" t="s">
+        <v>242</v>
+      </c>
+      <c r="V699" t="s">
         <v>243</v>
-      </c>
-      <c r="V699" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="700" spans="1:22" x14ac:dyDescent="0.25">
@@ -12553,13 +12556,13 @@
       <c r="C703" s="6"/>
       <c r="D703" s="6"/>
       <c r="R703" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S703">
         <v>105</v>
       </c>
-      <c r="V703" s="24" t="s">
-        <v>272</v>
+      <c r="V703" s="20" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="704" spans="1:22" x14ac:dyDescent="0.25">
@@ -12570,14 +12573,14 @@
       <c r="C704" s="6"/>
       <c r="D704" s="6"/>
       <c r="R704" t="s">
-        <v>202</v>
-      </c>
-      <c r="S704" s="23">
+        <v>201</v>
+      </c>
+      <c r="S704" s="19">
         <f>S703</f>
         <v>105</v>
       </c>
       <c r="U704" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="705" spans="1:22" x14ac:dyDescent="0.25">
@@ -12588,14 +12591,14 @@
       <c r="C705" s="6"/>
       <c r="D705" s="6"/>
       <c r="R705" t="s">
-        <v>202</v>
-      </c>
-      <c r="S705" s="23">
+        <v>201</v>
+      </c>
+      <c r="S705" s="19">
         <f>S703</f>
         <v>105</v>
       </c>
       <c r="U705" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="706" spans="1:22" x14ac:dyDescent="0.25">
@@ -12612,13 +12615,13 @@
       <c r="C707" s="6"/>
       <c r="D707" s="6"/>
       <c r="R707" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S707">
         <v>5.6</v>
       </c>
       <c r="V707" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="708" spans="1:22" x14ac:dyDescent="0.25">
@@ -12629,13 +12632,13 @@
       <c r="C708" s="6"/>
       <c r="D708" s="6"/>
       <c r="R708" t="s">
-        <v>201</v>
-      </c>
-      <c r="S708" s="25">
+        <v>200</v>
+      </c>
+      <c r="S708" s="21">
         <v>3</v>
       </c>
       <c r="V708" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="709" spans="1:22" x14ac:dyDescent="0.25">
@@ -12646,14 +12649,14 @@
       <c r="C709" s="6"/>
       <c r="D709" s="6"/>
       <c r="R709" t="s">
-        <v>201</v>
-      </c>
-      <c r="S709" s="23">
+        <v>200</v>
+      </c>
+      <c r="S709" s="19">
         <f>AVERAGE(S707:S708)</f>
         <v>4.3</v>
       </c>
       <c r="U709" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="710" spans="1:22" x14ac:dyDescent="0.25">
@@ -12664,9 +12667,9 @@
       <c r="C710" s="6"/>
       <c r="D710" s="6"/>
       <c r="R710" t="s">
-        <v>201</v>
-      </c>
-      <c r="S710" s="23">
+        <v>200</v>
+      </c>
+      <c r="S710" s="19">
         <f>AVERAGE(S707:S708)</f>
         <v>4.3</v>
       </c>
@@ -12679,9 +12682,9 @@
       <c r="C711" s="6"/>
       <c r="D711" s="6"/>
       <c r="R711" t="s">
-        <v>201</v>
-      </c>
-      <c r="S711" s="23">
+        <v>200</v>
+      </c>
+      <c r="S711" s="19">
         <f>AVERAGE(S707:S708)</f>
         <v>4.3</v>
       </c>
@@ -12694,9 +12697,9 @@
       <c r="C712" s="6"/>
       <c r="D712" s="6"/>
       <c r="R712" t="s">
-        <v>201</v>
-      </c>
-      <c r="S712" s="23">
+        <v>200</v>
+      </c>
+      <c r="S712" s="19">
         <f>AVERAGE(S707:S708)</f>
         <v>4.3</v>
       </c>
@@ -12709,9 +12712,9 @@
       <c r="C713" s="6"/>
       <c r="D713" s="6"/>
       <c r="R713" t="s">
-        <v>201</v>
-      </c>
-      <c r="S713" s="23">
+        <v>200</v>
+      </c>
+      <c r="S713" s="19">
         <f>AVERAGE(S707:S708)</f>
         <v>4.3</v>
       </c>
@@ -12724,7 +12727,7 @@
     </row>
     <row r="715" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B715" s="2"/>
       <c r="C715" s="2"/>
@@ -12750,14 +12753,14 @@
     </row>
     <row r="717" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R717" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="S717" s="22">
+        <v>222</v>
+      </c>
+      <c r="S717" s="18">
         <v>1.2</v>
       </c>
       <c r="T717" s="5"/>
       <c r="U717" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="719" spans="1:22" x14ac:dyDescent="0.25">
@@ -12793,7 +12796,7 @@
       <c r="R720" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="S720" s="12">
+      <c r="S720" s="10">
         <v>0</v>
       </c>
       <c r="T720" s="5" t="s">
@@ -12805,7 +12808,7 @@
     </row>
     <row r="721" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -12813,7 +12816,7 @@
       <c r="E721" s="1"/>
       <c r="Q721" s="5"/>
       <c r="R721" s="5"/>
-      <c r="S721" s="12"/>
+      <c r="S721" s="10"/>
       <c r="T721" s="5"/>
       <c r="U721" s="5"/>
     </row>
@@ -12827,7 +12830,7 @@
       <c r="R722" t="s">
         <v>138</v>
       </c>
-      <c r="S722" s="11">
+      <c r="S722" s="9">
         <f>8/1000*(14/(1*14+3*2))*100</f>
         <v>0.55999999999999994</v>
       </c>
@@ -12838,7 +12841,7 @@
         <v>115</v>
       </c>
       <c r="V722" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="723" spans="1:22" x14ac:dyDescent="0.25">
@@ -12851,7 +12854,7 @@
       <c r="R723" t="s">
         <v>138</v>
       </c>
-      <c r="S723" s="11">
+      <c r="S723" s="9">
         <f>15/1000*(14/(1*14+3*2))*100</f>
         <v>1.0499999999999998</v>
       </c>
@@ -12859,12 +12862,12 @@
         <v>109</v>
       </c>
       <c r="V723" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="724" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I724" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q724" t="s">
         <v>113</v>
@@ -12872,7 +12875,7 @@
       <c r="R724" t="s">
         <v>138</v>
       </c>
-      <c r="S724" s="11">
+      <c r="S724" s="9">
         <f>50/1000*(14/(1*14+3*2))*100</f>
         <v>3.4999999999999996</v>
       </c>
@@ -12880,11 +12883,11 @@
         <v>109</v>
       </c>
       <c r="V724" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="725" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="S725" s="11"/>
+      <c r="S725" s="9"/>
     </row>
     <row r="729" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
@@ -12996,7 +12999,7 @@
         <v>121</v>
       </c>
       <c r="N733" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q733" t="s">
         <v>113</v>
@@ -13112,7 +13115,7 @@
         <v>121</v>
       </c>
       <c r="N737" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q737" t="s">
         <v>113</v>
@@ -13216,7 +13219,7 @@
         <v>123</v>
       </c>
       <c r="N741" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q741" t="s">
         <v>113</v>
@@ -13320,7 +13323,7 @@
         <v>124</v>
       </c>
       <c r="N745" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q745" t="s">
         <v>113</v>
@@ -13421,7 +13424,7 @@
         <v>119</v>
       </c>
       <c r="N749" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q749" t="s">
         <v>113</v>
@@ -13516,7 +13519,7 @@
         <v>135</v>
       </c>
       <c r="N753" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q753" t="s">
         <v>113</v>
@@ -13559,7 +13562,7 @@
     </row>
     <row r="755" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K755" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N755" t="s">
         <v>131</v>
@@ -13582,7 +13585,7 @@
     </row>
     <row r="756" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K756" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N756" t="s">
         <v>146</v>
@@ -13689,7 +13692,7 @@
         <v>126</v>
       </c>
       <c r="N760" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q760" t="s">
         <v>113</v>
@@ -13793,7 +13796,7 @@
         <v>127</v>
       </c>
       <c r="N764" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q764" t="s">
         <v>113</v>
@@ -13897,7 +13900,7 @@
         <v>128</v>
       </c>
       <c r="N768" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q768" t="s">
         <v>113</v>
@@ -13998,7 +14001,7 @@
         <v>125</v>
       </c>
       <c r="N772" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q772" t="s">
         <v>113</v>
@@ -14093,7 +14096,7 @@
         <v>129</v>
       </c>
       <c r="M776" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N776" t="s">
         <v>130</v>
@@ -14119,7 +14122,7 @@
         <v>129</v>
       </c>
       <c r="M777" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N777" t="s">
         <v>131</v>
@@ -14145,7 +14148,7 @@
         <v>129</v>
       </c>
       <c r="M778" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N778" t="s">
         <v>132</v>
@@ -14171,7 +14174,7 @@
         <v>129</v>
       </c>
       <c r="M779" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N779" t="s">
         <v>131</v>
@@ -14197,7 +14200,7 @@
         <v>129</v>
       </c>
       <c r="M780" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N780" t="s">
         <v>132</v>
@@ -14220,13 +14223,13 @@
     </row>
     <row r="782" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B782" s="1"/>
     </row>
     <row r="783" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J783" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q783" t="s">
         <v>113</v>
@@ -14241,7 +14244,7 @@
         <v>114</v>
       </c>
       <c r="U783" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="785" spans="1:22" x14ac:dyDescent="0.25">
@@ -14404,22 +14407,22 @@
         <v>145</v>
       </c>
       <c r="R793" t="s">
-        <v>355</v>
-      </c>
-      <c r="S793" s="34">
+        <v>354</v>
+      </c>
+      <c r="S793" s="30">
         <f>S792</f>
         <v>1</v>
       </c>
-      <c r="T793" s="34" t="s">
+      <c r="T793" s="30" t="s">
         <v>109</v>
       </c>
       <c r="U793" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="795" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B795" s="2"/>
       <c r="C795" s="2"/>
@@ -14451,7 +14454,7 @@
         <v>0</v>
       </c>
       <c r="T796" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="U796" s="5" t="s">
         <v>12</v>
@@ -14459,7 +14462,7 @@
     </row>
     <row r="798" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E798" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q798" t="s">
         <v>145</v>
@@ -14479,31 +14482,31 @@
     </row>
     <row r="799" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E799" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q799" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R799" t="s">
         <v>163</v>
       </c>
-      <c r="S799" s="33">
+      <c r="S799" s="29">
         <f>6.1*(44/12)*1000</f>
         <v>22366.666666666664</v>
       </c>
       <c r="T799" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="V799" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="800" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E800" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q800" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="R800" t="s">
         <v>163</v>
@@ -14513,15 +14516,15 @@
         <v>58.3</v>
       </c>
       <c r="T800" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="V800" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="802" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E802" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q802" t="s">
         <v>145</v>
@@ -14536,39 +14539,39 @@
         <v>164</v>
       </c>
       <c r="U802" t="s">
+        <v>349</v>
+      </c>
+      <c r="V802" t="s">
         <v>350</v>
-      </c>
-      <c r="V802" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="803" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E803" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q803" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R803" t="s">
         <v>163</v>
       </c>
-      <c r="S803" s="33">
+      <c r="S803" s="29">
         <f>2.6*(44/12)*1000</f>
         <v>9533.3333333333339</v>
       </c>
       <c r="T803" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="V803" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="804" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E804" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q804" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="R804" t="s">
         <v>163</v>
@@ -14578,10 +14581,10 @@
         <v>7.9</v>
       </c>
       <c r="T804" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="V804" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="806" spans="1:22" x14ac:dyDescent="0.25">
@@ -14612,50 +14615,53 @@
     </row>
     <row r="808" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E808" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q808" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R808" t="s">
         <v>167</v>
       </c>
       <c r="S808">
-        <v>0.24</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="T808" t="s">
-        <v>169</v>
+        <v>168</v>
+      </c>
+      <c r="U808" t="s">
+        <v>359</v>
       </c>
       <c r="V808" t="s">
-        <v>168</v>
+        <v>358</v>
       </c>
     </row>
     <row r="809" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E809" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q809" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R809" t="s">
         <v>167</v>
       </c>
       <c r="S809">
-        <v>0.24</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="T809" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="V809" t="s">
-        <v>168</v>
+        <v>358</v>
       </c>
     </row>
     <row r="810" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E810" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q810" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R810" t="s">
         <v>167</v>
@@ -14664,46 +14670,46 @@
         <v>0</v>
       </c>
       <c r="T810" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U810" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="812" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A812" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="B812" s="26"/>
-      <c r="C812" s="27"/>
-      <c r="D812" s="27"/>
-      <c r="E812" s="27"/>
-      <c r="F812" s="27"/>
-      <c r="G812" s="27"/>
-      <c r="H812" s="27"/>
-      <c r="I812" s="27"/>
-      <c r="J812" s="27"/>
-      <c r="K812" s="27"/>
-      <c r="L812" s="27"/>
-      <c r="M812" s="27"/>
-      <c r="N812" s="27"/>
-      <c r="O812" s="27"/>
-      <c r="P812" s="27"/>
-      <c r="Q812" s="27"/>
-      <c r="R812" s="27"/>
-      <c r="S812" s="27"/>
-      <c r="T812" s="27"/>
-      <c r="U812" s="27"/>
-      <c r="V812" s="27"/>
+      <c r="A812" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="B812" s="22"/>
+      <c r="C812" s="23"/>
+      <c r="D812" s="23"/>
+      <c r="E812" s="23"/>
+      <c r="F812" s="23"/>
+      <c r="G812" s="23"/>
+      <c r="H812" s="23"/>
+      <c r="I812" s="23"/>
+      <c r="J812" s="23"/>
+      <c r="K812" s="23"/>
+      <c r="L812" s="23"/>
+      <c r="M812" s="23"/>
+      <c r="N812" s="23"/>
+      <c r="O812" s="23"/>
+      <c r="P812" s="23"/>
+      <c r="Q812" s="23"/>
+      <c r="R812" s="23"/>
+      <c r="S812" s="23"/>
+      <c r="T812" s="23"/>
+      <c r="U812" s="23"/>
+      <c r="V812" s="23"/>
     </row>
     <row r="814" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I814" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="R814" t="s">
-        <v>318</v>
-      </c>
-      <c r="S814" s="11">
+        <v>317</v>
+      </c>
+      <c r="S814" s="9">
         <f>213/(213 + 60)*100</f>
         <v>78.021978021978029</v>
       </c>
@@ -14711,17 +14717,17 @@
         <v>97</v>
       </c>
       <c r="V814" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="815" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I815" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="R815" t="s">
-        <v>318</v>
-      </c>
-      <c r="S815" s="11">
+        <v>317</v>
+      </c>
+      <c r="S815" s="9">
         <f>60/(213 + 60)*100</f>
         <v>21.978021978021978</v>
       </c>
@@ -14729,15 +14735,15 @@
         <v>97</v>
       </c>
       <c r="V815" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="817" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I817" t="s">
+        <v>319</v>
+      </c>
+      <c r="R817" t="s">
         <v>320</v>
-      </c>
-      <c r="R817" t="s">
-        <v>321</v>
       </c>
       <c r="S817">
         <v>45</v>
@@ -14746,15 +14752,15 @@
         <v>97</v>
       </c>
       <c r="V817" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="818" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I818" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="R818" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="S818">
         <v>48</v>
@@ -14763,25 +14769,25 @@
         <v>97</v>
       </c>
       <c r="V818" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="820" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R820" t="s">
-        <v>301</v>
-      </c>
-      <c r="S820" s="29">
+        <v>300</v>
+      </c>
+      <c r="S820" s="25">
         <f>S827</f>
         <v>-5.9999999999999995E-4</v>
       </c>
       <c r="T820" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="U820" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="V820" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="821" spans="1:22" x14ac:dyDescent="0.25">
@@ -14792,20 +14798,20 @@
         <v>139</v>
       </c>
       <c r="R821" t="s">
-        <v>301</v>
-      </c>
-      <c r="S821" s="28">
+        <v>300</v>
+      </c>
+      <c r="S821" s="24">
         <f>-(45.5*0.1+10.7*0.9)/1000</f>
         <v>-1.418E-2</v>
       </c>
       <c r="T821" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="U821" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="V821" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="822" spans="1:22" x14ac:dyDescent="0.25">
@@ -14816,14 +14822,14 @@
         <v>139</v>
       </c>
       <c r="R822" t="s">
-        <v>301</v>
-      </c>
-      <c r="S822" s="32">
+        <v>300</v>
+      </c>
+      <c r="S822" s="28">
         <f>S821</f>
         <v>-1.418E-2</v>
       </c>
       <c r="T822" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="823" spans="1:22" x14ac:dyDescent="0.25">
@@ -14834,20 +14840,20 @@
         <v>98</v>
       </c>
       <c r="R823" t="s">
-        <v>301</v>
-      </c>
-      <c r="S823" s="28">
+        <v>300</v>
+      </c>
+      <c r="S823" s="24">
         <f>-(45.5*0.4+10.7*0.6)/1000</f>
         <v>-2.4619999999999996E-2</v>
       </c>
       <c r="T823" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="U823" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="V823" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="824" spans="1:22" x14ac:dyDescent="0.25">
@@ -14858,14 +14864,14 @@
         <v>98</v>
       </c>
       <c r="R824" t="s">
-        <v>301</v>
-      </c>
-      <c r="S824" s="32">
+        <v>300</v>
+      </c>
+      <c r="S824" s="28">
         <f>S823</f>
         <v>-2.4619999999999996E-2</v>
       </c>
       <c r="T824" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="825" spans="1:22" x14ac:dyDescent="0.25">
@@ -14874,20 +14880,20 @@
       </c>
       <c r="B825" s="4"/>
       <c r="R825" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S825" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="T825" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="U825" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="V825" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="826" spans="1:22" x14ac:dyDescent="0.25">
@@ -14896,77 +14902,77 @@
       </c>
       <c r="B826" s="4"/>
       <c r="R826" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S826" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="T826" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="U826" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="V826" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="827" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C827" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R827" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S827">
         <f>-0.6/1000</f>
         <v>-5.9999999999999995E-4</v>
       </c>
       <c r="T827" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="V827" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="828" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B828" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R828" t="s">
-        <v>301</v>
-      </c>
-      <c r="S828" s="28">
+        <v>300</v>
+      </c>
+      <c r="S828" s="24">
         <f>-20*0.45/0.85/1000</f>
         <v>-1.0588235294117647E-2</v>
       </c>
       <c r="T828" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="U828" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="V828" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="830" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D830" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R830" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S830">
         <f>-9.2/1000</f>
         <v>-9.1999999999999998E-3</v>
       </c>
       <c r="T830" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="V830" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="832" spans="1:22" x14ac:dyDescent="0.25">
@@ -14974,16 +14980,16 @@
         <v>107</v>
       </c>
       <c r="R832" t="s">
-        <v>310</v>
-      </c>
-      <c r="S832" s="30">
+        <v>309</v>
+      </c>
+      <c r="S832" s="26">
         <v>-0.5</v>
       </c>
       <c r="T832" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="V832" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="833" spans="9:22" x14ac:dyDescent="0.25">
@@ -14991,132 +14997,132 @@
         <v>108</v>
       </c>
       <c r="R833" t="s">
-        <v>310</v>
-      </c>
-      <c r="S833" s="30">
+        <v>309</v>
+      </c>
+      <c r="S833" s="26">
         <v>-1</v>
       </c>
       <c r="T833" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="V833" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="834" spans="9:22" x14ac:dyDescent="0.25">
       <c r="I834" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R834" t="s">
-        <v>310</v>
-      </c>
-      <c r="S834" s="21">
+        <v>309</v>
+      </c>
+      <c r="S834" s="17">
         <v>-1</v>
       </c>
       <c r="T834" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="U834" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="835" spans="9:22" x14ac:dyDescent="0.25">
       <c r="R835" t="s">
-        <v>312</v>
-      </c>
-      <c r="S835" s="21">
+        <v>311</v>
+      </c>
+      <c r="S835" s="17">
         <f>-0.4 / ( (2*30.97) / (2*30.97 + 5*16) )</f>
         <v>-0.91662899580238943</v>
       </c>
       <c r="T835" t="s">
-        <v>313</v>
-      </c>
-      <c r="U835" s="31" t="s">
-        <v>328</v>
+        <v>312</v>
+      </c>
+      <c r="U835" s="27" t="s">
+        <v>327</v>
       </c>
       <c r="V835" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="836" spans="9:22" x14ac:dyDescent="0.25">
       <c r="R836" t="s">
-        <v>311</v>
-      </c>
-      <c r="S836" s="21">
+        <v>310</v>
+      </c>
+      <c r="S836" s="17">
         <f>0.6 / ( (2*39.1) / (2*39.1 + 16) )</f>
         <v>0.72276214833759589</v>
       </c>
       <c r="T836" t="s">
-        <v>313</v>
-      </c>
-      <c r="U836" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="U836" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="V836" t="s">
         <v>329</v>
-      </c>
-      <c r="V836" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="838" spans="9:22" x14ac:dyDescent="0.25">
       <c r="R838" t="s">
-        <v>303</v>
-      </c>
-      <c r="S838" s="30">
+        <v>302</v>
+      </c>
+      <c r="S838" s="26">
         <f>3/5</f>
         <v>0.6</v>
       </c>
       <c r="T838" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="U838" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="V838" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="840" spans="9:22" x14ac:dyDescent="0.25">
       <c r="I840" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q840" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R840" t="s">
-        <v>326</v>
-      </c>
-      <c r="S840" s="30">
+        <v>325</v>
+      </c>
+      <c r="S840" s="26">
         <f>0.12*(44/12)</f>
         <v>0.43999999999999995</v>
       </c>
       <c r="T840" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="841" spans="9:22" x14ac:dyDescent="0.25">
       <c r="I841" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q841" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R841" t="s">
-        <v>326</v>
-      </c>
-      <c r="S841" s="30">
+        <v>325</v>
+      </c>
+      <c r="S841" s="26">
         <f>0.13*(44/12)</f>
         <v>0.47666666666666668</v>
       </c>
       <c r="T841" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="842" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="S842" s="11"/>
+      <c r="S842" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="V479" r:id="rId1"/>
-    <hyperlink ref="V703" r:id="rId2"/>
+    <hyperlink ref="V479" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="V703" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D849481-FAFA-4D35-9359-07E2CC878DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3657ADE9-7677-4025-8F26-7588A230C27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35805" yWindow="2595" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1755" yWindow="870" windowWidth="21600" windowHeight="13785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="363">
   <si>
     <t>f_crop</t>
   </si>
@@ -1111,6 +1111,15 @@
   </si>
   <si>
     <t>Use factor from Finland. Sweden uses a more sophisticated model for N leaching</t>
+  </si>
+  <si>
+    <t>lime_effect_organic</t>
+  </si>
+  <si>
+    <t>kg CaO/kg P</t>
+  </si>
+  <si>
+    <t>Lime effect of non-manure organic fertiliser assumed same as manure</t>
   </si>
 </sst>
 </file>
@@ -1582,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V842"/>
+  <dimension ref="A1:V843"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="21" customWidth="1"/>
@@ -15035,7 +15044,7 @@
         <v>-0.91662899580238943</v>
       </c>
       <c r="T835" t="s">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="U835" s="27" t="s">
         <v>327</v>
@@ -15080,44 +15089,59 @@
         <v>307</v>
       </c>
     </row>
-    <row r="840" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I840" t="s">
+    <row r="839" spans="9:22" x14ac:dyDescent="0.25">
+      <c r="R839" t="s">
+        <v>360</v>
+      </c>
+      <c r="S839" s="26">
+        <f>3/5</f>
+        <v>0.6</v>
+      </c>
+      <c r="T839" t="s">
+        <v>304</v>
+      </c>
+      <c r="U839" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="841" spans="9:22" x14ac:dyDescent="0.25">
+      <c r="I841" t="s">
         <v>319</v>
       </c>
-      <c r="Q840" t="s">
+      <c r="Q841" t="s">
         <v>323</v>
       </c>
-      <c r="R840" t="s">
+      <c r="R841" t="s">
         <v>325</v>
       </c>
-      <c r="S840" s="26">
+      <c r="S841" s="26">
         <f>0.12*(44/12)</f>
         <v>0.43999999999999995</v>
       </c>
-      <c r="T840" t="s">
+      <c r="T841" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="841" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I841" t="s">
+    <row r="842" spans="9:22" x14ac:dyDescent="0.25">
+      <c r="I842" t="s">
         <v>333</v>
       </c>
-      <c r="Q841" t="s">
+      <c r="Q842" t="s">
         <v>323</v>
       </c>
-      <c r="R841" t="s">
+      <c r="R842" t="s">
         <v>325</v>
       </c>
-      <c r="S841" s="26">
+      <c r="S842" s="26">
         <f>0.13*(44/12)</f>
         <v>0.47666666666666668</v>
       </c>
-      <c r="T841" t="s">
+      <c r="T842" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="842" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="S842" s="9"/>
+    <row r="843" spans="9:22" x14ac:dyDescent="0.25">
+      <c r="S843" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/default/PlantNutrientMgmt.xlsx
+++ b/data/default/PlantNutrientMgmt.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3657ADE9-7677-4025-8F26-7588A230C27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B6E338-304D-4B90-82CD-2B09A6EB6B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="870" windowWidth="21600" windowHeight="13785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27540" yWindow="4305" windowWidth="26610" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="362">
   <si>
     <t>f_crop</t>
   </si>
@@ -366,9 +366,6 @@
     <t>Swedish IIR 2023. Table 5-23</t>
   </si>
   <si>
-    <t>Only three largest included for now</t>
-  </si>
-  <si>
     <t>f_compound</t>
   </si>
   <si>
@@ -456,9 +453,6 @@
     <t>Mineral fertiliser shares</t>
   </si>
   <si>
-    <t>No mineral N for organic</t>
-  </si>
-  <si>
     <t>fallback</t>
   </si>
   <si>
@@ -1120,6 +1114,9 @@
   </si>
   <si>
     <t>Lime effect of non-manure organic fertiliser assumed same as manure</t>
+  </si>
+  <si>
+    <t>If possible, N requirements on organic areas are met without mineral N. If not, mineral N is added. Check results to verify scenarios!!!</t>
   </si>
 </sst>
 </file>
@@ -1618,19 +1615,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>83</v>
@@ -1639,31 +1636,31 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>1</v>
@@ -1746,7 +1743,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1772,7 +1769,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R8" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S8" s="5">
         <v>0</v>
@@ -1788,28 +1785,31 @@
       <c r="G9" t="s">
         <v>98</v>
       </c>
+      <c r="I9" t="s">
+        <v>107</v>
+      </c>
       <c r="R9" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S9" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="U9" s="4" t="s">
-        <v>141</v>
+      <c r="U9" s="6" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="G10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I10" t="s">
         <v>107</v>
       </c>
       <c r="R10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S10">
         <v>59</v>
@@ -1817,22 +1817,20 @@
       <c r="T10" t="s">
         <v>109</v>
       </c>
-      <c r="U10" s="6" t="s">
-        <v>111</v>
-      </c>
+      <c r="U10" s="6"/>
       <c r="V10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="G11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I11" t="s">
         <v>108</v>
       </c>
       <c r="R11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S11">
         <v>7</v>
@@ -1846,13 +1844,13 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="G12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="R12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S12">
         <v>34</v>
@@ -1866,13 +1864,13 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R14" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="S14" s="5">
         <v>0</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="U14" s="5" t="s">
         <v>12</v>
@@ -1883,50 +1881,50 @@
         <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="S15" s="4">
         <v>100</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="U15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="G16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I16" t="s">
+        <v>202</v>
+      </c>
+      <c r="R16" t="s">
         <v>204</v>
-      </c>
-      <c r="R16" t="s">
-        <v>206</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="V16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R18" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="S18" s="5">
         <v>0</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="U18" s="5" t="s">
         <v>12</v>
@@ -1937,36 +1935,36 @@
         <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="S19" s="4">
         <v>100</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="U19" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="G20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="S20" s="4">
         <v>100</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -1976,7 +1974,7 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2002,7 +2000,7 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R24" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="S24">
         <v>66</v>
@@ -2011,15 +2009,15 @@
         <v>97</v>
       </c>
       <c r="U24" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="V24" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -2045,7 +2043,7 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -2069,7 +2067,7 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -2093,7 +2091,7 @@
     </row>
     <row r="29" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2119,7 +2117,7 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2145,7 +2143,7 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -2169,7 +2167,7 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -3311,7 +3309,7 @@
     </row>
     <row r="106" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="R106" s="4" t="s">
         <v>9</v>
@@ -3325,7 +3323,7 @@
     </row>
     <row r="107" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="R107" s="4" t="s">
         <v>10</v>
@@ -3336,7 +3334,7 @@
     </row>
     <row r="108" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="R108" s="4" t="s">
         <v>11</v>
@@ -3347,7 +3345,7 @@
     </row>
     <row r="109" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>85</v>
@@ -3364,7 +3362,7 @@
     </row>
     <row r="110" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>85</v>
@@ -3378,7 +3376,7 @@
     </row>
     <row r="111" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>85</v>
@@ -3392,7 +3390,7 @@
     </row>
     <row r="112" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>84</v>
@@ -3411,7 +3409,7 @@
     </row>
     <row r="113" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>84</v>
@@ -3426,7 +3424,7 @@
     </row>
     <row r="114" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>84</v>
@@ -3761,7 +3759,7 @@
     </row>
     <row r="135" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R135" s="4" t="s">
         <v>11</v>
@@ -3770,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="U135" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.25">
@@ -3803,7 +3801,7 @@
     </row>
     <row r="138" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="R138" s="4" t="s">
         <v>11</v>
@@ -3812,12 +3810,12 @@
         <v>30</v>
       </c>
       <c r="U138" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="139" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="R139" s="4" t="s">
         <v>11</v>
@@ -3826,12 +3824,12 @@
         <v>30</v>
       </c>
       <c r="U139" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="140" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R140" s="4" t="s">
         <v>11</v>
@@ -3840,7 +3838,7 @@
         <v>75</v>
       </c>
       <c r="V140" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="141" spans="1:22" x14ac:dyDescent="0.25">
@@ -4001,10 +3999,10 @@
         <v>75</v>
       </c>
       <c r="U152" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V152" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.25">
@@ -4016,7 +4014,7 @@
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
       <c r="G153" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I153" s="4"/>
       <c r="J153" s="4"/>
@@ -4034,7 +4032,7 @@
         <v>18.5</v>
       </c>
       <c r="U153" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.25">
@@ -4046,7 +4044,7 @@
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
       <c r="G154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I154" s="4"/>
       <c r="J154" s="4"/>
@@ -4091,7 +4089,7 @@
         <v>12</v>
       </c>
       <c r="U155" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
@@ -4146,7 +4144,7 @@
       </c>
       <c r="T157" s="4"/>
       <c r="U157" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.25">
@@ -4563,7 +4561,7 @@
         <v>1.3846000000000001</v>
       </c>
       <c r="U174" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.25">
@@ -4802,7 +4800,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="U183" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="V183" s="8"/>
     </row>
@@ -4887,7 +4885,7 @@
         <v>3.3332999999999999</v>
       </c>
       <c r="U186" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="187" spans="1:22" x14ac:dyDescent="0.25">
@@ -4940,7 +4938,7 @@
         <v>3.3332999999999999</v>
       </c>
       <c r="U188" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.25">
@@ -5037,10 +5035,10 @@
         <v>65</v>
       </c>
       <c r="U192" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="V192" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="193" spans="1:22" x14ac:dyDescent="0.25">
@@ -5119,7 +5117,7 @@
         <v>100</v>
       </c>
       <c r="U195" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="196" spans="1:22" x14ac:dyDescent="0.25">
@@ -5146,7 +5144,7 @@
         <v>4.2</v>
       </c>
       <c r="V196" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.25">
@@ -5173,7 +5171,7 @@
         <v>3.3</v>
       </c>
       <c r="V197" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="198" spans="1:22" x14ac:dyDescent="0.25">
@@ -5201,7 +5199,7 @@
         <v>3.75</v>
       </c>
       <c r="U198" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.25">
@@ -5355,7 +5353,7 @@
         <v>20</v>
       </c>
       <c r="U204" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="205" spans="1:22" x14ac:dyDescent="0.25">
@@ -5445,7 +5443,7 @@
     </row>
     <row r="209" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -5504,13 +5502,13 @@
       <c r="P211" s="5"/>
       <c r="Q211" s="5"/>
       <c r="R211" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S211" s="5">
         <v>0</v>
       </c>
       <c r="T211" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="U211" s="5" t="s">
         <v>12</v>
@@ -5531,16 +5529,16 @@
       <c r="P212" s="4"/>
       <c r="Q212" s="4"/>
       <c r="R212" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S212">
         <v>35</v>
       </c>
       <c r="U212" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="V212" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="213" spans="1:22" x14ac:dyDescent="0.25">
@@ -5558,16 +5556,16 @@
       <c r="P213" s="4"/>
       <c r="Q213" s="4"/>
       <c r="R213" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S213">
         <v>35</v>
       </c>
       <c r="U213" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="V213" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="214" spans="1:22" x14ac:dyDescent="0.25">
@@ -5587,16 +5585,16 @@
       <c r="P214" s="4"/>
       <c r="Q214" s="4"/>
       <c r="R214" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S214">
         <v>25</v>
       </c>
       <c r="U214" t="s">
+        <v>229</v>
+      </c>
+      <c r="V214" t="s">
         <v>231</v>
-      </c>
-      <c r="V214" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="215" spans="1:22" x14ac:dyDescent="0.25">
@@ -5616,16 +5614,16 @@
       <c r="P215" s="4"/>
       <c r="Q215" s="4"/>
       <c r="R215" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S215">
         <v>25</v>
       </c>
       <c r="U215" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="V215" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="216" spans="1:22" x14ac:dyDescent="0.25">
@@ -5645,16 +5643,16 @@
       <c r="P216" s="4"/>
       <c r="Q216" s="4"/>
       <c r="R216" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S216">
         <v>40</v>
       </c>
       <c r="U216" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="V216" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="217" spans="1:22" x14ac:dyDescent="0.25">
@@ -5674,16 +5672,16 @@
       <c r="P217" s="4"/>
       <c r="Q217" s="4"/>
       <c r="R217" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S217">
         <v>20</v>
       </c>
       <c r="U217" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="V217" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="218" spans="1:22" x14ac:dyDescent="0.25">
@@ -5703,7 +5701,7 @@
       <c r="P218" s="4"/>
       <c r="Q218" s="4"/>
       <c r="R218" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S218">
         <v>10</v>
@@ -5712,7 +5710,7 @@
         <v>96</v>
       </c>
       <c r="V218" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="219" spans="1:22" x14ac:dyDescent="0.25">
@@ -5732,7 +5730,7 @@
       <c r="P219" s="4"/>
       <c r="Q219" s="4"/>
       <c r="R219" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S219">
         <v>10</v>
@@ -5741,7 +5739,7 @@
         <v>96</v>
       </c>
       <c r="V219" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="220" spans="1:22" x14ac:dyDescent="0.25">
@@ -5761,13 +5759,13 @@
       <c r="P220" s="4"/>
       <c r="Q220" s="4"/>
       <c r="R220" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S220">
         <v>25</v>
       </c>
       <c r="V220" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="221" spans="1:22" x14ac:dyDescent="0.25">
@@ -5788,7 +5786,7 @@
       <c r="P221" s="4"/>
       <c r="Q221" s="4"/>
       <c r="R221" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="222" spans="1:22" x14ac:dyDescent="0.25">
@@ -5800,7 +5798,7 @@
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
       <c r="G222" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I222" s="4"/>
       <c r="J222" s="4"/>
@@ -5812,16 +5810,16 @@
       <c r="P222" s="4"/>
       <c r="Q222" s="4"/>
       <c r="R222" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S222" s="6">
         <v>10</v>
       </c>
       <c r="U222" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="V222" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="223" spans="1:22" x14ac:dyDescent="0.25">
@@ -5845,7 +5843,7 @@
       <c r="P223" s="4"/>
       <c r="Q223" s="4"/>
       <c r="R223" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S223" s="6">
         <v>40</v>
@@ -5860,7 +5858,7 @@
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
       <c r="G224" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I224" s="4"/>
       <c r="J224" s="4"/>
@@ -5872,7 +5870,7 @@
       <c r="P224" s="4"/>
       <c r="Q224" s="4"/>
       <c r="R224" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S224" s="6">
         <v>10</v>
@@ -5899,7 +5897,7 @@
       <c r="P225" s="4"/>
       <c r="Q225" s="4"/>
       <c r="R225" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S225" s="6">
         <v>40</v>
@@ -5911,10 +5909,10 @@
       </c>
       <c r="B226" s="4"/>
       <c r="G226" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R226" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S226" s="6">
         <v>10</v>
@@ -5929,7 +5927,7 @@
         <v>98</v>
       </c>
       <c r="R227" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S227" s="6">
         <v>40</v>
@@ -5941,16 +5939,16 @@
       </c>
       <c r="B228" s="4"/>
       <c r="R228" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S228" s="4">
         <v>60</v>
       </c>
       <c r="U228" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="V228" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="229" spans="1:22" x14ac:dyDescent="0.25">
@@ -5962,56 +5960,56 @@
         <v>98</v>
       </c>
       <c r="R229" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S229" s="4">
         <f>60*0.5</f>
         <v>30</v>
       </c>
       <c r="U229" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="230" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R230" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S230" s="4">
         <v>35</v>
       </c>
       <c r="U230" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="231" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="R231" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S231" s="4">
         <v>25</v>
       </c>
       <c r="U231" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="232" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="R232" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S232" s="4">
         <v>25</v>
       </c>
       <c r="U232" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="233" spans="1:22" x14ac:dyDescent="0.25">
@@ -6021,7 +6019,7 @@
     </row>
     <row r="234" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -6047,19 +6045,19 @@
     </row>
     <row r="235" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A235" s="14" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B235" s="4"/>
     </row>
     <row r="236" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A236" s="14" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B236" s="4"/>
     </row>
     <row r="237" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A237" s="14" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B237" s="4"/>
     </row>
@@ -6067,35 +6065,35 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="R238" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="S238" s="6">
         <v>40</v>
       </c>
       <c r="T238" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U238" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="V238" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="239" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="R239" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="S239" s="6">
         <v>40</v>
       </c>
       <c r="T239" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U239" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="240" spans="1:22" x14ac:dyDescent="0.25">
@@ -6104,7 +6102,7 @@
     </row>
     <row r="241" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B241" s="12"/>
       <c r="C241" s="12"/>
@@ -6130,7 +6128,7 @@
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -6156,7 +6154,7 @@
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A243" s="14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -6164,7 +6162,7 @@
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A244" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -6172,21 +6170,21 @@
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R245" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S245" s="5">
         <v>0</v>
       </c>
       <c r="T245" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="U245" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R246" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S246" s="5">
         <v>0</v>
@@ -6195,12 +6193,12 @@
         <v>99</v>
       </c>
       <c r="U246" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A247" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B247" s="16"/>
       <c r="C247" s="16"/>
@@ -6215,10 +6213,10 @@
         <v>6</v>
       </c>
       <c r="O248" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R248" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S248">
         <v>3</v>
@@ -6229,10 +6227,10 @@
         <v>6</v>
       </c>
       <c r="O249" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R249" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S249">
         <v>3</v>
@@ -6243,10 +6241,10 @@
         <v>6</v>
       </c>
       <c r="O250" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R250" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S250">
         <v>3</v>
@@ -6257,10 +6255,10 @@
         <v>6</v>
       </c>
       <c r="O251" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R251" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S251">
         <v>3</v>
@@ -6271,10 +6269,10 @@
         <v>6</v>
       </c>
       <c r="O252" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R252" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S252">
         <v>9</v>
@@ -6285,10 +6283,10 @@
         <v>6</v>
       </c>
       <c r="O253" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R253" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S253">
         <v>4</v>
@@ -6299,10 +6297,10 @@
         <v>6</v>
       </c>
       <c r="O254" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R254" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S254">
         <v>-6</v>
@@ -6313,10 +6311,10 @@
         <v>6</v>
       </c>
       <c r="O255" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R255" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S255">
         <v>-16</v>
@@ -6327,10 +6325,10 @@
         <v>24</v>
       </c>
       <c r="O256" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R256" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S256" s="15">
         <f>S248</f>
@@ -6342,10 +6340,10 @@
         <v>24</v>
       </c>
       <c r="O257" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R257" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S257" s="15">
         <f t="shared" ref="S257:S263" si="4">S249</f>
@@ -6357,10 +6355,10 @@
         <v>24</v>
       </c>
       <c r="O258" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R258" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S258" s="15">
         <f t="shared" si="4"/>
@@ -6372,10 +6370,10 @@
         <v>24</v>
       </c>
       <c r="O259" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R259" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S259" s="15">
         <f t="shared" si="4"/>
@@ -6387,10 +6385,10 @@
         <v>24</v>
       </c>
       <c r="O260" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R260" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S260" s="15">
         <f t="shared" si="4"/>
@@ -6402,10 +6400,10 @@
         <v>24</v>
       </c>
       <c r="O261" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R261" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S261" s="15">
         <f t="shared" si="4"/>
@@ -6417,10 +6415,10 @@
         <v>24</v>
       </c>
       <c r="O262" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R262" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S262" s="15">
         <f t="shared" si="4"/>
@@ -6432,10 +6430,10 @@
         <v>24</v>
       </c>
       <c r="O263" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R263" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S263" s="15">
         <f t="shared" si="4"/>
@@ -6447,10 +6445,10 @@
         <v>20</v>
       </c>
       <c r="O264" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R264" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S264" s="15">
         <f>S248</f>
@@ -6462,10 +6460,10 @@
         <v>20</v>
       </c>
       <c r="O265" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R265" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S265" s="15">
         <f t="shared" ref="S265:S271" si="5">S249</f>
@@ -6477,10 +6475,10 @@
         <v>20</v>
       </c>
       <c r="O266" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R266" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S266" s="15">
         <f t="shared" si="5"/>
@@ -6492,10 +6490,10 @@
         <v>20</v>
       </c>
       <c r="O267" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R267" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S267" s="15">
         <f t="shared" si="5"/>
@@ -6507,10 +6505,10 @@
         <v>20</v>
       </c>
       <c r="O268" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R268" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S268" s="15">
         <f t="shared" si="5"/>
@@ -6522,10 +6520,10 @@
         <v>20</v>
       </c>
       <c r="O269" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R269" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S269" s="15">
         <f t="shared" si="5"/>
@@ -6537,10 +6535,10 @@
         <v>20</v>
       </c>
       <c r="O270" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R270" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S270" s="15">
         <f t="shared" si="5"/>
@@ -6552,10 +6550,10 @@
         <v>20</v>
       </c>
       <c r="O271" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R271" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S271" s="15">
         <f t="shared" si="5"/>
@@ -6567,10 +6565,10 @@
         <v>22</v>
       </c>
       <c r="O272" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R272" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S272" s="15">
         <f>S248</f>
@@ -6582,10 +6580,10 @@
         <v>22</v>
       </c>
       <c r="O273" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R273" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S273" s="15">
         <f t="shared" ref="S273:S279" si="6">S249</f>
@@ -6597,10 +6595,10 @@
         <v>22</v>
       </c>
       <c r="O274" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R274" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S274" s="15">
         <f t="shared" si="6"/>
@@ -6612,10 +6610,10 @@
         <v>22</v>
       </c>
       <c r="O275" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R275" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S275" s="15">
         <f t="shared" si="6"/>
@@ -6627,10 +6625,10 @@
         <v>22</v>
       </c>
       <c r="O276" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R276" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S276" s="15">
         <f t="shared" si="6"/>
@@ -6642,10 +6640,10 @@
         <v>22</v>
       </c>
       <c r="O277" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R277" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S277" s="15">
         <f t="shared" si="6"/>
@@ -6657,10 +6655,10 @@
         <v>22</v>
       </c>
       <c r="O278" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R278" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S278" s="15">
         <f t="shared" si="6"/>
@@ -6672,10 +6670,10 @@
         <v>22</v>
       </c>
       <c r="O279" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R279" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S279" s="15">
         <f t="shared" si="6"/>
@@ -6684,7 +6682,7 @@
     </row>
     <row r="281" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A281" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B281" s="16"/>
       <c r="C281" s="16"/>
@@ -6695,10 +6693,10 @@
         <v>13</v>
       </c>
       <c r="O282" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R282" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S282">
         <v>3</v>
@@ -6709,10 +6707,10 @@
         <v>13</v>
       </c>
       <c r="O283" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R283" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S283">
         <v>3</v>
@@ -6723,10 +6721,10 @@
         <v>13</v>
       </c>
       <c r="O284" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R284" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S284">
         <v>3</v>
@@ -6737,10 +6735,10 @@
         <v>13</v>
       </c>
       <c r="O285" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R285" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S285">
         <v>3</v>
@@ -6751,10 +6749,10 @@
         <v>13</v>
       </c>
       <c r="O286" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R286" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S286">
         <v>10</v>
@@ -6765,10 +6763,10 @@
         <v>13</v>
       </c>
       <c r="O287" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R287" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S287">
         <v>5</v>
@@ -6779,10 +6777,10 @@
         <v>13</v>
       </c>
       <c r="O288" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R288" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S288">
         <v>0</v>
@@ -6793,10 +6791,10 @@
         <v>13</v>
       </c>
       <c r="O289" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R289" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S289">
         <v>-10</v>
@@ -6807,10 +6805,10 @@
         <v>14</v>
       </c>
       <c r="O290" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R290" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S290" s="15">
         <f>S282</f>
@@ -6822,10 +6820,10 @@
         <v>14</v>
       </c>
       <c r="O291" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R291" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S291" s="15">
         <f t="shared" ref="S291:S297" si="7">S283</f>
@@ -6837,10 +6835,10 @@
         <v>14</v>
       </c>
       <c r="O292" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R292" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S292" s="15">
         <f t="shared" si="7"/>
@@ -6852,10 +6850,10 @@
         <v>14</v>
       </c>
       <c r="O293" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R293" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S293" s="15">
         <f t="shared" si="7"/>
@@ -6867,10 +6865,10 @@
         <v>14</v>
       </c>
       <c r="O294" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R294" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S294" s="15">
         <f t="shared" si="7"/>
@@ -6882,10 +6880,10 @@
         <v>14</v>
       </c>
       <c r="O295" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R295" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S295" s="15">
         <f t="shared" si="7"/>
@@ -6897,10 +6895,10 @@
         <v>14</v>
       </c>
       <c r="O296" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R296" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S296" s="15">
         <f t="shared" si="7"/>
@@ -6912,10 +6910,10 @@
         <v>14</v>
       </c>
       <c r="O297" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R297" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S297" s="15">
         <f t="shared" si="7"/>
@@ -6927,10 +6925,10 @@
         <v>18</v>
       </c>
       <c r="O298" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R298" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S298" s="15">
         <f>S282</f>
@@ -6942,10 +6940,10 @@
         <v>18</v>
       </c>
       <c r="O299" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R299" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S299" s="15">
         <f t="shared" ref="S299:S305" si="8">S283</f>
@@ -6957,10 +6955,10 @@
         <v>18</v>
       </c>
       <c r="O300" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R300" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S300" s="15">
         <f t="shared" si="8"/>
@@ -6972,10 +6970,10 @@
         <v>18</v>
       </c>
       <c r="O301" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R301" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S301" s="15">
         <f t="shared" si="8"/>
@@ -6987,10 +6985,10 @@
         <v>18</v>
       </c>
       <c r="O302" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R302" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S302" s="15">
         <f t="shared" si="8"/>
@@ -7002,10 +7000,10 @@
         <v>18</v>
       </c>
       <c r="O303" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R303" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S303" s="15">
         <f t="shared" si="8"/>
@@ -7017,10 +7015,10 @@
         <v>18</v>
       </c>
       <c r="O304" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R304" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S304" s="15">
         <f t="shared" si="8"/>
@@ -7032,10 +7030,10 @@
         <v>18</v>
       </c>
       <c r="O305" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R305" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S305" s="15">
         <f t="shared" si="8"/>
@@ -7044,13 +7042,13 @@
     </row>
     <row r="306" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O306" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R306" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S306" s="15">
         <f>S282</f>
@@ -7059,13 +7057,13 @@
     </row>
     <row r="307" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O307" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R307" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S307" s="15">
         <f t="shared" ref="S307:S313" si="9">S283</f>
@@ -7074,13 +7072,13 @@
     </row>
     <row r="308" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O308" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R308" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S308" s="15">
         <f t="shared" si="9"/>
@@ -7089,13 +7087,13 @@
     </row>
     <row r="309" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O309" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R309" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S309" s="15">
         <f t="shared" si="9"/>
@@ -7104,13 +7102,13 @@
     </row>
     <row r="310" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O310" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R310" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S310" s="15">
         <f t="shared" si="9"/>
@@ -7119,13 +7117,13 @@
     </row>
     <row r="311" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O311" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R311" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S311" s="15">
         <f t="shared" si="9"/>
@@ -7134,13 +7132,13 @@
     </row>
     <row r="312" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O312" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R312" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S312" s="15">
         <f t="shared" si="9"/>
@@ -7149,13 +7147,13 @@
     </row>
     <row r="313" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O313" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R313" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S313" s="15">
         <f t="shared" si="9"/>
@@ -7167,10 +7165,10 @@
         <v>21</v>
       </c>
       <c r="O314" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R314" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S314" s="15">
         <f t="shared" ref="S314:S321" si="10">S282</f>
@@ -7182,10 +7180,10 @@
         <v>21</v>
       </c>
       <c r="O315" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R315" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S315" s="15">
         <f t="shared" si="10"/>
@@ -7197,10 +7195,10 @@
         <v>21</v>
       </c>
       <c r="O316" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R316" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S316" s="15">
         <f t="shared" si="10"/>
@@ -7212,10 +7210,10 @@
         <v>21</v>
       </c>
       <c r="O317" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R317" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S317" s="15">
         <f t="shared" si="10"/>
@@ -7227,10 +7225,10 @@
         <v>21</v>
       </c>
       <c r="O318" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R318" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S318" s="15">
         <f t="shared" si="10"/>
@@ -7242,10 +7240,10 @@
         <v>21</v>
       </c>
       <c r="O319" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R319" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S319" s="15">
         <f t="shared" si="10"/>
@@ -7257,10 +7255,10 @@
         <v>21</v>
       </c>
       <c r="O320" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R320" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S320" s="15">
         <f t="shared" si="10"/>
@@ -7272,10 +7270,10 @@
         <v>21</v>
       </c>
       <c r="O321" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R321" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S321" s="15">
         <f t="shared" si="10"/>
@@ -7287,10 +7285,10 @@
         <v>26</v>
       </c>
       <c r="O322" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R322" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S322" s="15">
         <f t="shared" ref="S322:S329" si="11">S282</f>
@@ -7302,10 +7300,10 @@
         <v>26</v>
       </c>
       <c r="O323" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R323" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S323" s="15">
         <f t="shared" si="11"/>
@@ -7317,10 +7315,10 @@
         <v>26</v>
       </c>
       <c r="O324" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R324" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S324" s="15">
         <f t="shared" si="11"/>
@@ -7332,10 +7330,10 @@
         <v>26</v>
       </c>
       <c r="O325" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R325" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S325" s="15">
         <f t="shared" si="11"/>
@@ -7347,10 +7345,10 @@
         <v>26</v>
       </c>
       <c r="O326" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R326" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S326" s="15">
         <f t="shared" si="11"/>
@@ -7362,10 +7360,10 @@
         <v>26</v>
       </c>
       <c r="O327" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R327" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S327" s="15">
         <f t="shared" si="11"/>
@@ -7377,10 +7375,10 @@
         <v>26</v>
       </c>
       <c r="O328" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R328" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S328" s="15">
         <f t="shared" si="11"/>
@@ -7392,10 +7390,10 @@
         <v>26</v>
       </c>
       <c r="O329" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R329" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S329" s="15">
         <f t="shared" si="11"/>
@@ -7407,10 +7405,10 @@
         <v>25</v>
       </c>
       <c r="O330" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R330" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S330" s="15">
         <f t="shared" ref="S330:S337" si="12">S282</f>
@@ -7422,10 +7420,10 @@
         <v>25</v>
       </c>
       <c r="O331" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R331" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S331" s="15">
         <f t="shared" si="12"/>
@@ -7437,10 +7435,10 @@
         <v>25</v>
       </c>
       <c r="O332" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R332" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S332" s="15">
         <f t="shared" si="12"/>
@@ -7452,10 +7450,10 @@
         <v>25</v>
       </c>
       <c r="O333" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R333" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S333" s="15">
         <f t="shared" si="12"/>
@@ -7467,10 +7465,10 @@
         <v>25</v>
       </c>
       <c r="O334" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R334" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S334" s="15">
         <f t="shared" si="12"/>
@@ -7482,10 +7480,10 @@
         <v>25</v>
       </c>
       <c r="O335" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R335" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S335" s="15">
         <f t="shared" si="12"/>
@@ -7497,10 +7495,10 @@
         <v>25</v>
       </c>
       <c r="O336" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R336" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S336" s="15">
         <f t="shared" si="12"/>
@@ -7512,10 +7510,10 @@
         <v>25</v>
       </c>
       <c r="O337" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R337" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S337" s="15">
         <f t="shared" si="12"/>
@@ -7530,17 +7528,17 @@
       <c r="C338" s="6"/>
       <c r="D338" s="6"/>
       <c r="O338" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R338" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S338" s="15">
         <f t="shared" ref="S338:S345" si="13">S282</f>
         <v>3</v>
       </c>
       <c r="U338" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="339" spans="1:21" x14ac:dyDescent="0.25">
@@ -7551,10 +7549,10 @@
       <c r="C339" s="6"/>
       <c r="D339" s="6"/>
       <c r="O339" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R339" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S339" s="15">
         <f t="shared" si="13"/>
@@ -7569,10 +7567,10 @@
       <c r="C340" s="6"/>
       <c r="D340" s="6"/>
       <c r="O340" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R340" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S340" s="15">
         <f t="shared" si="13"/>
@@ -7587,10 +7585,10 @@
       <c r="C341" s="6"/>
       <c r="D341" s="6"/>
       <c r="O341" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R341" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S341" s="15">
         <f t="shared" si="13"/>
@@ -7605,10 +7603,10 @@
       <c r="C342" s="6"/>
       <c r="D342" s="6"/>
       <c r="O342" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R342" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S342" s="15">
         <f t="shared" si="13"/>
@@ -7623,10 +7621,10 @@
       <c r="C343" s="6"/>
       <c r="D343" s="6"/>
       <c r="O343" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R343" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S343" s="15">
         <f t="shared" si="13"/>
@@ -7641,10 +7639,10 @@
       <c r="C344" s="6"/>
       <c r="D344" s="6"/>
       <c r="O344" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R344" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S344" s="15">
         <f t="shared" si="13"/>
@@ -7659,10 +7657,10 @@
       <c r="C345" s="6"/>
       <c r="D345" s="6"/>
       <c r="O345" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R345" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S345" s="15">
         <f t="shared" si="13"/>
@@ -7677,17 +7675,17 @@
       <c r="C346" s="6"/>
       <c r="D346" s="6"/>
       <c r="O346" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R346" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S346" s="15">
         <f>S282</f>
         <v>3</v>
       </c>
       <c r="U346" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="347" spans="1:21" x14ac:dyDescent="0.25">
@@ -7698,10 +7696,10 @@
       <c r="C347" s="6"/>
       <c r="D347" s="6"/>
       <c r="O347" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R347" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S347" s="15">
         <f t="shared" ref="S347:S353" si="14">S283</f>
@@ -7716,10 +7714,10 @@
       <c r="C348" s="6"/>
       <c r="D348" s="6"/>
       <c r="O348" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R348" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S348" s="15">
         <f t="shared" si="14"/>
@@ -7734,10 +7732,10 @@
       <c r="C349" s="6"/>
       <c r="D349" s="6"/>
       <c r="O349" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R349" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S349" s="15">
         <f t="shared" si="14"/>
@@ -7752,10 +7750,10 @@
       <c r="C350" s="6"/>
       <c r="D350" s="6"/>
       <c r="O350" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R350" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S350" s="15">
         <f t="shared" si="14"/>
@@ -7770,10 +7768,10 @@
       <c r="C351" s="6"/>
       <c r="D351" s="6"/>
       <c r="O351" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R351" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S351" s="15">
         <f t="shared" si="14"/>
@@ -7786,10 +7784,10 @@
       </c>
       <c r="B352" s="4"/>
       <c r="O352" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R352" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S352" s="15">
         <f t="shared" si="14"/>
@@ -7802,10 +7800,10 @@
       </c>
       <c r="B353" s="4"/>
       <c r="O353" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R353" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S353" s="15">
         <f t="shared" si="14"/>
@@ -7814,7 +7812,7 @@
     </row>
     <row r="354" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A354" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B354" s="16"/>
       <c r="C354" s="16"/>
@@ -7825,10 +7823,10 @@
         <v>31</v>
       </c>
       <c r="O355" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R355" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S355">
         <v>7</v>
@@ -7839,10 +7837,10 @@
         <v>31</v>
       </c>
       <c r="O356" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R356" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S356">
         <v>7</v>
@@ -7853,10 +7851,10 @@
         <v>31</v>
       </c>
       <c r="O357" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R357" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S357">
         <v>7</v>
@@ -7867,10 +7865,10 @@
         <v>31</v>
       </c>
       <c r="O358" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R358" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S358">
         <v>7</v>
@@ -7881,10 +7879,10 @@
         <v>31</v>
       </c>
       <c r="O359" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R359" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S359">
         <v>15.5</v>
@@ -7895,10 +7893,10 @@
         <v>31</v>
       </c>
       <c r="O360" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R360" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S360">
         <v>10.5</v>
@@ -7909,10 +7907,10 @@
         <v>31</v>
       </c>
       <c r="O361" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R361" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S361">
         <v>0.5</v>
@@ -7923,10 +7921,10 @@
         <v>31</v>
       </c>
       <c r="O362" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R362" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S362">
         <v>-9.5</v>
@@ -7937,10 +7935,10 @@
         <v>32</v>
       </c>
       <c r="O363" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R363" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S363">
         <v>7</v>
@@ -7951,10 +7949,10 @@
         <v>32</v>
       </c>
       <c r="O364" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R364" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S364">
         <v>7</v>
@@ -7965,10 +7963,10 @@
         <v>32</v>
       </c>
       <c r="O365" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R365" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S365">
         <v>7</v>
@@ -7979,10 +7977,10 @@
         <v>32</v>
       </c>
       <c r="O366" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R366" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S366">
         <v>7</v>
@@ -7993,10 +7991,10 @@
         <v>32</v>
       </c>
       <c r="O367" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R367" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S367">
         <v>16</v>
@@ -8007,10 +8005,10 @@
         <v>32</v>
       </c>
       <c r="O368" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R368" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S368">
         <v>11</v>
@@ -8021,10 +8019,10 @@
         <v>32</v>
       </c>
       <c r="O369" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R369" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S369">
         <v>1</v>
@@ -8035,10 +8033,10 @@
         <v>32</v>
       </c>
       <c r="O370" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R370" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S370">
         <v>-4</v>
@@ -8057,10 +8055,10 @@
         <v>37</v>
       </c>
       <c r="O373" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R373" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S373">
         <v>3</v>
@@ -8071,10 +8069,10 @@
         <v>37</v>
       </c>
       <c r="O374" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R374" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S374">
         <v>3</v>
@@ -8085,10 +8083,10 @@
         <v>37</v>
       </c>
       <c r="O375" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R375" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S375">
         <v>3</v>
@@ -8099,10 +8097,10 @@
         <v>37</v>
       </c>
       <c r="O376" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R376" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S376">
         <v>7</v>
@@ -8113,10 +8111,10 @@
         <v>37</v>
       </c>
       <c r="O377" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R377" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S377">
         <v>-3</v>
@@ -8127,10 +8125,10 @@
         <v>37</v>
       </c>
       <c r="O378" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R378" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S378">
         <v>-8</v>
@@ -8141,17 +8139,17 @@
         <v>67</v>
       </c>
       <c r="O379" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R379" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S379" s="19">
         <f>S373</f>
         <v>3</v>
       </c>
       <c r="U379" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="380" spans="1:21" x14ac:dyDescent="0.25">
@@ -8159,10 +8157,10 @@
         <v>67</v>
       </c>
       <c r="O380" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R380" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S380" s="19">
         <f t="shared" ref="S380:S384" si="15">S374</f>
@@ -8174,10 +8172,10 @@
         <v>67</v>
       </c>
       <c r="O381" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R381" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S381" s="19">
         <f t="shared" si="15"/>
@@ -8189,10 +8187,10 @@
         <v>67</v>
       </c>
       <c r="O382" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R382" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S382" s="19">
         <f t="shared" si="15"/>
@@ -8204,10 +8202,10 @@
         <v>67</v>
       </c>
       <c r="O383" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R383" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S383" s="19">
         <f t="shared" si="15"/>
@@ -8219,10 +8217,10 @@
         <v>67</v>
       </c>
       <c r="O384" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R384" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S384" s="19">
         <f t="shared" si="15"/>
@@ -8231,7 +8229,7 @@
     </row>
     <row r="386" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A386" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B386" s="16"/>
       <c r="C386" s="16"/>
@@ -8242,10 +8240,10 @@
         <v>39</v>
       </c>
       <c r="O387" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R387" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S387">
         <v>3</v>
@@ -8256,10 +8254,10 @@
         <v>39</v>
       </c>
       <c r="O388" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R388" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S388">
         <v>3</v>
@@ -8270,10 +8268,10 @@
         <v>39</v>
       </c>
       <c r="O389" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R389" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S389">
         <v>3</v>
@@ -8284,10 +8282,10 @@
         <v>39</v>
       </c>
       <c r="O390" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R390" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S390">
         <v>3</v>
@@ -8298,10 +8296,10 @@
         <v>39</v>
       </c>
       <c r="O391" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R391" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S391">
         <v>3</v>
@@ -8312,10 +8310,10 @@
         <v>39</v>
       </c>
       <c r="O392" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R392" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S392">
         <v>3</v>
@@ -8326,10 +8324,10 @@
         <v>39</v>
       </c>
       <c r="O393" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R393" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S393">
         <v>5</v>
@@ -8340,10 +8338,10 @@
         <v>39</v>
       </c>
       <c r="O394" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R394" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S394">
         <v>0</v>
@@ -8354,10 +8352,10 @@
         <v>39</v>
       </c>
       <c r="O395" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R395" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S395">
         <v>-5</v>
@@ -8368,10 +8366,10 @@
         <v>39</v>
       </c>
       <c r="O396" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R396" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S396">
         <v>-10</v>
@@ -8382,10 +8380,10 @@
         <v>39</v>
       </c>
       <c r="O397" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R397" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S397">
         <v>-15</v>
@@ -8396,10 +8394,10 @@
         <v>39</v>
       </c>
       <c r="O398" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R398" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S398">
         <v>-20</v>
@@ -8407,7 +8405,7 @@
     </row>
     <row r="400" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A400" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B400" s="16"/>
       <c r="C400" s="16"/>
@@ -8418,10 +8416,10 @@
         <v>33</v>
       </c>
       <c r="O401" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R401" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S401">
         <v>0.5</v>
@@ -8432,10 +8430,10 @@
         <v>33</v>
       </c>
       <c r="O402" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R402" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S402">
         <v>0.5</v>
@@ -8446,10 +8444,10 @@
         <v>33</v>
       </c>
       <c r="O403" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R403" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S403">
         <v>0.5</v>
@@ -8460,10 +8458,10 @@
         <v>33</v>
       </c>
       <c r="O404" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R404" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S404">
         <v>0.5</v>
@@ -8474,10 +8472,10 @@
         <v>33</v>
       </c>
       <c r="O405" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R405" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S405">
         <v>0.5</v>
@@ -8488,10 +8486,10 @@
         <v>33</v>
       </c>
       <c r="O406" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R406" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S406">
         <v>0.5</v>
@@ -8502,10 +8500,10 @@
         <v>33</v>
       </c>
       <c r="O407" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R407" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S407">
         <v>55</v>
@@ -8516,10 +8514,10 @@
         <v>33</v>
       </c>
       <c r="O408" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R408" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S408">
         <v>35</v>
@@ -8530,10 +8528,10 @@
         <v>33</v>
       </c>
       <c r="O409" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R409" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S409">
         <v>25</v>
@@ -8544,10 +8542,10 @@
         <v>33</v>
       </c>
       <c r="O410" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R410" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S410">
         <v>15</v>
@@ -8558,10 +8556,10 @@
         <v>33</v>
       </c>
       <c r="O411" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R411" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S411">
         <v>0</v>
@@ -8572,10 +8570,10 @@
         <v>33</v>
       </c>
       <c r="O412" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R412" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S412">
         <v>-5</v>
@@ -8586,10 +8584,10 @@
         <v>34</v>
       </c>
       <c r="O413" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R413" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S413" s="15">
         <f>S401</f>
@@ -8601,10 +8599,10 @@
         <v>34</v>
       </c>
       <c r="O414" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R414" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S414" s="15">
         <f t="shared" ref="S414:S424" si="16">S402</f>
@@ -8616,10 +8614,10 @@
         <v>34</v>
       </c>
       <c r="O415" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R415" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S415" s="15">
         <f t="shared" si="16"/>
@@ -8631,10 +8629,10 @@
         <v>34</v>
       </c>
       <c r="O416" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R416" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S416" s="15">
         <f t="shared" si="16"/>
@@ -8646,10 +8644,10 @@
         <v>34</v>
       </c>
       <c r="O417" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R417" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S417" s="15">
         <f t="shared" si="16"/>
@@ -8661,10 +8659,10 @@
         <v>34</v>
       </c>
       <c r="O418" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R418" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S418" s="15">
         <f t="shared" si="16"/>
@@ -8676,10 +8674,10 @@
         <v>34</v>
       </c>
       <c r="O419" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R419" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S419" s="15">
         <f t="shared" si="16"/>
@@ -8691,10 +8689,10 @@
         <v>34</v>
       </c>
       <c r="O420" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R420" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S420" s="15">
         <f t="shared" si="16"/>
@@ -8706,10 +8704,10 @@
         <v>34</v>
       </c>
       <c r="O421" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R421" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S421" s="15">
         <f t="shared" si="16"/>
@@ -8721,10 +8719,10 @@
         <v>34</v>
       </c>
       <c r="O422" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R422" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S422" s="15">
         <f t="shared" si="16"/>
@@ -8736,10 +8734,10 @@
         <v>34</v>
       </c>
       <c r="O423" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R423" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S423" s="15">
         <f t="shared" si="16"/>
@@ -8751,10 +8749,10 @@
         <v>34</v>
       </c>
       <c r="O424" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R424" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S424" s="15">
         <f t="shared" si="16"/>
@@ -8763,7 +8761,7 @@
     </row>
     <row r="426" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A426" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B426" s="16"/>
       <c r="C426" s="16"/>
@@ -8774,10 +8772,10 @@
         <v>27</v>
       </c>
       <c r="O427" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R427" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S427">
         <v>20</v>
@@ -8788,10 +8786,10 @@
         <v>27</v>
       </c>
       <c r="O428" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R428" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S428">
         <v>15</v>
@@ -8802,10 +8800,10 @@
         <v>27</v>
       </c>
       <c r="O429" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R429" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S429">
         <v>10</v>
@@ -8813,31 +8811,31 @@
     </row>
     <row r="430" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="O430" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R430" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S430" s="15">
         <f>S427</f>
         <v>20</v>
       </c>
       <c r="U430" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="431" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="O431" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R431" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S431" s="15">
         <f t="shared" ref="S431:S432" si="17">S428</f>
@@ -8846,13 +8844,13 @@
     </row>
     <row r="432" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="O432" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R432" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S432" s="15">
         <f t="shared" si="17"/>
@@ -8864,10 +8862,10 @@
         <v>29</v>
       </c>
       <c r="O433" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R433" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S433" s="15">
         <f>S427</f>
@@ -8879,10 +8877,10 @@
         <v>29</v>
       </c>
       <c r="O434" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R434" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S434" s="15">
         <f t="shared" ref="S434:S435" si="18">S428</f>
@@ -8894,10 +8892,10 @@
         <v>29</v>
       </c>
       <c r="O435" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R435" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S435" s="15">
         <f t="shared" si="18"/>
@@ -8909,10 +8907,10 @@
         <v>35</v>
       </c>
       <c r="O436" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R436" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S436">
         <v>60</v>
@@ -8923,10 +8921,10 @@
         <v>35</v>
       </c>
       <c r="O437" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R437" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S437">
         <v>45</v>
@@ -8937,10 +8935,10 @@
         <v>35</v>
       </c>
       <c r="O438" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R438" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S438">
         <v>35</v>
@@ -8951,10 +8949,10 @@
         <v>35</v>
       </c>
       <c r="O439" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R439" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S439">
         <v>25</v>
@@ -8965,10 +8963,10 @@
         <v>35</v>
       </c>
       <c r="O440" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R440" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S440">
         <v>10</v>
@@ -8979,10 +8977,10 @@
         <v>38</v>
       </c>
       <c r="O441" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R441" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S441">
         <v>15</v>
@@ -8993,10 +8991,10 @@
         <v>38</v>
       </c>
       <c r="O442" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R442" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S442">
         <v>5</v>
@@ -9010,19 +9008,19 @@
       <c r="C443" s="6"/>
       <c r="D443" s="6"/>
       <c r="O443" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R443" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S443">
         <v>25</v>
       </c>
       <c r="U443" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="V443" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="444" spans="1:22" x14ac:dyDescent="0.25">
@@ -9033,10 +9031,10 @@
       <c r="C444" s="6"/>
       <c r="D444" s="6"/>
       <c r="O444" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R444" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S444">
         <v>25</v>
@@ -9050,10 +9048,10 @@
       <c r="C445" s="6"/>
       <c r="D445" s="6"/>
       <c r="O445" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R445" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S445">
         <v>25</v>
@@ -9061,7 +9059,7 @@
     </row>
     <row r="447" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A447" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B447" s="16"/>
       <c r="C447" s="16"/>
@@ -9072,7 +9070,7 @@
         <v>45</v>
       </c>
       <c r="R448" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S448">
         <v>0.46200000000000002</v>
@@ -9083,7 +9081,7 @@
         <v>45</v>
       </c>
       <c r="R449" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S449">
         <v>13.85</v>
@@ -9097,14 +9095,14 @@
       <c r="C450" s="6"/>
       <c r="D450" s="6"/>
       <c r="R450" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S450" s="15">
         <f>S448</f>
         <v>0.46200000000000002</v>
       </c>
       <c r="U450" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="451" spans="1:21" x14ac:dyDescent="0.25">
@@ -9115,7 +9113,7 @@
       <c r="C451" s="6"/>
       <c r="D451" s="6"/>
       <c r="R451" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S451" s="15">
         <f>S449</f>
@@ -9127,7 +9125,7 @@
         <v>44</v>
       </c>
       <c r="R452" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S452">
         <v>2.5</v>
@@ -9138,7 +9136,7 @@
         <v>44</v>
       </c>
       <c r="R453" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S453">
         <v>-45</v>
@@ -9149,13 +9147,13 @@
         <v>47</v>
       </c>
       <c r="R454" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S454">
         <v>2.6669999999999998</v>
       </c>
       <c r="U454" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="455" spans="1:21" x14ac:dyDescent="0.25">
@@ -9163,7 +9161,7 @@
         <v>47</v>
       </c>
       <c r="R455" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S455">
         <v>-33.33</v>
@@ -9177,14 +9175,14 @@
       <c r="C456" s="6"/>
       <c r="D456" s="6"/>
       <c r="R456" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S456" s="15">
         <f>S454</f>
         <v>2.6669999999999998</v>
       </c>
       <c r="U456" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="457" spans="1:21" x14ac:dyDescent="0.25">
@@ -9195,7 +9193,7 @@
       <c r="C457" s="6"/>
       <c r="D457" s="6"/>
       <c r="R457" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S457" s="15">
         <f>S455</f>
@@ -9208,14 +9206,14 @@
       </c>
       <c r="B458" s="4"/>
       <c r="R458" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S458" s="15">
         <f>S456</f>
         <v>2.6669999999999998</v>
       </c>
       <c r="U458" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="459" spans="1:21" x14ac:dyDescent="0.25">
@@ -9224,7 +9222,7 @@
       </c>
       <c r="B459" s="4"/>
       <c r="R459" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S459" s="15">
         <f>S457</f>
@@ -9236,7 +9234,7 @@
         <v>48</v>
       </c>
       <c r="R460" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S460">
         <v>0.5</v>
@@ -9247,7 +9245,7 @@
         <v>48</v>
       </c>
       <c r="R461" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S461">
         <v>15</v>
@@ -9258,7 +9256,7 @@
         <v>49</v>
       </c>
       <c r="R462" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S462">
         <v>0.66700000000000004</v>
@@ -9269,7 +9267,7 @@
         <v>49</v>
       </c>
       <c r="R463" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S463">
         <v>-3.33</v>
@@ -9280,7 +9278,7 @@
         <v>50</v>
       </c>
       <c r="R464" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S464" s="15">
         <f>S462</f>
@@ -9292,7 +9290,7 @@
         <v>50</v>
       </c>
       <c r="R465" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S465" s="15">
         <f>S463</f>
@@ -9304,13 +9302,13 @@
         <v>66</v>
       </c>
       <c r="R467" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S467">
         <v>0</v>
       </c>
       <c r="U467" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="468" spans="1:22" x14ac:dyDescent="0.25">
@@ -9318,7 +9316,7 @@
         <v>69</v>
       </c>
       <c r="R468" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S468">
         <v>0</v>
@@ -9329,7 +9327,7 @@
         <v>70</v>
       </c>
       <c r="R469" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S469">
         <v>0</v>
@@ -9340,7 +9338,7 @@
         <v>42</v>
       </c>
       <c r="R470" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S470">
         <v>0</v>
@@ -9351,7 +9349,7 @@
         <v>43</v>
       </c>
       <c r="R471" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S471">
         <v>0</v>
@@ -9373,13 +9371,13 @@
       <c r="C474" s="6"/>
       <c r="D474" s="6"/>
       <c r="R474" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S474">
         <v>10</v>
       </c>
       <c r="V474" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="475" spans="1:22" x14ac:dyDescent="0.25">
@@ -9390,16 +9388,16 @@
       <c r="C475" s="6"/>
       <c r="D475" s="6"/>
       <c r="R475" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S475">
         <v>15</v>
       </c>
       <c r="U475" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V475" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="476" spans="1:22" x14ac:dyDescent="0.25">
@@ -9434,13 +9432,13 @@
       <c r="C479" s="6"/>
       <c r="D479" s="6"/>
       <c r="R479" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S479">
         <v>15</v>
       </c>
       <c r="V479" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="480" spans="1:22" x14ac:dyDescent="0.25">
@@ -9451,14 +9449,14 @@
       <c r="C480" s="6"/>
       <c r="D480" s="6"/>
       <c r="R480" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S480" s="19">
         <f>S479</f>
         <v>15</v>
       </c>
       <c r="U480" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="481" spans="1:22" x14ac:dyDescent="0.25">
@@ -9469,14 +9467,14 @@
       <c r="C481" s="6"/>
       <c r="D481" s="6"/>
       <c r="R481" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S481" s="19">
         <f>S479</f>
         <v>15</v>
       </c>
       <c r="U481" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="482" spans="1:22" x14ac:dyDescent="0.25">
@@ -9493,13 +9491,13 @@
       <c r="C483" s="6"/>
       <c r="D483" s="6"/>
       <c r="R483" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S483">
         <v>0.6</v>
       </c>
       <c r="V483" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="484" spans="1:22" x14ac:dyDescent="0.25">
@@ -9510,13 +9508,13 @@
       <c r="C484" s="6"/>
       <c r="D484" s="6"/>
       <c r="R484" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S484" s="4">
         <v>1.6</v>
       </c>
       <c r="V484" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="485" spans="1:22" x14ac:dyDescent="0.25">
@@ -9527,14 +9525,14 @@
       <c r="C485" s="6"/>
       <c r="D485" s="6"/>
       <c r="R485" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S485" s="19">
         <f>AVERAGE(S483:S484)</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="U485" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="486" spans="1:22" x14ac:dyDescent="0.25">
@@ -9545,7 +9543,7 @@
       <c r="C486" s="6"/>
       <c r="D486" s="6"/>
       <c r="R486" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S486" s="19">
         <f>AVERAGE(S483:S484)</f>
@@ -9560,7 +9558,7 @@
       <c r="C487" s="6"/>
       <c r="D487" s="6"/>
       <c r="R487" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S487" s="19">
         <f>AVERAGE(S483:S484)</f>
@@ -9575,7 +9573,7 @@
       <c r="C488" s="6"/>
       <c r="D488" s="6"/>
       <c r="R488" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S488" s="19">
         <f>AVERAGE(S483:S484)</f>
@@ -9590,7 +9588,7 @@
       <c r="C489" s="6"/>
       <c r="D489" s="6"/>
       <c r="R489" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S489" s="19">
         <f>AVERAGE(S483:S484)</f>
@@ -9599,7 +9597,7 @@
     </row>
     <row r="491" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
@@ -9625,7 +9623,7 @@
     </row>
     <row r="492" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A492" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B492" s="14"/>
       <c r="C492" s="14"/>
@@ -9633,7 +9631,7 @@
     </row>
     <row r="493" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A493" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B493" s="14"/>
       <c r="C493" s="14"/>
@@ -9641,7 +9639,7 @@
     </row>
     <row r="494" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A494" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B494" s="14"/>
       <c r="C494" s="14"/>
@@ -9649,19 +9647,19 @@
     </row>
     <row r="495" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R495" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="S495" s="18">
         <v>1</v>
       </c>
       <c r="T495" s="5"/>
       <c r="U495" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="496" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C496" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D496" s="4"/>
       <c r="E496" s="4"/>
@@ -9678,20 +9676,20 @@
       <c r="P496" s="4"/>
       <c r="Q496" s="4"/>
       <c r="R496" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="S496" s="17">
         <v>1.4</v>
       </c>
       <c r="T496" s="4"/>
       <c r="U496" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="V496" s="4"/>
     </row>
     <row r="497" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C497" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D497" s="4"/>
       <c r="E497" s="4"/>
@@ -9708,20 +9706,20 @@
       <c r="P497" s="4"/>
       <c r="Q497" s="4"/>
       <c r="R497" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="S497" s="17">
         <v>1.4</v>
       </c>
       <c r="T497" s="4"/>
       <c r="U497" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="V497" s="4"/>
     </row>
     <row r="498" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C498" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E498" s="4"/>
       <c r="F498" s="4"/>
@@ -9737,14 +9735,14 @@
       <c r="P498" s="4"/>
       <c r="Q498" s="4"/>
       <c r="R498" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="S498" s="17">
         <v>1.2</v>
       </c>
       <c r="T498" s="4"/>
       <c r="U498" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="V498" s="4"/>
     </row>
@@ -9766,14 +9764,14 @@
       <c r="P499" s="4"/>
       <c r="Q499" s="4"/>
       <c r="R499" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="S499" s="17">
         <v>1.25</v>
       </c>
       <c r="T499" s="4"/>
       <c r="U499" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="V499" s="4"/>
     </row>
@@ -9785,7 +9783,7 @@
     </row>
     <row r="501" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B501" s="12"/>
       <c r="C501" s="12"/>
@@ -9811,7 +9809,7 @@
     </row>
     <row r="502" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
@@ -9837,7 +9835,7 @@
     </row>
     <row r="503" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A503" s="14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B503" s="14"/>
       <c r="C503" s="14"/>
@@ -9845,7 +9843,7 @@
     </row>
     <row r="504" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A504" s="14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B504" s="14"/>
       <c r="C504" s="14"/>
@@ -9853,30 +9851,30 @@
     </row>
     <row r="505" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R505" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S505" s="5">
         <v>0</v>
       </c>
       <c r="T505" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="U505" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="506" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R506" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S506" s="5">
         <v>0</v>
       </c>
       <c r="T506" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="U506" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="507" spans="1:22" x14ac:dyDescent="0.25">
@@ -9887,7 +9885,7 @@
     </row>
     <row r="508" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A508" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B508" s="16"/>
       <c r="C508" s="16"/>
@@ -9902,10 +9900,10 @@
         <v>6</v>
       </c>
       <c r="P509" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R509" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S509">
         <v>5</v>
@@ -9916,10 +9914,10 @@
         <v>6</v>
       </c>
       <c r="P510" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R510" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S510" s="4">
         <v>5</v>
@@ -9930,10 +9928,10 @@
         <v>6</v>
       </c>
       <c r="P511" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R511" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S511" s="4">
         <v>5</v>
@@ -9944,10 +9942,10 @@
         <v>6</v>
       </c>
       <c r="P512" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R512" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S512" s="4">
         <v>15</v>
@@ -9958,10 +9956,10 @@
         <v>6</v>
       </c>
       <c r="P513" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R513" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S513" s="4">
         <v>5</v>
@@ -9972,10 +9970,10 @@
         <v>6</v>
       </c>
       <c r="P514" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R514" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S514" s="4">
         <v>-15</v>
@@ -9986,10 +9984,10 @@
         <v>24</v>
       </c>
       <c r="P515" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R515" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S515" s="15">
         <f t="shared" ref="S515:S520" si="19">S509</f>
@@ -10001,10 +9999,10 @@
         <v>24</v>
       </c>
       <c r="P516" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R516" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S516" s="15">
         <f t="shared" si="19"/>
@@ -10016,10 +10014,10 @@
         <v>24</v>
       </c>
       <c r="P517" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R517" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S517" s="15">
         <f t="shared" si="19"/>
@@ -10031,10 +10029,10 @@
         <v>24</v>
       </c>
       <c r="P518" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R518" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S518" s="15">
         <f t="shared" si="19"/>
@@ -10046,10 +10044,10 @@
         <v>24</v>
       </c>
       <c r="P519" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R519" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S519" s="15">
         <f t="shared" si="19"/>
@@ -10061,10 +10059,10 @@
         <v>24</v>
       </c>
       <c r="P520" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R520" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S520" s="15">
         <f t="shared" si="19"/>
@@ -10076,10 +10074,10 @@
         <v>20</v>
       </c>
       <c r="P521" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R521" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S521" s="15">
         <f t="shared" ref="S521:S526" si="20">S509</f>
@@ -10091,10 +10089,10 @@
         <v>20</v>
       </c>
       <c r="P522" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R522" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S522" s="15">
         <f t="shared" si="20"/>
@@ -10106,10 +10104,10 @@
         <v>20</v>
       </c>
       <c r="P523" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R523" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S523" s="15">
         <f t="shared" si="20"/>
@@ -10121,10 +10119,10 @@
         <v>20</v>
       </c>
       <c r="P524" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R524" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S524" s="15">
         <f t="shared" si="20"/>
@@ -10136,10 +10134,10 @@
         <v>20</v>
       </c>
       <c r="P525" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R525" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S525" s="15">
         <f t="shared" si="20"/>
@@ -10151,10 +10149,10 @@
         <v>20</v>
       </c>
       <c r="P526" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R526" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S526" s="15">
         <f t="shared" si="20"/>
@@ -10166,10 +10164,10 @@
         <v>22</v>
       </c>
       <c r="P527" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R527" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S527" s="15">
         <f t="shared" ref="S527:S532" si="21">S509</f>
@@ -10181,10 +10179,10 @@
         <v>22</v>
       </c>
       <c r="P528" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R528" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S528" s="15">
         <f t="shared" si="21"/>
@@ -10196,10 +10194,10 @@
         <v>22</v>
       </c>
       <c r="P529" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R529" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S529" s="15">
         <f t="shared" si="21"/>
@@ -10211,10 +10209,10 @@
         <v>22</v>
       </c>
       <c r="P530" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R530" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S530" s="15">
         <f t="shared" si="21"/>
@@ -10226,10 +10224,10 @@
         <v>22</v>
       </c>
       <c r="P531" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R531" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S531" s="15">
         <f t="shared" si="21"/>
@@ -10241,10 +10239,10 @@
         <v>22</v>
       </c>
       <c r="P532" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R532" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S532" s="15">
         <f t="shared" si="21"/>
@@ -10253,7 +10251,7 @@
     </row>
     <row r="534" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A534" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B534" s="16"/>
       <c r="C534" s="16"/>
@@ -10264,10 +10262,10 @@
         <v>13</v>
       </c>
       <c r="P535" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R535" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S535">
         <v>5</v>
@@ -10278,10 +10276,10 @@
         <v>13</v>
       </c>
       <c r="P536" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R536" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S536">
         <v>5</v>
@@ -10292,10 +10290,10 @@
         <v>13</v>
       </c>
       <c r="P537" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R537" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S537">
         <v>5</v>
@@ -10306,10 +10304,10 @@
         <v>13</v>
       </c>
       <c r="P538" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R538" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S538">
         <v>15</v>
@@ -10320,10 +10318,10 @@
         <v>13</v>
       </c>
       <c r="P539" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R539" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S539">
         <v>5</v>
@@ -10334,10 +10332,10 @@
         <v>13</v>
       </c>
       <c r="P540" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R540" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S540">
         <v>-15</v>
@@ -10348,10 +10346,10 @@
         <v>14</v>
       </c>
       <c r="P541" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R541" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S541" s="15">
         <f t="shared" ref="S541:S546" si="22">S535</f>
@@ -10363,10 +10361,10 @@
         <v>14</v>
       </c>
       <c r="P542" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R542" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S542" s="15">
         <f t="shared" si="22"/>
@@ -10378,10 +10376,10 @@
         <v>14</v>
       </c>
       <c r="P543" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R543" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S543" s="15">
         <f t="shared" si="22"/>
@@ -10393,10 +10391,10 @@
         <v>14</v>
       </c>
       <c r="P544" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R544" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S544" s="15">
         <f t="shared" si="22"/>
@@ -10408,10 +10406,10 @@
         <v>14</v>
       </c>
       <c r="P545" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R545" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S545" s="15">
         <f t="shared" si="22"/>
@@ -10423,10 +10421,10 @@
         <v>14</v>
       </c>
       <c r="P546" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R546" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S546" s="15">
         <f t="shared" si="22"/>
@@ -10438,10 +10436,10 @@
         <v>18</v>
       </c>
       <c r="P547" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R547" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S547" s="15">
         <f t="shared" ref="S547:S552" si="23">S535</f>
@@ -10453,10 +10451,10 @@
         <v>18</v>
       </c>
       <c r="P548" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R548" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S548" s="15">
         <f t="shared" si="23"/>
@@ -10468,10 +10466,10 @@
         <v>18</v>
       </c>
       <c r="P549" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R549" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S549" s="15">
         <f t="shared" si="23"/>
@@ -10483,10 +10481,10 @@
         <v>18</v>
       </c>
       <c r="P550" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R550" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S550" s="15">
         <f t="shared" si="23"/>
@@ -10498,10 +10496,10 @@
         <v>18</v>
       </c>
       <c r="P551" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R551" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S551" s="15">
         <f t="shared" si="23"/>
@@ -10513,10 +10511,10 @@
         <v>18</v>
       </c>
       <c r="P552" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R552" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S552" s="15">
         <f t="shared" si="23"/>
@@ -10525,13 +10523,13 @@
     </row>
     <row r="553" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P553" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R553" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S553" s="15">
         <f t="shared" ref="S553:S558" si="24">S535</f>
@@ -10540,13 +10538,13 @@
     </row>
     <row r="554" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P554" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R554" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S554" s="15">
         <f t="shared" si="24"/>
@@ -10555,13 +10553,13 @@
     </row>
     <row r="555" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A555" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P555" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R555" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S555" s="15">
         <f t="shared" si="24"/>
@@ -10570,13 +10568,13 @@
     </row>
     <row r="556" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A556" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P556" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R556" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S556" s="15">
         <f t="shared" si="24"/>
@@ -10585,13 +10583,13 @@
     </row>
     <row r="557" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A557" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P557" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R557" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S557" s="15">
         <f t="shared" si="24"/>
@@ -10600,13 +10598,13 @@
     </row>
     <row r="558" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P558" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R558" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S558" s="15">
         <f t="shared" si="24"/>
@@ -10618,10 +10616,10 @@
         <v>21</v>
       </c>
       <c r="P559" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R559" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S559" s="15">
         <f t="shared" ref="S559:S564" si="25">S535</f>
@@ -10633,10 +10631,10 @@
         <v>21</v>
       </c>
       <c r="P560" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R560" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S560" s="15">
         <f t="shared" si="25"/>
@@ -10648,10 +10646,10 @@
         <v>21</v>
       </c>
       <c r="P561" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R561" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S561" s="15">
         <f t="shared" si="25"/>
@@ -10663,10 +10661,10 @@
         <v>21</v>
       </c>
       <c r="P562" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R562" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S562" s="15">
         <f t="shared" si="25"/>
@@ -10678,10 +10676,10 @@
         <v>21</v>
       </c>
       <c r="P563" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R563" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S563" s="15">
         <f t="shared" si="25"/>
@@ -10693,10 +10691,10 @@
         <v>21</v>
       </c>
       <c r="P564" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R564" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S564" s="15">
         <f t="shared" si="25"/>
@@ -10708,10 +10706,10 @@
         <v>26</v>
       </c>
       <c r="P565" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R565" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S565" s="15">
         <f t="shared" ref="S565:S570" si="26">S535</f>
@@ -10723,10 +10721,10 @@
         <v>26</v>
       </c>
       <c r="P566" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R566" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S566" s="15">
         <f t="shared" si="26"/>
@@ -10738,10 +10736,10 @@
         <v>26</v>
       </c>
       <c r="P567" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R567" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S567" s="15">
         <f t="shared" si="26"/>
@@ -10753,10 +10751,10 @@
         <v>26</v>
       </c>
       <c r="P568" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R568" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S568" s="15">
         <f t="shared" si="26"/>
@@ -10768,10 +10766,10 @@
         <v>26</v>
       </c>
       <c r="P569" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R569" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S569" s="15">
         <f t="shared" si="26"/>
@@ -10783,10 +10781,10 @@
         <v>26</v>
       </c>
       <c r="P570" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R570" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S570" s="15">
         <f t="shared" si="26"/>
@@ -10798,10 +10796,10 @@
         <v>25</v>
       </c>
       <c r="P571" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R571" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S571" s="15">
         <f t="shared" ref="S571:S576" si="27">S535</f>
@@ -10813,10 +10811,10 @@
         <v>25</v>
       </c>
       <c r="P572" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R572" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S572" s="15">
         <f t="shared" si="27"/>
@@ -10828,10 +10826,10 @@
         <v>25</v>
       </c>
       <c r="P573" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R573" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S573" s="15">
         <f t="shared" si="27"/>
@@ -10843,10 +10841,10 @@
         <v>25</v>
       </c>
       <c r="P574" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R574" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S574" s="15">
         <f t="shared" si="27"/>
@@ -10858,10 +10856,10 @@
         <v>25</v>
       </c>
       <c r="P575" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R575" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S575" s="15">
         <f t="shared" si="27"/>
@@ -10873,10 +10871,10 @@
         <v>25</v>
       </c>
       <c r="P576" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R576" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S576" s="15">
         <f t="shared" si="27"/>
@@ -10891,17 +10889,17 @@
       <c r="C577" s="6"/>
       <c r="D577" s="6"/>
       <c r="P577" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R577" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S577" s="15">
         <f t="shared" ref="S577:S582" si="28">S535</f>
         <v>5</v>
       </c>
       <c r="U577" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="578" spans="1:21" x14ac:dyDescent="0.25">
@@ -10912,10 +10910,10 @@
       <c r="C578" s="6"/>
       <c r="D578" s="6"/>
       <c r="P578" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R578" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S578" s="15">
         <f t="shared" si="28"/>
@@ -10930,10 +10928,10 @@
       <c r="C579" s="6"/>
       <c r="D579" s="6"/>
       <c r="P579" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R579" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S579" s="15">
         <f t="shared" si="28"/>
@@ -10948,10 +10946,10 @@
       <c r="C580" s="6"/>
       <c r="D580" s="6"/>
       <c r="P580" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R580" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S580" s="15">
         <f t="shared" si="28"/>
@@ -10966,10 +10964,10 @@
       <c r="C581" s="6"/>
       <c r="D581" s="6"/>
       <c r="P581" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R581" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S581" s="15">
         <f t="shared" si="28"/>
@@ -10984,10 +10982,10 @@
       <c r="C582" s="6"/>
       <c r="D582" s="6"/>
       <c r="P582" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R582" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S582" s="15">
         <f t="shared" si="28"/>
@@ -11002,17 +11000,17 @@
       <c r="C583" s="6"/>
       <c r="D583" s="6"/>
       <c r="P583" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R583" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S583" s="15">
         <f t="shared" ref="S583:S588" si="29">S535</f>
         <v>5</v>
       </c>
       <c r="U583" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="584" spans="1:21" x14ac:dyDescent="0.25">
@@ -11023,10 +11021,10 @@
       <c r="C584" s="6"/>
       <c r="D584" s="6"/>
       <c r="P584" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R584" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S584" s="15">
         <f t="shared" si="29"/>
@@ -11041,10 +11039,10 @@
       <c r="C585" s="6"/>
       <c r="D585" s="6"/>
       <c r="P585" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R585" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S585" s="15">
         <f t="shared" si="29"/>
@@ -11059,10 +11057,10 @@
       <c r="C586" s="6"/>
       <c r="D586" s="6"/>
       <c r="P586" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R586" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S586" s="15">
         <f t="shared" si="29"/>
@@ -11077,10 +11075,10 @@
       <c r="C587" s="6"/>
       <c r="D587" s="6"/>
       <c r="P587" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R587" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S587" s="15">
         <f t="shared" si="29"/>
@@ -11093,10 +11091,10 @@
       </c>
       <c r="B588" s="4"/>
       <c r="P588" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R588" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S588" s="15">
         <f t="shared" si="29"/>
@@ -11105,7 +11103,7 @@
     </row>
     <row r="589" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A589" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B589" s="16"/>
       <c r="C589" s="16"/>
@@ -11116,10 +11114,10 @@
         <v>31</v>
       </c>
       <c r="P590" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R590" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S590">
         <v>10</v>
@@ -11130,10 +11128,10 @@
         <v>31</v>
       </c>
       <c r="P591" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R591" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S591">
         <v>10</v>
@@ -11144,10 +11142,10 @@
         <v>31</v>
       </c>
       <c r="P592" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R592" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S592">
         <v>10</v>
@@ -11158,10 +11156,10 @@
         <v>31</v>
       </c>
       <c r="P593" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R593" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S593">
         <v>10</v>
@@ -11172,10 +11170,10 @@
         <v>31</v>
       </c>
       <c r="P594" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R594" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S594">
         <v>20</v>
@@ -11186,10 +11184,10 @@
         <v>31</v>
       </c>
       <c r="P595" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R595" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S595">
         <v>10</v>
@@ -11200,10 +11198,10 @@
         <v>31</v>
       </c>
       <c r="P596" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R596" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S596">
         <v>-10</v>
@@ -11214,10 +11212,10 @@
         <v>31</v>
       </c>
       <c r="P597" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R597" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S597">
         <v>-25</v>
@@ -11228,10 +11226,10 @@
         <v>32</v>
       </c>
       <c r="P598" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R598" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S598">
         <v>10</v>
@@ -11242,10 +11240,10 @@
         <v>32</v>
       </c>
       <c r="P599" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R599" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S599">
         <v>10</v>
@@ -11256,10 +11254,10 @@
         <v>32</v>
       </c>
       <c r="P600" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R600" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S600">
         <v>10</v>
@@ -11270,10 +11268,10 @@
         <v>32</v>
       </c>
       <c r="P601" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R601" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S601">
         <v>20</v>
@@ -11284,10 +11282,10 @@
         <v>32</v>
       </c>
       <c r="P602" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R602" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S602">
         <v>10</v>
@@ -11298,10 +11296,10 @@
         <v>32</v>
       </c>
       <c r="P603" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R603" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S603">
         <v>-10</v>
@@ -11320,10 +11318,10 @@
         <v>37</v>
       </c>
       <c r="P606" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R606" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S606">
         <v>10</v>
@@ -11334,10 +11332,10 @@
         <v>37</v>
       </c>
       <c r="P607" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R607" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S607">
         <v>10</v>
@@ -11348,10 +11346,10 @@
         <v>37</v>
       </c>
       <c r="P608" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R608" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S608">
         <v>10</v>
@@ -11362,10 +11360,10 @@
         <v>37</v>
       </c>
       <c r="P609" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R609" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S609">
         <v>10</v>
@@ -11376,10 +11374,10 @@
         <v>37</v>
       </c>
       <c r="P610" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R610" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S610">
         <v>86.7</v>
@@ -11390,10 +11388,10 @@
         <v>37</v>
       </c>
       <c r="P611" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R611" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S611">
         <v>46.7</v>
@@ -11404,10 +11402,10 @@
         <v>37</v>
       </c>
       <c r="P612" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R612" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S612">
         <v>6.7</v>
@@ -11418,10 +11416,10 @@
         <v>37</v>
       </c>
       <c r="P613" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R613" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S613">
         <v>-26.7</v>
@@ -11432,17 +11430,17 @@
         <v>67</v>
       </c>
       <c r="P614" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R614" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S614" s="19">
         <f>S606</f>
         <v>10</v>
       </c>
       <c r="U614" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="615" spans="1:21" x14ac:dyDescent="0.25">
@@ -11450,10 +11448,10 @@
         <v>67</v>
       </c>
       <c r="P615" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R615" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S615" s="19">
         <f t="shared" ref="S615:S621" si="30">S607</f>
@@ -11465,10 +11463,10 @@
         <v>67</v>
       </c>
       <c r="P616" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R616" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S616" s="19">
         <f t="shared" si="30"/>
@@ -11480,10 +11478,10 @@
         <v>67</v>
       </c>
       <c r="P617" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R617" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S617" s="19">
         <f t="shared" si="30"/>
@@ -11495,10 +11493,10 @@
         <v>67</v>
       </c>
       <c r="P618" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R618" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S618" s="19">
         <f t="shared" si="30"/>
@@ -11510,10 +11508,10 @@
         <v>67</v>
       </c>
       <c r="P619" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R619" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S619" s="19">
         <f t="shared" si="30"/>
@@ -11525,10 +11523,10 @@
         <v>67</v>
       </c>
       <c r="P620" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R620" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S620" s="19">
         <f t="shared" si="30"/>
@@ -11540,10 +11538,10 @@
         <v>67</v>
       </c>
       <c r="P621" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R621" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S621" s="19">
         <f t="shared" si="30"/>
@@ -11552,7 +11550,7 @@
     </row>
     <row r="623" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A623" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B623" s="16"/>
       <c r="C623" s="16"/>
@@ -11563,10 +11561,10 @@
         <v>39</v>
       </c>
       <c r="P624" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R624" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S624">
         <v>6.9</v>
@@ -11577,10 +11575,10 @@
         <v>39</v>
       </c>
       <c r="P625" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R625" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S625">
         <v>9.6</v>
@@ -11591,10 +11589,10 @@
         <v>39</v>
       </c>
       <c r="P626" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R626" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S626">
         <v>10</v>
@@ -11605,10 +11603,10 @@
         <v>39</v>
       </c>
       <c r="P627" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R627" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S627">
         <v>10</v>
@@ -11619,10 +11617,10 @@
         <v>39</v>
       </c>
       <c r="P628" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R628" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S628">
         <v>68.400000000000006</v>
@@ -11633,10 +11631,10 @@
         <v>39</v>
       </c>
       <c r="P629" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R629" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S629">
         <v>22.4</v>
@@ -11647,10 +11645,10 @@
         <v>39</v>
       </c>
       <c r="P630" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R630" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S630">
         <v>-20</v>
@@ -11661,10 +11659,10 @@
         <v>39</v>
       </c>
       <c r="P631" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R631" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S631">
         <v>-50</v>
@@ -11672,7 +11670,7 @@
     </row>
     <row r="633" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A633" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B633" s="16"/>
       <c r="C633" s="16"/>
@@ -11683,10 +11681,10 @@
         <v>33</v>
       </c>
       <c r="P634" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R634" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S634">
         <v>4</v>
@@ -11697,10 +11695,10 @@
         <v>33</v>
       </c>
       <c r="P635" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R635" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S635">
         <v>4</v>
@@ -11711,10 +11709,10 @@
         <v>33</v>
       </c>
       <c r="P636" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R636" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S636">
         <v>4</v>
@@ -11725,10 +11723,10 @@
         <v>33</v>
       </c>
       <c r="P637" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R637" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S637">
         <v>4</v>
@@ -11739,10 +11737,10 @@
         <v>33</v>
       </c>
       <c r="P638" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R638" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S638">
         <v>140</v>
@@ -11753,10 +11751,10 @@
         <v>33</v>
       </c>
       <c r="P639" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R639" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S639">
         <v>90</v>
@@ -11767,10 +11765,10 @@
         <v>33</v>
       </c>
       <c r="P640" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R640" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S640">
         <v>40</v>
@@ -11781,10 +11779,10 @@
         <v>33</v>
       </c>
       <c r="P641" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R641" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S641">
         <v>-10</v>
@@ -11795,10 +11793,10 @@
         <v>34</v>
       </c>
       <c r="P642" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R642" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S642" s="15">
         <f t="shared" ref="S642:S649" si="31">S634</f>
@@ -11810,10 +11808,10 @@
         <v>34</v>
       </c>
       <c r="P643" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R643" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S643" s="15">
         <f t="shared" si="31"/>
@@ -11825,10 +11823,10 @@
         <v>34</v>
       </c>
       <c r="P644" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R644" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S644" s="15">
         <f t="shared" si="31"/>
@@ -11840,10 +11838,10 @@
         <v>34</v>
       </c>
       <c r="P645" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R645" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S645" s="15">
         <f t="shared" si="31"/>
@@ -11855,10 +11853,10 @@
         <v>34</v>
       </c>
       <c r="P646" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R646" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S646" s="15">
         <f t="shared" si="31"/>
@@ -11870,10 +11868,10 @@
         <v>34</v>
       </c>
       <c r="P647" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R647" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S647" s="15">
         <f t="shared" si="31"/>
@@ -11885,10 +11883,10 @@
         <v>34</v>
       </c>
       <c r="P648" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R648" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S648" s="15">
         <f t="shared" si="31"/>
@@ -11900,10 +11898,10 @@
         <v>34</v>
       </c>
       <c r="P649" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R649" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S649" s="15">
         <f t="shared" si="31"/>
@@ -11912,7 +11910,7 @@
     </row>
     <row r="651" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A651" s="16" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B651" s="16"/>
       <c r="C651" s="16"/>
@@ -11923,10 +11921,10 @@
         <v>27</v>
       </c>
       <c r="P652" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R652" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S652">
         <v>50</v>
@@ -11937,10 +11935,10 @@
         <v>27</v>
       </c>
       <c r="P653" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R653" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S653">
         <v>40</v>
@@ -11951,10 +11949,10 @@
         <v>27</v>
       </c>
       <c r="P654" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R654" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S654">
         <v>20</v>
@@ -11962,31 +11960,31 @@
     </row>
     <row r="655" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A655" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P655" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R655" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S655" s="15">
         <f>S652</f>
         <v>50</v>
       </c>
       <c r="U655" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="656" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A656" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P656" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R656" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S656" s="15">
         <f t="shared" ref="S656:S657" si="32">S653</f>
@@ -11995,13 +11993,13 @@
     </row>
     <row r="657" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A657" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P657" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R657" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S657" s="15">
         <f t="shared" si="32"/>
@@ -12013,10 +12011,10 @@
         <v>29</v>
       </c>
       <c r="P658" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R658" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S658" s="15">
         <f>S652</f>
@@ -12028,10 +12026,10 @@
         <v>29</v>
       </c>
       <c r="P659" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R659" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S659" s="15">
         <f t="shared" ref="S659:S660" si="33">S653</f>
@@ -12043,10 +12041,10 @@
         <v>29</v>
       </c>
       <c r="P660" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R660" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S660" s="15">
         <f t="shared" si="33"/>
@@ -12058,10 +12056,10 @@
         <v>35</v>
       </c>
       <c r="P661" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R661" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S661">
         <v>120</v>
@@ -12072,10 +12070,10 @@
         <v>35</v>
       </c>
       <c r="P662" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R662" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S662">
         <v>90</v>
@@ -12086,10 +12084,10 @@
         <v>35</v>
       </c>
       <c r="P663" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R663" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S663">
         <v>50</v>
@@ -12100,10 +12098,10 @@
         <v>35</v>
       </c>
       <c r="P664" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R664" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S664">
         <v>30</v>
@@ -12114,10 +12112,10 @@
         <v>38</v>
       </c>
       <c r="P665" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R665" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S665">
         <v>40</v>
@@ -12128,10 +12126,10 @@
         <v>38</v>
       </c>
       <c r="P666" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R666" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S666">
         <v>20</v>
@@ -12145,19 +12143,19 @@
       <c r="C667" s="6"/>
       <c r="D667" s="6"/>
       <c r="P667" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R667" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S667">
         <v>155</v>
       </c>
       <c r="U667" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="V667" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="668" spans="1:22" x14ac:dyDescent="0.25">
@@ -12168,10 +12166,10 @@
       <c r="C668" s="6"/>
       <c r="D668" s="6"/>
       <c r="P668" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R668" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S668">
         <v>155</v>
@@ -12185,10 +12183,10 @@
       <c r="C669" s="6"/>
       <c r="D669" s="6"/>
       <c r="P669" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R669" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S669">
         <v>155</v>
@@ -12196,7 +12194,7 @@
     </row>
     <row r="671" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A671" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B671" s="16"/>
       <c r="C671" s="16"/>
@@ -12207,7 +12205,7 @@
         <v>45</v>
       </c>
       <c r="R672" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S672">
         <v>3.4</v>
@@ -12218,7 +12216,7 @@
         <v>45</v>
       </c>
       <c r="R673" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S673">
         <v>62</v>
@@ -12232,14 +12230,14 @@
       <c r="C674" s="6"/>
       <c r="D674" s="6"/>
       <c r="R674" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S674" s="15">
         <f>S672</f>
         <v>3.4</v>
       </c>
       <c r="U674" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="675" spans="1:21" x14ac:dyDescent="0.25">
@@ -12250,7 +12248,7 @@
       <c r="C675" s="6"/>
       <c r="D675" s="6"/>
       <c r="R675" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S675" s="15">
         <f>S673</f>
@@ -12262,7 +12260,7 @@
         <v>44</v>
       </c>
       <c r="R676" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S676">
         <v>0.31</v>
@@ -12273,7 +12271,7 @@
         <v>44</v>
       </c>
       <c r="R677" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S677">
         <v>129</v>
@@ -12284,13 +12282,13 @@
         <v>47</v>
       </c>
       <c r="R678" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S678">
         <v>0.62</v>
       </c>
       <c r="U678" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="679" spans="1:21" x14ac:dyDescent="0.25">
@@ -12298,7 +12296,7 @@
         <v>47</v>
       </c>
       <c r="R679" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S679">
         <v>98</v>
@@ -12312,14 +12310,14 @@
       <c r="C680" s="6"/>
       <c r="D680" s="6"/>
       <c r="R680" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S680" s="15">
         <f>S678</f>
         <v>0.62</v>
       </c>
       <c r="U680" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="681" spans="1:21" x14ac:dyDescent="0.25">
@@ -12330,7 +12328,7 @@
       <c r="C681" s="6"/>
       <c r="D681" s="6"/>
       <c r="R681" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S681" s="15">
         <f>S679</f>
@@ -12343,14 +12341,14 @@
       </c>
       <c r="B682" s="4"/>
       <c r="R682" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S682" s="15">
         <f>S680</f>
         <v>0.62</v>
       </c>
       <c r="U682" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="683" spans="1:21" x14ac:dyDescent="0.25">
@@ -12359,7 +12357,7 @@
       </c>
       <c r="B683" s="4"/>
       <c r="R683" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S683" s="15">
         <f>S681</f>
@@ -12371,7 +12369,7 @@
         <v>48</v>
       </c>
       <c r="R684" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S684">
         <v>2</v>
@@ -12382,7 +12380,7 @@
         <v>48</v>
       </c>
       <c r="R685" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S685">
         <v>120</v>
@@ -12394,7 +12392,7 @@
       </c>
       <c r="B686" s="6"/>
       <c r="R686" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="687" spans="1:21" x14ac:dyDescent="0.25">
@@ -12403,7 +12401,7 @@
       </c>
       <c r="B687" s="6"/>
       <c r="R687" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="688" spans="1:21" x14ac:dyDescent="0.25">
@@ -12411,7 +12409,7 @@
         <v>50</v>
       </c>
       <c r="R688" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S688" s="15">
         <f>S686</f>
@@ -12423,7 +12421,7 @@
         <v>50</v>
       </c>
       <c r="R689" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S689" s="15">
         <f>S687</f>
@@ -12435,13 +12433,13 @@
         <v>66</v>
       </c>
       <c r="R691" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S691">
         <v>0</v>
       </c>
       <c r="U691" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="692" spans="1:22" x14ac:dyDescent="0.25">
@@ -12449,7 +12447,7 @@
         <v>69</v>
       </c>
       <c r="R692" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S692">
         <v>0</v>
@@ -12460,7 +12458,7 @@
         <v>70</v>
       </c>
       <c r="R693" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S693">
         <v>0</v>
@@ -12471,7 +12469,7 @@
         <v>42</v>
       </c>
       <c r="R694" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S694">
         <v>0</v>
@@ -12482,7 +12480,7 @@
         <v>43</v>
       </c>
       <c r="R695" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S695">
         <v>0</v>
@@ -12504,13 +12502,13 @@
       <c r="C698" s="6"/>
       <c r="D698" s="6"/>
       <c r="R698" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S698">
         <v>20</v>
       </c>
       <c r="V698" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="699" spans="1:22" x14ac:dyDescent="0.25">
@@ -12521,16 +12519,16 @@
       <c r="C699" s="6"/>
       <c r="D699" s="6"/>
       <c r="R699" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S699">
         <v>22.5</v>
       </c>
       <c r="U699" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V699" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="700" spans="1:22" x14ac:dyDescent="0.25">
@@ -12565,13 +12563,13 @@
       <c r="C703" s="6"/>
       <c r="D703" s="6"/>
       <c r="R703" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S703">
         <v>105</v>
       </c>
       <c r="V703" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="704" spans="1:22" x14ac:dyDescent="0.25">
@@ -12582,14 +12580,14 @@
       <c r="C704" s="6"/>
       <c r="D704" s="6"/>
       <c r="R704" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S704" s="19">
         <f>S703</f>
         <v>105</v>
       </c>
       <c r="U704" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="705" spans="1:22" x14ac:dyDescent="0.25">
@@ -12600,14 +12598,14 @@
       <c r="C705" s="6"/>
       <c r="D705" s="6"/>
       <c r="R705" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S705" s="19">
         <f>S703</f>
         <v>105</v>
       </c>
       <c r="U705" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="706" spans="1:22" x14ac:dyDescent="0.25">
@@ -12624,13 +12622,13 @@
       <c r="C707" s="6"/>
       <c r="D707" s="6"/>
       <c r="R707" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S707">
         <v>5.6</v>
       </c>
       <c r="V707" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="708" spans="1:22" x14ac:dyDescent="0.25">
@@ -12641,13 +12639,13 @@
       <c r="C708" s="6"/>
       <c r="D708" s="6"/>
       <c r="R708" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S708" s="21">
         <v>3</v>
       </c>
       <c r="V708" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="709" spans="1:22" x14ac:dyDescent="0.25">
@@ -12658,14 +12656,14 @@
       <c r="C709" s="6"/>
       <c r="D709" s="6"/>
       <c r="R709" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S709" s="19">
         <f>AVERAGE(S707:S708)</f>
         <v>4.3</v>
       </c>
       <c r="U709" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="710" spans="1:22" x14ac:dyDescent="0.25">
@@ -12676,7 +12674,7 @@
       <c r="C710" s="6"/>
       <c r="D710" s="6"/>
       <c r="R710" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S710" s="19">
         <f>AVERAGE(S707:S708)</f>
@@ -12691,7 +12689,7 @@
       <c r="C711" s="6"/>
       <c r="D711" s="6"/>
       <c r="R711" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S711" s="19">
         <f>AVERAGE(S707:S708)</f>
@@ -12706,7 +12704,7 @@
       <c r="C712" s="6"/>
       <c r="D712" s="6"/>
       <c r="R712" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S712" s="19">
         <f>AVERAGE(S707:S708)</f>
@@ -12721,7 +12719,7 @@
       <c r="C713" s="6"/>
       <c r="D713" s="6"/>
       <c r="R713" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S713" s="19">
         <f>AVERAGE(S707:S708)</f>
@@ -12736,7 +12734,7 @@
     </row>
     <row r="715" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B715" s="2"/>
       <c r="C715" s="2"/>
@@ -12762,19 +12760,19 @@
     </row>
     <row r="717" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R717" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="S717" s="18">
         <v>1.2</v>
       </c>
       <c r="T717" s="5"/>
       <c r="U717" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="719" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B719" s="2"/>
       <c r="C719" s="2"/>
@@ -12800,24 +12798,24 @@
     </row>
     <row r="720" spans="1:22" x14ac:dyDescent="0.25">
       <c r="Q720" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R720" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S720" s="10">
         <v>0</v>
       </c>
       <c r="T720" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U720" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="721" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -12834,10 +12832,10 @@
         <v>107</v>
       </c>
       <c r="Q722" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R722" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S722" s="9">
         <f>8/1000*(14/(1*14+3*2))*100</f>
@@ -12847,10 +12845,10 @@
         <v>109</v>
       </c>
       <c r="U722" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V722" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="723" spans="1:22" x14ac:dyDescent="0.25">
@@ -12858,10 +12856,10 @@
         <v>108</v>
       </c>
       <c r="Q723" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R723" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S723" s="9">
         <f>15/1000*(14/(1*14+3*2))*100</f>
@@ -12871,18 +12869,18 @@
         <v>109</v>
       </c>
       <c r="V723" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="724" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I724" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q724" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R724" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S724" s="9">
         <f>50/1000*(14/(1*14+3*2))*100</f>
@@ -12892,7 +12890,7 @@
         <v>109</v>
       </c>
       <c r="V724" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="725" spans="1:22" x14ac:dyDescent="0.25">
@@ -12900,1365 +12898,1365 @@
     </row>
     <row r="729" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
       <c r="D729" s="1"/>
       <c r="E729" s="1"/>
       <c r="F729" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="730" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K730" t="s">
+        <v>118</v>
+      </c>
+      <c r="L730" t="s">
         <v>119</v>
       </c>
-      <c r="L730" t="s">
+      <c r="M730" t="s">
         <v>120</v>
       </c>
-      <c r="M730" t="s">
-        <v>121</v>
-      </c>
       <c r="N730" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q730" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R730" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S730">
         <v>33</v>
       </c>
       <c r="T730" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V730" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="731" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K731" t="s">
+        <v>118</v>
+      </c>
+      <c r="L731" t="s">
         <v>119</v>
       </c>
-      <c r="L731" t="s">
+      <c r="M731" t="s">
         <v>120</v>
       </c>
-      <c r="M731" t="s">
-        <v>121</v>
-      </c>
       <c r="N731" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q731" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R731" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S731">
         <v>38</v>
       </c>
       <c r="T731" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V731" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="732" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K732" t="s">
+        <v>118</v>
+      </c>
+      <c r="L732" t="s">
         <v>119</v>
       </c>
-      <c r="L732" t="s">
+      <c r="M732" t="s">
         <v>120</v>
       </c>
-      <c r="M732" t="s">
-        <v>121</v>
-      </c>
       <c r="N732" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q732" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R732" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S732">
         <v>41</v>
       </c>
       <c r="T732" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V732" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="733" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K733" t="s">
+        <v>118</v>
+      </c>
+      <c r="L733" t="s">
         <v>119</v>
       </c>
-      <c r="L733" t="s">
+      <c r="M733" t="s">
         <v>120</v>
       </c>
-      <c r="M733" t="s">
-        <v>121</v>
-      </c>
       <c r="N733" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q733" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R733" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S733">
         <v>33</v>
       </c>
       <c r="T733" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V733" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="734" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K734" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L734" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M734" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N734" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q734" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R734" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S734">
         <v>32</v>
       </c>
       <c r="T734" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V734" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="735" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K735" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L735" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M735" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N735" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q735" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R735" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S735">
         <v>39</v>
       </c>
       <c r="T735" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V735" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="736" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K736" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L736" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M736" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N736" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q736" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R736" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S736">
         <v>46</v>
       </c>
       <c r="T736" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V736" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="737" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K737" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L737" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M737" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N737" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q737" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R737" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S737">
         <v>32</v>
       </c>
       <c r="T737" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V737" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="738" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K738" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M738" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N738" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q738" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R738" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S738">
         <v>32</v>
       </c>
       <c r="T738" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V738" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="739" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K739" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M739" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N739" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q739" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R739" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S739">
         <v>38</v>
       </c>
       <c r="T739" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V739" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="740" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K740" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M740" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N740" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q740" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R740" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S740">
         <v>47</v>
       </c>
       <c r="T740" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V740" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="741" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K741" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M741" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N741" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q741" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R741" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S741">
         <v>32</v>
       </c>
       <c r="T741" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V741" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="742" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K742" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M742" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N742" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q742" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R742" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S742">
         <v>33</v>
       </c>
       <c r="T742" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V742" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="743" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K743" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M743" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N743" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q743" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R743" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S743">
         <v>39</v>
       </c>
       <c r="T743" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V743" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="744" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K744" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M744" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N744" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q744" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R744" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S744">
         <v>47</v>
       </c>
       <c r="T744" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V744" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="745" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K745" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M745" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N745" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q745" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R745" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S745">
         <v>33</v>
       </c>
       <c r="T745" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V745" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="746" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K746" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N746" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q746" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R746" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S746">
         <v>32</v>
       </c>
       <c r="T746" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U746" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V746" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="747" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K747" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N747" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q747" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R747" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S747">
         <v>39</v>
       </c>
       <c r="T747" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U747" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V747" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="748" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K748" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N748" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q748" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R748" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S748">
         <v>46</v>
       </c>
       <c r="T748" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U748" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V748" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="749" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K749" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N749" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q749" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R749" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S749">
         <v>32</v>
       </c>
       <c r="T749" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U749" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V749" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="750" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K750" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N750" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q750" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R750" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S750">
         <v>14</v>
       </c>
       <c r="T750" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V750" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="751" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K751" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N751" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q751" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R751" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S751">
         <v>43</v>
       </c>
       <c r="T751" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V751" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="752" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K752" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N752" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q752" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R752" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S752">
         <v>47</v>
       </c>
       <c r="T752" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V752" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="753" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K753" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N753" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Q753" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R753" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S753">
         <v>43</v>
       </c>
       <c r="T753" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V753" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="754" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K754" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N754" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q754" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R754" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S754">
         <v>35</v>
       </c>
       <c r="T754" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V754" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="755" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K755" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N755" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q755" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R755" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S755">
         <v>43</v>
       </c>
       <c r="T755" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V755" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="756" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K756" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N756" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q756" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R756" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S756">
         <v>9</v>
       </c>
       <c r="T756" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V756" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="757" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K757" t="s">
+        <v>124</v>
+      </c>
+      <c r="M757" t="s">
         <v>125</v>
       </c>
-      <c r="M757" t="s">
-        <v>126</v>
-      </c>
       <c r="N757" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q757" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R757" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S757">
         <v>30</v>
       </c>
       <c r="T757" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V757" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="758" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K758" t="s">
+        <v>124</v>
+      </c>
+      <c r="M758" t="s">
         <v>125</v>
       </c>
-      <c r="M758" t="s">
-        <v>126</v>
-      </c>
       <c r="N758" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q758" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R758" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S758">
         <v>35</v>
       </c>
       <c r="T758" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V758" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="759" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K759" t="s">
+        <v>124</v>
+      </c>
+      <c r="M759" t="s">
         <v>125</v>
       </c>
-      <c r="M759" t="s">
-        <v>126</v>
-      </c>
       <c r="N759" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q759" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R759" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S759">
         <v>48</v>
       </c>
       <c r="T759" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V759" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="760" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K760" t="s">
+        <v>124</v>
+      </c>
+      <c r="M760" t="s">
         <v>125</v>
       </c>
-      <c r="M760" t="s">
-        <v>126</v>
-      </c>
       <c r="N760" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q760" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R760" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S760">
         <v>30</v>
       </c>
       <c r="T760" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V760" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="761" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K761" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M761" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N761" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q761" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R761" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S761">
         <v>29</v>
       </c>
       <c r="T761" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V761" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="762" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K762" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M762" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N762" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q762" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R762" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S762">
         <v>34</v>
       </c>
       <c r="T762" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V762" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="763" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K763" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M763" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N763" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q763" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R763" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S763">
         <v>46</v>
       </c>
       <c r="T763" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V763" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="764" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K764" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M764" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N764" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q764" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R764" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S764">
         <v>29</v>
       </c>
       <c r="T764" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V764" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="765" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K765" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M765" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N765" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q765" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R765" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S765">
         <v>29</v>
       </c>
       <c r="T765" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V765" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="766" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K766" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M766" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N766" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q766" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R766" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S766">
         <v>35</v>
       </c>
       <c r="T766" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V766" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="767" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K767" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M767" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N767" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q767" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R767" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S767">
         <v>48</v>
       </c>
       <c r="T767" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V767" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="768" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K768" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M768" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N768" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q768" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R768" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S768">
         <v>29</v>
       </c>
       <c r="T768" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V768" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="769" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K769" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N769" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q769" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R769" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S769">
         <v>29</v>
       </c>
       <c r="T769" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U769" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V769" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="770" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K770" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N770" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q770" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R770" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S770">
         <v>35</v>
       </c>
       <c r="T770" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U770" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V770" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="771" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K771" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N771" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q771" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R771" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S771">
         <v>44</v>
       </c>
       <c r="T771" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U771" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V771" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="772" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K772" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N772" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q772" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R772" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S772">
         <v>29</v>
       </c>
       <c r="T772" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U772" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V772" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="773" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K773" t="s">
+        <v>128</v>
+      </c>
+      <c r="N773" t="s">
         <v>129</v>
       </c>
-      <c r="N773" t="s">
-        <v>130</v>
-      </c>
       <c r="Q773" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R773" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S773">
         <v>29</v>
       </c>
       <c r="T773" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V773" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="774" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K774" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N774" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q774" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R774" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S774">
         <v>40</v>
       </c>
       <c r="T774" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V774" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="775" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K775" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N775" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q775" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R775" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S775">
         <v>56</v>
       </c>
       <c r="T775" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V775" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="776" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K776" t="s">
+        <v>128</v>
+      </c>
+      <c r="M776" t="s">
+        <v>355</v>
+      </c>
+      <c r="N776" t="s">
         <v>129</v>
       </c>
-      <c r="M776" t="s">
-        <v>357</v>
-      </c>
-      <c r="N776" t="s">
-        <v>130</v>
-      </c>
       <c r="Q776" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R776" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S776">
         <v>30</v>
       </c>
       <c r="T776" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V776" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="777" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K777" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M777" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="N777" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q777" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R777" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S777">
         <v>41</v>
       </c>
       <c r="T777" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V777" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="778" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K778" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M778" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="N778" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q778" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R778" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S778">
         <v>56</v>
       </c>
       <c r="T778" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V778" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="779" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K779" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M779" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N779" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q779" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R779" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S779">
         <v>41</v>
       </c>
       <c r="T779" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V779" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="780" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K780" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M780" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N780" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q780" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R780" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S780">
         <v>41</v>
       </c>
       <c r="T780" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V780" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="782" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B782" s="1"/>
     </row>
     <row r="783" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J783" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q783" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R783" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S783" s="6">
         <v>30</v>
       </c>
       <c r="T783" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U783" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="785" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B785" s="2"/>
       <c r="C785" s="2"/>
@@ -14284,10 +14282,10 @@
     </row>
     <row r="787" spans="1:22" x14ac:dyDescent="0.25">
       <c r="Q787" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R787" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="S787">
         <v>1</v>
@@ -14296,18 +14294,18 @@
         <v>109</v>
       </c>
       <c r="U787" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="V787" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="788" spans="1:22" x14ac:dyDescent="0.25">
       <c r="Q788" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R788" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="S788">
         <v>1</v>
@@ -14316,24 +14314,24 @@
         <v>109</v>
       </c>
       <c r="U788" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V788" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="789" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K789" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N789" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q789" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R789" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="S789">
         <v>2</v>
@@ -14342,21 +14340,21 @@
         <v>109</v>
       </c>
       <c r="U789" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="V789" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="790" spans="1:22" x14ac:dyDescent="0.25">
       <c r="N790" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q790" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R790" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="S790">
         <v>1</v>
@@ -14365,18 +14363,18 @@
         <v>109</v>
       </c>
       <c r="U790" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="V790" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="791" spans="1:22" x14ac:dyDescent="0.25">
       <c r="Q791" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R791" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="S791">
         <v>1</v>
@@ -14385,18 +14383,18 @@
         <v>109</v>
       </c>
       <c r="U791" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="V791" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="792" spans="1:22" x14ac:dyDescent="0.25">
       <c r="Q792" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R792" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S792">
         <v>1</v>
@@ -14405,18 +14403,18 @@
         <v>109</v>
       </c>
       <c r="U792" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="V792" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="793" spans="1:22" x14ac:dyDescent="0.25">
       <c r="Q793" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R793" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="S793" s="30">
         <f>S792</f>
@@ -14426,12 +14424,12 @@
         <v>109</v>
       </c>
       <c r="U793" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="795" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B795" s="2"/>
       <c r="C795" s="2"/>
@@ -14457,13 +14455,13 @@
     </row>
     <row r="796" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R796" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="S796" s="5">
         <v>0</v>
       </c>
       <c r="T796" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="U796" s="5" t="s">
         <v>12</v>
@@ -14471,134 +14469,134 @@
     </row>
     <row r="798" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E798" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q798" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R798" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="S798">
         <v>13</v>
       </c>
       <c r="T798" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="V798" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="799" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E799" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q799" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="R799" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="S799" s="29">
         <f>6.1*(44/12)*1000</f>
         <v>22366.666666666664</v>
       </c>
       <c r="T799" t="s">
+        <v>346</v>
+      </c>
+      <c r="V799" t="s">
         <v>348</v>
-      </c>
-      <c r="V799" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="800" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E800" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q800" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="R800" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="S800">
         <f>0+58.3</f>
         <v>58.3</v>
       </c>
       <c r="T800" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="V800" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="802" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E802" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Q802" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R802" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="S802">
         <v>2.8</v>
       </c>
       <c r="T802" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="U802" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="V802" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="803" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E803" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Q803" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="R803" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="S803" s="29">
         <f>2.6*(44/12)*1000</f>
         <v>9533.3333333333339</v>
       </c>
       <c r="T803" t="s">
+        <v>346</v>
+      </c>
+      <c r="V803" t="s">
         <v>348</v>
-      </c>
-      <c r="V803" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="804" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E804" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Q804" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="R804" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="S804">
         <f>2.5+5.4</f>
         <v>7.9</v>
       </c>
       <c r="T804" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="V804" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="806" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B806" s="2"/>
       <c r="C806" s="2"/>
@@ -14624,70 +14622,70 @@
     </row>
     <row r="808" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E808" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q808" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R808" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="S808">
         <v>0.14399999999999999</v>
       </c>
       <c r="T808" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="U808" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="V808" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="809" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E809" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Q809" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R809" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="S809">
         <v>0.14399999999999999</v>
       </c>
       <c r="T809" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V809" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="810" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E810" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q810" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R810" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="S810">
         <v>0</v>
       </c>
       <c r="T810" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="U810" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="812" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A812" s="22" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B812" s="22"/>
       <c r="C812" s="23"/>
@@ -14713,10 +14711,10 @@
     </row>
     <row r="814" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I814" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="R814" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="S814" s="9">
         <f>213/(213 + 60)*100</f>
@@ -14726,15 +14724,15 @@
         <v>97</v>
       </c>
       <c r="V814" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="815" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I815" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="R815" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="S815" s="9">
         <f>60/(213 + 60)*100</f>
@@ -14744,15 +14742,15 @@
         <v>97</v>
       </c>
       <c r="V815" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="817" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I817" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="R817" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="S817">
         <v>45</v>
@@ -14761,15 +14759,15 @@
         <v>97</v>
       </c>
       <c r="V817" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="818" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I818" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="R818" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="S818">
         <v>48</v>
@@ -14778,25 +14776,25 @@
         <v>97</v>
       </c>
       <c r="V818" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="820" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R820" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S820" s="25">
         <f>S827</f>
         <v>-5.9999999999999995E-4</v>
       </c>
       <c r="T820" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U820" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="V820" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="821" spans="1:22" x14ac:dyDescent="0.25">
@@ -14804,23 +14802,23 @@
         <v>37</v>
       </c>
       <c r="G821" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R821" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S821" s="24">
         <f>-(45.5*0.1+10.7*0.9)/1000</f>
         <v>-1.418E-2</v>
       </c>
       <c r="T821" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U821" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="V821" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="822" spans="1:22" x14ac:dyDescent="0.25">
@@ -14828,17 +14826,17 @@
         <v>38</v>
       </c>
       <c r="G822" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R822" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S822" s="28">
         <f>S821</f>
         <v>-1.418E-2</v>
       </c>
       <c r="T822" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="823" spans="1:22" x14ac:dyDescent="0.25">
@@ -14849,20 +14847,20 @@
         <v>98</v>
       </c>
       <c r="R823" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S823" s="24">
         <f>-(45.5*0.4+10.7*0.6)/1000</f>
         <v>-2.4619999999999996E-2</v>
       </c>
       <c r="T823" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U823" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="V823" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="824" spans="1:22" x14ac:dyDescent="0.25">
@@ -14873,14 +14871,14 @@
         <v>98</v>
       </c>
       <c r="R824" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S824" s="28">
         <f>S823</f>
         <v>-2.4619999999999996E-2</v>
       </c>
       <c r="T824" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="825" spans="1:22" x14ac:dyDescent="0.25">
@@ -14889,20 +14887,20 @@
       </c>
       <c r="B825" s="4"/>
       <c r="R825" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S825" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="T825" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U825" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="V825" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="826" spans="1:22" x14ac:dyDescent="0.25">
@@ -14911,77 +14909,77 @@
       </c>
       <c r="B826" s="4"/>
       <c r="R826" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S826" s="4">
         <f>-10.7/1000</f>
         <v>-1.0699999999999999E-2</v>
       </c>
       <c r="T826" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U826" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="V826" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="827" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C827" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="R827" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S827">
         <f>-0.6/1000</f>
         <v>-5.9999999999999995E-4</v>
       </c>
       <c r="T827" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="V827" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="828" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B828" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="R828" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S828" s="24">
         <f>-20*0.45/0.85/1000</f>
         <v>-1.0588235294117647E-2</v>
       </c>
       <c r="T828" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U828" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="V828" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="830" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D830" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="R830" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="S830">
         <f>-9.2/1000</f>
         <v>-9.1999999999999998E-3</v>
       </c>
       <c r="T830" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="V830" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="832" spans="1:22" x14ac:dyDescent="0.25">
@@ -14989,16 +14987,16 @@
         <v>107</v>
       </c>
       <c r="R832" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="S832" s="26">
         <v>-0.5</v>
       </c>
       <c r="T832" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="V832" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="833" spans="9:22" x14ac:dyDescent="0.25">
@@ -15006,138 +15004,138 @@
         <v>108</v>
       </c>
       <c r="R833" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="S833" s="26">
         <v>-1</v>
       </c>
       <c r="T833" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="V833" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="834" spans="9:22" x14ac:dyDescent="0.25">
       <c r="I834" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="R834" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="S834" s="17">
         <v>-1</v>
       </c>
       <c r="T834" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="U834" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="835" spans="9:22" x14ac:dyDescent="0.25">
       <c r="R835" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="S835" s="17">
         <f>-0.4 / ( (2*30.97) / (2*30.97 + 5*16) )</f>
         <v>-0.91662899580238943</v>
       </c>
       <c r="T835" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="U835" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="V835" t="s">
         <v>327</v>
-      </c>
-      <c r="V835" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="836" spans="9:22" x14ac:dyDescent="0.25">
       <c r="R836" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="S836" s="17">
         <f>0.6 / ( (2*39.1) / (2*39.1 + 16) )</f>
         <v>0.72276214833759589</v>
       </c>
       <c r="T836" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="U836" s="27" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="V836" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="838" spans="9:22" x14ac:dyDescent="0.25">
       <c r="R838" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="S838" s="26">
         <f>3/5</f>
         <v>0.6</v>
       </c>
       <c r="T838" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="U838" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="V838" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="839" spans="9:22" x14ac:dyDescent="0.25">
       <c r="R839" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="S839" s="26">
         <f>3/5</f>
         <v>0.6</v>
       </c>
       <c r="T839" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="U839" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="841" spans="9:22" x14ac:dyDescent="0.25">
       <c r="I841" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Q841" t="s">
+        <v>321</v>
+      </c>
+      <c r="R841" t="s">
         <v>323</v>
-      </c>
-      <c r="R841" t="s">
-        <v>325</v>
       </c>
       <c r="S841" s="26">
         <f>0.12*(44/12)</f>
         <v>0.43999999999999995</v>
       </c>
       <c r="T841" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="842" spans="9:22" x14ac:dyDescent="0.25">
       <c r="I842" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q842" t="s">
+        <v>321</v>
+      </c>
+      <c r="R842" t="s">
         <v>323</v>
-      </c>
-      <c r="R842" t="s">
-        <v>325</v>
       </c>
       <c r="S842" s="26">
         <f>0.13*(44/12)</f>
         <v>0.47666666666666668</v>
       </c>
       <c r="T842" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="843" spans="9:22" x14ac:dyDescent="0.25">
